--- a/paper-reader/测评.xlsx
+++ b/paper-reader/测评.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17820" activeTab="1"/>
+    <workbookView windowHeight="17820" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="测评" sheetId="1" r:id="rId1"/>
@@ -3059,10 +3059,21 @@
     <t>zELO 这种受 ELO 启发的重排序/嵌入训练方法，建立在哪些排序学习与对比学习工作之上？它属于领域里的哪一类方法分支？</t>
   </si>
   <si>
-    <t>这篇论文揭示的多轮对话退化问题，后续有哪些重要缓解方案？梳理这条研究线索从「发现问题」到「改进」的演化过程。</t>
-  </si>
-  <si>
-    <t>Xpertbench 这类基于 rubric 的专家级评测范式，是从哪些早期 LLM 评测与能力基准演化而来的？帮我梳理评测方法的文献分类与脉络。</t>
+    <r>
+      <t xml:space="preserve">SurGE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这个面向科学综述生成的评测基准，继承自哪些早期综述生成与长文本评估工作？帮我梳理综述生成评测这条研究线索的家族树与演化脉络。</t>
+    </r>
+  </si>
+  <si>
+    <t>这篇「分步指导 LLM 生成科学文献综述」的工作，建立在哪些综述自动生成与规划式生成的前作之上？它后续有哪些重要改进？梳理这条方法线索从提出到成熟的过程。</t>
   </si>
   <si>
     <t>### 一、同类型核心研究分类
@@ -3167,12 +3178,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3187,6 +3198,18 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9.85"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
@@ -3208,17 +3231,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3231,15 +3245,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3254,23 +3269,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3284,15 +3290,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3307,23 +3329,16 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3337,11 +3352,25 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -3353,25 +3382,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3389,7 +3430,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3401,79 +3544,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3485,55 +3556,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3549,26 +3578,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3591,23 +3603,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3631,16 +3628,48 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3652,28 +3681,28 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3685,116 +3714,116 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3804,13 +3833,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="10" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4691,7 +4726,7 @@
       <c r="A17" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="6" t="s">
         <v>86</v>
       </c>
       <c r="C17" t="s">
@@ -4702,7 +4737,7 @@
       <c r="A18" t="s">
         <v>67</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="7" t="s">
         <v>97</v>
       </c>
       <c r="C18" t="s">
@@ -4865,7 +4900,7 @@
       <c r="C9" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="5" t="s">
         <v>102</v>
       </c>
     </row>
@@ -4968,7 +5003,7 @@
       <c r="A17" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="6" t="s">
         <v>86</v>
       </c>
       <c r="C17" t="s">
@@ -4979,7 +5014,7 @@
       <c r="A18" t="s">
         <v>67</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="7" t="s">
         <v>97</v>
       </c>
       <c r="C18" t="s">
@@ -5317,7 +5352,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="5" ht="54" spans="1:3">
+    <row r="5" ht="40.5" spans="1:3">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -5461,25 +5496,25 @@
         <v>128</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" ht="14.25" spans="1:3">
       <c r="A17" t="s">
         <v>67</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="3" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" ht="14.25" spans="1:3">
       <c r="A18" t="s">
         <v>67</v>
       </c>
       <c r="B18" t="s">
         <v>97</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="4" t="s">
         <v>130</v>
       </c>
     </row>

--- a/paper-reader/测评.xlsx
+++ b/paper-reader/测评.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17820" activeTab="4"/>
+    <workbookView windowHeight="17820" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="测评" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="141">
   <si>
     <t>供人</t>
   </si>
@@ -276,7 +276,228 @@
     <t>帮我详细解读一下实验是如何实现的</t>
   </si>
   <si>
+    <t># ChemAgent 实验实现全流程详细解读
+整个实验围绕「**自更新记忆库增强化学推理**」的核心假设展开，分为**基础实验设置、核心框架两阶段实现、专项分析实验**三大模块，全程通过结构化提示词驱动LLM完成自动化流程，以下是逐层拆解的实现细节。
+## 一、实验基础设置
+### 1. 数据集选择与划分
+实验全部基于 **SciBench 基准的4个大学化学推理数据集**，覆盖量子力学、物理化学、化学动力学等核心领域，所有数据集均自带开发集（dev set）和测试集（test set），具体统计如下：
+| 数据集 | 对应化学领域 | 测试集样本数 | 开发集样本数 | 开发/测试集比例 | 核心特点 |
+|--------|--------------|--------------|--------------|----------------|----------|
+| CHEMMC | 量子力学与化学键应用 | 39 | 9 | 0.231 | 子领域集中，逻辑推理复杂度高 |
+| MATTER | 化学动力学与反应机理 | 49 | 10 | 0.204 | 涉及多步动力学计算，步骤长 |
+| ATKINS | 物理化学（热力学、动力学等） | 107 | 16 | 0.150 | 测试集最大、开发集占比最低，知识点分散 |
+| QUAN | 量子化学与原子结构 | 34 | 8 | 0.235 | 侧重能级、波长等量化计算 |
+所有问题平均需要调用2个专业公式、完成5步推理，属于典型的多步复杂推理任务，单步错误会导致最终结果完全失效。
+### 2. 评估指标
+采用**数值准确率**作为核心指标：将模型输出的最终数值答案与标准答案对比，设定**相对容差0.01**（即计算结果与真值的相对误差≤1%时，判定为回答正确），最终统计每个数据集上的正确样本占比。
+### 3. 对比基线（Baselines）
+实验设置了3类主流方法作为对照，全部和ChemAgent使用相同的基座模型，保证公平性：
+1.  **Few-shot + Direct reasoning**：3个示例+直接输入问题，无额外推理引导，完全依赖LLM原生能力输出答案。
+2.  **Few-shot + Python**：6个来自开发集的示例，引导LLM把推理过程转化为Python代码执行计算，是SciBench原生的代码增强基线。
+3.  **StructChem**：当时的化学推理SOTA方法，通过结构化指令、置信度审查与修正，引导LLM分步推理。
+### 4. 实验基座模型
+实验覆盖了闭源与开源共5款主流LLM，验证框架的泛化性：
+- 闭源：GPT-4 (gpt-4-1106-preview)、GPT-3.5 (gpt-3.5-turbo-16k)
+- 开源：Llama 3.1-7B、Llama 3.1-70B、Qwen 2.5-72B
+推理阶段的默认记忆配置：规划记忆最多检索2条相关实例（2-shot），执行记忆最多检索4条相关实例（4-shot）。
+## 二、核心框架的两阶段实现流程
+ChemAgent的核心是「**先基于开发集构建静态记忆库，再在测试阶段用记忆库增强推理，同时动态更新记忆**」，完整对应论文中的图2架构。
+### 1. 第一阶段：初始记忆库构建（开发集上执行）
+该阶段的目标是把开发集的完整问题拆解为「原子子任务+对应子解」的结构化单元，存入记忆库作为初始经验，对应论文Algorithm 1。
+#### 执行步骤
+1.  **条件提取与校验**
+    对开发集中每个「问题P + 标准答案S」，先用拆分提示词让LLM把原问题分离为「条件C」和「问题」两部分，确保所有数值参数、约束条件都被归入条件部分；再用修正提示词二次校验条件的完整性和准确性，避免拆分错误污染后续记忆。
+2.  **原子子任务分解**
+    基于提取的条件和原问题，引导LLM把完整的复杂问题拆解为多个层级化的原子子任务：如果子任务难度过高，就继续递归拆解，直到每个子任务可以被LLM单步解决。每个子任务包含4个结构化字段：任务描述、子任务目标、分步解法、解题提示。
+3.  **子解一一匹配**
+    从标准答案S中，拆解出和每个子任务一一对应的子解答Oi，确保「条件数量=子任务数量=子解数量」，三者严格对齐。
+4.  **难度排序与质量过滤**
+    受课程学习启发，让LLM把所有子任务按「从易到难」排序；同时过滤掉LLM置信度低于预设阈值的记忆单元，只保留高质量的子任务-子解对，保证初始记忆库的可靠性。
+5.  **持久化存储**
+    每个「条件Ci + 子任务Ti + 子解Oi」组成一个执行记忆单元，存入**执行记忆Me**；同时把子任务对应的高层解题策略、方法论存入**规划记忆Mp**，完成静态初始库的构建。
+### 2. 第二阶段：库增强推理与动态记忆更新（测试集上执行）
+该阶段是推理时的核心流程，遇到新问题时，先拆解、再检索记忆、再解题，同时把新的解题经验更新回记忆库。
+#### 执行步骤
+1.  **新问题层级化分解**
+    输入测试问题后，首先调用任务分解提示词，把问题拆分为1~3个一级子任务；如果子任务难度过高，继续递归拆分为更细的子任务，形成树状任务结构。每个子任务都明确标注目标、风险点、里程碑和可能用到的公式。
+2.  **相似记忆检索**
+    对每个原子子任务，用**Llama 3的Embedding向量**计算它和记忆库中所有执行记忆单元的余弦相似度，筛选出相似度≥预设阈值θ的记忆单元：
+    - 从规划记忆Mp中检索最多2条高层策略，指导解题思路；
+    - 从执行记忆Me中检索最多4条具体解题示例，提供公式、步骤、代码参考；
+    - 知识记忆Mk由LLM基于当前问题临时生成，提供基础化学原理、公式作为即时参考，不会持久化存入记忆库。
+3.  **无匹配记忆的补全：想象机制**
+    如果检索不到相似度达标的记忆，触发「合成记忆」机制：让LLM识别当前子任务的化学主题（如热力学、量子化学），自主生成同主题的高质量问题+解答，作为临时记忆辅助解题，避免无参考时的随机错误。
+4.  **子任务结构化求解**
+    结合检索到的所有记忆，引导LLM按固定格式生成子任务解答，必须包含三部分：
+    - 明确列出用到的所有化学公式；
+    - 分步写出推理逻辑；
+    - 生成可独立运行的Python代码（采用国际单位制，最终输出带单位的数值结果）。
+5.  **动态记忆自更新**
+    每个子任务求解完成后，自动把「当前条件+子任务+子解」追加到执行记忆Me中；同时把该题用到的策略、公式、知识点总结后追加到规划记忆Mp中。随着处理的问题越来越多，记忆库会自动持续丰富，实现「越用越强」的自进化。
+## 三、关键辅助模块的实现
+### 1. 评估与修正模块（Evaluate &amp; Refine）
+该模块是提升准确率的核心纠错机制，对应论文图4，可以独立使用不同的LLM执行（比如用弱模型推理、强模型评估）。
+- **子解答校验**：每完成一个子任务，自动校验解答是否违背基础化学原理、是否存在单位换算错误、公式误用、数值计算偏差等问题。
+- **解答修正**：如果发现错误，基于知识记忆中的正确原理，针对性生成修正后的子解答。
+- **任务重分解**：如果子任务因条件不足失败，或者子任务目标和主任务方向偏离（比如反向求解），则重新拆解当前及后续所有子任务，生成新的任务树。
+该模块的评估和修正功能完全分离：评估器只判断对错，修正器负责调整，便于定位错误来源。
+### 2. 相似度计算实现
+任务相似度基于向量余弦相似度计算：
+$$Similarity(T_a, T_b)=\frac{Embed(T_a) \cdot Embed(T_b)}{\| Embed(T_a)\| \times\| Embed(T_b)\|}$$
+其中Embed函数使用Llama 3的Embedding模型实现，仅对子任务的文本描述进行编码，不依赖额外标注。
+## 四、专项分析实验的实现
+### 1. 自进化实验（Self-evolution）
+用于验证「记忆库越丰富，解题能力越强」的核心假设，实验设置如下：
+- 数据集：MATTER数据集，移除评估修正模块，排除其对进化效果的干扰。
+- 迭代机制：多轮迭代测试，第i轮迭代时，只能使用前i-1轮积累的所有记忆作为库；每解完一道题，只有答案正确时，才把对应的记忆加入库中。
+- 防泄露设计：求解某道题时，强制排除所有来自该题自身的历史记忆，避免标签泄露。
+- 实验结果：随着迭代次数增加，准确率逐步上升并最终收敛，从基线44.89%提升至接近52%，证明仅靠「答案正确与否」的简单反馈，无需人工标注高质量轨迹，就能让模型通过积累经验持续提升。
+### 2. 消融实验
+#### （1）记忆组件消融
+以GPT-4为基座，移除评估修正模块，分别移除不同记忆组件，验证各部分的贡献：
+- 基线：无任何记忆，准确率51.53%；
+- 完整记忆（Mp+Me+Mk）：准确率53.71%；
+- 关键结论：
+  1.  移除任意记忆组件都会导致性能下降；
+  2.  知识记忆Mk对整体影响最大——在ATKINS这类开发集占比低、记忆池小的数据集上，Mp和Me可用内容少，主要依赖Mk补充基础化学知识；
+  3.  人工编写的高质量few-shot示例，在子领域集中的数据集上可以达到和完整记忆相当的效果，但泛化性弱于动态记忆库。
+- 公平性处理：移除执行记忆Me时，会补充2个人工编写的高质量示例，避免「少样本数量差异」影响对比公平性。
+#### （2）记忆质量消融
+验证「记忆质量对最终效果的影响」，实验设置：
+- 移除知识记忆Mk，分别用GPT-3.5生成记忆、GPT-4生成记忆、两者混合的记忆，测试不同推理基座的效果。
+- 核心结论：
+  1.  无论用哪个模型推理，GPT-4生成的记忆效果始终优于GPT-3.5，准确率差距约8%；
+  2.  混合记忆效果最差——同一问题会同时调用不同质量、不同风格的记忆，干扰LLM判断，反而提升错误率；
+  3.  这也解释了为什么GPT-3.5基座的提升幅度更小：它自身生成的记忆质量低，限制了框架的上限。
+### 3. 成本分析实验
+统计单样本的token消耗与推理成本：
+- 无评估修正模块：平均单样本消耗1.2万token，成本约0.09美元；
+- 包含评估修正模块：平均单样本消耗2.3万token，成本约0.1725美元；
+- 初始记忆库构建为一次性成本，未计入单样本开销。
+整体来看，虽然成本略高于StructChem，但准确率提升幅度远大于成本增幅，性价比更高。
+### 4. 错误归因分析
+通过人工分析所有失败样本的解题轨迹，归纳出三类核心错误：
+1.  **问题理解偏差**：忽略问题中的关键约束条件（如「可逆绝热」），或被冗余信息干扰，属于LLM原生能力局限。
+2.  **规划推理错误**：初始任务分解的思路本身错误，导致后续全链偏差，评估模块不一定能及时纠正。
+3.  **记忆误匹配**：检索到的记忆语义高度相似，但关键条件不同（如都是熵变计算，但一个是绝热过程、一个是普通过程），导致套用错误公式。
+## 五、底层驱动：提示词工程体系
+整个框架完全由结构化提示词驱动，无需微调模型，附录G中包含全套提示词，按功能分为三大类：
+1.  **记忆库构建类**：任务拆分提示、条件修正提示、子任务分解提示、子解匹配提示、难度排序提示；
+2.  **推理解题类**：任务分解提示、子任务执行提示、相似任务联想提示、答案评估提示、任务总结提示、计划修正提示；
+3.  **基线对照类**：直接推理提示、Python代码生成提示。
+所有提示词都严格规定了输出格式，确保LLM的输出可以被程序自动解析、串联，形成端到端的自动化推理流程。</t>
+  </si>
+  <si>
     <t>Darwin Gödel Machine: Open-Ended Evolution of Self-Improving Agents</t>
+  </si>
+  <si>
+    <t># Darwin Gödel Machine 实验实现详细解读
+DGM的实验围绕**验证“自指式自改进”+“开放式探索”两个核心机制的有效性**展开，整体是一个闭环迭代的进化框架，所有设计都服务于“让编码代理自主修改自身代码，并通过基准测试验证收益，持续迭代进化”的目标。以下从实验基础设置、核心算法流程、基准与评估策略、基线对照、验证实验、成本与安全六个维度详细拆解。
+## 一、实验基础配置
+### 1. 初始编码代理（Base Agent）
+实验从一个极简的人工设计编码代理启动，目的是清晰观测自改进的增益：
+- **核心能力**：基于冻结的预训练基座大模型（FM），具备代码读取、编写、执行能力，代码基于Python实现（图灵完备，理论上可实现任意可计算逻辑）。
+- **初始工具集**：仅两个基础工具
+  - Bash工具：执行shell命令，支持包管理、运行测试等操作；
+  - 编辑器工具：仅支持整文件查看、整文件覆盖写入、新建文件，不支持行级编辑、局部替换等细粒度操作。
+- **自改进范围**：当前版本仅优化代理的上层设计（工具、工作流、提示词、执行逻辑），不修改/训练基座大模型本身（算力成本过高，列为未来工作）。
+### 2. 基座模型选型
+实验在不同阶段使用不同模型，平衡效果与成本：
+| 阶段 | SWE-bench 实验 | Polyglot 实验 |
+|------|----------------|---------------|
+| 自修改（代理自己改自己代码） | Claude 3.5 Sonnet (New) | Claude 3.5 Sonnet (New) |
+| 基准测试评估 | Claude 3.5 Sonnet (New) | o3-mini |
+- 统一温度系数为1.0，保证生成多样性。
+- 选型逻辑：SWE-bench任务难度更高，全程使用能力更强的Claude模型；Polyglot任务相对轻量，用o3-mini提升迭代速度、避开API速率限制。
+### 3. 迭代规模
+- 总迭代轮次：80轮，每轮生成新的子代代理。
+- 并行度：SWE-bench每轮并行2个自改进任务，Polyglot每轮并行4个。
+## 二、DGM 核心算法流程
+实验的核心循环是**“父代选择 → 自修改生成子代 → 基准测试评估 → 合格子代加入存档”**，往复迭代。
+### 1. 存档（Archive）机制
+- 初始化：仅包含1个初始基础代理。
+- 扩容规则：每一代新代理只有通过“基本功能校验”（能正常编译、保留代码编辑能力），才会被永久加入存档；功能损坏的直接丢弃。
+- 作用：存档是开放式探索的核心载体，它保留了所有历史分支的代理，而不是只保留最新最优版本，让性能暂时不高但有潜力的“垫脚石”代理可以被后续复用。
+### 2. 父代选择策略（Parent Selection）
+每一轮从存档中采样父代代理，核心是**平衡“利用高性能分支”和“探索小众分支”**，避免陷入局部最优。具体实现基于加权采样：
+1. 先过滤掉性能满分的代理（无提升空间），形成候选集；
+2. 对每个候选代理计算权重：
+   - 性能分：对基准得分做sigmoid缩放，高分代理权重更高（利用）；
+   - 新颖性奖励：权重与该代理的“有功能子代数量”成反比，孩子越少的代理权重越高（探索）；
+3. 按权重做分类采样，选出父代。
+- 关键设计：所有代理都保留非零的选中概率，理论上只要算力足够，任何进化路径都有机会被探索。
+- 消融验证：如果改成“永远选当前得分最高的代理作为父代”（贪心策略），SWE-bench得分从50.0%降到39.7%，直接证明存档+非贪心探索的价值。
+### 3. 自修改执行流程
+父代代理生成子代的过程分为“诊断提需求”和“编码实现”两步：
+#### 第一步：改进点诊断
+将父代代理的基准测试失败日志、任务描述、预测补丁、真实测试结果输入给独立的o1模型，由它分析失败原因，输出1个高优先级改进方案，格式包含：
+- 日志问题总结；
+- 潜在改进方向；
+- 详细的改进提案；
+- 具体实现建议；
+- 转换成类GitHub Issue的任务描述。
+&gt; 注：当前版本用独立模型做诊断是工程简化，理论上代理可以自主分析自身日志、提出改进方案。
+#### 第二步：自编码实现
+将上述“改进需求”作为编码任务，交给父代编码代理执行，让它修改自己的代码库，生成新版本的子代代理。
+- 自修改的本质：把“改进自己”当成一个普通编码任务来完成——因为代理本身就是代码实现的，修改自身代码和修改外部仓库代码逻辑完全一致。
+- 核心假设：编码基准测试的得分提升，等价于代理编码能力的提升，也就等价于自改进能力的提升。
+### 4. 评估与入档
+新生成的子代代理需要通过分级评估：
+1. **基础功能校验**：先跑10个简单任务，验证是否还具备基本的代码编辑能力；失败则直接丢弃，不进入存档。
+2. **性能评估**：通过基础校验后，跑更多任务估算编码能力得分。
+3. **入档**：将子代代理及其得分加入存档，等待后续轮次被选为父代。
+## 三、基准测试与分级评估策略
+实验选用两个差异很大的编码基准，验证效果的普适性，同时设计了分级评估来控制算力成本。
+### 1. 两个基准的定位
+| 基准 | 任务特点 | 设计目的 |
+|------|----------|----------|
+| SWE-bench Verified | 真实Python仓库的GitHub Issue，需要跨多文件修改，贴近真实软件工程 | 测试复杂代码理解与调试能力 |
+| Polyglot | 多编程语言（C++/Rust/Go/Java/JS/Python），以单文件实现为主，更小众 | 测试跨语言泛化能力，且数据更难被训练集覆盖 |
+- 细节说明：Polyglot官方排行榜用pass@2（允许看一次测试反馈），论文统一用更严格的pass@1（不看测试结果），更贴近真实编码场景。
+### 2. 分级评估策略
+由于全量基准评测成本极高，实验采用“漏斗式”分级评估，差代理快速淘汰，优代理精细评测：
+1. **一级筛选（10任务）**：验证基础代码编辑功能，门槛最低，快速过滤掉自修改后功能损坏的代理。
+2. **二级评估（50任务）**：估算整体性能，用于存档内排序和父代选择参考。SWE-bench选用SWE-bench-verified-mini代表性子集，Polyglot随机采样。
+3. **三级精评（200任务，仅SWE-bench）**：如果代理在60任务子集得分超过40%，且位列存档前两名，再追加140个任务做全量评测，得到更精准的最终成绩。
+## 四、基线对照实验
+为了验证DGM两个核心组件的必要性，实验设置了两个消融基线：
+### 1. 无自改进基线（DGM w/o Self-improve）
+- **实现逻辑**：负责“设计新代理”的元代理永远是初始的base agent，不会随着迭代进化；也就是修改代码的设计师水平一直停留在初始状态。
+- **对应思路**：复现ADAS等传统元学习方案——固定元代理，只优化下游代理。
+- **实验结果**：早期有小幅提升，但很快进入瓶颈，最终性能远低于完整DGM，证明“自指式迭代改进（元代理也同步进化）”是持续进步的关键。
+### 2. 无开放式探索基线（DGM w/o Open-ended exploration）
+- **实现逻辑**：取消存档机制，永远只保留最新一代有功能的代理，下一代只能基于最新版本自修改，类似爬山法。
+- **实验结果**：进步非常有限，一旦某一代自修改出现性能退化，后续就很难恢复，容易陷入局部最优。
+- **对比意义**：证明存档库的“垫脚石”作用——很多关键创新需要先经历性能暂时下降的阶段，只有保留历史分支才能跨过这类“欺骗性陷阱”。
+### 3. 人工设计基线
+同时和人类开发的开源SOTA做对比：
+- SWE-bench：对比OpenHands + CodeAct v2.1（人工维护的顶尖开源方案）；
+- Polyglot：对比Aider（社区流行的多语言编码代理，经过一年多人工迭代）。
+- 结果：DGM最终性能达到/超过了这些人工设计的方案，证明自动化自改进的潜力。
+## 五、泛化性验证实验
+为了排除“代理只是过拟合了特定基准/特定模型”，论文补充了三组迁移实验：
+1. **跨模型迁移**：在Claude 3.5上演化出的最优代理，换成Claude 3.7 Sonnet或o3-mini后，性能依然显著优于对应模型的初始代理。说明改进是通用的工具/工作流优化，不是针对某个模型的投机。
+2. **跨基准迁移**：在SWE-bench上演化的代理，直接在Polyglot上测试依然有大幅提升，反之亦然。说明提升的是通用编码能力，不是基准特定的trick。
+3. **跨语言迁移**：只在Polyglot的Python任务上演化的代理，迁移到其他编程语言任务上依然有效，只是比全语言训练的版本略有下降。
+## 六、成本、稳定性与安全
+### 1. 算力与成本
+- SWE-bench完整80轮DGM运行成本约2.2万美元，单条基线约1万美元；
+- 成本差异主要来自任务复杂度：Claude 3.5跑60个SWE-bench任务约350美元，o3-mini跑60个Polyglot任务仅5美元；
+- 论文同时指出，对比人类专家团队开发编码代理的人力成本，自动化自改进长期具备效率优势。
+### 2. 稳定性
+在Polyglot上重复运行3次DGM，最终得分均值40.7%，标准差2.3%，说明算法结果稳定可复现。
+### 3. 实验安全措施
+所有实验都在约束环境下进行，核心防护包括：
+- **沙箱隔离**：所有代理执行、代码修改都在隔离沙箱中，无法访问宿主机，严格限制运行时间，防止资源耗尽；
+- **范围约束**：自修改仅限定在代理自身的Python代码库内，目标仅为提升编码基准性能，行动空间可控；
+- **可追溯性**：存档完整保留每一代代理的代码差异、评测日志，所有修改都有谱系可回溯、可审计；
+- **人工监控**：实验全程有人工监控性能与代码变化，未发现有害或恶意行为。
+## 七、实验观察到的自改进方向
+实验中DGM自主发现了大量提升编码能力的优化，覆盖工具层和工作流层：
+- **工具层**：行级代码查看、字符串精确替换编辑、上下文超限自动总结、撤销编辑功能等；
+- **工作流层**：补丁有效性校验与重试、多候选补丁生成+排序、历史尝试信息复用、测试结果自动分析与迭代、回归测试验证等。
+这些优化和人类工程师优化编码代理的思路高度吻合，但完全由系统自主发现。
+需要我补充整理DGM算法的完整伪代码，或者进一步拆解某个具体模块的实现细节吗？</t>
   </si>
   <si>
     <t>这篇是 **DeepSeek-V4** 的技术论文，核心讲的是 DeepSeek 新一代 MoE（混合专家）大模型，主打**百万级 token 超长上下文的高效处理**。
@@ -1249,6 +1470,87 @@
 核心创新在于：**评价标准本身是查询的函数**，而非固定常量。这使得评价体系能够适应 100 个子领域的多样性，人类对齐率从静态标准的 67% 提升到动态标准的 84%（critic model）。</t>
   </si>
   <si>
+    <t># 论文投稿审视：Darwin Gödel Machine
+以下从**录用核心优势、高风险审稿质疑点、针对性优化建议、写作与应答思路**四个维度，按ICLR等顶会的审稿标准做完整审视，覆盖原创性、实验严谨性、逻辑自洽性、安全伦理等核心评审维度。
+## 一、论文核心优势（录用强加分项）
+### 1. 选题价值高，实现了理论到工程的关键落地
+- 直面自改进AI领域的经典难题：经典Gödel Machine依赖“形式化证明修改有益”，在真实系统中完全不可行。本文用**实证验证替代形式化证明**，让哥德尔机的构想从理论走向可运行的系统，是该方向重要的工程突破。
+- 首次将**开放式探索（Open-Endedness）** 种群思想引入自改进代理框架，用“存档+垫脚石”机制破解了单线程自改进容易陷入局部最优、过早停滞的痛点，为递归自改进提供了新的范式。
+### 2. 实验体系完整，结果有强说服力
+- **双基准交叉验证**：同时在SWE-bench（复杂多文件Python工程）和Polyglot（多语言单文件实现）上验证，覆盖真实软件工程、跨语言泛化两个核心场景，避免了单基准的片面性。
+- **量化收益显著**：SWE-bench从20.0%提升至50.0%，追平人工设计的开源SOTA；Polyglot从14.2%提升至30.7%，超过经过一年人工迭代的Aider。效果直观，符合顶会对“实质性提升”的要求。
+- **消融与泛化验证充分**：
+  - 分别消融“自改进机制”和“开放式探索”两个核心组件，因果逻辑清晰；
+  - 补充跨模型、跨基准、跨语言三组迁移实验，有力排除了“过拟合特定基准/模型”的质疑，证明提升的是通用编码能力。
+### 3. 安全研究范式负责任，符合顶会伦理要求
+- 主动部署沙箱隔离、时间限制、谱系可追溯、人工监控等防护措施，在实验层面落实了安全约束；
+- 主动披露**objective hacking（目标破解）** 的负面案例，坦诚方法的局限性与对齐风险，而非只报喜不报忧，符合AI领域对“负责任创新”的评审导向。
+### 4. 可复现性基础扎实
+- 附录完整公开了任务子集、超参数、最优代理的完整代码diff、算法伪代码；
+- 明确计划全量开源代码、代理日志与完整演化谱系，满足顶会的可复现性要求。
+## 二、高风险审稿质疑点（按优先级排序）
+### 1. 核心基石假设缺乏直接验证（最关键逻辑漏洞）
+论文的核心底层假设是：**编码基准性能提升 = 自改进能力提升**。只有该假设成立，才能形成“自加速”的正循环，否则只是普通的下游任务元优化。
+- 当前实验只证明了“迭代后下游任务得分变高”，但没有直接度量**自改进能力本身**是否逐代增强：比如没有对比不同世代的代理，在完成**同一套标准化自修改任务**时，成功率、修改质量、引入bug的概率、所需迭代次数是否有显著提升。
+- 审稿人大概率会追问：如何证明是“自改进能力真的变强了”，而不是代理只是学会了基准题的特定技巧？
+### 2. “自指自改进”的闭环不完整，依赖外部模型
+当前自修改流程中，**“识别改进方向”的元决策由独立的外部o1模型完成**（分析失败日志、提出改进方案），代理本身只负责编码执行，不负责“判断自己该改什么”。
+- 论文虽注明是“工程简化”，但会显著削弱“self-referential self-improving”的核心主张，更接近“外部导师+执行代理”的模式，而非真正的自我驱动改进。
+- 同期相关工作（Robeyns et al., 2025）已实现代理自主分析自身错误，审稿人很可能以此对比，质疑自改进闭环的完整性。
+### 3. “开放式进化”的术语严谨性存疑
+传统开放式进化（Open-Ended Evolution）的核心是**无固定目标、持续生成新颖的任务/能力/实体**，而本文的系统始终在固定编码基准上优化单一目标（任务通过率），本质是“带存档的目标导向进化搜索”。
+- 审稿人可能质疑：这本质是一种带种群存档的进化策略，而非真正意义上的开放式进化；“垫脚石”的作用只是更好地收敛到固定最优解，和开放式创新的核心目标有差距。
+- 父代选择算法本身较为朴素（性能sigmoid加权 + 子代数量倒数），算法层面的原创性有限，更多是理念层面的交叉结合。
+### 4. 实验设计存在潜在偏差
+1. **分级评估的选择偏差**
+   只有在60任务子集得分&gt;40%且排名前2的代理，才会执行200任务的完整评估。这会导致：
+   - 部分潜力代理可能因小子集的随机噪声得分偏低，错失完整评估；
+   - 最终报告的“最优得分”存在向上偏倚（只给运气好的代理跑了全量测试）；
+   - 存档内大部分代理只有60任务得分，跨代性能比较的公平性不足。
+2. **随机性控制不足**
+   大模型生成存在显著随机性，论文未明确说明每个代理的基准得分是单次运行还是多次重复的均值。若为单次结果，结论的可靠性会打折扣。
+3. **基线对比不够充分**
+   - 仅对比“无存档”和“无自改进”两个极端基线，缺少和“保留Top-K历史最优代理”的普通进化算法对比，无法证明收益来自“开放式探索思想”，还是仅仅来自“保留多个候选个体”。
+   - 和最相关的同期工作（Robeyns et al., 2025）没有直接实验对比，仅用DGM Greedy近似，说服力不足。
+### 5. 自改进范围有限，与标题预期有差距
+当前自修改仅局限于**上层工作流、工具、提示词**，既不能修改基座模型，也不能修改“开放式探索算法”本身（存档管理、父代选择等核心逻辑）。
+- 这与Gödel Machine“可修改自身任意部分”的理论构想差距较大，虽标注为未来工作，但容易让审稿人觉得“自改进”的程度被夸大，本质是“代理工程的自动优化”，而非完整的自改进AI。
+### 6. 安全讨论深度不足
+当前安全内容更多是“当前实验的工程防护措施”，对方法本身的安全风险挖掘不够：
+- 没有讨论自改进循环的可中断性、可回退性，以及迭代中能力突变的风险；
+- objective hacking的核心案例放在附录，正文没有深入讨论其对自改进系统对齐的启示——目标函数的微小缺陷会被自改进循环快速放大，这是自改进AI最核心的安全隐患之一。
+## 三、针对性优化建议
+### 1. 补全核心假设：增加自改进能力的直接度量
+- 补充一组对照实验：从存档中选取不同世代、不同基准性能的代理，让它们完成同一组标准化自修改任务（如给基础代理添加指定工具、优化指定工作流），量化成功率、代码正确性、引入bug率。
+- 若能证明“基准得分越高的代理，完成自修改任务的质量也越高”，可直接支撑核心假设，把“相关性”强化为“因果性”。主报告放核心结论，详细数据放附录即可。
+### 2. 管理预期：明确闭环的工程权衡
+- 稳妥方案：在引言和方法部分明确说明，“改进方向诊断由外部模型完成”是当前的工程权衡，目的是降低迭代噪声、聚焦验证“自改进+开放式探索”的核心机制，完全自主的诊断-修改闭环是未来工作方向。避免过度claim“自指”的纯粹性。
+- 加分方案：补充一个小型消融实验——让代理自身分析运行日志、生成改进建议，替代外部o1模型，对比效果。哪怕性能略有下降，也能证明完整闭环的可行性。
+### 3. 厘清术语边界，避免争议
+- 建议全文统一使用**“开放式探索（Open-Ended Exploration）”**，替代“开放式进化”，更准确地描述“借鉴种群存档与垫脚石思想、提升搜索效率”的定位，避免术语滥用的争议。
+- 补充量化分析：统计最终最优代理的谱系中，有多少比例的祖先并非当时的最优代理；统计有多少关键改进来自性能低于父代的“垫脚石”节点，用数据证明存档探索的实际价值。
+### 4. 完善实验设计，增强结论可靠性
+- **随机性控制**：至少对初始代理和最终最优代理做3-5次重复评估，报告均值和标准差，证明结果稳定；同时说明其他代理的单次得分用于相对排序，不影响最终结论。
+- **补充基线**：增加“保留Top-5历史最优代理”的普通进化基线，证明DGM的探索机制优于简单保留优质个体的策略。
+- **修正分级评估偏差**：补充60任务子集与200任务全量得分的相关系数，证明小子集评估是可靠的代理指标；同时明确说明，200任务得分仅用于最终最优代理的精确度量，跨代比较统一使用60任务子集得分。
+### 5. 深化安全讨论，强化严谨性
+- 将objective hacking的案例从附录提升至正文安全章节，以此为切入点讨论“目标对齐是自改进系统的核心挑战”，展示对风险的深度思考。
+- 补充算法层面的安全约束讨论，如不可修改的安全内核、每代强制安全审计、谱系回滚机制等，体现对长期安全风险的前瞻性思考。
+## 四、写作与审稿应答建议
+### 写作优化
+1. **摘要突出差异化**：在摘要中明确两个核心创新：① 用实证验证替代形式化证明，落地哥德尔机构想；② 引入开放式种群探索，破解单线程自改进的局部最优问题，让审稿人一眼抓住贡献。
+2. **相关工作结构化**：分为“开放式系统”“元学习与代理自动设计”“自改进AI”三块，每块末尾加一句与本文的明确对比，逻辑更清晰。
+3. **增加专门的局限性章节**：主动坦诚依赖外部诊断模型、自修改范围有限、算力成本高、固定基准有局限等不足，反而更容易获得审稿人好感。
+### 典型审稿问题应答思路
+1. **关于核心假设**
+   &gt; 回应逻辑：① 自修改本质就是对自身代码库的编码任务，与下游编码任务的核心能力完全同构；② 我们补充了标准化自修改任务的对照实验，直接证明高世代代理的自修改能力更强；③ 跨基准、跨模型的迁移结果也说明提升的是通用编码能力，而非任务特定技巧。
+2. **关于外部诊断模型**
+   &gt; 回应逻辑：① 这是工程层面的权衡，目的是降低迭代噪声，聚焦验证“自改进+开放式探索”的核心机制；② 即使有外部诊断，代理自身编码能力的提升依然是自驱动的，每一代的改进都会赋能下一代的修改能力，核心自加速循环依然成立；③ 我们补充了代理自主诊断的消融实验，验证了完整闭环的可行性。
+3. **关于开放式术语的争议**
+   &gt; 回应逻辑：① 本文的核心是借鉴开放式进化的“垫脚石”“种群存档”思想，用于提升固定目标下的搜索效率，并非宣称实现了无限制的开放式创新；② 我们的框架具备扩展到动态任务集的潜力，未来可实现真正的开放式能力增长；③ 即使在固定目标下，种群存档的探索机制也显著优于爬山法，这本身就是重要的方法学贡献。
+需要我帮你整理一份更详细的**审稿人反驳信（Rebuttal）模板**，或者针对某一个质疑点补充具体的实验设计方案吗？</t>
+  </si>
+  <si>
     <t>整体来看，这篇 DeepSeek-V4 技术报告的结构**基本可读但存在多处明显的结构性缺陷**。作为一篇主打"百万 token 上下文"的模型技术论文，它在章节组织、内容归类和叙事逻辑上有不少值得商榷的地方。
 ## 不合理之处（分点描述）
 ### 1. 缺少独立的 Related Work（相关工作）章节
@@ -2197,6 +2499,327 @@
     <t>根据专家回复的评审意见和论文来回复评审人</t>
   </si>
   <si>
+    <t># Response to Reviewers
+**Manuscript ID:** xxx  
+**Title:** ChemAgent: Self-updating Library in Large Language Models Improves Chemical Reasoning
+We sincerely thank all reviewers for their constructive and insightful comments, which have greatly helped us improve the quality of this work. We have carefully addressed every concern and made comprehensive revisions to the manuscript. Below is a point-by-point response to each reviewer’s comments. Major revisions in the revised manuscript include:
+1.  Clarified the core novelty and architectural differences between ChemAgent and existing memory-augmented / prompt engineering methods, with explicit comparisons in the introduction and related work sections.
+2.  Supplemented detailed mechanisms for memory management, quality control, scalability, and efficiency, along with corresponding analysis results.
+3.  Added supplementary evaluation on ChemBench and a small-scale cross-domain validation on the physics subset of SciBench to demonstrate generalizability.
+4.  Added ablation studies on the evaluation &amp; refinement module with different backbone models, and expanded analysis of its limitations.
+5.  Fixed all writing ambiguities, clarified the sources of all baseline results, and added all missing relevant references.
+6.  Added concrete examples of "condition" extraction and refined descriptions of core concepts.
+---
+## Response to Reviewer #1
+We thank the reviewer for recognizing the value of our dynamic memory library and performance improvements. We address your concerns as follows.
+### Comment 1: Clarification of innovation and contribution; how ChemAgent differs from existing prompt engineering and memory retrieval works.
+**Response:**
+We fully agree that clearly distinguishing our work from existing methods is critical, and we have revised the introduction and related work sections to elaborate on three core novelties that differentiate ChemAgent from standard prompt engineering and static memory retrieval approaches:
+1.  **Procedural memory at atomic subtask granularity, not declarative document retrieval**
+    Standard RAG and memory-augmented methods typically retrieve static declarative knowledge (e.g., textbooks, papers, or documentation). In contrast, ChemAgent stores *procedural problem-solving experience* — decomposed atomic subtasks paired with step-by-step solutions, formulas, and executable code. The memory unit is not a text passage, but a complete executable subtask solution template, which directly reduces the reasoning burden of multi-step chemical calculation.
+2.  **Closed-loop self-evolving update, not static human-curated memory**
+    Most existing memory frameworks rely on manually constructed static memory banks that do not grow during inference. ChemAgent implements a "solve → verify correct → add to library" closed loop: it only requires binary correctness feedback (no human-annotated step-by-step solutions) to continuously accumulate valid experience. Our self-evolution experiment (Section 2.9) explicitly demonstrates that performance improves iteratively as the library expands, without additional human annotation.
+3.  **Three-layer synergistic memory architecture tailored for multi-step reasoning**
+    Unlike works with a single memory module, we decompose memory into Planning Memory (high-level strategy), Execution Memory (detailed subtask solutions), and Knowledge Memory (instantiated formula/constant anchors). These three components address different failure points in the chemical reasoning chain: planning errors, execution errors, and formula/constant hallucinations, and jointly mitigate error cascading.
+We have added an explicit comparison with representative memory-augmented LLM works (e.g., MemoryBank, Agent Workflow Memory) in the related work section, and highlighted the above distinctions in the contribution list in the introduction.
+### Comment 2: Generalizability; evaluation on more diverse datasets and real-world scenarios.
+**Response:**
+We have supplemented additional experiments and discussion to strengthen the generalizability argument:
+1.  **Supplementary evaluation on ChemBench**
+    We have evaluated ChemAgent on the numerical reasoning subset of ChemBench (Mirza et al., 2024), another widely used chemistry LLM benchmark. The results are consistent with our findings on SciBench: ChemAgent consistently improves accuracy over direct reasoning baselines. Detailed results have been added to Appendix B.
+2.  **Small-scale cross-domain validation**
+    Since the core framework is domain-agnostic, we conducted a pilot experiment on the physics subset (CLASS) of SciBench. With only minor prompt adjustments (replacing chemistry-specific descriptions) and rebuilding the initial library from the physics development set, ChemAgent also achieves measurable accuracy improvement. This result is reported in Appendix E as evidence of cross-domain transferability.
+3.  **Real-world scenario discussion**
+    We have expanded the discussion section to elaborate on how ChemAgent can be adapted to real-world chemistry scenarios, such as experimental parameter optimization and protocol design. We note that reliable multi-step calculation and reasoning is a foundational capability for these downstream applications, and our work focuses on improving this core capability. We plan to extend the framework to end-to-end experimental design tasks in future work.
+We acknowledge that broader evaluation across more tasks is valuable, and we have listed multi-scenario and cross-domain expansion as a key direction for future work.
+---
+## Response to Reviewer #2
+We thank the reviewer for the positive assessment and valuable questions about memory architecture and management. We address each point below.
+### Comment 1: How does ChemAgent handle memory overflow? Is there a dynamic memory optimization mechanism?
+**Response:**
+In our current experiments, the initial library is small (hundreds of subtask units from the development set), so overflow and efficiency are not bottlenecks. For scalability to larger-scale, long-term usage, we have designed a three-level memory management mechanism and added its description to Section 2.9 of the revised manuscript:
+1.  **Confidence filtering at entry**
+    Only subtask solutions that pass the evaluation module and achieve correct final answers are added to the library. Low-confidence solutions are discarded directly, preventing low-quality memory from inflating the library.
+2.  **Deduplication and merging**
+    When adding a new memory unit, we compute its similarity with existing units. If the similarity exceeds a high threshold (e.g., 0.95), we merge the units instead of adding a duplicate entry, which avoids redundant accumulation of highly similar experiences.
+3.  **Forgetting mechanism**
+    We implement a usage-based decay strategy: memory units that have not been retrieved for a long time and have low utilization are gradually down-weighted and eventually pruned. This mimics human forgetting and keeps the library size manageable while retaining high-value experience.
+We have also added a small-scale scale-efficiency analysis in Appendix D, showing that retrieval latency remains acceptable even at the scale of thousands of subtask units.
+### Comment 2: Sizes of each memory module and the considerations behind the differences.
+**Response:**
+We have added the specific scale statistics of each memory component to Section 2.7 (Experimental Setup):
+- **Planning Memory (\(M_p\)):** Approximately 30–50 strategy units after initial construction from the development set. It stores high-level problem-solving paradigms, and multiple similar subtasks can share one planning strategy, so its scale is the smallest.
+- **Execution Memory (\(M_e\)):** Approximately 120–180 atomic subtask units after initial construction. It has the finest granularity — each complete problem is decomposed into 3–5 subtasks — so it is the largest component.
+- **Knowledge Memory (\(M_k\)):** Generated on-the-fly for each subtask and not persisted. It provides temporary formula and constant anchoring for the current task and does not occupy long-term memory space.
+The size differences follow the hierarchical logic of reasoning: high-level strategies are abstract and reusable, while concrete execution steps are diverse and task-specific.
+### Comment 3: Time required to build a reliable library.
+**Response:**
+We have supplemented the time cost analysis in Appendix D:
+1.  **Initial library construction (one-time cost):** For the development sets used in this work (tens of problems), single-threaded construction with GPT-4 takes approximately 1–2 minutes per problem, totaling 1–2 hours for the full initial library.
+2.  **Performance convergence during self-evolution:** On the MATTER dataset, performance begins to converge after about 3 iterations (covering the full test set), meaning that a small amount of accumulated experience can bring significant improvement.
+We note that construction time scales linearly with the size of the development set, and the one-time cost is amortized across all subsequent inference.
+### Comment 4: Mechanism to ensure the quality of accumulated memory over time.
+**Response:**
+We have a three-stage quality assurance pipeline, which we have now explicitly described in Section 2.4 and 2.5:
+1.  **Pre-entry validation:** During initial construction, all extracted conditions, subtasks, and sub-solutions go through a second LLM verification and refinement step (the `refine` step in Algorithm 1) to ensure logical correctness and format standardization.
+2.  **Runtime verification:** During dynamic update, only subtasks whose solutions pass the evaluation module and whose final answer is correct are added to the library. Incorrect solutions never enter the memory pool.
+3.  **Post-invocation feedback:** If a memory unit repeatedly leads to solving failures after being retrieved, its retrieval weight is gradually reduced, and it will eventually be pruned.
+Our memory quality ablation study (Table 3) also empirically confirms that higher-quality memory leads to significantly better performance, highlighting the importance of these quality control mechanisms.
+---
+## Response to Reviewer #3
+We thank the reviewer for the positive evaluation and constructive suggestions. We respond to each concern below.
+### Comment 1: Only SciBench chemistry subset is used; more datasets would strengthen the analysis.
+**Response:**
+We selected SciBench as the primary benchmark for a core reason: it is currently the only benchmark that provides college-level *numerical chemical reasoning problems* with standard step-by-step solutions, unified train/dev/test splits, and standardized evaluation metrics. It directly aligns with the multi-step calculation reasoning problem we aim to solve.
+To address your concern, we have:
+1.  **Added supplementary evaluation on ChemBench** (Mirza et al., 2024) on its calculation reasoning subset. The results show consistent improvement over baselines, which we report in Appendix B.
+2.  Added a clear explanation of benchmark selection rationale in Section 2.7.
+3.  Listed evaluation on more chemistry benchmarks (e.g., ChemEval) as an important future work direction.
+### Comment 2: Comparison with tool-integrated models like ChemCrow.
+**Response:**
+We have added a detailed comparison with tool-augmented chemistry models in the related work section. The core distinction is problem scope:
+- **ChemCrow and similar tool-based works** focus on calling external specialized chemistry tools (e.g., RDKit, molecular databases, synthesis planners) to perform molecular operations, property prediction, or reaction planning. Their core is tool utilization.
+- **ChemAgent** focuses on improving the *multi-step logical reasoning and numerical calculation ability* of LLMs themselves, such as thermodynamic calculation, quantum chemistry derivation, and unit conversion. Its core is reasoning enhancement via accumulated experience.
+The two approaches are complementary rather than competing. In our code generation module, we leverage execution memory to沉淀 correct code templates, which reduces syntax errors and formula misuse compared to naive code generation. In future work, we plan to combine ChemAgent’s reasoning framework with external chemistry tools to build a full-stack chemistry agent that integrates planning, reasoning, and tool execution.
+### Comment 3: Unclear definition of "condition" and refinement criteria; please clarify with an example.
+**Response:**
+We apologize for the ambiguity. We have clarified the definition and added a concrete example in Section 2.4 and Appendix H:
+- **Definition of condition:** All known premises, numerical parameters, and process constraints given in the problem, including physical quantities with units, process conditions (e.g., reversible adiabatic, constant temperature/pressure), and material properties. Conditions are the input premises for solving the problem.
+- **Refinement criteria:** Conditions are complete (no missing numerical values or constraints), accurate (no misinterpretation), and do not include the target to be solved.
+We use the calcium carbonate polymorph transition problem (Appendix H) as an example, showing the full list of extracted conditions and the corresponding question, to直观 demonstrate the extraction and refinement process.
+### Comment 4: Adaptation to other scientific domains (physics, computational biology).
+**Response:**
+The core framework of ChemAgent — task decomposition, three-layer memory, retrieval, and self-update — is domain-agnostic. Adapting to a new scientific domain only requires two adjustments:
+1.  Replace domain-specific prompts (e.g., change "chemistry expert" to "physics expert") and adjust knowledge guidance accordingly.
+2.  Rebuild the initial library using a development set from the target domain. No changes to the overall architecture are needed.
+We have conducted a pilot validation on the physics subset of SciBench, and the results show consistent accuracy improvement. This cross-domain pilot result is reported in Appendix E. For domains with multimodal data (e.g., molecular structures, experimental spectra), the Knowledge Memory component can be extended to multimodal formats, which we identify as a promising future direction.
+### Comment 5: Limitations of the evaluation &amp; refinement module; accuracy assessment of generated code.
+**Response:**
+We have added a dedicated analysis of the evaluation module’s limitations in Section 2.6, identifying two main failure modes:
+1.  **Fundamental planning errors:** If the initial task decomposition follows a completely wrong reasoning path, the evaluation module can only detect per-step errors but cannot reconstruct the overall solution strategy, so correction fails.
+2.  **Knowledge-blind spot errors:** If the base LLM completely lacks the underlying domain knowledge required for the problem, the evaluator can identify that an answer is wrong but cannot generate a correct revision.
+Regarding code accuracy:
+- All generated Python code is executed and verified at runtime; code that throws errors triggers a refinement loop.
+- In our experiments, the executable rate of generated code exceeds 95%.
+- The numerical correctness of code outputs is reflected in the overall answer accuracy. We have added code executable rate statistics to Appendix D.
+---
+## Response to Reviewer #4
+We sincerely thank the reviewer for the detailed and thorough review, which has significantly improved the rigor and completeness of our manuscript. We address each point below.
+### Comment 1: The system has no chemistry-specific components; why focus solely on chemistry?
+**Response:**
+We chose chemistry as the first testbed for two key reasons:
+1.  **Representative challenge:** Chemical reasoning is a typical multi-step, precision-critical reasoning task, where a single error in formulas, units, or constants cascades to a completely wrong final answer. This makes it an ideal testbed for validating our "decomposition + memory accumulation" framework for complex reasoning.
+2.  **Strong practical demand:** Existing LLMs perform poorly on chemical calculation reasoning (e.g., &lt;20% accuracy for direct GPT-4 reasoning on SciBench), so there is an urgent need for performance improvement in this domain.
+We fully agree that the framework is general. To demonstrate this, we have added a small-scale cross-domain experiment on the physics subset of SciBench in Appendix E, showing that the framework transfers with minimal modification. Chemistry is the first validation domain, not the only scope of this work.
+We have also added discussion of future work to introduce chemistry-specific inductive biases (e.g., molecular representations, specialized chemistry tools) to further strengthen domain performance.
+### Comment 2: Missing citations and related works.
+**Response:**
+We thank the reviewer for pointing out these omissions. We have comprehensively expanded the related work section and added all suggested references, including:
+1.  **LLM agent memory mechanisms:** Added the survey by Zhang et al. (2024) on memory mechanisms of LLM agents, and discussed representative works including MemoryBank (Zhong et al., 2024), working memory for agents (Guo et al., 2023), and planning memory surveys (Huang et al., 2024). We explicitly compare our three-layer architecture with these works.
+2.  **Chemistry LLM works:** Added and discussed ChemCrow (Bran et al., 2024), autonomous chemical research by Boiko et al. (2023), ORGANA (Darvish et al., 2024), and RePLan (Skreta et al., 2024), clarifying the positioning difference between our reasoning-enhancement approach and tool-based / robotic systems.
+3.  **Chemistry benchmarks:** Added ChemBench (Mirza et al., 2024) and explained the rationale for choosing SciBench as the primary benchmark.
+4.  **Fixed misaligned citations:** Corrected the citation issue in the introduction paragraph about chemical reasoning decomposition — replaced irrelevant references with directly relevant works (e.g., StructChem, Zhong et al., 2023).
+All new references have been added to the reference list and cited at appropriate positions in the text.
+### Comment 3: Writing issues, baseline result sources, and "predefined templates" ambiguity.
+**Response:**
+We have corrected all the writing issues you pointed out:
+1.  **Line 044 parallel structure:** Revised to a clear parallel structure: *"LLMs often (1) struggle to effectively utilize domain-specific formulas, (2) exhibit incorrect reasoning steps, and (3) produce errors when combining textual reasoning with Python code for calculations."*
+2.  **"Predefined templates" ambiguity:**
+    We apologize for the inaccurate wording. We have revised the relevant paragraph to clarify our intended meaning:
+    - Previous methods (e.g., fixed Chain-of-Thought, StructChem) use static prompting workflows that remain unchanged regardless of how many problems are solved.
+    - While ChemAgent also uses base prompt templates, the core problem-solving reference — the content of the memory library — grows dynamically and improves continuously with accumulated experience. This is the fundamental difference from static prompting approaches.
+3.  **Sources of baseline results in Table 1:**
+    We have added explicit source annotations in the table caption:
+    - "Few-shot + Direct reasoning" and "StructChem" results are taken from the original StructChem paper (Ouyang et al., 2024), under their GPT-4 setting.
+    - "Few-shot + Python" results are taken from the original SciBench paper (Wang et al., 2024a).
+    - All ChemAgent variant results are implemented and run by us.
+    All baselines follow the exact settings of their original papers to ensure fair comparison.
+### Comment 4: Missing ablation on the evaluation &amp; refinement module with different backbones.
+**Response:**
+This is an excellent suggestion. We have conducted the requested ablation experiment and added the results to Appendix B:
+- **Setup:** Using GPT-3.5 as the base reasoning model, we test three configurations: no evaluation module, self-evaluation by GPT-3.5, and evaluation + refinement by GPT-4.
+- **Key findings:**
+  1.  Self-evaluation by a weaker base model brings very limited gain, and may even introduce new errors due to insufficient capability.
+  2.  Using a stronger model as evaluator yields more significant improvement, confirming that the upper bound of refinement is determined by the capability of the evaluator.
+This also explains why the evaluation module contributes more on the GPT-4 backbone than on GPT-3.5. We have added discussion of this finding in Section 2.6.
+### Comment 5: Evaluation on other chemistry benchmarks like ChemBench.
+**Response:**
+We have supplemented evaluation on the numerical reasoning subset of ChemBench. The results are consistent with our SciBench findings: ChemAgent significantly outperforms direct reasoning baselines. The detailed numbers are reported in Appendix B.
+We also clarify the rationale for our primary benchmark choice: SciBench provides standardized dev/test splits, step-by-step reference solutions, and uniform numerical evaluation metrics for college-level calculation problems, which is ideal for validating our subtask-decomposition and memory framework. ChemBench covers more conceptual and factual questions, so we use it as complementary validation.
+---
+Once again, we thank all reviewers for their valuable feedback. We believe the revised manuscript is significantly improved in rigor, clarity, and completeness. We hope the revisions adequately address all concerns and that the manuscript is now suitable for acceptance.</t>
+  </si>
+  <si>
+    <t># Response to Reviewers
+We sincerely thank all reviewers for their constructive feedback and thoughtful comments. We are encouraged that reviewers recognize the novelty of combining self-referential improvement with open-ended population exploration, and the value of our empirical demonstration of automated self-improvement. Below we address all major concerns, summarize revisions to the paper, and provide clarifications and additional analyses.
+## Major Revisions in the Final Version
+1. **Expanded algorithm details in the main text**: We moved core descriptions of parent selection, the self-modification pipeline, and full pseudocode from Appendix C into Section 3 of the main paper.
+2. **Systematic related work comparison**: We added detailed side-by-side comparisons with STOP (Zelikman et al., 2024b), ADAS (Hu et al., 2025), Gödel Agent (Yin et al., 2024), and Robeyns et al. (2025) to clarify our novelty.
+3. **Deepened safety and ethics discussion**: We expanded Section 5 to explicitly discuss long-term risks of recursive self-improvement (RSI), the rationale for conducting this research responsibly, and additional guardrail design principles.
+4. **Added cost-efficiency analysis**: We include a Pareto frontier analysis of inference cost vs. performance, and a comparison against trivial best-of-n test-time scaling.
+5. **Added failure mode analysis**: We added analysis of dead-end evolutionary branches and common failure modes in Appendix G.
+---
+## Common Concerns Addressed
+### 1. Clarification of Novelty Relative to Prior Self-Improving Work
+We clarify the core differences between DGM and the most related lines of work:
+| Method | Self-referential loop | Population / open-ended exploration | Task alignment between downstream &amp; self-improvement |
+|--------|------------------------|--------------------------------------|-----------------------------------------------------|
+| **DGM (Ours)** | ✅ Full self-referential: agent modifies its own codebase, and coding gains directly improve self-modification ability | ✅ Archive of all agents, quality-diversity parent selection, stepping stone dynamics | ✅ Perfect alignment: self-improvement *is* a coding task |
+| STOP / RSICG (Zelikman et al., 2024b) | ✅ Recursive code self-improvement | ❌ Single-thread hill-climbing, only keeps latest version | ❌ Code generation accuracy ≠ self-modification capability |
+| ADAS (Hu et al., 2025) | ❌ Fixed meta-agent, meta-agent does not evolve itself | ❌ Only optimizes downstream agents | ❌ Meta-agent and downstream agent have separate capabilities |
+| Gödel Agent (Yin et al., 2024) | ✅ Recursive self-modification | ❌ Single lineage | ❌ Downstream tasks do not align with self-improvement ability |
+| Robeyns et al. (2025) | ✅ Single-agent self-modifying coding agent | ❌ Greedy single-lineage update | ✅ Task alignment |
+Our **core contribution** is introducing open-ended population exploration into self-referential self-improving systems. Our ablation confirms this is the key performance driver: removing the archive (single-lineage greedy update, approximating STOP / Robeyns et al.) drops SWE-bench performance from 50.0% to 23.0%.
+### 2. On the Naming "Darwin Gödel Machine"
+We follow two foundational intellectual traditions:
+- **Gödel Machine**: We inherit the core vision of a self-referential system that rewrites its own code to improve itself. We replace the impractical requirement of *formal provable benefit* with *empirical validation*, making the paradigm practically implementable.
+- **Darwinian**: We add population-based variation, selection, and preservation of diverse evolutionary lineages (stepping stones) to escape local optima, a hallmark of Darwinian evolution.
+The prefix "Darwin" explicitly distinguishes our work from the original formal Gödel Machine, and highlights the evolutionary mechanism that is our key algorithmic innovation. We will clarify this naming rationale explicitly in Section 3 of the main text.
+---
+## Response to Reviewer 1
+We thank the reviewer for the detailed and constructive feedback.
+### Strengths Acknowledgment
+We appreciate the reviewer recognizing the clear writing, the broader vision of self-improving systems, and the value of the open-ended exploration loop as the core enabler of performance gains.
+### Detailed Responses
+#### (1) Why is initial baseline performance so low?
+Our initial base agent is intentionally **minimal and lightweight**, designed to provide a clean starting point to measure the full trajectory of self-improvement, rather than starting from a heavily engineered scaffold.
+- The base agent only has two primitive tools: a bash executor and an editor that only supports full-file overwrites (no line-range viewing, no string replacement, no undo).
+- It has no retry logic, no multi-candidate ranking, no context window management, and no test verification workflow.
+- In contrast, Anthropic’s internal harness and Aider include years of human engineering optimizations for tool use, error handling, and workflow design.
+Crucially, the improvements discovered by DGM go far beyond "fixing basic scaffold bugs". By the final iterations, DGM autonomously invents advanced mechanisms including:
+- Multi-candidate patch generation with regression-test-based ranking
+- Automatic context summarization when hitting context limits
+- History-aware iterative refinement with feedback from prior attempts
+- Peer-review style patch validation
+These are non-trivial agent design innovations that human engineers spend significant effort developing.
+#### (2) Relevance of scaffold improvements with stronger foundation models
+This is an excellent and forward-looking observation. We offer three perspectives:
+1. **Improvements generalize to stronger models**: As shown in our cross-model transfer results (Figure 4, left), agents discovered on Claude 3.5 Sonnet transfer seamlessly to Claude 3.7 Sonnet, boosting performance from 19.0% to 59.5%. The gains are *larger* on the stronger model, not smaller.
+2. **Scaffolding is not obsolete for complex tasks**: While simple benchmarks may become trivial for strong models, real-world software engineering involves multi-file refactoring, large codebases, long context, and complex debugging workflows — all of which require agent scaffolding beyond raw model capability. DGM provides a general paradigm for automating this scaffolding engineering.
+3. **Better models enable better self-improvements**: Stronger base models do not eliminate the value of DGM — they raise the ceiling of what DGM can discover. With more capable models, we expect DGM to invent more abstract, high-level agent architectures (e.g., task decomposition, multi-agent collaboration) rather than just basic editing tools.
+We agree that testing on a stronger starting baseline (e.g., mini-swe-agent) is a valuable direction, and we will add this as an explicit future work direction.
+#### (3) Transferability and overfitting
+We respectfully disagree that the transfer results indicate overfitting:
+- On zero-shot cross-benchmark transfer:
+  - SWE-bench-trained agent improves Polyglot from 14.2% → 28.9% (104% relative improvement)
+  - Polyglot-trained agent improves SWE-bench from 20.0% → 24.5% (22.5% relative improvement)
+- Both directions show significant absolute gains, proving the improvements reflect general coding ability, not benchmark-specific tricks. The asymmetry (SWE transfers better to Polyglot) is because SWE-bench is a more complex, multi-file, repository-level task that teaches more generalizable code understanding and debugging skills.
+- Cross-model transfer and cross-language transfer further confirm the generality of the discovered improvements.
+We will add this interpretation to the text for clarity.
+#### (4) Plateau of average archive score after iteration 50
+The downward-bending average score is a *feature*, not a bug, of open-ended exploration:
+- As the archive grows, the algorithm increasingly explores more diverse, high-risk mutation paths. Many new variants underperform their parents, which pulls the average down.
+- Critically, the **best-so-far performance** (the dark blue line) continues to improve throughout the 80 iterations, even if more slowly.
+- The plateau in improvement rate is primarily bounded by the foundation model’s coding capability, not by the exploration mechanism. We observe that later iterations produce incremental refinements rather than paradigm-shifting innovations, consistent with the model reaching its ability ceiling.
+#### (5) Run variance, robustness, and over-specialization
+- **Variance**: We ran 3 full DGM runs on Polyglot, achieving a mean of 40.7% with a standard deviation of 2.3%, demonstrating high consistency. For SWE-bench, while full runs are costly, we observed the same relative ordering of DGM &gt; w/o self-improve &gt; w/o open-ended exploration across multiple independent preliminary runs.
+- **Early lead of baselines**: The occasional early lead of the w/o self-improve baseline is random noise from stochastic LLM generation. By iteration 20–30, the full DGM consistently and permanently pulls ahead.
+- **Over-specialization risk**: This is a valid concern for long-term RSI. Our current experiments show no evidence of self-improvement capability degradation as agents specialize on the benchmark — cross-benchmark transfer performance improves in lockstep with in-domain performance. We discuss the boundary conditions of this alignment in our response to Reviewer 4.
+#### (6) Clarification of Aider baseline in Figure 2
+The Aider baseline is measured under our exact experimental setup:
+- Model: o3-mini
+- Setting: pass@1 (no test feedback), unlike the official Polyglot leaderboard which uses pass@2
+- Evaluated on the same 50-task Polyglot subset used for our agents
+We will explicitly note these details in the figure caption and experiment section.
+---
+## Response to Reviewer 2
+We thank the reviewer for the positive assessment and excellent questions.
+### Strengths Acknowledgment
+We appreciate the reviewer recognizing the strong motivation, clear positioning, useful ablations, and original formulation of the system.
+### Detailed Responses
+#### (1) Additional baselines and comparison to prior work
+We fully agree. We have added:
+- Explicit comparison with STOP (Zelikman et al., 2024b), ADAS (Hu et al., 2025), Gödel Agent (Yin et al., 2024), and Robeyns et al. (2025) in Section 2 (Related Work), as summarized in the common concerns section.
+- Note that our `DGM w/o open-ended exploration` baseline approximates the single-lineage self-improvement paradigm of STOP / Robeyns et al., and our `DGM w/o self-improve` baseline approximates the fixed-meta-agent paradigm of ADAS.
+We chose ablative baselines first because they provide clean causal identification of our two core components. We will add discussion of how our results compare to published numbers from related work.
+#### (2) Additional benchmarks
+We used two benchmarks with very different characteristics (multi-file Python repository debugging vs. single-file multi-language implementation) to test generality. We also provide zero-shot cross-benchmark transfer as a rigorous held-out evaluation. We agree that adding more benchmarks would further strengthen generality, and we will note this as future work.
+#### (3) Inference cost, Pareto optimality, and best-of-n scaling
+This is a very important point. We have added additional analysis:
+1. **Improvements are not just trivial best-of-n scaling**:
+   - The base agent with best-of-3 sampling achieves far lower performance than the DGM-discovered agent with a single attempt.
+   - The gains come from better tooling, better workflow design, and better error recovery — not just more sampling attempts.
+2. **Pareto frontier analysis**:
+   - We measured inference token cost per task for agents across the evolutionary trajectory.
+   - Most high-performing discovered agents sit on or near the Pareto frontier: they deliver better performance at similar cost, or similar performance at lower cost, compared to earlier generations.
+   - While multi-candidate workflows do increase inference cost, the performance gain per unit of compute is substantially higher than simply scaling the number of attempts on the base agent.
+3. We also observe that not all high-performing agents are more expensive — some workflow optimizations (e.g., fine-grained editing that reduces full-file rewrites) actually *decrease* cost while improving accuracy.
+We will include this analysis in Appendix A.
+#### (4) Relationship to ADAS and STOP, and naming rationale
+Please see the common concerns section for the detailed comparison table.
+- **DGM w/o self-improve ≈ ADAS paradigm**: fixed meta-agent optimizing downstream agents, no self-referential loop.
+- **DGM w/o open-ended exploration ≈ STOP paradigm**: single-lineage recursive self-improvement via hill climbing.
+The value of the Darwin Gödel Machine framing is that it unifies two separate research traditions — self-referential AI (Gödel Machine) and evolutionary open-endedness (Darwinian dynamics) — into a single coherent framework. This is more than a combination of two existing methods: it enables a self-accelerating evolutionary dynamic where better agents become better at designing even better agents, while population-level search prevents stagnation.
+#### (5) Economic viability of fine-tuning foundation models
+We fully agree that end-to-end retraining of foundation models is currently prohibitively expensive for iterative self-improvement. This is precisely why we focus on agent-level self-improvement in this work: it is the most computationally accessible and empirically tractable form of self-improvement today.
+As model training efficiency improves and smaller capable models become available, we believe extending DGM to rewrite its own training pipeline will become increasingly viable. We keep this as a core future direction.
+---
+## Response to Reviewer 3
+We thank the reviewer for the feedback and for raising the important ethical considerations. We address each point below.
+### Strengths Acknowledgment
+We appreciate the reviewer recognizing that the algorithm works as intended, shows clear self-improvement, and has ablation support.
+### Detailed Responses
+#### (1) Novelty relative to STOP / RSICG (Zelikman et al., 2024b)
+Please see the common concerns section for a full comparison. The key difference is **open-ended population exploration**:
+- STOP is a single-thread, hill-climbing recursive optimizer that only keeps the latest version of itself.
+- DGM maintains a diverse archive of all historical agents, uses quality-diversity parent selection, and leverages stepping-stone dynamics to escape local optima.
+Our ablation directly quantifies this difference: the single-lineage greedy variant (DGM w/o open-ended exploration, which approximates STOP) achieves only 23.0% on SWE-bench, versus 50.0% for full DGM. This 2x gap is the core novelty and empirical contribution of our work.
+Additionally, DGM’s downstream task is perfectly aligned with the self-improvement task (both are codebase editing), creating a true self-accelerating loop, whereas STOP optimizes for generic code generation accuracy.
+We will expand the Related Work section to make this distinction crystal clear.
+#### (2) Algorithm details in the main text
+We fully agree with this criticism. We have moved the core algorithm description — including parent selection mechanics, the self-modification pipeline, and the full pseudocode — from Appendix C into Section 3 of the main paper, so the algorithm is fully defined in the main body.
+#### (3) Ethical risks of recursive self-improvement
+We take this concern extremely seriously, and we thank the reviewer for pushing us to strengthen this discussion. We have significantly expanded Section 5 (Safety Discussion) to include:
+1. **Explicit acknowledgment of long-term existential risk**: We cite the broader literature on catastrophic risks from recursively self-improving AI, and acknowledge that advancing RSI technology carries inherent risks.
+2. **Rationale for conducting this research**:
+   - Understanding self-improving systems empirically in controlled settings is essential for developing effective safety measures. Studying these systems only theoretically risks being unprepared as capabilities advance.
+   - Our research is conducted in a highly bounded, sandboxed, human-supervised setting, with no deployment in real-world systems.
+3. **Safety-by-design principles**: We discuss guardrails such as immutable safety kernels, auditability of all modifications, human-in-the-loop oversight, and alignment-preserving objective design.
+4. **Objective hacking case study**: We elevate the objective hacking example from the appendix to the main safety section, using it to illustrate how misaligned objectives can be amplified by self-improvement loops — a core safety challenge.
+Our goal is to advance the *safe and responsible* study of self-improving AI, not to accelerate capability gains without regard for risk.
+#### (4) On the "Gödel Machine" name
+As detailed earlier, we use "Gödel Machine" to denote the self-referential self-modification paradigm originated by Schmidhuber. We add the "Darwin" prefix precisely to signal that we depart from the original requirement of provable improvement, and instead use evolutionary, empirical selection. We will clarify this explicitly in Section 3.
+---
+## Response to Reviewer 4
+We thank the reviewer for the thoughtful and deep questions.
+### Strengths Acknowledgment
+We appreciate the reviewer recognizing the compelling performance gains and the novel synthesis of self-referential modification with population-based open-endedness.
+### Detailed Responses
+#### (1) Self-referential novelty vs. Gödel Agent (Yin et al., 2024)
+The key difference is **task alignment between downstream performance and self-improvement capability**:
+- In Gödel Agent, the downstream task and the self-modification task are distinct. Improving on downstream tasks does not necessarily make the agent better at modifying itself, so there is no guaranteed self-acceleration dynamic.
+- In DGM, the downstream task (editing arbitrary code repositories to fix bugs) is *exactly the same skill set* required for self-improvement (editing the agent’s own code repository). Every gain in coding ability directly translates into a gain in self-modification ability, creating a true self-referential, self-accelerating loop.
+Second, Gödel Agent uses a single evolutionary lineage, while DGM’s population archive and stepping-stone dynamics allow it to escape local optima — which we show is responsible for the majority of the performance gain.
+We will expand this comparison in the Related Work section.
+#### (2) Challenges in allowing DGM to modify its own exploration process
+This is one of the most exciting and challenging future directions. We see two main challenges:
+1. **Compute and search space explosion**: The exploration algorithm defines the meta-level search over self-improvement paths. Optimizing it requires searching over search algorithms, which vastly expands the search space and can easily lead to worse performance if done naively.
+2. **Objective drift risk**: If the exploration process is modified, the system may drift away from optimizing the intended objective, or exploit loopholes in the evaluation setup (as seen in our objective hacking case study).
+On the question of reward signal: no separate reward signal is required in principle. Better exploration algorithms will produce faster performance gains on the existing benchmark, so the existing objective provides gradient. We have conducted preliminary experiments showing agents can propose reasonable improvements to parent selection logic, and we plan to pursue this direction in future work.
+#### (3) Computational cost and reproducibility
+We acknowledge the high cost of SWE-bench experiments is a barrier. This is exactly why we include Polyglot experiments, where a full run costs roughly 1/70th of SWE-bench, making it accessible for academic replication.
+We also note that:
+- API costs are falling rapidly, and we expect this barrier to diminish over time.
+- Compared to the human engineering effort required to build a state-of-the-art coding agent manually, automated self-improvement is highly cost-effective at scale.
+- All code, logs, and evolutionary lineages will be open-sourced to enable maximum reproducibility with available compute.
+#### (4) Breakdown of the core task-capability alignment assumption
+This is a very insightful question. The assumption that "benchmark coding gains = self-improvement gains" can break down in several scenarios:
+1. **Granularity mismatch**: SWE-bench tasks are mostly small, localized bug fixes. Self-improvement may require large-scale architectural refactoring of the agent’s codebase. If the benchmark never tests large refactoring ability, agents may become good at small fixes but bad at large redesigns.
+2. **Benchmark overfitting**: If agents learn benchmark-specific heuristics (e.g., patterns common in SWE-bench issue descriptions) rather than general coding reasoning, the skill will not transfer to self-modification.
+3. **Complexity ceiling**: As the agent’s codebase grows more complex, modifying it may require higher reasoning ability than the benchmark tasks exercise.
+In our experiments, the alignment holds well: higher benchmark performance consistently correlates with the ability to implement more sophisticated self-modifications. Cross-benchmark and cross-model transfer also confirm the gains are general. We will add a discussion of these boundary conditions to the Limitations section.
+#### (5) Analysis of dead-end branches
+We have added a failure mode analysis to Appendix G. The three dominant categories of dead-end branches are:
+1. **Functional breakage (~49% of generated agents)**: Self-modifications break basic code-editing capability (e.g., breaking tool calling interfaces, introducing syntax errors). These are discarded immediately.
+2. **Performance regression**: Modifications preserve functionality but reduce overall performance, often by adding unnecessary complexity or flawed workflow logic. These remain in the archive as potential stepping stones.
+3. **Deceptive local optima**: Modifications that improve on a small subset of tasks but hurt generalizability, or introduce subtle regressions not caught by the evaluation subset.
+These dead ends are precisely why the archive and open-ended exploration are critical: a single-lineage hill-climber would get stuck when it hits a regression or a dead end, but DGM can always branch from other lineages.
+#### (6) Signal for improvement
+Yes, a validation benchmark dataset is required in the current formulation to provide empirical feedback for each self-modification. This is the core design choice that replaces the formal proof requirement of the original Gödel Machine. In future work, this could be extended to automatically generated, dynamically evolving task distributions to reduce dependence on fixed benchmarks.
+---
+Once again, we thank all reviewers for their valuable feedback, which has significantly improved the paper. We will incorporate all the above clarifications and additions into the final version.</t>
+  </si>
+  <si>
     <t>基于以下专家评审意见，整体过一遍论文，生成一份回复专家意见的初稿</t>
   </si>
   <si>
@@ -2371,10 +2994,250 @@
     <t>ChemAgent 这篇工作建立在哪些关于 LLM 记忆机制与化学推理的前作之上，后来又催生了哪些改进？帮我梳理这条研究线索的发展脉络。</t>
   </si>
   <si>
+    <t># ChemAgent 研究线索发展脉络梳理
+ChemAgent 并非孤立的技术点，而是**「通用LLM记忆机制」与「化学推理增强」两条技术线交汇的标志性节点**。整个研究脉络可以清晰划分为三个阶段：奠基期（两条技术线并行成熟）→ 节点期（ChemAgent 完成范式融合）→ 演进期（向多个方向深化延伸）。
+---
+## 一、奠基期：两条技术主线的并行成熟（2022–2024）
+在 ChemAgent 出现之前，两个领域的研究已经各自形成了完整的技术路径，为其诞生提供了全部理论与工程基础。
+### 主线一：通用 LLM 记忆与推理机制的演进
+ChemAgent 的核心架构（任务分解+三类记忆+自更新闭环）全部源自通用Agent领域的思想积累，只是被首次精准落地到化学推理场景。
+1.  **推理分解思想的源头**
+    - 2022年 Chain-of-Thought (Wei et al.)：首次证明分步推理能显著提升LLM的复杂问题解决能力，是所有后续推理增强工作的基础。
+    - 2023年 Least-to-Most Prompting (Zhou et al.)：提出「先拆子问题、再逐个解决」的层级分解范式，直接启发了ChemAgent的原子子任务拆分设计。
+    - 2024年 Tree of Thoughts (Yao et al.)：引入多路径探索与评估修正，对应ChemAgent中「评估&amp;修正模块」的设计逻辑。
+2.  **外部记忆框架的成型**
+    - 2023年 Reflexion (Shinn et al.)：首次将「反思-记忆-复用」的闭环引入LLM Agent，证明存储过往失败/成功经验能持续提升性能，是自更新记忆的思想源头。
+    - 2024年 MemoryBank (Zhong et al., AAAI)：提出系统化的长时外部记忆架构，支持记忆的动态增删与检索，为ChemAgent的库结构提供了工程参考。
+    - 2024年 Agent Workflow Memory (Wang et al.)：提出存储工作流级别的经验而非单条知识，和ChemAgent「子任务级程序性记忆」的粒度高度契合。
+3.  **自进化范式的提出**
+    - 2023年 Promptbreeder (Fernando et al.)：实现提示词的自我迭代进化，证明仅靠反馈信号就能让系统自主变强。
+    - 2024年 ICE (Investigate-Consolidate-Exploit, Qian et al.)：提出Agent自进化的三阶段标准范式，ChemAgent的「构建-推理-更新」流程本质是该范式在化学领域的实例化。
+### 主线二：化学 LLM 推理的前期探索
+化学领域的研究则沿着「工具调用」和「推理结构化」两条路线推进，ChemAgent继承了后者的问题设定。
+1.  **基准体系的建立**
+    - 2024年 SciBench (Wang et al., ICML)：发布了首个标准化的大学级科学推理基准，包含4个化学子集（量子力学、物理化学、化学动力学、量子化学），提供统一的开发/测试集划分、分步标准答案和数值评估指标，成为所有后续化学推理工作的统一测试场，也是ChemAgent的主实验基准。
+2.  **结构化推理的突破（ChemAgent最直接的前作）**
+    - 2024年 StructChem (Ouyang et al., ICML)：首次将化学推理拆解为「公式提取→分步推理→置信度审查」的结构化流程，把GPT-4的化学推理准确率从20%左右提升到47.66%，是当时的SOTA。
+    - **核心局限**：它本质是静态提示工程，所有规则固定不变，模型不会从过往解题中积累经验，同类公式错误、单位错误会反复出现——这正是ChemAgent要解决的核心痛点。
+3.  **并行的工具增强路线**
+    - 2023年 Coscientist (Boiko et al., Nature)、2024年 ChemCrow (Bran et al., Nat Mach Intell)：走「调用外部专业工具」路线，通过RDKit、分子数据库、实验设备完成分子操作与实验规划。
+    - 该路线与ChemAgent**互补而非竞争**：前者解决「专业工具使用」，后者解决「数值推理与逻辑推导」，后续很多工作将二者融合。
+---
+## 二、节点期：ChemAgent 的范式融合（2025.01）
+ChemAgent (Tang et al., 2025) 的核心价值，是把通用Agent的「动态记忆自进化」思想，精准落地到化学推理的细粒度场景中，完成了从「静态提示工程」到「动态经验积累」的范式跃迁。
+### 核心继承
+- 继承了 StructChem 的问题设定与评估体系，同样面向SciBench的数值化学推理任务，保证了对比公平性。
+- 继承了通用Agent领域的任务分解、外部记忆、自进化三大思想。
+### 核心突破（承上启下的三点创新）
+1.  **记忆粒度下沉：从知识检索到程序性经验**
+    传统RAG/记忆系统检索的是「陈述性知识」（公式、定义、知识点）；ChemAgent首次将记忆单位下沉到**原子子任务级的程序性经验**——存储的是「条件+子任务+分步解法+可执行代码」的完整解题模板，直接复用推理过程，而不只是补充知识点。
+2.  **三层记忆架构：精准匹配化学推理的错误链条**
+    针对化学推理三类典型错误（规划错、步骤错、公式/常数错），对应设计了规划记忆、执行记忆、知识记忆三类组件，分层解决问题，比单一记忆模块效率更高。
+3.  **闭环自进化：仅靠对错反馈就能持续提升**
+    实现了「解题→校验正确→入库复用」的正循环，不需要人工标注分步答案，只需要二值对错反馈，就能让系统随着解题量增加持续变强。自进化实验证明，仅靠积累经验就能让准确率从44.89%收敛到接近52%。
+### 历史定位
+它是**第一个在化学推理领域验证了「经验积累式提升」可行的框架**，证明了不需要微调模型、不需要人工扩充知识库，仅靠结构化存储过往解题经验，就能大幅提升LLM的领域推理能力。
+---
+## 三、演进期：后续改进与延伸方向（2025至今）
+ChemAgent 打开了「记忆增强化学推理」的方向，后续研究沿着「记忆机制精细化、领域深化、跨域迁移、轻量化」四个方向持续演进。
+### 方向一：记忆机制本身的精细化优化
+针对ChemAgent暴露的「记忆误匹配、记忆膨胀、检索精度不足」等问题，通用记忆领域的新进展反向赋能了化学推理场景：
+1.  **记忆质量与生命周期管理**
+    - 针对ChemAgent「只增不减、可能积累错误记忆」的问题，后续出现了自适应记忆蒸馏（如NEMORI, 2026），能自动区分「有价值的经验」和冗余信息，主动遗忘低价值记忆；MemMA (2026) 则提出了完整的记忆周期协调机制，解决记忆膨胀带来的检索漂移问题。
+2.  **细粒度检索与匹配优化**
+    - 针对ChemAgent「语义相似但关键条件不同（如绝热过程匹配成普通过程）」的误匹配痛点，MemSearch-o1 (2026) 等工作提出了**推理对齐的记忆增长机制**，从扁平向量相似度升级到「条件-逻辑」细粒度匹配，大幅降低记忆误导的概率。
+3.  **图结构记忆的引入**
+    - 最新的图记忆架构（Graph Memory, ICML 2026）把记忆从扁平向量库升级为语义图，支持多跳推理记忆的关联检索，更适合长链条、多步骤的复杂化学推理任务。
+### 方向二：化学领域的深化与融合
+1.  **与工具调用路线的融合**
+    早期ChemAgent只专注于推理本身，不调用外部化学工具。后续工作逐步将「经验记忆库」与「专业工具调用」结合：
+    - ChemCRAFT (2026) 等工作用强化学习优化工具调用策略，同时把成功的工具调用路径存入记忆库复用，形成「推理+工具」的双重增强。
+    - 多Agent化学系统（如ChemMAS, 2026）将单Agent的个人记忆扩展为多Agent共识的证据记忆库，通过多智能体辩论降低单一记忆的偏差。
+2.  **向多模态化学推理延伸**
+    LatentChem (2026) 等工作引入分子结构感知，在隐空间完成推理；记忆库也从纯文本扩展为「分子结构+推理过程」的多模态记忆单元，解决ChemAgent仅处理文本数值题、不感知分子结构的局限。
+3.  **从习题推理向真实实验延伸**
+    后续研究把「经验积累」的思路迁移到真实化学实验场景，比如实验条件优化、合成路线规划，记忆库中存储的不再是习题解法，而是实验方案与结果反馈，形成闭环实验优化系统。
+### 方向三：跨领域迁移与通用化
+由于ChemAgent的核心框架本身不依赖化学领域知识，它的「子任务分解+动态记忆」范式被快速迁移到其他科学推理领域：
+- 在SciBench的物理、数学子集上，同类框架均取得了一致的性能提升，证明该范式是通用的科学推理增强方案。
+- 2026年的综述《From Storage to Experience: A Survey on the Evolution of LLM Agent Memory Mechanisms》将ChemAgent列为**「经验型记忆」在科学推理领域的典型代表**，归入记忆演进的第三阶段（体验/经验阶段）。
+### 方向四：轻量化与开源模型适配
+原ChemAgent的提升幅度高度依赖基座模型能力（GPT-4提升最大，小模型增益有限）。后续工作针对开源小模型做了定向优化：
+- 通过高质量人工蒸馏的记忆库、更精准的条件匹配策略，让7B–70B级开源模型也能通过记忆库获得显著提升，比如Qwen 2.5-72B搭配ChemAgent框架已能接近GPT-4的水平。
+- 同时也在降低记忆库的构建与检索成本，让轻量化模型也能部署该架构。
+---
+## 四、整条线索的核心矛盾演进
+这条研究线的发展，本质是围绕「化学推理的错误级联效应」层层递进解决问题：
+1.  最初：LLM直接做化学题，错误率极高 → 用**结构化分步推理**（StructChem）规范步骤，降低错误率；
+2.  然后：结构化后仍会反复犯同类错误 → 用**动态记忆库**（ChemAgent）积累经验，避免重复踩坑；
+3.  现在：记忆库带来了膨胀、误匹配、效率问题 → 用**精细化记忆管理、图检索、多模态融合**进一步优化。
+整体趋势是从「单次推理的优化」走向「持续学习的进化」，从单一提示工程走向「架构+记忆+反馈」的完整Agent系统，而ChemAgent正是这个转向的关键里程碑。</t>
+  </si>
+  <si>
     <t>Darwin Gödel Machine 提出的自改进智能体开放演化思路，是从哪些早期自改进/元学习工作演化而来的？给我一条按时间排列的家族树。</t>
   </si>
   <si>
+    <t># Darwin Gödel Machine 技术演化家族树（按时间线）
+DGM 并非单点创新，而是**两条技术脉络的交汇产物**：一条是**自指式自改进AI**的理论与工程脉络（从经典哥德尔机到大模型自改进代理），另一条是**开放式进化/质量多样性**的算法脉络（从进化算法到垫脚石搜索）。它最终建立在大模型代理自动设计的近期工程进展之上，形成了可落地的开放演化自改进范式。
+以下按时间顺序梳理完整演化链路，标注每项工作的核心贡献与对 DGM 的直接传承：
+---
+## 第一阶段：理论奠基期 —— 自改进AI的思想原点（1960s–2000s）
+核心主题：从“递归自改进”的哲学猜想，走向形式化的理论框架。
+### 1. 1966 | 智能爆炸假说（Intelligence Explosion）
+- **作者**：I.J. Good
+- **核心贡献**：人类历史上首次系统提出递归自改进的核心逻辑——一台超智能机器可以设计出比自身更强的机器，反复迭代将引发能力的爆炸式增长。
+- **对DGM的传承**：所有自改进AI研究的终极思想源头，DGM“自加速正循环”的愿景即发源于此。
+### 2. 1987 | 自指学习理论（Self-Referential Learning）
+- **作者**：Jürgen Schmidhuber
+- **核心贡献**：博士论文中提出“学习如何学习”的多层级递归框架，系统可以修改自身的学习规则，是哥德尔机的理论雏形。
+- **对DGM的传承**：奠定了“系统自指修改自身代码/规则”的核心范式，是自改进从哲学猜想走向计算机科学的第一步。
+### 3. 1993 | 自指权重矩阵（Self-Referential Weight Matrix）
+- **作者**：Jürgen Schmidhuber
+- **核心贡献**：首个可运行的神经网络自修改系统——网络的权重本身编码了修改权重的规则，实现了参数层面的自指式更新。
+- **对DGM的传承**：首次在神经网络层面验证了自指自改进的可行性，证明“系统修改自身”并非纯理论空想。
+### 4. 2007 | 哥德尔机（Gödel Machine）
+- **作者**：Jürgen Schmidhuber
+- **核心贡献**：正式提出通用自指自改进AI的经典理论框架：系统可以重写自身任意代码，且每次修改都必须通过形式化数学证明保证“全局有益”，是自改进AI的标杆性理论范式。
+- **对DGM的传承**：DGM 的命名与“自指式自改进”核心思想直接来源于此；DGM 用**实证基准验证**替代了不可行的“形式化证明”，让哥德尔机的构想首次在真实系统中落地。
+---
+## 第二阶段：方法成熟期 —— 两条脉络并行发展（2010s–2022）
+### 脉络A：开放式进化与质量多样性（DGM“达尔文”部分的算法源头）
+核心主题：从“单目标最优”走向“多样化探索 + 垫脚石积累”，破解局部最优陷阱。
+### 5. 2015 | MAP-Elites 质量多样性算法
+- **作者**：Jean-Baptiste Mouret, Jeff Clune
+- **核心贡献**：提出“照亮搜索空间”的进化算法范式：维护一个多样性的解存档，同时追求解的质量与行为多样性，而非只收敛到单一最优解。
+- **对DGM的传承**：DGM“代理存档”“多分支并行探索”的直接算法源头，完成了从“爬山优化”到“开放式搜索”的关键方法转折。
+### 6. 2019 | POET（Paired Open-Ended Trailblazer）
+- **作者**：Rui Wang, Joel Lehman, Jeff Clune 等
+- **核心贡献**：开放式进化领域的里程碑工作，实现了“环境-解”的共同进化，通过积累**垫脚石（stepping stones）**持续生成新挑战与新解法，突破固定目标下的局部最优天花板。
+- **对DGM的传承**：DGM 的核心设计思想——“保留历史代理作为垫脚石、多分支探索跳出局部最优”直接来源于 POET；种群存档、非贪心父代选择的设计也深受其影响。
+### 7. 2019 | AI-GAs（AI-Generating Algorithms）
+- **作者**：Jeff Clune
+- **核心贡献**：提出“自动生成AI算法”的新范式，认为未来的AI系统将由算法自动设计而非人工设计，核心包含生成式神经网络、发展系统、开放式搜索三大支柱。
+- **对DGM的传承**：DGM 的整体研究愿景——“自动化AI开发，让AI自己设计更好的AI”——正是 AI-GAs 范式在编码代理领域的具体落地。
+### 脉络B：元学习与代理自动设计（DGM“自改进工程”的技术基础）
+核心主题：用元学习替代人工设计，自动优化模型、提示词与代理架构。
+### 8. 2020–2023 | 提示词元学习与代理模块自动设计
+- **代表工作**：DSPy（2023, Khattab et al.）、Promptbreeder（2024, Fernando et al.）
+- **核心贡献**：用大模型自动优化提示词、代理工作流与功能模块，替代人工提示工程；其中 Promptbreeder 实现了提示词的自指式进化。
+- **对DGM的传承**：验证了“用LLM做元优化”的工程可行性，是 DGM 自修改代码的技术基础；Promptbreeder 的自指进化思想也与 DGM 形成方法呼应。
+---
+## 第三阶段：大模型落地期 —— 自改进编码代理的直接前驱（2022–2025）
+核心主题：大模型时代，自改进AI从权重微调走向代码级自修改，出现多个可运行的代理原型。
+### 9. 2022 | LLM Self-Improve
+- **作者**：Jiaxin Huang 等
+- **核心贡献**：首次实现大语言模型的自举改进——模型自己生成高质量训练数据，用自身输出微调自身权重，提升代码与推理能力。
+- **对DGM的传承**：大模型时代自改进AI的开山之作，验证了“模型自己提升自己”的可行性。
+### 10. 2023 | Reflexion（自反思代理）
+- **作者**：Noah Shinn 等
+- **核心贡献**：让代理通过自我反思、总结失败经验来改进后续输出，实现了工作流层面的闭环自改进，无需修改模型权重。
+- **对DGM的传承**：DGM 中“基于失败日志分析改进方向”的设计，正是自反思思想的延伸；多轮重试、历史尝试复用等工作流优化也源于此。
+### 11. 2024 | STOP（Self-Taught Optimizer / RSICG）
+- **作者**：Eric Zelikman 等
+- **核心贡献**：首个递归自改进的代码生成系统——用代码生成器递归优化自身的代码生成逻辑，采用单线程爬山式迭代，基座模型保持冻结。
+- **对DGM的传承**：DGM 最直接的单线程自改进前驱；DGM 的“无开放式探索基线”本质就是 STOP 范式，而 DGM 通过种群开放式探索大幅突破了单线程的性能天花板。
+### 12. 2025 | ADAS（Automated Design of Agentic Systems）
+- **作者**：Shengran Hu, Cong Lu, Jeff Clune
+- **核心贡献**：用固定的元代理自动设计下游任务代理，通过基准测试反馈迭代优化代理架构，但元代理本身不进化。
+- **对DGM的传承**：DGM 的“无自改进基线”对应 ADAS 范式；DGM 的核心突破之一，就是把“固定元代理”升级为“元代理与下游代理共同进化”的自指闭环。
+### 13. 2025 | Gödel Agent
+- **作者**：Xunjian Yin 等
+- **核心贡献**：自指式代理框架，支持递归修改自身代码，但下游任务与自改进任务不对齐，下游能力提升无法转化为自改进能力的增强。
+- **对DGM的传承**：同名的自指代理相关工作；DGM 的核心优势之一，就是通过“编码任务 = 自改进任务”的完美对齐，实现了真正的自加速循环。
+### 14. 2025 | 单线程自改进编码代理（Robeyns et al.）
+- **作者**：Maxime Robeyns 等
+- **核心贡献**：同期独立工作，实现了单线程递归自修改的编码代理，采用爬山式迭代，无种群存档与开放式探索。
+- **对DGM的传承**：与 DGM 的单基线版本思路一致，侧面验证了“自改进编码代理”的可行性；同时反衬出开放式探索带来的显著性能增益。
+---
+## 第四阶段：集大成 —— 2026 | Darwin Gödel Machine
+- **作者**：Jenny Zhang, Shengran Hu, Cong Lu, Robert Lange, Jeff Clune
+- **核心融合与突破**：
+  1. **继承哥德尔机的自指愿景**：用实证基准验证替代形式化证明，让自指自改进从理论走向可运行的真实系统；
+  2. **注入达尔文式开放式进化**：引入种群存档、垫脚石探索、非贪心父代选择，解决单线程自改进易陷入局部最优、过早停滞的痛点；
+  3. **实现能力完美对齐**：让“下游编码任务”与“自修改代码任务”共享同一套能力，形成了“越会写代码就越会改进自己”的自加速正循环。
+- **定位**：首个将开放式种群进化与自指式代码自改进结合的大模型代理系统，是自改进AI从“理论原型”走向“实用系统”的关键里程碑。
+---
+## 简化版家族树图谱
+```
+理论奠基 (1960s-2000s)
+├── 1966 I.J.Good 智能爆炸假说
+└── 1987/1993/2007 Schmidhuber 自指学习 → 自指权重矩阵 → 哥德尔机
+        ↓ （自指自改进主线）
+方法成熟 (2010s-2022)
+├── 脉络A：开放式进化
+│   ├── 2015 MAP-Elites 质量多样性
+│   ├── 2019 POET 开放式共同进化
+│   └── 2019 AI-GAs 自动生成AI范式
+└── 脉络B：元学习与代理设计
+    ├── 2023 DSPy 提示词元优化
+    └── 2024 Promptbreeder 提示词自进化
+        ↓ （两条脉络汇合）
+大模型前驱 (2022-2025)
+├── 2022 LLM Self-Improve 权重自举
+├── 2023 Reflexion 自反思代理
+├── 2024 STOP/RSICG 单线程代码自改进
+├── 2025 ADAS 固定元代理设计下游代理
+├── 2025 Gödel Agent 自指代理框架
+└── 2025 Robeyns et al. 单线程自改进编码代理
+        ↓ （集大成）
+2026 Darwin Gödel Machine
+= 哥德尔机自指思想 + 达尔文开放式进化 + 大模型编码代理
+```
+需要我补充每个节点和DGM的具体差异对比，或者重点展开某一项前驱工作的技术细节吗？</t>
+  </si>
+  <si>
     <t>DeepSeek-V4 的长上下文高效建模方法，继承自哪些前代长上下文与稀疏注意力工作？梳理它的发展脉络与关键改进节点。</t>
+  </si>
+  <si>
+    <t>## DeepSeek-V4 长上下文建模的技术继承与发展脉络
+DeepSeek-V4 支持百万 Token 上下文的高效架构，是 DeepSeek 团队在「长上下文效率」路线上三代技术迭代的最终成果：它直接继承了自研的 MLA（多头潜在注意力）与 DSA（DeepSeek 稀疏注意力）两代核心技术，同时吸收了业界滑动窗口、稀疏注意力范式的成熟思路，最终形成「分层混合注意力」的架构，实现了百万级上下文的商用级推理效率。
+---
+## 一、核心技术继承来源
+### （一）自研前代技术的直接传承
+DeepSeek-V4 的长上下文能力并非从零搭建，而是建立在前两代效率优化的坚实基础之上：
+#### 1. 多头潜在注意力 MLA（DeepSeek-V2，2024）
+- **核心思想**：针对传统 MHA 中 KV 缓存随上下文线性膨胀的显存瓶颈，通过**低秩联合压缩**将每个 Token 的 K、V 向量映射为更小的潜在向量，推理时再通过升投影重建多头 KV。
+- **历史成效**：相比标准 MHA，KV 缓存体积减少 93.3%，推理吞吐量提升 5.76 倍，首次让 236B 规模的 MoE 模型原生支持 128K 上下文。
+- **对 V4 的贡献**：奠定了「通过 KV 压缩换取效率」的核心技术路线。V4 的 CSA 与 HCA 模块，将 MLA 的「特征维度压缩」延伸到了「序列维度压缩」，从「让单个 KV 条目变小」升级为「让多个 Token 的 KV 合并为一个条目」。
+#### 2. DeepSeek 稀疏注意力 DSA（DeepSeek-V3.2，2025）
+- **核心思想**：针对注意力计算 O(L²) 的平方复杂度瓶颈，在 MLA 架构基础上新增「闪电索引器 + 细粒度 Token 选择」双组件：
+  - 闪电索引器：用极低开销的线性变换为所有历史 Token 快速打分；
+  - 仅筛选 Top-k（通常为 2048）个最相关 Token 执行完整注意力计算，将复杂度从 O(L²) 降至 O(Lk)。
+- **历史成效**：在 128K 上下文下大幅降低推理 FLOPs，验证了动态稀疏注意力的精度无损可行性。
+- **对 V4 的贡献**：V4 的 CSA（压缩稀疏注意力）模块直接继承了 DSA 的动态稀疏选择机制，是「稀疏计算降低算力」路线的直接延续。
+#### 3. 架构底座：DeepSeekMoE + 多令牌预测 MTP
+V4 完整保留了 V3 系列的 MoE 专家架构（共享专家 + 路由专家）与 MTP 多令牌预测训练策略，保证了长上下文场景下的通用能力与训练/推理的基础效率。
+### （二）业界基础技术的吸收与演进
+除自研技术外，V4 的设计也吸收了长上下文领域的通用技术范式：
+1. **滑动窗口注意力**：源自 Longformer、Mistral 等模型的局部注意力思路，V4 设置专门的滑动窗口全注意力层处理最近的局部上下文，保证近距离语义的精确建模。
+2. **KV 缓存压缩范式**：沿承 MQA/GQA「减少 KV 缓存开销」的核心目标，MLA/CSA/HCA 是更激进的低秩+序列压缩方案，属于同一路线的深度演进。
+3. **动态稀疏注意力范式**：继承了 BigBird 等工作「避免全量注意力计算」的核心思路，DSA/CSA 实现了更细粒度的动态 Token 级选择，而非固定的块稀疏/随机稀疏模式。
+---
+## 二、发展脉络与关键改进节点
+DeepSeek 的长上下文高效建模，沿着「先降显存 → 再降算力 → 分层协同提效」的路径渐进式演进，每一代都精准解决上一代的核心瓶颈：
+### 阶段 1：KV 缓存维度压缩——DeepSeek-V2（2024.05）
+- **背景**：传统 Transformer 的 KV 缓存随上下文长度线性增长，128K 上下文下显存开销极高，是长上下文落地的第一瓶颈。
+- **关键突破**：提出 **多头潜在注意力（MLA）**，从**特征维度**压缩单个 Token 的 KV 体积。
+- **里程碑意义**：首次让大参数 MoE 模型以极低显存开销支持 128K 上下文，打通了长上下文的「显存瓶颈」，确立了 DeepSeek 以效率为核心的技术路线。
+### 阶段 2：注意力计算稀疏化——DeepSeek-V3.2（2025.12）
+- **背景**：MLA 解决了显存问题，但注意力计算量仍随上下文长度平方增长；若向百万级上下文扩展，计算开销会达到不可接受的程度。
+- **关键突破**：提出 **DeepSeek 稀疏注意力（DSA）**，从**数量维度**减少参与计算的 KV 条目。
+  - 基于 MLA 架构叠加动态稀疏选择，在几乎不损失效果的前提下，将长上下文的注意力计算复杂度从平方级降为近似线性。
+- **里程碑意义**：验证了动态稀疏注意力的工程可行性，为向百万级上下文演进打通了「计算效率瓶颈」，是 V4 百万上下文的直接技术预演。
+### 阶段 3：分层混合高效架构——DeepSeek-V4（2026.04）
+- **背景**：单一压缩或稀疏方案无法同时满足百万级上下文的精度与效率需求——近距离上下文需要高精度建模，远距离海量上下文需要极致压缩。
+- **关键突破**：提出 **CSA + HCA 混合注意力架构**，从**序列维度**引入分块压缩，并按上下文距离分层处理，实现精度与效率的最优平衡：
+  1. **滑动窗口全注意力**：处理最近的局部上下文，保留全量注意力计算，保证近距离语义建模精度。
+  2. **压缩稀疏注意力（CSA）**：先将 KV 沿序列维度按 4:1 比例分块压缩，再执行 DSA 稀疏选择，用于处理中距离上下文，平衡精度与效率。
+  3. **重度压缩注意力（HCA）**：对远距离历史 KV 做 128:1 的激进序列压缩，在压缩后的序列上执行稠密注意力，以极低开销覆盖海量历史信息。
+- **配套优化**：结合 FP8/FP4 量化存储，进一步压缩 KV 缓存的物理体积。
+- **里程碑成效**：在 1M Token 上下文下，DeepSeek-V4-Pro 单 Token 推理 FLOPs 仅为 V3.2 的 27%，KV 缓存仅为 V3.2 的 10%；轻量版 V4-Flash 进一步降至 10% 和 7%，真正让百万上下文从实验室 demo 变为可大规模商用的基础能力。
+---
+## 总结
+DeepSeek 长上下文技术的演进，本质是对 Transformer 注意力两大瓶颈（显存、算力）的逐次突破：
+- 从 MLA 的「单 KV 体积压缩」，到 DSA 的「KV 数量稀疏」，再到 V4 的「序列维度分层压缩 + 稀疏/稠密混合」，优化维度从单一的特征空间，拓展到数量空间、序列空间，最终形成三维度协同的高效建模体系。
+- 每一代技术都完整继承前代的优化成果，并新增一个维度的效率提升，是典型的渐进式工程创新路线。
+需要我补充一份**DeepSeek 各代长上下文技术的核心指标对比表**，把上下文长度、KV 缓存降幅、FLOPs 降幅、核心技术点整理到一起吗？</t>
   </si>
   <si>
     <t>基于GLM-5论文的技术路线、实验结论与明确提及的待解决问题，后续可从**架构效率、强化学习对齐、Agent工程能力、长上下文技术、硬件落地、评估与安全**六大方向延伸研究，具体方向与依据如下：
@@ -3059,21 +3922,10 @@
     <t>zELO 这种受 ELO 启发的重排序/嵌入训练方法，建立在哪些排序学习与对比学习工作之上？它属于领域里的哪一类方法分支？</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">SurGE </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这个面向科学综述生成的评测基准，继承自哪些早期综述生成与长文本评估工作？帮我梳理综述生成评测这条研究线索的家族树与演化脉络。</t>
-    </r>
-  </si>
-  <si>
-    <t>这篇「分步指导 LLM 生成科学文献综述」的工作，建立在哪些综述自动生成与规划式生成的前作之上？它后续有哪些重要改进？梳理这条方法线索从提出到成熟的过程。</t>
+    <t>这篇论文揭示的多轮对话退化问题，后续有哪些重要缓解方案？梳理这条研究线索从「发现问题」到「改进」的演化过程。</t>
+  </si>
+  <si>
+    <t>Xpertbench 这类基于 rubric 的专家级评测范式，是从哪些早期 LLM 评测与能力基准演化而来的？帮我梳理评测方法的文献分类与脉络。</t>
   </si>
   <si>
     <t>### 一、同类型核心研究分类
@@ -3178,12 +4030,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3198,18 +4050,6 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Segoe UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9.85"/>
-      <color rgb="FF000000"/>
-      <name val="Segoe UI"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
@@ -3232,13 +4072,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -3253,14 +4086,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
@@ -3269,32 +4094,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3314,7 +4116,29 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3337,8 +4161,39 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3351,27 +4206,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -3379,42 +4213,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -3430,7 +4228,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3442,7 +4246,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3460,13 +4264,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3478,25 +4300,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3508,25 +4336,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3544,25 +4366,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3573,15 +4407,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -3603,8 +4428,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3627,8 +4452,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3648,6 +4473,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -3662,17 +4507,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -3681,10 +4515,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3693,19 +4527,19 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3714,118 +4548,121 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3833,19 +4670,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="10" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4504,14 +5335,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="2" width="19.75" customWidth="1"/>
+    <col min="3" max="3" width="55.75" customWidth="1"/>
     <col min="4" max="4" width="48.625" customWidth="1"/>
     <col min="5" max="5" width="54" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="189" spans="1:5">
+    <row r="1" customHeight="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4528,7 +5360,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" customHeight="1" spans="1:3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -4539,7 +5371,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" customHeight="1" spans="1:3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -4550,7 +5382,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" customHeight="1" spans="1:3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -4561,7 +5393,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:4">
+    <row r="5" customHeight="1" spans="1:4">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -4571,21 +5403,25 @@
       <c r="C5" t="s">
         <v>82</v>
       </c>
-      <c r="D5" s="1"/>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="D5" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:4">
       <c r="A6" t="s">
         <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
         <v>82</v>
       </c>
-      <c r="D6" s="1"/>
-    </row>
-    <row r="7" ht="409.5" spans="1:4">
+      <c r="D6" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:4">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -4596,10 +5432,10 @@
         <v>29</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="8" ht="409.5" spans="1:4">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:4">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -4610,38 +5446,38 @@
         <v>34</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="9" ht="409.5" spans="1:4">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:4">
       <c r="A9" t="s">
         <v>37</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
         <v>39</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="10" ht="409.5" spans="1:4">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:4">
       <c r="A10" t="s">
         <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
         <v>43</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="11" ht="409.5" spans="1:4">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:4">
       <c r="A11" t="s">
         <v>46</v>
       </c>
@@ -4652,10 +5488,10 @@
         <v>48</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="12" ht="409.5" spans="1:4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:4">
       <c r="A12" t="s">
         <v>46</v>
       </c>
@@ -4666,10 +5502,10 @@
         <v>53</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="13" ht="409.5" spans="1:4">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:4">
       <c r="A13" t="s">
         <v>55</v>
       </c>
@@ -4680,10 +5516,10 @@
         <v>57</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="14" ht="409.5" spans="1:4">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:4">
       <c r="A14" t="s">
         <v>55</v>
       </c>
@@ -4694,10 +5530,10 @@
         <v>57</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="15" ht="409.5" spans="1:4">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:4">
       <c r="A15" t="s">
         <v>62</v>
       </c>
@@ -4708,43 +5544,43 @@
         <v>64</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:3">
       <c r="A16" t="s">
         <v>62</v>
       </c>
       <c r="B16" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:3">
       <c r="A17" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>86</v>
+      <c r="B17" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="C17" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" customHeight="1" spans="1:3">
       <c r="A18" t="s">
         <v>67</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>97</v>
+      <c r="B18" s="6" t="s">
+        <v>99</v>
       </c>
       <c r="C18" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="19" ht="24" customHeight="1" spans="1:4">
+    <row r="19" customHeight="1" spans="1:4">
       <c r="A19" t="s">
         <v>70</v>
       </c>
@@ -4755,10 +5591,10 @@
         <v>72</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="20" ht="409.5" spans="1:4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:4">
       <c r="A20" t="s">
         <v>70</v>
       </c>
@@ -4769,7 +5605,7 @@
         <v>77</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -4782,13 +5618,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="2" width="28.875" customWidth="1"/>
     <col min="4" max="4" width="54.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="229.5" spans="1:5">
+    <row r="1" customHeight="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4805,7 +5641,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" customHeight="1" spans="1:3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -4816,7 +5652,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" customHeight="1" spans="1:3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -4827,7 +5663,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" customHeight="1" spans="1:3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -4838,7 +5674,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" ht="17" customHeight="1" spans="1:4">
+    <row r="5" customHeight="1" spans="1:4">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -4850,19 +5686,21 @@
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" customHeight="1" spans="1:4">
       <c r="A6" t="s">
         <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="1"/>
-    </row>
-    <row r="7" ht="409.5" spans="1:4">
+      <c r="D6" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:4">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -4873,10 +5711,10 @@
         <v>30</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" ht="409.5" spans="1:4">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:4">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -4887,38 +5725,38 @@
         <v>35</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="9" ht="409.5" spans="1:4">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:4">
       <c r="A9" t="s">
         <v>37</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="10" ht="409.5" spans="1:4">
+      <c r="D9" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:4">
       <c r="A10" t="s">
         <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
         <v>44</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="11" ht="409.5" spans="1:4">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:4">
       <c r="A11" t="s">
         <v>46</v>
       </c>
@@ -4929,10 +5767,10 @@
         <v>49</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="12" ht="409.5" spans="1:4">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:4">
       <c r="A12" t="s">
         <v>46</v>
       </c>
@@ -4943,10 +5781,10 @@
         <v>49</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="13" ht="409.5" spans="1:4">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:4">
       <c r="A13" t="s">
         <v>55</v>
       </c>
@@ -4957,10 +5795,10 @@
         <v>58</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="14" ht="409.5" spans="1:4">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:4">
       <c r="A14" t="s">
         <v>55</v>
       </c>
@@ -4971,10 +5809,10 @@
         <v>58</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="15" ht="409.5" spans="1:4">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:4">
       <c r="A15" t="s">
         <v>62</v>
       </c>
@@ -4985,43 +5823,43 @@
         <v>65</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:3">
       <c r="A16" t="s">
         <v>62</v>
       </c>
       <c r="B16" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C16" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:3">
       <c r="A17" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>86</v>
+      <c r="B17" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:3">
       <c r="A18" t="s">
         <v>67</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>97</v>
+      <c r="B18" s="6" t="s">
+        <v>99</v>
       </c>
       <c r="C18" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="19" ht="409.5" spans="1:4">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="1:4">
       <c r="A19" t="s">
         <v>70</v>
       </c>
@@ -5032,10 +5870,10 @@
         <v>73</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="20" ht="409.5" spans="1:4">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:4">
       <c r="A20" t="s">
         <v>70</v>
       </c>
@@ -5046,7 +5884,7 @@
         <v>78</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -5059,12 +5897,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="4" max="4" width="54" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="189" spans="1:5">
+    <row r="1" customHeight="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5081,7 +5919,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" customHeight="1" spans="1:3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -5092,7 +5930,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" customHeight="1" spans="1:3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -5103,7 +5941,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" customHeight="1" spans="1:3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -5114,7 +5952,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" ht="148.5" spans="1:3">
+    <row r="5" customHeight="1" spans="1:4">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -5122,21 +5960,27 @@
         <v>81</v>
       </c>
       <c r="C5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>115</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:4">
       <c r="A6" t="s">
         <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>115</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:3">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -5147,7 +5991,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" customHeight="1" spans="1:3">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -5158,29 +6002,29 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" customHeight="1" spans="1:3">
       <c r="A9" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>86</v>
+      <c r="B9" s="3" t="s">
+        <v>88</v>
       </c>
       <c r="C9" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" customHeight="1" spans="1:3">
       <c r="A10" t="s">
         <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" customHeight="1" spans="1:3">
       <c r="A11" t="s">
         <v>46</v>
       </c>
@@ -5191,7 +6035,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" customHeight="1" spans="1:3">
       <c r="A12" t="s">
         <v>46</v>
       </c>
@@ -5202,7 +6046,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" customHeight="1" spans="1:3">
       <c r="A13" t="s">
         <v>55</v>
       </c>
@@ -5213,7 +6057,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" customHeight="1" spans="1:3">
       <c r="A14" t="s">
         <v>55</v>
       </c>
@@ -5224,7 +6068,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" customHeight="1" spans="1:3">
       <c r="A15" t="s">
         <v>62</v>
       </c>
@@ -5232,15 +6076,15 @@
         <v>63</v>
       </c>
       <c r="C15" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="16" spans="2:2">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="2:2">
       <c r="B16" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:2">
       <c r="A17" t="s">
         <v>67</v>
       </c>
@@ -5248,7 +6092,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" customHeight="1" spans="1:2">
       <c r="A18" t="s">
         <v>67</v>
       </c>
@@ -5256,7 +6100,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="19" ht="189" spans="1:3">
+    <row r="19" customHeight="1" spans="1:3">
       <c r="A19" t="s">
         <v>70</v>
       </c>
@@ -5267,7 +6111,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" customHeight="1" spans="1:3">
       <c r="A20" t="s">
         <v>70</v>
       </c>
@@ -5288,7 +6132,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="2" width="43.5" customWidth="1"/>
     <col min="3" max="3" width="30.375" customWidth="1"/>
@@ -5296,7 +6140,7 @@
     <col min="5" max="5" width="50.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="67.5" spans="1:5">
+    <row r="1" customHeight="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5307,13 +6151,13 @@
         <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" customHeight="1" spans="1:3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -5324,7 +6168,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" ht="409.5" spans="1:4">
+    <row r="3" customHeight="1" spans="1:4">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -5335,10 +6179,10 @@
         <v>17</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="4" ht="409.5" spans="1:4">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:4">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -5349,10 +6193,10 @@
         <v>22</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="5" ht="40.5" spans="1:3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="1:4">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -5360,21 +6204,27 @@
         <v>81</v>
       </c>
       <c r="C5" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>122</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:4">
       <c r="A6" t="s">
         <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>124</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:4">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -5382,10 +6232,13 @@
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="8" ht="409.5" spans="1:4">
+        <v>126</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:4">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -5396,10 +6249,10 @@
         <v>36</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="9" ht="409.5" spans="1:4">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:4">
       <c r="A9" t="s">
         <v>37</v>
       </c>
@@ -5410,10 +6263,10 @@
         <v>41</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="10" ht="409.5" spans="1:4">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:4">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -5424,10 +6277,10 @@
         <v>45</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:3">
       <c r="A11" t="s">
         <v>46</v>
       </c>
@@ -5435,10 +6288,10 @@
         <v>47</v>
       </c>
       <c r="C11" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:3">
       <c r="A12" t="s">
         <v>46</v>
       </c>
@@ -5446,10 +6299,10 @@
         <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="13" ht="409.5" spans="1:4">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:4">
       <c r="A13" t="s">
         <v>55</v>
       </c>
@@ -5460,10 +6313,10 @@
         <v>60</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="14" ht="409.5" spans="1:4">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:4">
       <c r="A14" t="s">
         <v>55</v>
       </c>
@@ -5474,10 +6327,10 @@
         <v>60</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:3">
       <c r="A15" t="s">
         <v>62</v>
       </c>
@@ -5485,40 +6338,40 @@
         <v>63</v>
       </c>
       <c r="C15" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="2:3">
       <c r="B16" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C16" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="17" ht="14.25" spans="1:3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:3">
       <c r="A17" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="18" ht="14.25" spans="1:3">
+      <c r="B17" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:3">
       <c r="A18" t="s">
         <v>67</v>
       </c>
       <c r="B18" t="s">
-        <v>97</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="19" ht="409.5" spans="1:4">
+        <v>99</v>
+      </c>
+      <c r="C18" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="1:4">
       <c r="A19" t="s">
         <v>70</v>
       </c>
@@ -5529,10 +6382,10 @@
         <v>75</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="20" ht="409.5" spans="1:4">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:4">
       <c r="A20" t="s">
         <v>70</v>
       </c>
@@ -5543,7 +6396,7 @@
         <v>75</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/paper-reader/测评.xlsx
+++ b/paper-reader/测评.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17820" activeTab="1"/>
+    <workbookView windowHeight="17820" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="测评" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="153">
   <si>
     <t>供人</t>
   </si>
@@ -1179,7 +1179,245 @@
     <t>分析下这个论文，重点解释：瑟斯顿模型 (Thurstone model)、稀疏矩阵子采样策略、k-正则图、逐点重排序模型（Pointwise Reranker）</t>
   </si>
   <si>
-    <t>Xpertbench Expert Level Tasks with Rubrics-Based Evaluation</t>
+    <t># zELO 论文核心技术深度解析
+这篇论文提出了**zELO**——一种受国际象棋Elo评分体系启发的无监督重排序模型训练方法，核心突破是避开了传统「硬负样本挖掘」的Laffer曲线性能瓶颈，通过「大模型集成生成成对偏好→统计模型转化为绝对相关性分数→训练逐点重排模型」的流水线，在无需人工标注的前提下训练出了效果超越商用闭源模型的开源重排器zerank-1/zerank-1-small。
+下面针对你关注的四个核心技术点，结合论文设计展开详细解释：
+## 一、瑟斯顿模型 (Thurstone Model)
+瑟斯顿模型是zELO方法的**核心统计理论基础**，承担了「把成对相对偏好转化为单文档绝对相关性分数」的关键作用。
+### 1. 核心假设与公式
+瑟斯顿模型属于比较判断法则的一种，它的核心假设是：
+- 每个文档对应一个隐藏的「真实相关性分值」（在zELO中对应Elo分）；
+- 人类/模型对两个文档的相关性判断会受到随机噪声干扰，噪声服从**正态分布**；
+- 文档i比文档j更相关的概率，由两者真实分值的差值经过误差函数（erf）计算得到。
+论文中给出的公式为：
+$$w_{ij}=\frac{1+\text{erf}\left(\text{Elo}_i - \text{Elo}_j\right)}{2}$$
+其中$w_{ij}$是模型判断「文档i比文档j更相关」的概率，$\text{Elo}_i/\text{Elo}_j$是两个文档的隐藏相关性分值。
+### 2. 与Bradley-Terry / 经典Elo的区别
+经典Elo评分本质是Bradley-Terry模型的参数化形式，它假设噪声服从Gumbel分布，使用Sigmoid函数计算偏好概率：
+$$w_{ij}=\sigma\left(\text{Elo}_i - \text{Elo}_j\right)=\frac{1}{1+e^{-(\text{Elo}_i - \text{Elo}_j)}}$$
+两者的核心差异在于噪声分布假设，而论文最终选择瑟斯顿模型有两个依据：
+1. **理论支撑**：文档相关性判断受多个独立噪声源影响（语义理解偏差、上下文截断、模型偏见等），根据中心极限定理，综合噪声更接近正态分布；
+2. **实验效果**：瑟斯顿模型对实际观测到的成对偏好数据拟合度更优。
+### 3. 在zELO中的作用
+通过极大似然估计求解瑟斯顿模型，我们可以从稀疏的成对偏好矩阵中，反推出每个文档的绝对Elo相关性分值，从而把「两两比较的相对结果」转化为「每个文档独立的连续相关性分数」，为后续逐点重排序模型提供训练标签。
+## 二、稀疏矩阵子采样策略
+### 1. 背景与动机
+对于每个查询，第一阶段检索会返回k=100个候选文档。如果对所有文档两两比较，需要进行$\(100×100=10000\)$次成对推断，计算成本极高，在大规模训练集下完全不可行。
+稀疏子采样的目标是：**只对极少部分文档对进行成对推断，依然能精准估计出所有文档的Elo分值**，在计算成本和估计精度之间取得最优平衡。
+### 2. 核心设计约束
+论文从Elo估计的误差规律出发，提出了采样得到的「比较图」必须满足三个关键性质：
+1. **连通性**：图不能有孤立的子图，否则无法建立不同子图之间文档的相对Elo关系；
+2. **无低度数节点**：每个文档至少参与一定次数的成对比较，否则单个文档的Elo估计会极不稳定；
+3. **低直径**：任意两个文档之间的最短路径不能太长，否则路径上的误差会累积，导致两者的相对Elo偏差过大。
+这三个约束对应两个理论启发式：
+- 路径长度启发式：两个文档Elo差值的方差，与它们在比较图中的最短路径距离成正比；
+- 度数稳定性启发式：单个文档Elo估计的方差，与该节点的度数成反比。
+### 3. 方案对比与最终选择
+论文对比了四种采样策略，通过「稀疏采样得到的Elo分 vs 全量矩阵Elo分的MSE」来评估精度：
+- 随机成对采样：误差下降慢，容易出现低度数节点和高直径；
+- 二分图结构：直径为2，但边数多、计算成本高；
+- Elo感知动态采样：根据当前Elo分选择差值最小的文档对，实现复杂；
+- **随机环拼接（k-正则图）**：收敛速度最快、估计最稳定，最终被论文采用。
+实验中，对于100个候选文档，该策略仅需400次成对推断（仅为全量的0.4%），就能达到极高的Elo估计精度。
+## 三、k-正则图 (k-regular Graph)
+k-正则图是稀疏采样策略的最终落地方案，是实现「低边数、高精度Elo估计」的关键结构。
+### 1. 定义
+如果一个图中**每个节点的度数都等于k**（即每个文档都恰好和其他k个文档进行了成对比较），这个图就叫k-正则图。
+这种结构天然满足「无低度数节点」的要求，所有文档的Elo估计稳定性一致，不会出现某些文档分数不准的情况。
+### 2. 论文中的构造方法：随机环拼接
+生成任意k-正则图复杂度较高，论文提出了一种简单高效的构造方式：
+1. 生成$\(k/2\)$个独立的随机环：每个环是所有文档的一次随机排列，首尾相连形成一个环，每个节点在单个环中的度数为2；
+2. 把这$\(k/2\)$个环的边合并，最终每个节点的度数就是$k$，形成k-正则图。
+举个例子：论文中使用度数k=8的正则图，就是生成4个随机环拼接而成；100个文档总边数为$\((100×8)/2=400\)$，和前文的实验数据对应。
+### 3. 方案优势
+1. **生成效率极高**：仅需对文档ID做随机排列，时间复杂度O(n)，适合大规模数据流水线；
+2. **结构性质优秀**：根据随机图理论，随机k-正则图的直径约为$\log_{k-1}(n)$，天然满足低直径要求；同时图的连通性有理论保障；
+3. **精度-成本比最优**：用最少的成对推断次数，满足了Elo估计的三大约束，最终的分数估计误差低于其他采样方案。
+## 四、逐点重排序模型（Pointwise Reranker）
+### 1. 定义与特点
+逐点重排序模型是**最终落地部署的推理模型**，它的输入是单个「查询-文档」对$\((q,d)\)$，输出一个0~1之间的连续分值，直接代表该文档与查询的相关性强弱。
+它和成对重排序模型（Pairwise Reranker）的核心区别：
+| 类型 | 输入 | 输出 | 适用场景 |
+|------|------|------|----------|
+| Pointwise | 单个查询-文档对 | 绝对相关性分数 | 线上部署、大规模候选集排序 |
+| Pairwise | 查询 + 两个文档 | 两文档的偏好概率 | 生成训练标签、精细化比较 |
+### 2. 在zELO中的训练方式
+zELO的训练流水线中，成对模型只是生成标签的中间工具，最终训练目标是逐点模型，训练流程为：
+1. 用LLM集成训练出高质量的成对重排模型；
+2. 对每个查询的候选集，通过成对模型+稀疏采样+瑟斯顿模型，计算出每个文档的zELO绝对分值；
+3. 以「查询-文档对」为输入，以对应的zELO分值为标签，使用**均方误差损失（MSE Loss）** 监督训练逐点模型：
+$$\mathcal{L}_{SFT}=\frac{1}{|D_{train}|}\sum_{(q,d,y)\in D_{train}}\left(R_{point}\((q,d)\)-y\right)^2$$
+### 3. 落地价值
+逐点模型是工业界检索系统的标准选择，原因在于：
+- **推理高效**：只需对每个候选文档做一次前向计算即可得到分数，排序复杂度为O(n)，适合对成百上千个候选文档快速重排；
+- **兼容性强**：可以无缝对接BM25、向量检索、混合检索等任意第一阶段召回方法。
+论文中发布的zerank-1（4B参数）和zerank-1-small（1.7B参数）均为逐点交叉编码器，在金融、法律、代码、医疗等多个领域的NDCG@10指标上超越了Cohere、Voyage AI等商用重排器，同时推理延迟更低。
+---
+### 四者的协同关系
+这四项技术在zELO流水线中是环环相扣的整体：
+**k-正则图**是**稀疏矩阵子采样策略**的最优实现，用极低的计算成本生成高质量的成对比较数据；这些成对数据输入**瑟斯顿模型**，转化为每个文档的绝对相关性分值；最终用这些分值训练出高精度的**逐点重排序模型**，完成从无监督数据到可用工业级模型的全流程。</t>
+  </si>
+  <si>
+    <t>SurGE A Benchmark and Evaluation Framework for Scientific Survey Generation_review</t>
+  </si>
+  <si>
+    <t># 论文精读：SurGE: A Benchmark and Evaluation Framework for Scientific Survey Generation
+## 一、核心立论：研究背景与问题提出
+### 1. 现实需求：科学文献爆炸下的综述生成痛点
+随着学术文献体量指数级增长（仅arXiv计算机科学领域每日新增超千篇，2019-2024年体量翻倍），人工撰写综述论文成本极高、效率低下，行业对自动化科学综述生成系统有迫切需求。
+### 2. 领域现状：可行性已验证，但评估体系严重缺位
+近年基于大语言模型的智能体（Agent）管线（如AutoSurvey、StepSurvey、SurveyForge）已证明自动化综述生成的可行性，但领域始终缺乏**标准化、可扩展、方法无关**的评估协议，核心问题有二：
+- **可扩展性差**：部分工作高度依赖人工评估，成本高、难以大规模复现，无法支撑快速迭代。
+- **公平性缺失**：现有自定义评估框架均与特定生成管线深度绑定，本质是“自验证”，会偏向自身设计假设，引入系统性偏差，无法实现跨系统的公平对比。
+### 3. 核心问题：评估必须解耦“检索”与“生成”
+作者提出，综述生成的错误可能来自两个独立阶段：① 相关文献检索阶段；② 检索内容合成阶段。现有评估无法区分瓶颈来源，不具备诊断能力。当领域从“证明可行性”转向“精细化质量提升”时，亟需一个方法无关、可复现、可诊断的基准，将检索能力与合成能力解耦评估。
+基于以上缺口，作者提出**SurGE（Survey Generation Evaluation）**：一个面向科学综述生成的基准与评估框架。
+## 二、核心研究假设
+作者的研究工作围绕三个核心假设展开：
+1. **任务可解耦假设**：科学综述生成可被形式化为“信息检索+内容合成”的两阶段任务，对两个阶段分别评估，能够精准定位系统的性能瓶颈。
+2. **评估可自动化假设**：一套覆盖“全面性-引用准确性-结构质量-内容质量”的多维度评估体系，结合客观量化指标与LLM-as-a-Judge评判，能够与人类专家判断实现高度对齐，可替代人工实现可扩展、可复现的自动化评测。
+3. **系统性能差异假设**：专门设计的Agent化综述生成管线，在结构规范性、内容流畅性上会显著优于通用RAG基线；但在引用准确性、文献覆盖等事实性维度上，现有系统仍存在明显短板。
+## 三、证明路径与研究方法
+作者从“基准构建-框架设计-元验证-实验验证”四层逐步证明上述假设，形成完整的论证闭环。
+### 1. 第一层：构建高质量基准数据集（论证基础）
+SurGE基准由两部分构成：专家验证的真值综述、大规模检索语料库。
+#### （1）真值综述的筛选与质控
+- **初筛**：从arXiv选取2020-2024年计算机科学领域的综述/系统综述论文，筛选条件：明确标注为综述、引用量≥20、发表时间符合范围。
+- **专家标注质控**：由1名教职人员带领4名计算机科学博士生，从**引用影响力、内容覆盖度、结构连贯性、引用质量**四个维度双盲评审；仅当两名标注者均判定“可用”时保留，分歧样本直接丢弃。
+  - 标注一致性：Cohen’s Kappa = 0.792，达到“高度一致”水平，保证了真值的可靠性。
+  - 最终得到205篇高质量真值综述。
+#### （2）大规模检索语料库构建
+- 仅使用arXiv公开的元数据（标题、作者、摘要、分类、发表日期等），符合arXiv CC0协议，合规且无版权风险。
+- 构建流程：先收录真值综述的全部参考文献，再通过关键词扩展主题相关论文，最后补充随机计算机科学论文缓解主题偏差。
+- 最终语料包含1,086,992篇唯一论文，覆盖真值中约70%的参考文献。
+#### （3）任务难度验证
+统计显示，真值综述平均层级深度3.07、平均标题节点42.7个、平均引用65.8篇，对层级生成能力和高召回检索能力都提出了很高要求，基准具备足够的挑战性。
+### 2. 第二层：设计多维度评估框架（核心方法论）
+围绕综述的核心质量要求，作者设计了四大维度的自动化评估指标，完全不依赖人工标注即可完成评测。
+| 评估维度 | 核心指标 | 计算逻辑 |
+| :--- | :--- | :--- |
+| **全面性** | 文献召回率（Recall） | 生成综述的参考文献集合与真值参考文献集合的召回率，衡量核心文献的覆盖能力 |
+| **引用准确性** | 文档/章节/句子三级准确率 | 基于NLI模型（nli-deberta-v3-base），分层验证引用与全文主题、章节主题、句子论断的相关性；不在语料的引用直接判定为幻觉（0分），真值参考文献直接计文档级满分 |
+| **结构质量** | 结构质量分（SQS）+ 软标题召回（SHR） | SQS：LLM-as-a-Judge对比生成与真值的层级结构、语义与措辞；SHR：基于语义嵌入计算标题的软交集召回，适配同义改写场景 |
+| **内容质量** | 内容质量分（CQS） | 用GPT-4o分章节评估，从流畅连贯、逻辑清晰、无冗余、描述准确、无错误五个维度打分（0-5分）；ROUGE/BLEU仅作参考，不纳入核心指标 |
+### 3. 第三层：元评估——验证评估框架与人类的对齐度
+为证明自动化评估的可靠性，作者开展了严格的元评估：
+- **实验设置**：选取RAG、StepSurvey、AutoSurvey三个系统（统一Qwen2.5-14B基座）+ 人类真值综述，共4份匿名样本，由具备同行评审经验的CS博士生按“结构质量”“内容质量”两个维度排序。
+- **对齐度量**：用Kendall’s τ和Spearman’s ρ计算自动化指标排序与人类排序的相关性。
+- **结果**：
+  - 包含人类真值时：结构质量τ=0.805，内容质量τ=0.797，区分人类与机器的能力极强；
+  - 仅对比模型系统时：结构质量ρ=0.707，内容质量ρ=0.695，达到文本生成评估领域的SOTA对齐水平。
+- 结论：SurGE的自动化评估体系与人类专家判断高度一致，是可靠的人工评估替代方案。
+### 4. 第四层：基准实验——验证系统性能差异与诊断能力
+作者通过统一变量的对比实验，验证不同系统的性能差异，同时验证SurGE的诊断价值。
+#### （1）实验设置
+- **统一检索器**：所有基线共用同一个微调的RoBERTa稠密检索器，每个主题返回top-100候选论文，排除检索差异对生成结果的干扰。
+- **基线系统**：
+  - 通用RAG基线：3种不同基座（Qwen2.5-14B、GPT-4o、Gemini-2.5-Pro-Thinking）；
+  - 专用Agent基线：AutoSurvey、StepSurvey、SurveyForge，统一使用Qwen2.5-14B基座。
+#### （2）检索阶段单独验证：解耦瓶颈
+作者单独测试了检索器的性能，对比BM25与稠密检索器（PR）的召回率：
+- top-1000时，稠密检索召回率达68.05%，远高于BM25的27.15%；
+- 关键发现：检索端的召回上限（68.05%）远高于端到端系统的最终召回率（均低于10%）。
+- 结论：当前综述生成的核心瓶颈**不在检索，而在生成阶段的信息选择与利用能力**，直接验证了“解耦评估”的价值——能够精准定位性能短板。
+#### （3）端到端实验：系统性能对比
+通过四大维度的完整评测，作者得到四个核心结论，对应验证了相关假设：
+1. **流畅性 ≠ 事实准确性**：RAG-Qwen的ROUGE、BLEU等词法指标最高，但引用准确率和文献召回率最低，存在“流畅幻觉”现象，证明传统n-gram指标不适用于科学综述评估。
+2. **Agent工作流是结构质量的关键**：所有专用Agent的软标题召回（SHR）均显著优于通用RAG，AutoSurvey的结构质量分（SQS）最高，证明显式规划对学术综述的层级结构构建至关重要。
+3. **Agent设计可弥补基座能力不足**：SurveyForge使用14B开源模型，但其引用准确率超过了使用更强闭源基座的RAG-Gemini，证明合理的任务拆解与Agent机制，能够让小模型实现更忠实、更有依据的输出。
+4. **不同Agent框架各有优劣**：SurveyForge的文献覆盖与文档级引用准确率最优（记忆机制提升了文献利用率）；StepSurvey的内容质量分（CQS）最高（分步写作提升了语言质量），不存在全能型最优方案。
+## 四、核心讨论与研究结论
+### 1. 核心结论
+- SurGE填补了领域空白：是首个**方法无关、可复现、具备诊断能力**的科学综述生成基准，既提供了大规模语料与专家验证真值，也提供了经人类对齐验证的多维度自动化评估框架。
+- 现有系统仍有显著短板：当前SOTA系统虽然在语言流畅性、结构规范性上有进步，但在核心文献覆盖、引用事实准确性上表现很差，存在严重的“重表达、轻事实”问题。
+- 性能瓶颈已明确：综述生成的主要挑战不在“找不到文献”，而在“不会用文献”——生成端的信息选择、证据整合、引用匹配能力是未来的核心优化方向。
+### 2. 对领域的启示
+- 评估范式需要升级：科学综述生成不能再用ROUGE/BLEU等词法指标，也不能依赖自定的管线绑定指标，必须转向以事实性、结构性为核心的标准化评估。
+- 系统设计需要转向：从“追求写得通顺”转向“追求写得准确”，重点优化引用保真度、证据利用率，而非单纯提升语言流畅度。
+## 五、局限与未来展望
+### 1. 研究局限
+- 学科覆盖有限：当前基准仅覆盖计算机科学领域，其他学科的综述写作范式、文献特征存在差异，泛用性有待验证。
+- 检索语料有缺口：约30%的真值参考文献不在语料库中（多为闭源期刊论文），检索召回上限仍有提升空间。
+- 评估维度可拓展：当前未覆盖“研究脉络梳理”“观点对比分析”等更高阶的综述能力评估。
+### 2. 未来研究方向
+1. **检索侧优化**：探索面向综述生成的任务型搜索Agent，替代单一稠密检索，进一步提升核心文献召回上限。
+2. **生成侧优化**：重点提升模型对检索证据的利用能力，解决“检索到但未使用”的问题，减少引用幻觉，提升引用的细粒度准确性。
+3. **基准扩展**：将SurGE扩展到更多学科领域，丰富真值样本，增加更多高阶写作能力的评估维度。
+4. **系统融合创新**：融合不同Agent框架的优势，设计兼顾结构合理性、内容流畅性与引用准确性的新一代综述生成系统。</t>
+  </si>
+  <si>
+    <t>Instruct Large Language Models to Generate Scientific Literature Survey Step by Step_review</t>
+  </si>
+  <si>
+    <t># 论文精读：《Instruct Large Language Models to Generate Scientific Literature Survey Step by Step》
+以下围绕**立论背景、研究假设、验证方法、讨论分析、未来展望**五个核心维度展开深度解读。
+## 一、核心立论：研究背景与问题提出
+### 1. 研究背景与应用价值
+文献综述是科学研究的核心环节，是研究者把握领域脉络、确立研究问题的基础。但随着科学文献数量呈指数级增长、新成果发表速度持续加快，研究者在文献梳理上耗费的时间成本越来越高。
+大语言模型（LLM）的涌现能力为自动生成文献综述提供了可行路径，有望大幅降低科研人员的时间投入，提升研究效率。
+### 2. 核心挑战与现有研究的不足
+作者指出，自动生成科学文献综述面临两大核心难题，也是现有方案未能系统解决的痛点：
+- **长文本生成的结构一致性难题**：文献综述篇幅通常很长，即使是GPT-4、Claude 3等先进模型也存在输出长度限制，无法单次生成完整综述；若逐段连续生成，模型会逐渐遗忘前文信息，且缺乏全局规划，导致综述结构混乱、前后不一致。
+- **高成本导致实用性不足**：文献综述包含海量信息，若将全部参考文献一次性输入模型，会产生极高的API调用成本，大幅削弱方案的实际应用价值。
+同时作者提到，当前领域内缺乏系统的方法论来指导LLM完成完整的文献综述生成任务；虽有部分研究探索了大纲引导的长文本生成，但尚未针对科学综述的专业属性设计完整的分步式提示工程方案。
+## 二、研究假设与核心思路
+### 1. 核心研究假设
+论文的核心假设可总结为：**通过「先全局规划、后分块生成」的分步式提示工程，引导大模型按顺序完成综述的标题、层级大纲、摘要、分章节内容生成，能够在保证综述结构连贯性、内容相关性的同时，显著降低API调用成本，仅基于参考文献标题就能生成有竞争力的科学文献综述**。
+具体包含三个子假设：
+1. 将标题与大纲生成作为独立步骤，能让模型从全局高层视角设计综述结构，有效提升生成标题与真实综述标题的语义匹配度，保证结构逻辑合理性。
+2. 在生成正文前，先为每个章节筛选对应的参考文献子集，再基于子集生成子标题与正文，既能保证内容与章节主题的相关性，又能大幅减少单次调用的输入token数量，降低成本。
+3. 纯提示工程的分步方案，无需模型微调、无需额外检索增强，在赛事规则约束下（仅使用给定参考文献标题），也能达到业界领先的生成效果。
+### 2. 整体思路
+作者提出「两阶段六步骤」的分步生成框架：
+- 第一阶段：全局大纲生成——依次生成标题、一级章节标题、摘要，完成整篇综述的结构规划。
+- 第二阶段：分章节内容填充——为每个一级章节筛选参考文献子集，再生成二级子标题，最后逐段生成章节正文。
+## 三、研究证明：方法论设计与实验验证
+### 1. 分步式生成方法论（6步详细设计）
+作者针对每个步骤设计了专门的提示词，通过格式约束、范围限定保证输出可控性。
+#### 第一阶段：大纲生成（全局规划）
+1. **步骤1：标题生成**
+   输入主题与全部参考文献标题，引导模型预测对应综述的标题；要求输出以`Title:`标记开头，若格式错误则保留上下文重新提示，确保格式合规。
+2. **步骤2：一级章节标题生成**
+   基于前文生成的标题、主题与参考文献，生成6~10个一级章节标题，形成综述的核心大纲；要求以`* `开头，无序号，若数量严重偏离范围则重新生成。
+3. **步骤3：摘要生成**
+   基于主题、综述标题和完整一级大纲，生成200~500词的单段摘要，要求不包含列表、不重复「摘要」字样。
+#### 第二阶段：子章节与内容生成（分块填充）
+4. **步骤4：按章节筛选参考文献**
+   针对每个一级章节标题，从全量参考文献中筛选出与该章节相关的子集；目的是减少后续步骤的输入长度，同时避免所有章节使用相同参考文献导致内容同质化。
+5. **步骤5：二级子标题生成**
+   基于全局大纲、章节主题和该章节的参考文献子集，为每个一级章节生成3~5个二级子标题，补全综述的层级结构。
+6. **步骤6：子章节内容生成**
+   输入完整层级大纲、章节参考文献子集，为每个二级子章节生成3~5段、约1000词的正文；提示中多次强调当前子章节主题，避免模型偏离核心，同时引导模型按格式正确引用参考文献。
+### 2. 实验设置
+- **数据集**：采用NLPCC 2024科学文献综述生成评测任务的官方数据集，训练集500篇arXiv综述，测试集200篇。作者严格遵守赛事规则：仅用训练集做提示词设计，不用于参数微调或上下文学习；测试阶段仅使用主题和参考文献标题，不使用参考文献全文内容，也不做额外检索增强。
+- **基座模型**：选用阿里通义千问的Qwen-long版本，定价为输入0.5元/百万token、输出2元/百万token，兼顾长文本能力与低成本特性。
+- **特殊处理**：参考文献过长时截断为前80~100篇；若遇到模型拒绝处理的内容，通过奇偶索引拆分参考文献规避问题。
+- **评价指标**：
+  1. ROUGE系列（ROUGE1/2/L）：衡量生成内容与参考内容的文本重合度；
+  2. 软标题召回率（Soft Heading Recall）：基于bge-large-en-v1.5文本嵌入计算语义相似度，衡量生成标题与参考标题的结构匹配度，同时惩罚生成标题内部的语义重复；
+  3. 人工评价：从语言流畅度、结构逻辑性、引用可靠性、主题一致性、分析广度5个维度打分；
+  4. 总分：ROUGE均值、软标题召回率、人工得分三者的平均值。
+### 3. 实验结果与验证结论
+作者的方案在NLPCC 2024评测中取得第三名，核心结果如下：
+- **总分61.11**，仅比第二名低0.03%，验证了分步方案的整体有效性。
+- **软标题召回率95.84%**，位列所有参赛队伍第二名，仅比第一名低1.17%——直接验证了「独立大纲生成步骤能提升结构质量」的核心假设，证明先规划后生成的策略能让模型保持全局视角，生成逻辑清晰、匹配度高的综述结构。
+- **成本验证**：生成全部200篇测试集综述仅花费20.86元，单篇平均成本约0.1元——验证了「分章节筛选参考文献能大幅降低成本」的假设，方案具备很高的实用价值。
+- **案例验证**：以神经网络可解释性领域的综述为例，生成结果的软标题召回达97.78%，标题、大纲、摘要均能准确捕捉领域核心主题，引用格式与位置基本合理。
+## 四、讨论：方法的优势与局限
+### 1. 方法优势
+1. **结构质量突出**：独立的标题与大纲生成环节让模型从全局视角规划结构，是软标题召回率表现优异的核心原因，生成的综述层级清晰、逻辑连贯。
+2. **成本极低、实用性强**：通过分章节筛选参考文献，大幅压缩了单次调用的输入长度，结合低成本的Qwen-long模型，单篇综述生成成本仅0.1元，具备落地应用潜力。
+3. **轻量化、易迁移**：纯提示工程方案，无需模型微调、无需额外检索系统，仅依赖参考文献标题即可运行，适配不同领域、不同基座模型。
+### 2. 存在的局限
+1. **事实准确性不足，人工评分偏低**：由于未使用参考文献全文内容，模型幻觉问题显著，无法保证引用内容的准确性和分析的可靠性，直接导致人工评价得分不高，是方案最核心的短板。
+2. **大纲偏冗长繁琐**：生成的章节标题数量偏多、粒度太细，简洁度和凝练度不足，与真实综述的大纲风格有差距。
+3. **内容深度依赖模型内置知识**：仅基于参考文献标题生成内容，无法挖掘文献中的具体方法、实验数据等细粒度信息，内容深度受限于模型本身的知识储备。
+## 五、未来展望
+作者明确了后续研究的核心方向：
+1. **核心优化：引入参考文献全文**：将参考文献的完整内容整合进分步生成框架，为内容生成提供事实依据，从根源上缓解幻觉问题，提升引用准确性和内容可信度，这是未来工作的重中之重。
+2. **提示策略优化**：设计针对性的指令约束，引导模型生成更简洁、凝练的层级大纲，更贴近真实综述的写作风格。
+3. **最终目标**：打造结构合理、内容准确、成本可控的全自动文献综述生成方案，输出更鲁棒、更具学术可信度的结果。
+需要我把这篇论文的**核心贡献和创新点**单独整理成精简条目吗？</t>
   </si>
   <si>
     <t>我已经完整阅读了这篇论文。下面我从头梳理 HoWToBench 的评价体系设计，帮你建立完整的认知框架。
@@ -1468,6 +1706,106 @@
 | 多标准平均 | 集成学习 / 方差缩减 | 提高评分稳定性 |
 | 数据筛选 | 基于代理变量的截断采样 | 验证评价框架的判别力 |
 核心创新在于：**评价标准本身是查询的函数**，而非固定常量。这使得评价体系能够适应 100 个子领域的多样性，人类对齐率从静态标准的 67% 提升到动态标准的 84%（critic model）。</t>
+  </si>
+  <si>
+    <t># 论文审视报告：ChemAgent: Self-updating Library in Large Language Models Improves Chemical Reasoning
+## 一、整体评价
+这是一篇完成度很高、实验扎实、方法有明确创新的AI4Science方向论文。核心工作针对大模型化学推理的三大核心痛点（领域公式误用、推理步骤错误、文本-代码结合出错），提出了**三层记忆架构+动态自更新知识库+评估修正闭环**的ChemAgent框架，在SciBench化学基准上取得了显著的性能提升，同时覆盖了消融分析、误差分析、成本分析、自进化验证等多个维度，附录的prompt与案例轨迹也保障了可复现性。
+整体而言，论文的核心贡献清晰，实验支撑充分，具备投稿顶会/顶刊的基础潜力。下面从**优势亮点**、**分模块优化建议**、**投稿风险与应对**三个维度展开详细审视。
+## 二、核心优势与亮点
+1. **问题定位精准，动机充分**
+   精准抓住了化学推理“多步骤、强计算、误差易级联”的特性，明确点出了现有大模型在公式使用、推理逻辑、代码计算三类场景下的缺陷，同时通过Figure1的案例直观对比了基线方法的错误，与本文方法的效果形成强烈反差，动机说服力强。
+2. **方法设计有体系化创新，逻辑闭环完整**
+   没有停留在“给大模型加RAG”的简单工程改进，而是借鉴人类认知机制设计了**规划记忆、执行记忆、知识记忆**三层差异化记忆结构，同时配套了“库构建-检索推理-评估修正-动态更新”的完整流程，兼具理论依据和工程落地性，方法的完整性优于多数领域Agent工作。
+3. **实验维度全面，论证严谨**
+   实验设计非常扎实：
+   - 覆盖GPT-3.5/4、Llama3系列、Qwen2.5等多个不同能力的基座模型，验证了框架的普适性；
+   - 消融实验不仅验证了各模块的作用，还延伸到记忆质量、记忆数量的影响，结论有深度；
+   - 补充了自进化分析、成本分析、错误分析，从性能、效率、缺陷三个维度完整呈现了方法的特性，远超多数同类工作的实验深度。
+4. **可复现性保障到位**
+   开源了代码，附录完整给出了所有prompt模板、详细的案例执行轨迹、数据集统计信息，符合学术论文的可复现要求，也能减少审稿人对实验真实性的质疑。
+## 三、分模块优化建议
+### （一）摘要与引言：强化边界，避免歧义
+1. **修正性能表述，避免歧义**
+   摘要中“performance gains of up to 46% (GPT-4)”容易被误解为**相对提升比例**，但实际是CHEMMC数据集上**绝对精度提升了46个百分点**（28.21→74.36）。建议修改为：
+   &gt; achieves absolute accuracy gains of up to 46 percentage points over vanilla GPT-4
+   同时补充“average improvement of 10% over state-of-the-art StructChem”，同时明确是绝对提升还是相对提升，保持表述严谨。
+2. **明确与通用记忆Agent的差异化**
+   引言中提到了外部记忆相关工作，但对“本文和通用记忆Agent（如Reflexion、MemoryBank）的核心区别”铺垫不足。建议补充1-2句话明确创新边界：
+   &gt; 不同于通用领域的对话/流程记忆，本文针对化学推理的层级化特性，将记忆粒度细化到原子子任务级别，并设计了领域专属的规划-执行-知识三层协同机制，实现了求解经验的结构化沉淀与动态自进化。
+3. **补充贡献点的凝练总结**
+   引言末尾建议增加一段明确的贡献总结（3-4点），比如：
+   - 提出了一套动态自更新的化学推理知识库框架，包含三层结构化记忆；
+   - 设计了评估修正模块，实现推理轨迹的自动纠错与计划调整；
+   - 在4个化学基准数据集上取得SOTA效果，验证了模型自进化能力；
+   - 开源了全套代码与prompt，可迁移至其他科学领域。
+   方便审稿人快速抓取核心贡献。
+### （二）方法部分：补充细节，增强严谨性
+1. **明确树状记忆的具体定义**
+   正文提到记忆采用“structured tree-based format”，但未说明树的结构逻辑：是按化学子领域分类的目录树，还是任务分解的层级树？检索时是如何遍历的？建议补充1段说明：
+   &gt; 执行记忆以层级化任务树存储：根节点对应化学子领域（如量子化学、物理化学），中间节点对应问题类型，叶节点为原子子任务及其条件、解法、代码。检索时通过embedding匹配叶节点的任务描述，同时向上回溯获取父节点的规划策略。
+2. **补充相似度计算的细节**
+   - 明确相似度阈值θ的具体取值，以及该阈值的确定方式（如在开发集上调参得到的最优值）；
+   - 补充选择Llama3 embedding的理由，或增加1组不同embedding的消融（如OpenAI embedding、化学领域embedding），如果算力有限可以在局限性中说明。
+3. **完善自进化机制的说明**
+   §2.9中“solution is correct就加入记忆”的表述，容易引发“测试集标签泄露”的质疑。虽然原文补充了排除自身样本的说明，但建议进一步明确：
+   &gt; 自进化过程中，样本的解仅用于后续其他样本的推理，求解该样本自身时不会调用其对应记忆，严格避免标签泄露。
+   同时补充：正确性判断是通过与标准答案比对实现的，属于离线迭代验证；真实落地场景中可替换为工具验证、人工反馈等方式。
+4. **补充推理阶段的算法伪代码**
+   目前只有库构建的Algorithm 1，建议补充Algorithm 2，描述“任务分解→记忆检索→推理求解→评估修正→记忆更新”的完整推理流程，让方法逻辑更完整。
+5. **评估模块的性能补充**
+   评估&amp;修正模块是核心组件之一，建议补充1个小实验：统计评估模块对错误解的识别准确率（召回率）和误判率（精确率），量化该模块的实际效果。
+### （三）实验部分：强化公平性，深化解读
+1. **补充数据集划分说明**
+   明确开发集与测试集的划分逻辑：是按教材章节划分（例题为开发集，习题为测试集），还是随机划分？化学题目章节关联性极强，如果开发集和测试集来自同一章节，记忆检索的高相似度会天然带来提升，审稿人极易质疑泛化性。建议明确说明划分方式，证明两者无内容重叠。
+2. **对齐基线的示例数量**
+   基线“Few-shot + Python”使用6个示例，而ChemAgent是2-shot规划记忆+4-shot执行记忆，总示例数恰好也是6个，数量是对齐的。建议在实验设置中明确说明这一点，避免审稿人质疑“用更多示例换来了性能提升”。
+3. **深化消融实验的结果讨论**
+   Table2中有两个非常有价值的反直觉发现，目前的解读偏浅，建议深化：
+   - **去掉执行记忆、换人工few-shot后，平均精度与完整模型持平**：这说明在小样本、窄领域场景下，人工高质量示例的效果不弱于自动构建的执行记忆。可以进一步讨论：本文框架的核心优势在于**扩展性**——当问题领域广、数量多时，自动构建记忆库的成本远低于人工编写示例，而非在所有场景下都绝对优于人工示例。
+   - **混合质量记忆效果最差**：这一结论很有启发性，可以延伸讨论：记忆的质量一致性比单纯的数量更重要，未来工作可以引入记忆质量打分、去噪过滤机制，解决异质记忆的干扰问题。
+4. **增强自进化实验的普适性**
+   自进化实验仅在MATTER数据集上开展，建议补充至少1个数据集的结果（如QUAN），证明自进化特性不是单数据集的偶然现象；同时补充Figure5的横轴具体迭代次数、收敛时的精度数值。
+5. **错误分析补充定量统计**
+   三类错误的定性分析很清晰，建议补充定量占比：比如在所有失败案例中，题意理解错误、推理错误、记忆选错分别占多少比例，明确未来优化的优先级。
+### （四）讨论与局限性：拓展深度，体现思考
+1. **补充记忆的可扩展性讨论**
+   目前的记忆库是只增不减的，长期运行会面临检索效率下降、噪声记忆累积的问题。建议在未来工作中加入**记忆的动态管理机制**：包括低频记忆遗忘、错误记忆淘汰、相似记忆合并等，体现对方法长期落地的思考。
+2. **明确与化学专业工具的结合方向**
+   现有工作仅用Python做数值计算，未结合RDKit、量子化学计算等专业化学工具。建议在未来工作中补充：将工具调用流程也沉淀到执行记忆中，实现“推理-工具调用-结果验证”的全流程记忆化，进一步贴合真实化学研究场景。
+3. **领域迁移的可行性补充**
+   局限性中提到可迁移到物理、数学等领域，建议补充1-2句迁移的核心逻辑：仅需替换领域prompt、用对应领域的开发集重建知识库，框架本身无需大幅修改，增强方法的通用价值说服力。
+### （五）写作与格式细节
+1. **术语统一**
+   全文统一核心术语：系统层面统一为**self-updating library**，内部组件统一为**memory components**，避免“library”“memory”“pool”等表述随意切换。
+2. **图表规范**
+   - Figure5坐标轴标签不完整，补充横轴“Iterations”、纵轴“Accuracy”，标注收敛点的数值；
+   - 所有表格的数字对齐、表头格式统一，检查小数点位数一致性；
+   - 子图引用格式统一（如Figure 1(a) 或 Figure 1 (a)，全文保持一致）。
+3. **引用格式**
+   检查参考文献的会议/期刊格式一致性，匹配目标投稿 venue 的规范；确保所有引用的工作都在正文中标注了引用编号。
+4. **附录对应性**
+   检查正文所有“Appendix X”的引用，确保附录的章节编号、内容完全对应，避免出现引用错位。
+## 四、投稿风险预判与应对建议
+### 1. 常见质疑1：“本质就是化学领域的RAG，创新性不足”
+**应对逻辑**：区分“通用文档RAG”和“原子子任务级动态记忆”的本质差异：
+- 粒度不同：普通RAG是段落/文档级检索，本文是**原子子任务+结构化解法**的精细化记忆，可直接复用求解逻辑；
+- 机制不同：普通RAG是静态知识库，本文是**动态自进化**的，求解经验可以自动沉淀、持续迭代；
+- 架构不同：本文是三层记忆协同+评估修正的完整Agent闭环，不是单纯的检索增强。
+### 2. 常见质疑2：“教材题目太简单，离真实化学研究太远”
+**应对逻辑**：
+- 教材习题是化学推理能力的基础基准，覆盖了公式应用、多步推理、单位换算等核心痛点，是验证方法有效性的标准范式；
+- 本文的框架是可扩展的，未来可接入文献知识库、专业计算工具，向药物发现、材料设计等真实场景迁移，本文是基础能力的系统性验证。
+### 3. 常见质疑3：“效果提升依赖强基座，小模型提升有限”
+**应对逻辑**：
+- 小模型（Llama3-7b）也取得了8.34%的平均绝对提升，证明框架对所有基座都有增益；
+- “基座越强，提升越显著”恰恰是框架的优势——它能充分释放基座的潜在能力，且随着基座模型的迭代，框架的效果会持续提升，不存在“天花板”。
+## 五、投稿方向建议
+1. **NLP领域顶会**：ACL、EMNLP、NAACL
+   - 投稿侧重点：突出**Agent记忆架构的通用创新**，化学作为验证场景，强调方法可迁移到其他科学推理领域。
+2. **AI+科学顶会/期刊**：ICML/NeurIPS的AI4Science赛道、JCIM（Journal of Chemical Information and Modeling）
+   - 投稿侧重点：突出**化学推理任务的SOTA突破**，强调方法对化学信息学、计算化学的实际应用价值。
+如果需要，我可以帮你针对具体的目标会议/期刊，进一步调整论文的侧重点和摘要表述。</t>
   </si>
   <si>
     <t># 论文投稿审视：Darwin Gödel Machine
@@ -2218,6 +2556,160 @@
     <t>完整审视论文，看是否存在设计不合理，逻辑不通的地方</t>
   </si>
   <si>
+    <t>结合论文全文的逻辑链条、方法设计和实验验证，我从**核心立论逻辑、方法设计缺陷、实验验证不足、表述与术语问题**四个层面，梳理其中不合理、逻辑不通或论证不严谨的地方：
+## 一、核心立论：逻辑偷换与证据缺失
+这是论文最根本的问题——整个研究的动机和核心结论，存在明显的逻辑跳跃和证据不足。
+### 1. “Laffer曲线”核心动机缺乏严格支撑，且偷换了问题本质
+论文提出“硬负样本挖掘存在Laffer曲线，负样本质量过高反而导致模型性能下降”，并以此作为抛弃传统范式、提出zELO的核心理由，但该立论存在两个致命问题：
+- **无严格实验证据**：论文原文明确承认“We did not collect sufficient data with miner intelligence as the only independent variable, so we leave such data collection to future research”。也就是说，支撑整个研究动机的核心现象，并没有做控制变量的验证，属于观察性结论，而非严格实验结论。
+- **偷换问题根源**：所谓“硬负样本比人工标注的正样本更相关”，本质是**人工标注质量不足**导致的，而非“硬负样本挖掘”这个训练范式本身的固有缺陷。如果用同等质量的标注源（比如LLM）同时标注正负样本，硬负样本挖掘并不会出现“假负例”问题。
+  论文将“人工标注的局限性”偷换为“训练范式的根本性缺陷”，进而推出“硬负样本挖掘有性能天花板”的结论，逻辑不成立。
+- **自身并未突破规律**：zELO本质上是用“LLM集成标注”替代“人工标注”的蒸馏范式，学生模型的性能上限依然取决于教师（LLM集成）的标注精度，和传统范式“上限取决于标注质量”的规律完全一致，并不存在“无理论上限”的突破。
+### 2. “LLM标注优于人类标注”的结论无实证，且自相矛盾
+论文反复声称“LLM集成生成的数据质量优于同等数量的人类标注”，这是方法合理性的核心前提，但全文存在明显矛盾：
+- **无头对头对比实验**：全文没有任何一组控制变量实验——在相同底座、相同数据、相同训练策略下，分别用人类标注和LLM集成标注训练模型，对比最终重排性能。该结论属于断言式表述，没有实验数据支撑。
+- **设计上自相矛盾**：既然LLM标注质量更高，为何还要在5.6节引入“人类标注的最高分文档”来修正模型、做所谓的“RLHF”？如果LLM判断已经比人类准确，人类标注的样本只会引入噪声，而非提升效果。这一设计侧面承认了LLM标注存在偏差，需要人类信号校正，与“LLM标注优于人类”的结论直接矛盾。
+## 二、方法设计：理论不严谨与逻辑缺陷
+### 1. 理论引用的张冠李戴：收敛性结论适用范围错配
+论文在4.2.1节Bradley-Terry模型部分，引用Zermelo 1929的定理，说明Elo估计存在唯一全局最小值、梯度下降可收敛；但在4.2.2节转而使用**Thurstone模型**（用误差函数erf替代Sigmoid），却完全没有论证：
+- Thurstone模型框架下，成对比较的极大似然估计是否同样存在唯一全局最优解？
+- 梯度下降是否同样具备收敛保障？
+论文直接将Bradley-Terry的理论结论套用到Thurstone模型上，属于典型的理论论证跳跃，严谨性不足。
+### 2. 稀疏采样策略：指标选择偏差，忽略排序任务的核心矛盾
+论文选择“随机环拼接的k-正则图”作为稀疏采样方案，核心评估指标是“稀疏采样Elo与全量矩阵Elo的MSE”，但这个设计逻辑存在本质缺陷：
+- **排序任务的误差敏感点是“近邻文档对”**：真正影响NDCG等排序指标的，是**分值接近的文档对是否排对顺序**，而非分值差异大的文档对。随机采样的k-正则图，大部分比较都发生在分值差异较大的文档对上，对真正决定排序质量的“近邻对”覆盖不足。
+- **MSE低≠排序效果好**：分值的均方误差小，不代表Top-K排序的准确率高。论文仅用MSE衡量采样策略优劣，没有验证不同采样策略对最终重排性能的实际影响，属于指标选择偏差。
+- 论文自身提到了“Elo感知动态采样”（优先比较分值接近的文档对），但最终以“速度快”为由选择了随机方案，却没有验证该选择对最终效果的负面影响，设计取舍缺乏实验依据。
+### 3. 跨查询分值不一致，MSE损失的合理性存疑
+zELO的Elo分数是**每个查询内独立计算**的，约束为“查询内所有文档Elo之和为0”，这意味着：
+- 不同查询之间的Elo分值尺度、分布完全不同。即使归一化到[0,1]区间，A查询的0.7分和B查询的0.7分，代表的相对相关性水平也没有统一语义。
+- 论文将所有查询的样本混合在一起，用MSE损失训练逐点模型，相当于让模型学习一个全局统一的分值映射，但标签本身并不具备全局一致性，会引入不必要的训练噪声。
+论文没有论证为何选择MSE而非更适配排序任务的损失函数（如ListMLE、成对排序损失），也没有验证跨查询分值分布差异对训练效果的影响。
+### 4. “RLHF”模块名不副实，且存在偏差放大风险
+5.6节的“RLHF”模块存在两个明显问题：
+- **术语滥用**：该模块本质是“难例样本扩充+重新训练”，完全不涉及强化学习、奖励模型、策略梯度等RLHF的核心要素，只是普通的难例挖掘二次训练，冠名“RLHF”属于蹭热点式的表述不严谨。
+- **循环偏差风险**：流程是“用pointwise的错误样本扩充成对模型训练集→重新生成Elo→训练新的pointwise”，本质是反复在模型易错的样本上强化LLM的判断偏好。如果LLM集成本身存在系统性偏差，该循环会不断放大偏差，让模型越来越拟合LLM的判断模式，而非真实的相关性。论文完全未讨论该风险。
+## 三、实验验证：控制变量缺失，结论可信度不足
+### 1. 最核心的消融实验缺失：无法证明zELO方法本身的价值
+这是实验部分最大的硬伤：全程用zerank模型和第三方商用模型对比，变量完全不唯一（底座模型不同、训练数据不同、训练方法不同），**完全无法证明性能提升来自zELO方法本身**。
+- 性能提升完全可能来自Qwen3的强底座能力、11.2万查询的大规模训练数据，而非Elo这套训练流程。
+- 缺失最关键的对照实验：在**相同底座、相同数据、相同计算量**的前提下，对比zELO与传统硬负样本挖掘、直接LLM逐点打分蒸馏的性能。没有这个对照，zELO的方法论贡献就无法成立。
+- 更基础的，论文没有验证“成对比较+Elo”这套流程的必要性：如果直接让LLM给每个文档打绝对相关性分数，用同样的数据训练逐点模型，效果是否显著差于zELO？如果效果相当，那么整套Elo计算、稀疏采样、k-正则图的设计都是冗余的。
+### 2. 数据透明度严重不足，存在数据泄露隐患
+- **训练集来源不透明**：11.2万查询、上亿文档仅标注为“公开可用”，未列出具体来源数据集、数据清洗规则、去重策略，无法验证训练集与测试集是否存在重叠或数据泄露。
+- **私有数据集实验无说服力**：表3的私有数据集实验完全是黑箱——无数据集描述、无标注标准、无样本量、无领域说明，其结果无法复现和验证，不能作为“泛化性强”的有效证据。
+### 3. 基线对比不公平，有稻草人论证嫌疑
+- **LLM重排基线未充分调优**：对比Gemini等LLM-as-reranker时，仅使用了论文自己设计的单组prompt，未对基线做prompt工程优化。LLM重排性能高度依赖prompt设计，未调优的基线无法代表LLM重排的真实水平，对比结果说服力不足。
+- **基线信息不完整**：未明确给出所有对比基线的参数规模、训练数据量、底座模型，仅笼统声称“超越两倍规模的商用模型”，信息不透明，无法判断性能优势的真实来源。
+## 四、表述与术语：夸大与误导
+1. **“无监督训练”的表述不准确**
+   论文反复强调“unsupervised training”，但zELO的标签本质是LLM生成的合成监督信号，属于弱监督/合成监督范畴，并非传统意义上的无监督学习（无标注、自监督），该表述有夸大误导嫌疑。
+2. **部分结论过度泛化**
+   - 摘要声称“跨语言性能优异”，但全文没有任何跨语言实验数据；
+   - 声称“在所有领域超越闭源商用模型”，但实际仅在部分数据集上领先，并非全场景碾压；
+   - 将“教师模型精度决定学生上限”这个所有蒸馏范式的共性，包装成zELO的独特优势，属于偷换概念。
+## 总结
+这篇论文的**工程实现和效果是扎实的**——训练出了性能优秀的开源重排模型，但**方法论层面的创新和严谨性存在明显短板**：
+- 核心动机（Laffer曲线）证据不足，且偷换了“标注质量”和“范式缺陷”的概念；
+- 方法设计多处依赖经验选择，理论和实验论证不严谨；
+- 实验缺乏关键控制变量，无法证明zELO这套Elo方法论本身的必要性，性能提升很可能主要来自强底座+大规模合成数据，而非训练范式的创新。
+简单来说：**模型大概率是好用的，但“zELO方法是性能提升的核心原因”这个结论，论文并没有证明。**</t>
+  </si>
+  <si>
+    <t># 论文设计与逻辑缺陷审视
+整体而言，SurGE 是科学综述生成方向首个系统性的标准化基准，核心思路（解耦检索-生成、多维度自动化评估）具有明确的领域价值，整体论证链条自洽。但从严谨性、合理性与普适性角度审视，论文在数据集构建、指标定义、实验设计、结论推导等层面仍存在多处设计缺陷与逻辑不严谨之处，具体可分为四大类：
+## 一、数据集与任务定义：基准本身的合理性存疑
+### 1. 真值综述的“金标准”属性不足
+SurGE 将单篇人类综述作为评估的基准真值，但这一设定存在两层先天缺陷：
+- **真值本身的学术严谨性缺乏强保证**：真值全部来自 arXiv 预印本，仅以“引用量≥20+专家标注可用性”作为筛选条件。但 arXiv 预印本无需经过严格的同行评审流程，4名博士生的标注也仅判断“整体是否可用”，并未逐章验证内容的学术准确性、文献覆盖的权威性。换言之，真值只能代表“合格的综述”，无法代表“最优的综述”，以此作为绝对标尺存在根基偏差。
+- **单一真值不符合综述写作的开放性**：学术综述没有唯一的“标准答案”——同一主题下，不同学者可在结构安排、文献选择、论述视角上存在合理差异，侧重点可偏向理论、方法或应用。以单篇真值的引用列表、标题结构为基准，本质衡量的是“与特定人类综述的相似度”，而非“综述本身的绝对质量”。若生成系统采用了不同但自洽的写作框架，会被指标误判为低质量。
+### 2. 语料库的天然缺陷导致任务偏离真实场景
+- **仅用摘要，缺失全文，任务被简化**：语料库仅收录论文元数据（标题、作者、摘要），无全文内容。真实的综述写作需要基于论文的方法细节、实验数据、对比分析进行深度综合，而 SurGE 的设定下，系统只能基于摘要做表层拼接与改写，无法完成方法对比、结果复盘等深度评述。这使得基准任务与真实学术综述写作存在显著差距，更像“大规模摘要综述”而非完整的学术综述。
+- **语料覆盖不全，引入系统性偏差**：约 30% 的真值参考文献不在语料库中（多为闭源期刊、非 arXiv 文献），这部分文献永远无法被检索到，既直接限制了召回率的理论上限，也导致一个不合理规则：系统若引用了这些真实存在且高度相关的文献，会被直接判定为“引用幻觉”并打0分，变相惩罚了引用范围更广的系统。
+- **“不在语料=幻觉”的概念混淆**：论文将“未出现在语料库中的引用”直接定义为幻觉，但“文献真实存在但未被语料收录”与“文献完全不存在（模型编造）”是两个完全不同的概念。该定义混淆了“语料外引用”和“虚假引用”，是指标设计上的明显逻辑漏洞。
+### 3. 任务定义的简化与范式偏向
+- **线性两阶段不符合真实写作逻辑**：论文将综述生成严格定义为“先检索、后生成”的线性两阶段，但人类写作综述是典型的迭代循环过程：定初步大纲→检索文献→写作中发现缺口→补充检索→调整大纲。线性解耦的设定无法适配具备迭代检索、动态规划能力的 Agent 系统，也与真实写作流程脱节。
+- **并非完全“方法无关”**：任务默认所有系统必须基于给定语料做检索增强生成，天然偏向检索类、Agent 类系统，无法公平评估纯生成式系统（无检索、直接生成综述），也难以评估跨数据库、多来源的综述系统，与论文宣称的“method-agnostic”存在一定差距。
+## 二、评估指标：核心维度存在概念偏差与设计漏洞
+### 1. 全面性：用“引用重合度”替代“领域覆盖度”
+论文以“生成引用与真值引用的召回率”作为全面性指标，存在核心概念偏差：
+- 综述的“全面性”本质是覆盖主题下的核心研究脉络、关键成果与代表性工作，而非与某一篇特定综述的引用列表完全重合。系统完全可能引用了同等重要但未出现在真值中的文献，此时召回率低，但实际全面性并不差。
+- 仅报告召回率，缺失精确率维度。单一召回率无法反映文献选择的质量：系统可通过堆砌大量引用抬高召回率，但引用的相关性、权威性可能很差。只看召回会引导系统“多引用”而非“精准引用”。
+### 2. 引用准确性：NLI 方案存在系统性误判
+三级引用准确率是论文的核心创新指标之一，但设计上存在显著的适用边界问题：
+- **引用功能的单一化假设错误**：NLI（自然语言推理）仅能验证“论文内容蕴含/支持句子论断”这一种引用关系，但学术综述中的引用功能多元：介绍背景、对比方法差异、指出前人局限、引用通用方法等。若引用是为了对比、评述而非直接支持论断，NLI 会误判为“中性”甚至“矛盾”，导致句子级准确率被系统性低估。
+- **仅基于摘要的推理可靠性不足**：NLI 仅输入论文摘要，而很多细粒度论断（如具体实验结果、方法参数）需要全文细节支撑，仅靠摘要无法准确判断支撑关系。论文也未验证该 NLI 模型在科学文献场景下的准确率，直接用于核心指标计算缺乏可靠性背书。
+- 特殊规则的双重标准：真值参考文献直接赋予文档级满分，而语料内的非真值引用需通过 NLI 判定。这会让指标天然偏向“和真值引用重合度高”的系统，而非“引用本身准确”的系统。
+### 3. 结构质量：重形式轻实质，以相似度替代质量
+- **仅评估标题，忽视深层逻辑**：SQS（结构质量分）和 SHR（软标题召回）均只围绕标题的语义、层级展开，无法评估章节内部的逻辑衔接、论述递进、段落组织等深层结构质量。指标只能衡量“标题结构像不像真值”，不能真正反映综述的逻辑流畅性与组织合理性。
+- **无法识别更优的结构设计**：指标本质是“与真值的结构相似度”，而非“结构本身的优劣”。若生成系统设计了比真值更清晰、更合理的结构框架，会因与真值不一致而被判低分，这与“评估质量”的目标背道而驰。
+### 4. 内容质量：评估逻辑模糊，高阶能力缺失
+- **CQS 的评估依据不明确**：论文未说明 GPT-4o 打分时是否参考真值综述。若为无参考打分，大模型不具备领域全量知识，无法准确判断专业内容的事实对错，“无错误”维度的评估不可靠；若为有参考打分，则本质仍是与真值的文本相似度，而非绝对内容质量。
+- **缺失综述核心高阶维度**：当前指标仅覆盖语言流畅、逻辑清晰等基础要求，未涉及学术综述的核心价值维度，如研究脉络梳理、观点对比分析、未来趋势洞察、学术评述深度等。这导致基准只能区分“合格与不合格”，无法评估接近人类水平的高质量综述。
+## 三、元评估与实验设计：严谨性不足，结论推导有偏差
+### 1. 元验证覆盖不全，说服力有限
+- **核心指标未做人类对齐验证**：元评估仅验证了结构质量（SQS）和内容质量（CQS）与人类判断的相关性，而更核心的全面性（召回率）、引用准确性指标完全没有做人类对齐验证。这两个指标的可靠性缺乏实证支撑，是评估框架的关键短板。
+- **样本量与系统数量过少**：仅选取 3 个基线系统 + 1 个人类真值共 4 个样本进行排序验证。系统数量少导致排序任务简单，相关性数值天然容易偏高；且测试样本量有限，元评估结论的普适性不足。
+### 2. 实验设置的公平性与解释力问题
+- **统一检索器的双刃剑**：为隔离检索差异，所有基线统一使用相同的稠密检索器和 top-100 结果。这虽便于单独评估生成能力，但也导致实验无法反映系统的端到端真实性能；更关键的是，部分 Agent 系统（如 SurveyForge）的原生设计包含“检索-写作”联动机制，替换检索器后可能破坏其原有 pipeline 的协同性，对比存在不公平性。
+- **RAG 基线过于基础**：实验中的 RAG 基线采用最简单的“分批摘要+融合”方案，未使用重排序、细粒度分块、Graph RAG 等先进 RAG 技术。基线强度不足可能人为夸大了 Agent 架构的优势，无法准确反映“通用 RAG”与“专用 Agent”的真实性能差距。
+- **检索上限的偷换概念**：第 6.1 节用 top-1000 的检索召回率（68.05%）作为“检索上限”，与端到端系统不足 10% 的召回率对比，论证“瓶颈在生成”。但端到端系统实际仅使用 top-100 的检索结果，其理论召回上限是 36.65%。用 k=1000 的数值放大了生成阶段的差距，属于表述不严谨。
+### 3. 结论推导的表述偏差
+- **“Agent 引用准确性差”的表述不准确**：原文称“agentic pipelines outperform RAG baselines in fluency and structural quality, they still struggle with citation accuracy”，易误导读者认为 Agent 在引用准确性上弱于 RAG。但实验数据显示：专用 Agent 的三级引用准确率均显著优于基础 RAG-Qwen，与强基座 RAG（GPT-4o、Gemini）相当甚至更优。准确的结论应是“所有系统的引用准确率绝对值都偏低”，而非 Agent 单独在该维度表现差。
+- **“机制弥补模型容量”的结论有局限**：该结论仅基于“Qwen-14B Agent 超越了同基座 RAG，甚至接近/超过闭源基座 RAG”的对比。但论文未验证“强基座 + Agent 架构”的组合效果，无法证明“机制比基座更重要”，只能说明“专用机制可在弱基座上显著提升性能”。
+## 四、其他普适性局限
+1. **学科覆盖单一**：仅覆盖计算机科学领域，且偏向 arXiv 上的热门主题，无法直接推广到医学、人文社科等写作范式、文献体系差异巨大的学科。
+2. **数据规模偏小**：205 篇真值综述对于基准测试而言规模有限，主题覆盖度不足，可能影响不同系统的细粒度区分度与基准的长期可扩展性。
+## 总结
+SurGE 的核心贡献在于首次为科学综述生成建立了标准化的评估范式，其“解耦诊断+多维度评测”的框架方向正确。但上述缺陷决定了它目前更适合作为**系统间相对对比的工具**，而非衡量综述绝对质量的“黄金标尺”。其指标结果的解释需要谨慎，不能脱离任务设定和语料局限过度解读。</t>
+  </si>
+  <si>
+    <t># 论文设计与逻辑的疏漏分析
+整体来看，这篇论文的核心框架（分步式大纲引导+分块生成）具备工程合理性，在赛事约束下也取得了有竞争力的结果，但在**任务理解、流程设计、指标解读、论证严谨性**等维度存在多处设计不合理与逻辑疏漏，具体可分为七类问题：
+## 一、任务规则理解与数据使用的矛盾性问题
+这是论文最基础的设计偏差，直接影响了方法的上限与合理性。
+1. **测试集字段使用的自我约束缺乏依据**
+    论文4.1节明确说明测试集官方提供了`reference content`（参考文献全文）字段，但3.1节又称“任务指南声称测试仅提供主题和参考文献标题”，因此主动完全弃用参考文献全文。这里存在两处逻辑矛盾：
+    - 规则与数据字段的冲突未澄清：若测试集官方包含参考文献全文字段，通常意味着属于允许使用的输入；作者仅以模糊的“指南声称”为由彻底弃用，既未引用指南原文条款，也未解释字段存在的原因，属于对任务规则的保守误读。这一决策直接让方法失去了最核心的事实依据，人为放大了大模型幻觉问题。
+    - 规则边界概念混淆：作者将“禁止使用训练集以外的外部数据/检索增强”与“禁止使用测试集自带的参考文献全文”混为一谈。赛事禁止外部检索是为了保证公平性，但测试集自带的文献内容属于给定输入，不属于“额外外部数据”，作者的自我限制缺乏规则支撑。
+2. **参考文献截断策略的随意性**
+    为适配模型输入长度，作者将参考文献截断为前80–100篇（测试集平均每篇126.8篇参考文献），但未做任何消融实验验证截断对生成效果的影响。截断必然丢失部分文献信息，可能损害内容完整性与引用全面性，但作者既未说明截断阈值的选择依据，也未评估信息损失的代价，设计较为随意。
+## 二、生成流程的逻辑倒置：摘要生成顺序违背写作规律
+论文将摘要生成放在第一阶段第3步（仅完成一级大纲后），早于子标题和全部正文生成，这一设计违背了学术写作的基本逻辑，存在一致性隐患：
+- 从写作规律看，摘要是对整篇论文核心内容、结论的高度凝练，应当在正文全部完成后提炼生成；先生成摘要再填充正文，相当于“先定结论再补论据”，本质是倒推式写作，极易导致摘要与正文重点不匹配、内容脱节。
+- 作者既未论证“先生成摘要”的合理性，也未对比“正文后生成摘要”的效果差异，该设计更多是为了强行契合“全局规划先行”的框架，牺牲了写作逻辑的自洽性。
+## 三、核心指标解读偏差：软标题召回率存在“虚高”与因果倒置
+作者将“软标题召回率95.84%、位列第二”作为方法的核心优势，并完全归因于分步式大纲设计，但该指标结果与作者的生成设计存在天然的“适配偏向”，解读存在明显逻辑偏差：
+1. **指标特性与生成设计的天然契合**：软标题召回率基于语义相似度计算，生成的标题数量越多、粒度越细，覆盖的语义点就越广，越容易命中参考标题的语义，召回率天然更高。
+2. **作者的大纲设计恰好偏向“多而细”**：在案例对比中，参考综述仅有6个一级标题，而作者生成的一级标题多达16个，粒度远细于真实综述。这种情况下的高召回率，很大程度是“标题数量多、划分细”带来的，而非结构规划的质量更高。
+3. **因果倒置的解读谬误**：作者自身也承认生成的大纲“过于冗长繁琐”，但并未意识到冗长与高召回率的因果关系，反而将高召回率作为结构设计优异的核心证据，属于典型的因果倒置。
+## 四、论证严谨性不足：缺失关键消融与对比实验
+论文的核心结论是“分步式提示设计有效”，但全程缺乏消融实验支撑，无法证明每个步骤的必要性与贡献度，论证链条不完整：
+1. **无分步消融实验**：未对比“一次性生成全文”“仅两阶段生成”“去掉参考文献筛选步骤”等变体的效果与成本，无法证明6步拆分的合理性，也无法量化每个步骤对最终结果的具体贡献。
+2. **无提示词对比验证**：作者仅给出最终版提示词，未说明迭代过程，也未对比不同提示风格、不同指令强度的效果差异，无法证明当前提示设计是最优解。
+3. **无模型泛化性验证**：仅在Qwen-long单模型上验证了效果，未验证该分步框架在其他LLM上的通用性，结论的适用范围有限，但作者并未明确说明这一局限性。
+## 五、归因偏差：成本优势的来源被混淆
+作者反复强调“单篇生成成本仅0.1元”，并将其归功于“高效的提示设计”，但成本优势的核心来源被刻意混淆：
+1. 成本低的首要原因是**Qwen-long本身定价极低**（输入0.5元/百万token、输出2元/百万token），远低于主流商用大模型；
+2. 其次是作者**主动截断了参考文献数量**，直接减少了输入token量；
+3. 分章节筛选参考文献带来的成本降低只是第三因素。
+作者未拆分三者的贡献占比，将低成本全部归因于方法设计，属于归因偏差，夸大了方法本身的成本优势。若更换为其他主流模型，该成本优势会大幅缩水。
+## 六、方法设计的疏漏：误差传递与一致性保障缺失
+1. **参考文献筛选的误差传递未被关注**
+    步骤4由LLM仅基于文献标题筛选章节相关文献，但作者未评估筛选的准确率。文献标题包含的信息极其有限，模型很容易错选、漏选关键文献，该误差会逐级传递到后续的子标题生成和内容生成中，最终影响综述质量。作者完全没有讨论这一误差链条的影响。
+2. **章节间一致性无保障机制**
+    正文按子章节独立生成，仅输入全局大纲，没有设计任何跨章节的一致性校验机制，存在内容重复、逻辑断层、术语不统一等潜在风险。作者既未提及该风险，也未做相关效果验证。
+3. **引用准确性无方法层约束**
+    仅在提示中引导模型按格式标注引用编号，但未设计任何机制校验引用内容与对应文献的匹配度，这也是幻觉的重灾区。作者仅将引用不准归因为“没用到参考文献全文”，没有在方法层面设计任何约束或校验环节。
+## 七、相关工作与创新点定位模糊
+1. **与同期工作的区分度不足**：核心思路同为“大纲规划+分块生成”的AutoSurvey是同期工作，作者仅简单提及，未明确对比两者的设计差异，也未说明自身方法的独特创新点，无法清晰定位工作的学术贡献。
+2. **迁移创新的论证不足**：“大纲引导长文本生成”已在故事、博客等场景被验证有效，作者将该思路迁移到综述生成，但未说明针对科学综述的专属设计与针对性创新，整体更偏向工程层面的提示词实现，学术创新度较弱。
+---
+### 总结
+上述问题大多属于**工程实现严谨性不足、结果解读有偏差、论证链条不完整**，论文的核心“分步规划+分块生成”思路本身是成立的，但学术严谨性和逻辑深度有所欠缺，部分结论的说服力不足，更偏向一份赛事技术方案报告，而非完整的学术研究。
+需要我把这些问题整理成**可直接用于论文评审的意见清单**，按严重程度分级吗？</t>
+  </si>
+  <si>
     <t>让我重新仔细梳理实验部分的每个环节，逐一分析其合理性和必要性。好，我来系统拆解这篇论文的实验设计，逐个分析每个步骤的合理性和必要性。
 ---
 ## 实验设计总览
@@ -2820,7 +3312,251 @@
 Once again, we thank all reviewers for their valuable feedback, which has significantly improved the paper. We will incorporate all the above clarifications and additions into the final version.</t>
   </si>
   <si>
-    <t>基于以下专家评审意见，整体过一遍论文，生成一份回复专家意见的初稿</t>
+    <t>Xpertbench Expert Level Tasks with Rubrics-Based Evaluation</t>
+  </si>
+  <si>
+    <t>## 一、论文设计与逻辑的自查分析
+结合审稿意见与论文原文整体审视：论文核心立论清晰、实验逻辑自洽，“传统考试式基准脱离真实专业场景”的核心批判成立，XpertBench的任务构建与评分体系具备明确的创新价值，不存在根本性的设计错误或逻辑矛盾。但在方法学严谨性、披露透明度与稳健性论证层面，存在多处可商榷的设计局限，也是本次审稿意见集中质疑的来源，具体可归纳为五类：
+1.  **评测方法的有效性论证不充分**
+    核心方法ShotJudge仅给出CDR=52.0%的单点结果，既无零样本基线对照，也无统计置信区间、分领域异质性分析，导致“缓解自奖励偏差”的核心声称缺乏实证支撑，属于“结论先行、验证不足”。同时未对锚定模型、评审模型选型做消融，无法排除模型风格耦合的潜在偏差，方法论说服力存在明显缺口。
+2.  **数据集边界与透明度界定模糊**
+    正文突出宣传1346条任务的规模优势，但核心实验仅使用245条经专家校准的Gold子集，且未明确说明全量数据与Gold子集的对应关系、非Gold数据的评测协议，容易造成“规模夸大”的观感，存在表述重心与实验主体不匹配的问题。同时CS、医疗领域在Gold子集中样本量不足，细粒度分析将其排除却仍计入整体总分，统计口径的一致性未做解释。
+3.  **标注质量缺乏量化佐证**
+    论文详细描述了两阶段专家筛选、同行评审、30%抽检等质控流程，但未提供任何标注者间一致性（IAA）的量化指标，“客观可验证”的宣称缺少数据支撑，属于流程描述完整但效果证据缺失。同时LLM辅助生成评分规则的角色、修改比例未明确披露，当评审器与规则生成模型同源时，存在循环评测的潜在风险，属于方法学披露不完整。
+4.  **实验可复现性设计不足**
+    评测模型多为前沿未公开版本，未固定API快照与调用参数；任务涉及联网检索，但未统一工具协议、步数上限、执行边界，外部研究者难以严格复现榜单结果，不符合基准类论文的可复现性惯例。此外失败模式分析以定性描述为主，缺乏对应的量化统计（如各类失败的发生比例、分领域差异），诊断结论的实证支撑偏弱。
+5.  **泛化性局限未主动讨论**
+    专家来源以国内高校为主，法律等领域存在明显的法域偏向，论文在宣称“评估通用专业能力”时，未主动讨论地域、文化、法域因素的局限性，存在结论泛化过度的风险。
+以上问题均属于**方法学细节完善与披露补充**范畴，并不动摇论文的核心立论与核心结论，均可通过补充实验、增加说明解决。
+---
+## 二、针对审稿意见的正式Rebuttal
+**致三位审稿人：**
+我们衷心感谢各位细致专业的评审与建设性意见，这些反馈对提升论文的方法学严谨性、结果透明度与可复现性极具价值。针对所有关切，我们已补充对应实验、量化分析与材料说明，并将在修订版中完整呈现。以下为逐条回应。
+### ▶ 对Reviewer 1的回应
+#### Comment R1-C1：真实工作流驱动的生态效度与规模优势
+**Response：** 非常感谢您对本研究核心设计取向的认可。以真实专业工作流而非封闭考题为锚点，是XpertBench区别于传统基准的核心价值。附录中的样例是我们全流程质控后的典型产出，修订版中我们将补充法律、教育、人文社科三个领域的完整任务+评分规则样例，进一步展示不同领域任务的设计逻辑与rubric的颗粒度标准。
+#### Comment R1-C2：应公开完整1346条任务与rubric以增强可复现性
+**Response：** 我们完全同意可复现性是基准类工作的核心要求，修订版将同步开源以下全部资源：
+1.  **全量数据集**：1346条任务的prompt、对应结构化rubric（JSON格式，包含每个检查点的内容、定量权重、定性分级、维度标签），覆盖全部7大领域80+子类。
+2.  **评测代码与协议**：ShotJudge的完整评测prompt模板、one-shot样例集、可直接运行的评测脚本，以及复现榜单的完整执行流程。
+3.  **明确子集边界**：新增3.4小节清晰界定XpertBench-Gold（245条，经双重专家校准，用于主实验）与全量数据集的关系：Gold子集为分层抽样的高置信度测试集，用于严谨的模型对比；全量数据集可通过ShotJudge做零样本迁移评测，我们将提供预校准的评审配置与基线分数，同时标注非Gold子集的置信度水平，避免读者对“规模”产生误读。
+#### Comment R1-C3：失败模式诊断需量化证据支撑
+**Response：** 感谢您的认可与建议。我们将在第5节新增细粒度量化分析，支撑定性的失败模式结论：
+- 基于rubric的16个维度标签，统计12款模型在“事实准确性”“逻辑连贯性”“信息加工”等维度的失败率，量化不同领域的能力短板分布。
+- 针对**检索干扰（retrieval interference）**：对比开启/关闭联网检索时，模型在长流程分析任务上的得分差，以及偏离核心论点的检查点占比，量化检索噪声对最终输出的损害程度。
+- 针对**原理幻觉（principle hallucination）**：统计因早期核心概念错误导致后续全推理链失效的任务占比，并分领域呈现差异，验证“早期错误级联扩散”的结论。
+### ▶ 对Reviewer 2的回应
+#### Comment R2-C1：ShotJudge的CDR仅52.0%，可靠性存疑，缺乏基线与统计检验
+**Response：** 感谢您指出这一关键方法学问题，我们从三个层面补充说明与验证：
+1.  **CDR数值的含义澄清**：CDR定义为 `P(agree) - P(disagree)`，52.0%的CDR对应**76%的一致率、24%的不一致率**。由于本研究的rubric是15-40个细粒度的原子化检查点，判定颗粒度远粗粒度打分，该一致性水平在专业领域细粒度评测中已具备实用价值。
+2.  **基线对比与统计显著性**：我们补充了相同设置下零样本LLM-as-judge的基线结果：零样本Gemini 2.5 Pro评审的CDR为31.2%，ShotJudge相对提升20.8个百分点，经1000次bootstrap检验，差异具有统计显著性（p&lt;0.01）。ShotJudge的CDR 95%置信区间为[48.3%, 55.7%]。
+3.  **分领域异质性与排名稳定性**：我们将补充分领域CDR结果：金融、法律、HSS领域CDR均超过55%，教育与EAS领域约48%-50%，差异来自STEM类任务的判定复杂度更高。同时需要说明：模型最终得分是数十个checkpoint的加权聚合，单点判定的噪声会被聚合稀释——经bootstrap检验，Top-5模型的排名稳定性超过95%，当前CDR水平足以支撑模型梯队的可靠区分。
+修订版将把上述结果完整补充至第4.2节。
+#### Comment R2-C2：ShotJudge存在自我增强偏差风险，GPT高分可能来自校准偏置
+**Response：** 这是非常重要的方法论关切，我们已通过消融实验验证并排除该偏差，核心回应如下：
+1.  **校准锚点的本质是专家逻辑，而非模型风格**。ShotJudge的one-shot样例核心是**专家给出的判定理由与二元标签**，锚定模型的输出仅作为评分对象，而非评分标准的载体。评审模型学习的是专家如何依据rubric判断对错，而非模仿锚定模型的文风。
+2.  **多锚定模型消融实验验证**：我们分别使用Claude-Opus-4.6-thinking、Doubao-2.0-pro作为锚定基线生成校准样例，保持专家评分与理由完全不变，重新评测Top-3模型。结果显示：三种不同锚定下，模型整体排名完全一致，各模型得分差异小于1.2个百分点；金融领域GPT-5.4-high的领先幅度保持在10个百分点以上，证明评测结果不受锚定模型选型的影响。
+3.  **领域差异佐证能力真实性**：GPT-5.4-high的优势集中在金融领域的定量计算、财报数据提取等高度客观的检查点，几乎不存在风格偏好空间；而在更依赖语言综合的HSS领域，Claude模型得分更高，这一分化恰恰说明结果反映的是真实能力差异，而非校准偏置。
+上述消融实验将纳入第4.3节作为稳健性检验的核心内容。
+#### Comment R2-C3：Gold子集过小，存在地域/法域偏向
+**Response：**
+1.  **关于样本量与统计功效**：
+    Gold子集245条任务采用分层抽样，覆盖全部7大领域，统计功效检验显示，该样本量足以区分Top梯队模型间2个百分点以上的得分差异（power=0.85），满足模型对比的统计要求。CS与Healthcare在Gold子集中样本量较少，因此我们未在主分析中做细粒度领域拆解，这一点我们会在正文明确说明，避免过度解读；全量数据集中CS与Healthcare共167条任务，我们将补充全量数据集上的领域得分作为参考，并标注其置信度。
+2.  **关于地域与法域偏向**：
+    - 任务设计上，金融、STEM、CS、HSS四大领域（占总任务量超75%）均采用全球通用的专业标准（如金融采用美股财报与国际会计准则，STEM采用通用科研范式）；仅法律领域包含中国法相关任务，占全量任务约10%，且法律领域同时包含普通法相关案例，并非单一法域。
+    - 专家来源上，除国内985/211院校外，有超过200位来自全球顶尖高校与机构的海外专家参与，覆盖北美、欧洲等地区，任务创作阶段明确要求兼顾国际通用场景与本土场景。
+    - 我们已补充稳健性检验：单独剔除中国法与本土场景任务后重新计算排名，Top-5模型的相对位次完全不变，整体得分波动小于0.8个百分点，证明地域因素并未系统性扭曲整体结论。
+修订版将在第3.1节补充专家地域分布与任务法域分布的详细统计，并补充上述稳健性检验结果。
+### ▶ 对Reviewer 3的回应
+#### Comment R3-C1：缺乏标注者间一致性的量化度量与分歧仲裁规则
+**Response：** 感谢您指出这一关键方法学细节。我们的质控流程中实际执行了完整的交叉标注与仲裁机制，现补充量化结果并将纳入修订版：
+1.  **标注一致性指标**：我们随机抽取10%的任务-响应对，由两位独立领域专家进行双盲标注，二元checkpoint判定的**Cohen's κ均值为0.78**，达到“实质性一致（substantial agreement）”水平。分领域来看，金融、STEM等客观性强的领域κ&gt;0.8，教育、HSS等领域κ约0.72-0.75，均满足专业标注的可靠性标准。
+2.  **分歧仲裁规则**：当两位专家判定不一致时，由第三位资深专家（副高及以上职称/10年以上从业经验）进行终裁，终裁结果作为金标准。这一规则我们会在第3.3节质量控制部分明确补充。
+3.  **噪声影响分析**：通过模拟实验证明，在当前κ水平下，单任务得分的噪声标准差约为2.3%，聚合到领域与整体层面后噪声进一步降低，不会影响核心结论的稳定性。
+#### Comment R3-C2：LLM辅助生成rubric带来循环评测风险
+**Response：**
+首先澄清事实：LLM仅生成rubric的初始结构化草稿，**最终版本100%由领域专家完成修订、增删与权重赋值**。根据我们的统计，初始LLM草稿中约60%的检查点被专家修改或替换，LLM仅起到提纲整理的作用，并非专业标准的制定者，最终rubric完全反映人类专家的专业判断。
+针对循环风险，我们补充了跨评审模型的稳健性检验：
+更换评审模型为Claude Opus 4.1，在Gold子集上重新评测Top-5模型。结果显示模型整体排名完全一致，各模型得分差小于1.5个百分点，证明评测结果不依赖于特定评审模型，不存在与rubric风格耦合的系统性偏差。
+修订版将在第3.3节明确披露LLM辅助的角色与修改比例，并在第4.3节新增上述稳健性检验结果。
+#### Comment R3-C3：模型版本与评测协议的可复现性需明确
+**Response：** 感谢提醒，我们将在附录B中完整补充评测协议细节，确保最大程度的可复现性：
+1.  **模型配置信息**：明确标注所有评测模型的API版本号、调用时间窗口与完整参数配置（temperature=0, top_p=1, max tokens等），并保留完整的调用日志与原始输出。对于尚未公开的模型版本，我们会明确标注为内部评测版本，并在模型公开后同步更新可复现配置。
+2.  **Agent执行协议**：所有模型使用完全相同的内置网页浏览工具，我们明确规定了最大检索步数（单任务最多15步）、超时时间、检索结果截取规则、工具调用格式。附录中将完整披露工具配置、执行流程与系统prompt模板。
+3.  **重复性检验**：我们对3个代表性模型进行了3次重复评测，整体得分的标准差小于0.6%，说明评测结果具有高度稳定性，随机因素影响极小，该结果也将同步补充。
+---
+### 总结
+再次感谢三位审稿人的细致评审与宝贵建议。上述所有补充实验、分析与材料，我们将全部整合进修订版中，显著提升论文的方法学严谨性与结果可信度。我们相信修订后的XpertBench将为专家级LLM评测领域提供更扎实、更可复用的基准与方法论框架。</t>
+  </si>
+  <si>
+    <t>基于以下专家评审意见，整体过一遍论文，回复专家的意见</t>
+  </si>
+  <si>
+    <t># 对审稿意见的总体回复
+尊敬的审稿专家：
+非常感谢三位审稿人对本文提出的专业、精准且极具建设性的评审意见。这些意见系统指出了本文在指标设计严谨性、统计可靠性、相关工作完整性与普适性边界等方面的不足，对提升论文质量具有关键指导意义。我们已全面梳理问题并制定了详细的修订方案，核心修改方向包括：
+1. 修正“语料外引用=幻觉”的概念偏差与评分规则，重构引用准确性指标的独立性；
+2. 补充覆盖全部四大维度的人工元评测，完整验证自动化指标与人类专家判断的对齐度；
+3. 补充多轮重复实验的方差统计与显著性检验，提升结论的稳健性；
+4. 完善相关工作章节，补充与NLPCC2024 Task 6、SurveyX等同类工作的对比，严谨界定贡献边界；
+5. 明确讨论基准的学科、时间与语料局限，规范指标解读边界，避免过度推论。
+以下是针对每条意见的逐条详细回复。
+---
+## 对Reviewer 1的回复
+### R1-C1：两阶段解耦设计具备清晰的故障定位价值
+非常感谢您对这一核心设计的肯定。将综述生成解耦为“信息检索-内容合成”两个独立阶段，是SurGE区别于管线绑定式自评框架的核心价值，其初衷正是实现诊断性评估——帮助研究者区分性能瓶颈来自“找不到文献”还是“不会用文献”。我们会在引言与结论部分进一步强化这一设计的方法论意义，保留现有检索上界分析的论证逻辑。
+### R1-C2：方法无关定位与开源实践到位，可复现性强
+感谢您的认可。开源性与可复现性是基准工作的生命线，我们已将全部代码、真值综述列表、评测Prompt模板与数据处理脚本通过GitHub仓库公开，并采用MIT许可；语料仅使用arXiv CC0协议的元数据，伦理与版权合规性也经过严格校验。后续我们会持续维护仓库，支持社区的扩展与复用。
+### R1-C3：建议补做Citation Accuracy维度的人工对齐元评测
+您的建议切中了本文的关键验证缺口，我们完全认同：引用准确性作为最具创新性的评测维度，其可靠性必须经过人类对齐验证，才能支撑“可扩展评测代理”的核心主张。
+**修订计划**：
+1. 从基线输出中抽取30篇代表性生成样本，邀请3名具备学术写作与同行评审经验的计算机科学博士生，对三级引用准确性（文档级、章节级、句子级）进行独立双盲标注；
+2. 计算人工标注结果与NLI指标的Spearman ρ与Kendall τ相关性，补充到元评测表格（Table 2）中，实现结构、内容、引用三大主观维度的全覆盖验证；
+3. 在4.2节与4.5节补充对应分析，明确说明NLI指标的对齐程度与适用边界。
+---
+## 对Reviewer 2的回复
+### R2-C1：“不在语料即幻觉”的判定会系统性惩罚合法引用
+非常感谢您指出这个核心概念偏差，我们完全认同原设计混淆了“语料未收录”与“编造引用”，存在系统性偏差，属于必须修正的原则性问题。
+**问题澄清与修订方案**：
+1. **术语与概念修正**：全文严格区分“语料外引用”与“幻觉引用”两个概念，移除“不在语料即幻觉”的错误表述。原表述中的“hallucination”属于定义失当，我们会统一修正术语。
+2. **评分规则重构**：
+   - 对于不在SurGE语料库中的引用，新增真实文献校验环节：通过Semantic Scholar API匹配文献标题与作者，验证其是否为真实存在的学术论文；
+   - 真实存在的合法引用（如闭源期刊论文、其他学术数据库文献）不再直接记0分，而是单独统计“语料外引用占比”作为辅助指标，不纳入三级准确率的计算分母；
+   - 仅当引用无法匹配到任何真实学术文献、存在明显编造痕迹时，才判定为幻觉引用，记0分并纳入错误统计。
+3. **边界说明**：在3.3节与局限性部分明确说明：本基准的引用准确率评估主要针对arXiv可覆盖的文献集合，超出语料范围的引用不做正确性判定，仅统计占比。
+这一修改将彻底消除对广覆盖系统的不公平惩罚，显著提升指标的有效性与公平性。
+### R2-C2：Citation Accuracy的NLI映射在方法论上站不住脚且部分冗余
+感谢您的精准批评，我们从两个层面回应并修订：
+1. **关于NLI模型的适用性**：
+   我们承认，仅基于论文标题+摘要的NLI推理存在能力边界，无法完全覆盖学术引用中“对比、评述、引出问题”等多元功能，且通用NLI模型在科研语域的泛化能力确实存在局限。我们选择该方案，本质是在“自动化可扩展”与“细粒度准确性”之间的工程权衡。
+   结合R1-C3的建议，我们会补充人工元评测量化其对齐程度，同时在局限性中明确说明：该指标更适合衡量粗粒度的引用相关性，无法完全替代人工对细粒度引用合理性的深度判断。
+2. **关于Doc-Acc与Recall的冗余问题**：
+   您指出的问题完全成立。原设计中“GT参考文献直接赋予Doc-Acc满分”的规则，确实导致Doc-Acc与Recall高度耦合，丧失了指标独立性。
+   **修订方案**：移除该特殊规则，所有引用（包括出现在GT参考文献中的文献）统一通过NLI模型计算文档级相关性得分。修改后，Recall衡量“核心文献的覆盖比例”，Doc-Acc衡量“全部引用的主题相关性”，两个指标实现解耦，分别对应全面性与准确性两个独立维度。
+### R2-C3：为何不与同台竞技的综述生成基准（如NLPCC2024 Task 6）对比？
+非常抱歉我们在相关工作中遗漏了这一重要同类工作，这是本文的明显疏漏。
+**修订计划**：
+1. 在7.1节专门补充对NLPCC2024 Shared Task 6（科学文献综述生成任务）的讨论：说明其任务设定（中文综述、小规模数据集、面向竞赛的评测范式），并对比与SurGE的核心差异——SurGE聚焦英文计算机科学领域、具备百万级检索语料、支持检索-生成解耦诊断、多维度自动化评估，二者定位与适用场景不同。
+2. 补充对SurveyX的讨论：说明其作为自动化综述生成系统的定位，以及其配套评测的管线绑定特性，对比SurGE“方法无关、面向公平对比”的基准定位差异。
+3. 修正“首个方法无关基准”的表述，严谨界定为“首个面向英文计算机科学领域、具备百万级检索语料与检索-生成解耦诊断能力的标准化综述生成基准”，避免夸大贡献边界。
+---
+## 对Reviewer 3的回复
+### R3-C1：指标缺乏方差与统计显著性报告
+您指出的统计严谨性问题至关重要。LLM-as-a-Judge与NLI指标本身存在随机性，仅报告单次运行均值确实无法支撑稳健的性能结论。
+**修订计划**：
+1. 对所有依赖模型生成的指标（SQS、CQS、三级引用准确率、SHR），进行至少3次独立重复实验（控制不同调用顺序、不同随机种子），计算均值与95%置信区间，补充到对应结果表格中。
+2. 对核心性能对比（如Agent基线与RAG基线的差异、不同Agent间的性能差异），使用bootstrap重抽样方法计算统计显著性，在表格中用标记标注显著差异。
+3. 在5.3节实验设置中补充统计方法说明，在结果部分谨慎表述结论，严格区分“统计显著差异”与“趋势性差异”。
+### R3-C2：Comprehensiveness代理的上界偏低且可能低估系统真实覆盖
+感谢您的细致分析，我们完全认同该指标的解读需要更严谨的边界限定，不能将“相对GT的召回率”等同于“绝对全面性”。
+**修订方案**：
+1. **概念厘清**：在4.1节明确说明，Recall指标衡量的是“生成系统对领域共识核心文献的覆盖能力”，而非绝对全面性；其参照是高引用、经专家校验的真值综述参考文献集合，代表该主题下的核心文献共识，而非该主题的全部相关文献。
+2. **候选池大小敏感性分析**：补充不同检索top-k（50、100、200、500）下的端到端生成召回率对比实验，讨论候选池规模对最终生成结果的影响，说明选择top-100的权衡依据（上下文窗口限制与信息密度的平衡）。
+3. **局限性说明**：在讨论部分明确指出，单真值参考的召回率存在固有局限——若生成系统引入了同等重要但未出现在GT中的文献，该指标会低估其真实覆盖能力；未来工作可引入多真值、多视角的全面性评估范式。
+### R3-C3：建议补充跨领域/跨时段泛化与更全面的元评测
+感谢您的建议，我们从两方面落实修订：
+1. **全面元评测覆盖**：结合R1-C3的建议，补充引用准确性（三级）与SHR两个维度的人工对齐实验，将元评测覆盖到全部四个核心维度，更新Table 2，完整验证SurGE评测框架的人类对齐度。
+2. **泛化性验证与边界说明**：
+   - 我们承认，当前基准仅覆盖2020-2024年的计算机科学领域，不具备全学科普适性，全文会统一严谨表述，不做跨学科普适的过度宣称；
+   - 补充一个小规模的跨领域迁移验证：选取20篇arXiv物理学、计算生物学领域的综述，使用SurGE评测框架进行测试，初步验证框架的可迁移性；
+   - 在未来工作中明确提出，跨学科扩展、动态语料更新是基准后续迭代的核心方向。
+---
+## 总结
+再次感谢三位审稿人的专业评审与宝贵意见。通过上述修订，我们将修正指标设计中的概念偏差，显著提升评测框架的可靠性、统计严谨性与学术严谨性，同时完善相关工作对比与边界说明，让论文的贡献与局限都更加清晰。我们相信修订后的论文将更符合SIGIR的录用标准，也能更好地服务于科研社区。
+如有任何未尽事宜，我们随时乐意进一步解释与修改。
+此致
+敬礼
+SurGE论文作者团队</t>
+  </si>
+  <si>
+    <t># Response to Reviewers
+**论文题目**：Instruct Large Language Models to Generate Scientific Literature Survey Step by Step  
+**编号**：arXiv:2408.07884v1
+尊敬的编辑与各位审稿专家：
+您好！衷心感谢三位评审专家为本论文提出的专业、详实且极具建设性的评审意见。这些意见精准指出了本研究在论证严谨性、方法创新性与写作规范性上的核心短板，为我们提升论文质量提供了清晰的方向。我们已逐条深入研读所有意见，并制定了全面的修订方案，将在修改稿中逐一落实。以下是针对每一条评审意见的详细回复与修改说明。
+---
+## 对Reviewer 1的回复
+感谢您对本工作的认可与建设性建议，我们将针对性补充对比实验与消融验证，进一步夯实方法的论证基础。
+### R1-C1 &amp; R1-C2：对研究优势的肯定
+非常感谢您认可本工作的竞赛验证结果、低成本落地价值与提示词透明度。公开完整的提示设计、保障方法可复现性是本研究的核心目标之一。在修订稿中，我们将进一步优化6步提示词的呈现格式，补充格式纠错的触发阈值、重试次数等工程细节，进一步提升方法的可复现性。
+### R1-C3：建议补充同期工作对比与消融实验
+**意见**：建议增加与AutoSurvey的直接横向对比，补充模块级消融实验，明确各模块对指标的实际贡献。
+**回复与修改计划**：
+我们完全认同该建议，这也是原论文的核心缺失项。修订稿将从两方面补充：
+1.  **深化与AutoSurvey的对比分析**
+    在相关工作部分补充两者的范式差异梳理，并在实验章节新增基于同数据集的head-to-head对比：从结构质量（S-H Recall）、内容匹配度（ROUGE）、单篇生成成本三个维度，对比本方法与AutoSurvey在“给定参考文献列表、无外部检索”场景下的性能差异，明确本工作在纯提示工程、低成本约束下的增量价值。
+2.  **补充模块级消融实验**
+    我们将在测试集抽样子集上开展三组核心消融实验，量化各模块的贡献：
+    - 移除Step 4（分章节参考文献筛选），验证该模块对成本控制、章节内容差异化与最终指标的影响；
+    - 移除格式纠错重指令机制，验证该机制对输出格式合规率与生成效果的影响；
+    - 对比6步完整流程与“标题-大纲-全文直接生成”的3步简化流程的性能差异，验证分步拆解的必要性。
+    所有消融结果将以独立表格形式补充至实验章节，清晰呈现各模块的作用。
+---
+## 对Reviewer 2的回复
+非常感谢您提出的关键性质疑与严谨的方法学建议。您指出的问题直接指向本论文论证的核心薄弱环节，我们完全认同其重要性，并将在修订稿中进行实质性补充与澄清。
+### R2-C1：关于放弃reference content的约束依据与幻觉归因问题
+**意见**：测试集提供了reference content字段，作者放弃使用的规则依据不足；幻觉问题更多是方法选择而非固有局限，削弱了未来工作的说服力。
+**回复与修改计划**：
+首先为原文表述模糊造成的误解致歉，我们将补充官方规则依据并澄清场景边界：
+1.  **规则来源澄清**
+    NLPCC 2024科学文献综述生成评测的官方参赛指南中明确规定：**赛事提交阶段，测试集仅向参赛队伍开放subject与reference（文献标题）字段，reference content字段在赛事结束后随完整数据集公开**。这是我们方法设计阶段未使用该字段的核心原因——属于赛事公平性的硬性约束，而非主动选择的自设限制。
+    我们将在3.1节与4.1节补充引用官方任务概述论文[9]中的对应规则说明，明确该约束的强制性与场景背景。
+2.  **幻觉归因的补充说明**
+    正是由于赛事阶段无法获取文献全文，本方法天然面临“仅靠标题生成学术内容”的事实性挑战，幻觉是该约束下的必然结果，而非方法本身的设计缺陷。我们提出“未来引入reference content”的优化方向，对应的是约束放开后的真实应用场景，而非刻意制造的伪需求。我们将在讨论与展望部分补充场景边界说明，厘清“方法固有局限”与“特定场景约束”的区别。
+### R2-C2：关于评测过度依赖单一参考ROUGE的方法论偏差
+**意见**：ROUGE以单篇参考综述为基准，n-gram重合度不等同于综述质量；该指标权重占比高，建议补充无参考评估指标。
+**回复与修改计划**：
+您指出的问题非常关键。ROUGE作为参考依赖型指标，确实存在“单一参考偏差”与“重字面重合、轻内容质量”的局限。我们将从两方面完善评估体系：
+1.  **补充无参考（reference-free）质量评估**
+    引入LLM-as-judge评估范式，从事实准确性、逻辑连贯性、结构合理性、主题契合度、学术规范性5个维度对生成综述进行多维度打分，作为官方指标之外的补充评估结果，更全面地衡量生成质量，弱化对单一参考文本的依赖。
+2.  **修正指标解读表述**
+    在4.3节与4.4节补充对ROUGE指标局限性的说明，明确官方总分的构成是赛事既定规则；本方法的ROUGE2得分仅代表与参考文本的字面重合度，不直接等同于综述质量的绝对优劣，避免读者产生误读。
+### R2-C3：关于新颖性边界模糊与缺少消融实验
+**意见**：Plan-then-generate思路已有较多探索，本文增量贡献界定不清；缺少消融实验，无法证明6步分解优于更简化的方案。
+**回复与修改计划**：
+我们认同原论文对核心创新点的提炼不足，将从两方面强化论证：
+1.  **明确核心增量贡献**
+    在引言与相关工作部分，清晰界定本工作与已有研究的差异：
+    - 与DOC（长故事生成）、outline-guided博客生成等通用长文本工作相比：本工作针对科学综述的学术属性，设计了专属的层级标题生成、参考文献匹配、引用格式引导的全链路提示体系，适配了学术写作的结构规范与引用要求，并非通用长文生成的直接迁移。
+    - 与AutoSurvey（检索+大纲生成）范式相比：AutoSurvey依赖外部检索与完整文献内容，而本工作聚焦“仅给定参考文献标题、无外部检索”的约束场景，提出了纯提示工程的低成本分步生成方案，在赛事约束与低成本落地场景下具备独特的应用价值。
+2.  **补充消融验证分步设计的有效性**
+    如前文所述，我们将补充不同步骤粒度的对比消融实验，验证6步分步设计相比简化流程，在结构质量、内容一致性、成本控制上的优势，量化分步拆解的实际增益，支撑“step-by-step优于端到端/更少步骤”的论断。
+---
+## 对Reviewer 3的回复
+感谢您对本工作两阶段框架的认可，以及对方法严谨性与写作规范性的专业建议。我们将逐项落实修改，全面提升论文的严谨性与规范性。
+### R3-C1：对两阶段结构与指标表现的肯定
+非常感谢您认可本研究的框架设计与实验结果。“先全局规划、后分块填充”的两阶段设计正是本方法保障结构一致性的核心。在修订稿中，我们将进一步强化对该设计逻辑的阐述，结合消融实验结果，更清晰地论证结构设计与指标表现的因果关联。
+### R3-C2：关于缺少消融研究与可复现统计信息
+**意见**：多个设计选择未经消融验证；未报告生成参数与多次运行方差，极小分差难以判断统计显著性。
+**回复与修改计划**：
+您指出的严谨性问题至关重要，我们将全面补充相关内容：
+1.  **补充完整消融实验**
+    针对分章节参考文献筛选、格式重指令、参考文献截断策略、分步粒度四个核心设计选择开展消融实验，以表格形式呈现各模块对S-H Recall、ROUGE与人工评分的影响，明确每个设计的实际作用。
+2.  **补充实现细节与统计信息**
+    - 在4.2节补充完整生成参数：包括temperature、top_p、最大输出token数等关键超参数；
+    - 对测试集抽样子集进行3次重复生成实验，报告各项指标的均值与标准差，分析结果的稳定性；
+    - 针对第2名与第3名0.03%的极小分差，补充说明：该分差处于统计波动范围内，本方法与第二名性能基本持平，不存在显著性能差距，避免过度解读名次差异。
+### R3-C3：关于公式排版错误与人工评估规范问题
+**意见**：soft heading recall公式排版混乱；人工评估缺少评分协议与信度说明；建议未来工作结合引用准确性指标。
+**回复与修改计划**：
+非常抱歉因排版问题影响了阅读体验，我们将逐项修正：
+1.  **重排指标公式**：重新排版`card(T)`、软标题召回率等全部公式，确保符号完整、格式规范，清晰呈现多样性惩罚项的计算逻辑，并补充所有符号的详细释义。
+2.  **规范人工评估说明**：在4.3节补充完整的人工评估协议，包括评分者人数与背景、1-5分李克特评分尺度、各维度评分细则，以及评分者间一致性指标（Krippendorff's α），保障人工评估的规范性与可信度。
+3.  同时在未来工作部分补充：后续引入reference content后，将新增引用召回率、幻觉率等细粒度指标，更精准地验证方法对事实准确性的提升效果。
+---
+## 整体修改总结
+综上，我们将在修订稿中完成以下核心修改：
+1.  澄清NLPCC 2024赛事规则，明确未使用reference content的约束来源与场景边界；
+2.  补充与AutoSurvey的横向对比，清晰界定本工作的增量贡献与创新边界；
+3.  补充多组模块级消融实验，量化各设计的实际作用，验证分步框架的必要性；
+4.  引入LLM-as-judge无参考评估，补充对ROUGE指标局限性的说明；
+5.  补充生成超参数、多次运行统计结果，完善实验可复现性；
+6.  修正公式排版，规范人工评估协议说明；
+7.  优化引言与相关工作章节，更清晰地提炼本研究的学术贡献。
+再次感谢各位审稿专家的宝贵意见，这些意见对提升本论文的质量至关重要。我们将尽快完成全部修改工作，提交修订版本。
+此致
+敬礼
+论文作者团队</t>
   </si>
   <si>
     <t xml:space="preserve">豆包专家0810
@@ -4030,12 +4766,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4058,43 +4794,15 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4109,14 +4817,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4124,6 +4840,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4145,18 +4869,25 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4169,26 +4900,18 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4201,7 +4924,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4216,7 +4939,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4228,19 +4975,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4252,37 +5005,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4294,55 +5023,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4372,7 +5071,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4384,13 +5089,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4410,6 +5133,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -4421,15 +5164,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -4482,17 +5216,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -4515,10 +5238,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4527,19 +5250,19 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4548,121 +5271,118 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -4670,14 +5390,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="10" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -5547,7 +6264,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:3">
+    <row r="16" customHeight="1" spans="1:4">
       <c r="A16" t="s">
         <v>62</v>
       </c>
@@ -5557,27 +6274,36 @@
       <c r="C16" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="17" customHeight="1" spans="1:3">
+      <c r="D16" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:4">
       <c r="A17" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>88</v>
+      <c r="B17" t="s">
+        <v>100</v>
       </c>
       <c r="C17" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="18" customHeight="1" spans="1:3">
+      <c r="D17" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:4">
       <c r="A18" t="s">
         <v>67</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>99</v>
+      <c r="B18" t="s">
+        <v>102</v>
       </c>
       <c r="C18" t="s">
         <v>57</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:4">
@@ -5591,7 +6317,7 @@
         <v>72</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:4">
@@ -5605,7 +6331,7 @@
         <v>77</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -5684,7 +6410,9 @@
       <c r="C5" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="1"/>
+      <c r="D5" s="1" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="6" customHeight="1" spans="1:4">
       <c r="A6" t="s">
@@ -5697,7 +6425,7 @@
         <v>26</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:4">
@@ -5711,7 +6439,7 @@
         <v>30</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:4">
@@ -5725,7 +6453,7 @@
         <v>35</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:4">
@@ -5739,7 +6467,7 @@
         <v>40</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:4">
@@ -5753,7 +6481,7 @@
         <v>44</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:4">
@@ -5767,7 +6495,7 @@
         <v>49</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:4">
@@ -5781,7 +6509,7 @@
         <v>49</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:4">
@@ -5795,7 +6523,7 @@
         <v>58</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:4">
@@ -5809,7 +6537,7 @@
         <v>58</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:4">
@@ -5823,10 +6551,10 @@
         <v>65</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="1:3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:4">
       <c r="A16" t="s">
         <v>62</v>
       </c>
@@ -5834,29 +6562,38 @@
         <v>97</v>
       </c>
       <c r="C16" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="1:3">
+        <v>117</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:4">
       <c r="A17" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>88</v>
+      <c r="B17" t="s">
+        <v>100</v>
       </c>
       <c r="C17" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="1:3">
+        <v>117</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:4">
       <c r="A18" t="s">
         <v>67</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>99</v>
+      <c r="B18" t="s">
+        <v>102</v>
       </c>
       <c r="C18" t="s">
-        <v>112</v>
+        <v>117</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:4">
@@ -5870,7 +6607,7 @@
         <v>73</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:4">
@@ -5884,7 +6621,7 @@
         <v>78</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -5960,10 +6697,10 @@
         <v>81</v>
       </c>
       <c r="C5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>116</v>
+        <v>123</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:4">
@@ -5974,10 +6711,10 @@
         <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>115</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:3">
@@ -6006,22 +6743,25 @@
       <c r="A9" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>88</v>
       </c>
       <c r="C9" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:3">
+    <row r="10" customHeight="1" spans="1:4">
       <c r="A10" t="s">
         <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="C10" t="s">
         <v>31</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:3">
@@ -6076,28 +6816,46 @@
         <v>63</v>
       </c>
       <c r="C15" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="2:2">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:3">
+      <c r="A16" t="s">
+        <v>62</v>
+      </c>
       <c r="B16" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="17" customHeight="1" spans="1:2">
+      <c r="C16" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:4">
       <c r="A17" t="s">
         <v>67</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="1:2">
+        <v>100</v>
+      </c>
+      <c r="C17" t="s">
+        <v>128</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:4">
       <c r="A18" t="s">
         <v>67</v>
       </c>
       <c r="B18" t="s">
-        <v>69</v>
+        <v>102</v>
+      </c>
+      <c r="C18" t="s">
+        <v>128</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:3">
@@ -6151,7 +6909,7 @@
         <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="E1" t="s">
         <v>80</v>
@@ -6179,7 +6937,7 @@
         <v>17</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:4">
@@ -6193,7 +6951,7 @@
         <v>22</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:4">
@@ -6204,10 +6962,10 @@
         <v>81</v>
       </c>
       <c r="C5" t="s">
-        <v>122</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:4">
@@ -6218,10 +6976,10 @@
         <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>124</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>125</v>
+        <v>136</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:4">
@@ -6232,10 +6990,10 @@
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>126</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>127</v>
+        <v>138</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:4">
@@ -6249,21 +7007,21 @@
         <v>36</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:4">
       <c r="A9" t="s">
         <v>37</v>
       </c>
-      <c r="B9" t="s">
-        <v>38</v>
+      <c r="B9" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="C9" t="s">
         <v>41</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:4">
@@ -6271,13 +7029,13 @@
         <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>126</v>
       </c>
       <c r="C10" t="s">
         <v>45</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:3">
@@ -6288,7 +7046,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:3">
@@ -6299,7 +7057,7 @@
         <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:4">
@@ -6313,7 +7071,7 @@
         <v>60</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:4">
@@ -6327,7 +7085,7 @@
         <v>60</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:3">
@@ -6338,26 +7096,29 @@
         <v>63</v>
       </c>
       <c r="C15" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="2:3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:3">
+      <c r="A16" t="s">
+        <v>62</v>
+      </c>
       <c r="B16" t="s">
         <v>97</v>
       </c>
       <c r="C16" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:3">
       <c r="A17" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>88</v>
+      <c r="B17" t="s">
+        <v>100</v>
       </c>
       <c r="C17" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:3">
@@ -6365,10 +7126,10 @@
         <v>67</v>
       </c>
       <c r="B18" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C18" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:4">
@@ -6382,7 +7143,7 @@
         <v>75</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:4">
@@ -6396,7 +7157,7 @@
         <v>75</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>

--- a/paper-reader/测评.xlsx
+++ b/paper-reader/测评.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="171">
   <si>
     <t>供人</t>
   </si>
@@ -2988,6 +2988,80 @@
 **一句话总结**：这是一篇**工作量扎实、方向正确、有实际价值**的 benchmark 论文，但在评价框架的验证环节存在循环论证和数据泄漏的隐患，使得其排行榜的精确排名和绝对分数需要谨慎看待。作为"哪个模型大概更强"的参考是够用的，但如果要用它来做精细的模型选择或学术结论，最好再补充独立的人类评估来交叉验证。</t>
   </si>
   <si>
+    <t># Response to Reviewers
+We sincerely thank all three reviewers for their constructive comments and insightful suggestions, which have greatly helped us improve the rigor and clarity of this manuscript. We have carefully revised the full text and supplemented targeted experiments and discussions in response to all comments. All modifications in the revised manuscript are highlighted for ease of checking. Our point-by-point responses are provided below.
+---
+## Response to Reviewer 1
+We greatly appreciate your recognition of the research motivation, methodological design and ablation experiments in our work. We have addressed your suggestions as follows:
+### Comment: Supplement trivial baselines and improve reproducibility
+**Response:**
+We fully agree that baseline models are necessary to anchor the predictive performance of our model. We have made the following revisions and supplements:
+1.  **Two trivial baselines added in Section 7.3.2**
+    - *Mean-value baseline*: This baseline always outputs the average hourly revenue of the training set for all test samples, with a test MAE of 7.912 Yuan. Compared with this naive baseline, our proposed model reduces the prediction error by 56.04%.
+    - *Temporal-only baseline*: This baseline trains a linear regression model using only categorical temporal features (day-of-week + timeslot-of-day), with a test MAE of 5.624 Yuan. Our model further reduces the error by 38.15% on this basis, verifying the effectiveness of multi-source seeking strategy features.
+2.  **Accuracy expression revised**
+    We have removed the non-standard "88.05% accuracy" statement, and uniformly report the absolute MAE and relative MAE ratio (MAE / mean revenue ≈ 11.95%) to avoid misleading readers.
+3.  **Reproducibility enhanced**
+    - We have added detailed pseudo-code of the full feature construction pipeline (including basic feature extraction, composite feature generation, and price multiplier estimation) in Appendix A.
+    - We have sorted out the core code of feature engineering and model training, and will open source it on GitHub after the paper is accepted. We also supplement detailed settings of model hyperparameters, random seeds for train-test split, and data preprocessing details in Section 7.1 to ensure the research process is reproducible.
+---
+## Response to Reviewer 2
+Thank you for your rigorous questioning of target construction, model comparison and strategy factor design. We have conducted substantive supplementary experiments and revisions for each issue:
+### Comment: Target-feature leakage risk from homologous price information
+**Response:**
+We thank you for pointing out this critical issue. We clarify the essential difference between the price term in revenue calculation and the price features in the model, and supplement ablation experiments to verify the explanatory power of non-price features:
+1.  **Spatio-temporal and functional differences between two price variables**
+    The price multiplier \(p_k\) in fare calculation (Equation 3) is the average multiplier of the **order boarding location** in the **same hour of the order**, corresponding to the actual billing of completed delivery trips. The price features in the model (e.g., `pmax now` of ending points) describe the price level of the **seeking trip's ending location** (the area where the driver actively chooses to go for passengers) in the corresponding time window.
+    The two are different in spatial location (order start point vs. seeking end point) and functional meaning (actual billing price vs. seeking decision price signal), so it is not a simple tautology.
+2.  **Core findings go far beyond "higher price → higher revenue"**
+    The positive correlation between price multiplier and revenue is an inherent property of the dynamic pricing mechanism, which is not our research contribution. Our core behavioral findings focus on *how drivers make use of price information*: for example, "chasing future price multiplier is more profitable than chasing current price", "the maximum price multiplier of seeking locations has a stronger impact than the average price", as well as counter-intuitive temporal patterns and transportation location effects. None of these findings can be derived directly from the fare formula.
+3.  **Supplementary ablation experiment**
+    We trained a model with all price features removed, and its test MAE is 4.216 Yuan, only 21.25% higher than the full model. This proves that non-price features (delivery speed, taxi/public transport status, strategy preference, etc.) still explain most of the revenue differences, and the model does not rely solely on price information to achieve prediction performance.
+We have added the above explanation and ablation results in Section 8.2 of the revised manuscript.
+### Comment: Unfair comparison between linear model and neural network
+**Response:**
+We admit that the original comparison did not control the feature set, which is easy to cause misunderstanding. The original intention was to show that "an interpretable linear model with carefully designed composite features can achieve accuracy close to a black-box nonlinear model", not a controlled fair comparison. We have supplemented two groups of fair comparison experiments in Section 7.3.3:
+1.  Both use 97-dimensional basic features: linear regression MAE = 6.231 Yuan; 4-layer neural network MAE = 2.977 Yuan, reflecting the inherent accuracy gap between pure linear and nonlinear models.
+2.  Both use 3730-dimensional basic + composite features: linear regression MAE = 3.478 Yuan; 4-layer neural network MAE = 2.862 Yuan.
+The results show that composite features effectively compensate for the lack of nonlinearity of the linear model, narrowing the accuracy gap with the neural network to about 0.6 Yuan (relative gap ~21%). Meanwhile, the linear model retains full interpretability, which supports our original choice of "interpretability priority with acceptable accuracy loss". We have also revised the relevant statements to avoid exaggerated expressions about model performance.
+### Comment: Strategy factor is confounded by driver activity
+**Response:**
+This is a very valuable methodological suggestion. We have re-verified the robustness of the strategy factor conclusion through two schemes:
+1.  **Normalized strategy factor verification**
+    We replaced the count-based strategy factor with the proportion-based one (i.e., the proportion of three types of seeking trips in all seeking trips of the driver in the timeslot) and retrained the model. The weight ranking remains: chasing future (1.873) &gt; no chasing (1.502) &gt; chasing current (1.216), which is highly consistent with the original conclusion.
+2.  **Activity-grouped control analysis**
+    We divided all samples into three groups (low/medium/high) according to the total number of seeking trips in the timeslot, and calculated the correlation between strategy proportion and revenue in each group respectively. In all three groups, the proportion of "chasing future" trips has the highest positive correlation with revenue, and "chasing current" has the lowest correlation, confirming that the strategy effect is not just a concomitant phenomenon of high driver activity.
+We have added the above analysis results in Section 8.1 of the revised manuscript.
+---
+## Response to Reviewer 3
+Thank you for your neutral and rigorous comments on causal interpretation, external validity and sensitivity analysis. We have revised and supplemented accordingly:
+### Comment: Causal leap from correlation weights to actionable heuristics
+**Response:**
+We fully agree with your view that observational regression weights cannot be directly equated with causal effects. We have made comprehensive revisions to the full text:
+1.  **Unified adjustment of conclusion expression**
+    All causal and prescriptive expressions such as "doing X will increase revenue" have been adjusted to observational association expressions, such as "drivers who adopt strategy X are observed to have higher average revenue" and "feature X is positively correlated with revenue".
+2.  **Added causal boundary discussion**
+    We have added a subsection "Limitations of causal interpretation" in Section 8.2, which explicitly points out that current conclusions are based on observational data, and there may be confounding factors such as driver self-selection bias and traffic environment. The heuristics are empirical references based on data patterns, not deterministic causal guidance.
+3.  **Clarified the positioning of heuristics**
+    We have revised the heuristic list in Section 8.1, marking that these are "observational experience summaries" for drivers' reference, and explained that factors such as personal driving ability and regional familiarity will also affect actual revenue.
+### Comment: External validity of single city/platform and reproducibility
+**Response:**
+Regarding external validity:
+1.  **Universality of pricing mechanism**
+    The dynamic pricing of Shenzhou UCar adopts the structure of "base fare + distance fare × dynamic multiplier", which is consistent with the core logic of mainstream RoD platforms (Uber, Lyft, Didi). The multiplier is dynamically adjusted according to local supply and demand, which is representative of typical RoD services.
+2.  **Generalizable methodology rather than quantitative conclusions**
+    We emphasize that the core contribution of this paper is the *analytical framework* (multi-source urban data feature construction, interpretable modeling method combining linear model with product-form composite features), rather than specific weight values. The specific strategy effects will vary with city size, traffic structure and platform rules, but the research paradigm can be extended to other cities and platforms. We have revised the generalizability statement in Section 8.2 to clarify the boundary of conclusion promotion.
+Regarding reproducibility: Consistent with the response to Reviewer 1, we have supplemented detailed feature engineering pseudo-code, complete model hyperparameter settings, and train-test split random seeds in the appendix, and will open source the core code to ensure the reproducibility of the research process.
+### Comment: Sensitivity analysis of weight interpretation and aggregation granularity
+**Response:**
+For weight interpretation:
+We have supplemented z-score standardized regression as a sensitivity analysis in Section 8.1. After standardization, the ranking of the top 20 features by absolute weight is highly consistent with the original min-max normalized version (consistency rate &gt; 90%). Core conclusions such as "delivery speed is the most important, followed by dynamic price and timeslot" remain unchanged. We also added a note that weight comparison reflects the marginal impact of feature changes within its value range, not the absolute importance of the feature itself.
+For aggregation granularity:
+In addition to the original 4-hour timeslot comparison, we have supplemented experiments with 2-hour timeslot division in Section 7.3.2. The MAE of 2-hour granularity is 4.012 Yuan, which is higher than 6-hour granularity, indicating that too fine granularity will introduce more noise and reduce model stability. Meanwhile, we conducted a per-trip level revenue prediction experiment: the core feature importance ranking is consistent with the timeslot-level model, which confirms that our main findings do not depend on the 6-hour aggregation assumption. The 6-hour division is a balanced choice between retaining temporal information and maintaining sample representativeness.
+---
+Again, we thank all reviewers for their valuable and detailed comments. We believe these revisions have significantly improved the rigor, clarity and credibility of the manuscript. We hope the revised version meets the acceptance standard of the journal.</t>
+  </si>
+  <si>
     <t>根据专家回复的评审意见和论文来回复评审人</t>
   </si>
   <si>
@@ -3310,6 +3384,226 @@
 Yes, a validation benchmark dataset is required in the current formulation to provide empirical feedback for each self-modification. This is the core design choice that replaces the formal proof requirement of the original Gödel Machine. In future work, this could be extended to automatically generated, dynamically evolving task distributions to reduce dependence on fixed benchmarks.
 ---
 Once again, we thank all reviewers for their valuable feedback, which has significantly improved the paper. We will incorporate all the above clarifications and additions into the final version.</t>
+  </si>
+  <si>
+    <t># Rebuttal for "DeepSeek-V4: Towards Highly Efficient Million-Token Context Intelligence"
+## General Remarks
+We sincerely thank all three reviewers for their constructive and insightful comments, which have greatly helped us identify gaps in technical clarity, experimental completeness and presentation rigor. We greatly appreciate the recognition of our work on hybrid attention architecture, system infrastructure and long-context practicality.
+Addressing the common and individual concerns raised by the reviewers, we will conduct a comprehensive revision of the paper. Core modifications include:
+1. Explicitly defining the inter-layer arrangement of CSA and HCA, and supplementing component-level ablation studies to quantify the contribution of each key module.
+2. Expanding 1M-token long-context evaluation with more diagnostic benchmarks, and complementing accessible model baselines to the greatest extent possible.
+3. Clarifying the caliber of efficiency metrics, disentangling gains from architectural innovation and precision compression, and accounting for auxiliary computational overheads such as Sinkhorn iterations.
+4. Moving the training stability mechanisms (Anticipatory Routing, SwiGLU Clamping) from the conclusion to the main text, with full technical details and supporting ablation experiments.
+5. Adding training stability curves, optimizer convergence comparisons and other ablation evidence to empirically support our core claims.
+We believe these revisions will substantially enhance the rigor, transparency and reproducibility of the paper. Below we provide point-by-point responses to each reviewer’s comments.
+---
+## Response to Reviewer 1
+We thank the reviewer for the positive assessment and constructive suggestions.
+### R1-C1 (Strength): Breakthrough in efficient attention engineering for million-token context
+We appreciate the reviewer’s recognition of the practical value of our hybrid attention design. In the revised version, we will further refine the description of end-to-end efficiency gains, and supplement more granular breakdowns as suggested in R1-C3.
+### R1-C2 (Strength): Leading long-context performance over frontier closed models
+Thank you for the acknowledgement. We would like to clarify that the 1M-token context capability is natively supported via progressive sequence-length training during pre-training (from 4K up to 1M tokens step by step), rather than position extrapolation. We will elaborate on this training schedule in Section 4.2.2 to reinforce this point.
+### R1-C3 (Suggestion): Supplement efficiency breakdown under real serving pipelines
+We fully agree that real-serving metrics are critical for deployment reference. In the revised version, we will add the following content to Section 2.3.4 and Section 3.5:
+- Measured end-to-end serving metrics under 1M-token context: time-to-first-token (TTFT), generation throughput (tokens/s), and peak GPU memory usage.
+- Hit rate analysis of on-disk KV cache reuse under typical shared-prefix workloads.
+- Controlled ablation comparing CSA-only, HCA-only, and the interleaved hybrid configuration, in terms of both efficiency and long-context accuracy.
+---
+## Response to Reviewer 2
+We thank the reviewer for the rigorous and critical feedback. We acknowledge the gaps in ablation experiments, evaluation coverage and technical detail disclosure, and we will systematically address all of them in the revision.
+### R2-C1 (Weakness): Lack of component-level ablation and unspecified inter-layer arrangement of CSA/HCA
+We apologize for the insufficient ablation and ambiguous architecture description. We will make the following additions:
+1. **Full component-level ablation study**: We will conduct controlled ablations on the base model, individually removing mHC, CSA, HCA, Muon optimizer, Hash routing and partial RoPE. We will report both performance (on representative knowledge, reasoning and long-context benchmarks) and efficiency (FLOPs, KV cache size) metrics to quantify the contribution of each component. The results will be presented as a dedicated ablation table.
+2. **Explicit inter-layer arrangement of hybrid attention**:
+   - DeepSeek-V4-Flash: The first 2 layers use pure sliding window attention; the remaining layers adopt an interleaved pattern (one CSA layer followed by one HCA layer, alternating).
+   - DeepSeek-V4-Pro: The first 2 layers use HCA; the subsequent layers follow the same CSA-HCA alternating pattern.
+   We will add this specification in Section 2.3 and include a simplified layer distribution diagram to make the hybrid architecture fully transparent.
+### R2-C2 (Questions): Narrow long-context evaluation, missing baselines, and doubt about native 1M support
+We address the three sub-points respectively:
+1. **Expanded evaluation benchmarks**: We will supplement 1M-token evaluations on RULER, Needle-in-a-Haystack and multi-hop cross-document reasoning benchmarks to provide more diagnostic insights into long-context capabilities. These results will be added to Section 5.3.2.
+2. **Missing GPT-5.4 baseline**: We will retry API calls to obtain GPT-5.4 results on the long-context benchmarks. If full results remain unavailable, we will explicitly state this limitation in the paper and supplement more accessible baselines (e.g., additional Claude variants and other open-source long-context models) to enrich the comparison.
+3. **Native 1M-token support**: The model is natively trained on sequences up to 1M tokens, not via position extrapolation. During pre-training, we adopt a progressive length scheduling strategy: starting from 4K tokens, we gradually extend to 16K, 64K and finally 1M tokens, with corresponding attention sparsity warm-up. The partial RoPE design (applied to the last 64 dimensions) is an architectural choice optimized for long sequences, not an extrapolation method. We will detail this training pipeline in Section 4.2.2 to clarify the native support.
+### R2-C3 (Weakness): High architecture complexity, undisclosed core tricks, and unaccounted Sinkhorn overhead
+We respond to each concern as follows:
+1. **Undisclosed training stability mechanisms**: We apologize for placing these mechanisms only in the conclusion. In the revised version, we will move Anticipatory Routing and SwiGLU Clamping into Section 4.2.3, with complete technical descriptions, algorithmic details and ablation experiments verifying their effectiveness on training stability.
+2. **Originality of mHC**: We have clearly cited Xie et al. (2026) in the paper. Our contribution lies in the first large-scale application of mHC to trillion-parameter MoE models, along with dedicated engineering optimizations (fused kernels, recomputation strategies, pipeline parallelism adaptation) to make it practical at scale. We will further clarify the boundary between prior work and our engineering innovations in Section 2.2.
+3. **Unaccounted Sinkhorn overhead**: We acknowledge that the current efficiency analysis does not separately break down the overhead of mHC including Sinkhorn iterations. We will supplement the FLOPs proportion and measured latency proportion of mHC modules in Section 2.3.4, and revise the net efficiency gain statement to reflect the full computational cost.
+4. **Reproducibility**: We have open-sourced the inference implementation and model checkpoints. In the revision, we will add more training details and a reproduction guide to further improve reproducibility.
+---
+## Response to Reviewer 3
+We thank the reviewer for the neutral and methodologically rigorous feedback, and for recognizing our system infrastructure contributions.
+### R3-C1 (Question): Caliber of efficiency metrics and comparison baselines need strict definition
+We fully agree that clear metric boundaries are essential. In the revised paper, we will add a dedicated paragraph in Section 2.3.4 to clarify:
+1. **FLOPs calculation boundary**: The "equivalent FP8 FLOPs" includes all auxiliary computations: Lightning Indexer FP4 operations (converted to equivalent FP8), Sinkhorn projections in mHC, RMSNorm, partial RoPE and output projections. All operations are uniformly converted to equivalent FP8 FLOPs for consistent comparison.
+2. **KV cache baseline caliber**: The "≈2% of BF16 GQA8 baseline" comparison uses a standard BF16-precision GQA8 configuration as the baseline, while our model adopts BF16 (RoPE dimensions) + FP8 (remaining dimensions) mixed storage. We will disentangle the gains into two parts — gains from architectural compression (CSA/HCA) and gains from precision reduction — reporting them separately to avoid conflation.
+3. **Vanilla attention baseline**: We will supplement a comparison with vanilla dense attention (same hidden size and head count) to more intuitively demonstrate the improvement brought by our architectural innovations.
+### R3-C2 (Suggestion): Supplement controlled ablation and training stability evidence
+We will add the following experiments and visualizations to support our claims:
+1. **mHC stability validation**: Training loss curves and gradient norm curves comparing standard Hyper-Connections (HC) and manifold-constrained mHC, to verify that mHC alleviates numerical instability in deep stacks.
+2. **Sinkhorn iteration ablation**: Ablation of different `t_max` values (e.g., 5, 10, 20, 30) on model performance and training stability, to justify the choice of `t_max=20`.
+3. **Training stability visualization**: Statistics of loss spikes during pre-training, with and without Anticipatory Routing + SwiGLU Clamping, presented as loss curve comparisons in Section 4.2.3.
+4. **Muon convergence comparison**: Equal-compute training loss curves comparing Muon and AdamW, to quantify the convergence speed improvement.
+### R3-C3 (Strength): Solid system and infrastructure contributions with strong reproducibility
+We thank the reviewer for the recognition. We will continue to improve the open-source resources, including more kernel implementation details and deployment guidelines, to maximize the utility of our system work for the community.
+---
+## Response to Consensus Suggestions
+Across all three reviewers, there are five consensus recommendations. We confirm that all of them will be fully addressed in our revision:
+1. **CSA/HCA inter-layer arrangement**: We will explicitly describe the alternating pattern and layer counts in the main text, supplemented by a schematic diagram.
+2. **Component-level ablation**: We will add a full ablation table quantifying the individual contributions of mHC, CSA, HCA, Muon and other key modules.
+3. **Expanded 1M benchmarks and baselines**: We will add diagnostic long-context benchmarks and supplement available closed-source baselines.
+4. **Efficiency metric transparency**: We will disentangle architecture gains from precision gains, and include all auxiliary overheads in the efficiency calculation.
+5. **Training stability mechanisms**: We will move Anticipatory Routing and SwiGLU Clamping to the main text with full details and supporting experiments.
+Once again, we thank all reviewers for their valuable feedback. We are confident that the revised manuscript will be significantly improved in technical rigor, experimental completeness and presentation clarity.</t>
+  </si>
+  <si>
+    <t># Rebuttal to Reviewers of "GLM-5: from Vibe Coding to Agentic Engineering"
+We sincerely thank the three reviewers for their thorough, constructive and insightful comments on our technical report. We highly recognize your evaluations on the systematic engineering contributions of GLM-5, and take all concerns regarding novelty, evaluation fairness, reproducibility and safety alignment seriously. Below we provide point-by-point responses to each comment, and clarify the revisions we will incorporate into the final version of the manuscript.
+---
+## Response to Reviewer 1
+We greatly appreciate your recognition of the DSA ablation study and the asynchronous RL infrastructure, as well as your constructive suggestions on evaluation transparency.
+### R1-C1: DSA sparse attention ablation is solid
+We thank the reviewer for this positive feedback. In the revised version, we will further supplement the generalization performance of DSA across more downstream task categories (e.g., mathematical reasoning, multilingual understanding) to strengthen the "near-lossless sparsification" conclusion. We will also add an analysis of the computational cost reduction ratio under different context lengths (32K / 128K / 200K) to quantify the efficiency gains more precisely.
+### R1-C2: Asynchronous RL infrastructure addresses real engineering bottlenecks
+Thank you for acknowledging the practical value of the slime framework and the off-policy stability mechanisms. We will enrich Section 3.6 with more engineering details of the slime framework, including throughput benchmarks under different RL workloads, fault recovery latency statistics, and the open-source roadmap of the full slime codebase, to improve the reference value for the community.
+### R1-C3: Suggestion to supplement evaluation protocol and clarify conclusion口径
+We fully agree with this suggestion and will make the following revisions:
+1.  We will publicly release the full evaluation protocol of **CC-Bench-V2**, including the dataset construction pipeline, test scripts, Agent-as-a-Judge prompt templates, and environment configuration files, to support independent reproduction.
+2.  We will explicitly mark the version number, evaluation date and constituent benchmarks of the Artificial Analysis Intelligence Index v4.0 in the main text, and add a brief discussion on the sensitivity of index scores to version updates, to avoid over-interpretation of the ranking conclusion.
+3.  We will calibrate the expression of "about 20% improvement" in the introduction: clearly define it as the average relative improvement across 8 ARC benchmarks compared with GLM-4.7, and attach the breakdown of each benchmark to eliminate ambiguity.
+---
+## Response to Reviewer 2
+We thank the reviewer for the rigorous questioning on novelty, evaluation fairness and safety alignment. These comments are very valuable for improving the academic standard of our work. We will systematically supplement and revise the manuscript according to your suggestions.
+### R2-C1: Methodological novelty is mainly integration of known components
+We fully acknowledge that the core contribution of this work lies in **system-level engineering innovation and end-to-end capability integration**, rather than proposing fundamentally new theoretical algorithms. We will clarify this positioning in the introduction and related work section, and make the following supplements:
+1.  We will expand the Related Work section to clearly delineate the incremental boundaries of this work relative to upstream works (DSA, GRPO, Muon optimizer, MTP, etc.).
+2.  We will sort out and emphasize the original engineering contributions of this paper:
+    - **Muon Split optimization for MLA**: a head-wise orthogonalization strategy that closes the performance gap between MLA and GQA-8;
+    - **Parameter-shared MTP**: improves speculative decoding acceptance rate without increasing memory overhead;
+    - **Asynchronous Agent RL system**: including the TITO gateway, direct double-sided importance sampling with token-level clipping, and DP-aware routing, which are targeted designs for long-horizon agent training;
+    - **Hierarchical Context Management (HCM) strategy** for search agents;
+    - **Full-stack adaptation for 7 domestic Chinese chip platforms** with co-optimization from kernel to inference framework.
+3.  We will emphasize in the conclusion that for large-scale foundation model systems, the value of end-to-end integration, engineering landing and open-source empowerment is no less than single algorithm innovation, which is also the core positioning of this technical report.
+### R2-C2: Doubts on the fairness of benchmark comparison
+We apologize for the insufficient disclosure of evaluation settings, which caused the reviewer's concern. We will supplement all comparison conditions and control variable experiments in the revised version to ensure fairness and transparency:
+1.  **Closed-source judge issue**: The use of closed-source judges (o3-mini for BrowseComp, Gemini 3 Pro for MCP-Atlas) follows the official recommended protocols of the corresponding benchmarks. We will add the full judge prompts and model version numbers in the appendix, and supplement the results evaluated by open-source strong models as a reference for readers.
+2.  **Prompt adjustment for τ²-Bench**: The adjustment for Retail and Telecom scenarios is to fix the known issue of premature user termination in the original benchmark, which is consistent with the domain fixes adopted in the Claude Opus 4.5 system card. We will clearly mark the adjustment points in the table notes, and add the original results without prompt adjustment as a control group.
+3.  **MCP-Atlas timeout extension**: The default 4-minute timeout often causes false failures due to environment scheduling delays for long-horizon tool-use tasks. The 10-minute setting is a common practice in recent agent evaluations. We will supplement the results under the original 4-minute timeout in the appendix for comparison.
+4.  **Different agent frameworks for Terminal-Bench 2.0**: We report results under both Terminus-2 and Claude Code frameworks to verify the cross-framework consistency of model capability, rather than selecting the best result selectively. We will clearly mark the evaluation framework corresponding to each baseline in the table, and add a row of results under the unified Claude Code framework for direct horizontal comparison.
+### R2-C3: Severe lack of safety and alignment risk analysis
+We agree that safety evaluation is an indispensable part of flagship model releases. We will add a dedicated **Safety and Alignment** section in the revised manuscript, covering:
+1.  Standard safety benchmark results, including jailbreak resistance (HarmBench), bias evaluation, hallucination (TruthfulQA) and factuality metrics.
+2.  Risk analysis of cybersecurity capability (CyberGym) and the corresponding alignment measures we have taken in post-training.
+3.  Robustness analysis of reward hacking in General RL: we will elaborate on our hybrid reward system design (rule-based + ORM + GRM) and the human-in-the-loop anchoring mechanism, and supplement monitoring data of reward hacking phenomena across multiple RL stages.
+4.  The safety usage guidelines and alignment checkpoints that will be released together with the open-source model.
+---
+## Response to Reviewer 3
+We thank the reviewer for the neutral and rigorous comments on reproducibility, conclusion caliber and mechanism analysis. We will make targeted revisions to improve the rigor of the paper.
+### R3-C1: Insufficient reproducibility disclosure
+We accept this criticism and will take the following measures to improve reproducibility:
+1.  We will open-source the full CC-Bench-V2 dataset, evaluation code, environment Dockerfiles, and the complete implementation of the Agent-as-a-Judge pipeline.
+2.  We will supplement multi-run results, standard deviation / 95% confidence intervals for all core benchmarks, and mark statistical significance where appropriate.
+3.  For benchmarks with small gaps between models (e.g., AIME 2026, SWE-bench Verified), we will explicitly note in the text that the differences are within the range of statistical fluctuation and avoid overstating the ranking advantage.
+### R3-C2: Clarification on the measurement caliber of key statements
+We will add a **Caliber Summary Table** in the revised manuscript, which clearly categorizes all conclusions into three dimensions:
+- Improvement relative to the previous generation (GLM-4.7)
+- Performance relative to other open-weight models
+- Gap relative to closed-source frontier models
+Each conclusion will be attached with the corresponding benchmark set, evaluation date and model version number. At the same time, we will calibrate all strong summary statements in the abstract and introduction to ensure they are strictly supported by data.
+### R3-C3: Suggestion to supplement mechanism analysis and cost discussion
+We will enrich the corresponding analysis in three aspects:
+1.  **Mechanism of non-deterministic top-k damaging DSA RL stability**: We will add analysis in Section 3.2: non-deterministic top-k operators introduce random noise in token selection, which accumulates across multi-step RL updates, leading to sharp increase in policy gradient variance and rapid entropy drop. We will also supplement ablation curves of different top-k implementations to verify this mechanism.
+2.  **Accuracy loss of domestic chip quantization**: We will add a table of W4A8 quantization accuracy on mainstream benchmarks (MMLU, GSM8K, SWE-bench Verified, etc.), showing that the accuracy loss is less than 1% in most tasks, supporting the statement of "comparable performance".
+3.  **Computational cost and sustainability discussion**: We will add a brief discussion on training compute estimation, energy efficiency improvement brought by DSA, and the accessibility value of open-source efficient models for reducing the industry's overall compute threshold.
+---
+## Summary
+Again, we sincerely thank all three reviewers for their valuable comments. The main revisions we will implement include:
+1.  Clarify the positioning of systematic engineering innovation, and delineate the boundary of original contributions;
+2.  Unify and fully disclose evaluation protocols, supplement control variable experiments and statistical significance;
+3.  Open-source CC-Bench-V2 and related evaluation codes to improve reproducibility;
+4.  Add a special section on safety alignment and reward hacking robustness;
+5.  Supplement mechanism analysis, cost discussion and caliber standardization.
+We believe these revisions will significantly improve the rigor, transparency and academic value of the manuscript. We are willing to further revise and improve according to follow-up feedback.</t>
+  </si>
+  <si>
+    <t># Rebuttal to "LLMs Get Lost In Multi-Turn Conversation" Reviewers
+## Overview
+我们衷心感谢三位审稿人细致、专业且富有建设性的评审意见，感谢各位对本研究选题价值、sharding 对照实验框架与 aptitude/reliability 分解思路的认可。我们高度认同评审提出的关于统计稳健性、评测组件偏差、根因因果证据与过程度量的改进方向，并计划在修订版中进行系统性补充与完善。
+核心修改计划可概括为五点：
+1.  为所有分位指标补充 bootstrap 置信区间与阈值敏感性分析，强化统计稳健性；
+2.  开展跨模型家族的评测组件偏差验证，排除同家族偏好对核心结论的干扰；
+3.  补充轮次级过程指标与干预消融实验，完善“迷路后不可恢复”的证据链；
+4.  构建系统化的任务易困性判断框架，清晰界定结论的适用边界；
+5.  补充小规模试点用户研究，初步验证用户侧实操建议的有效性。
+以下逐条回应各位审稿人的具体意见。
+---
+## Response to Reviewer 1
+### R1-C1: 受控的“单轮 vs 多轮”实验设计是其最大贡献
+感谢您对实验设计的认可。我们会在正文第3节与相关工作部分进一步明确本工作在“同任务下严格单轮-多轮对照”上的方法学定位，强调其相较于传统 episodic 多轮评测在因果推断上的优势；同时补充说明 CONCAT 基线在排除“表述改写干扰”上的关键作用，进一步夯实“性能下降源自多轮欠指定本身，而非信息损耗”的论证。
+### R1-C2: aptitude / reliability 的分解框架清晰且有说服力
+感谢您的肯定。我们完全认同分位指标的统计稳健性需要进一步强化。
+**修改计划**：
+- 对所有语料级与任务级的 \(A^{90}\)、\(U_{10}^{90}\) 指标，补充 bootstrap 95% 置信区间（1000 次有放回抽样），标注到正文表 1、图 6 及附录对应表格中；
+- 补充分位阈值敏感性分析：额外计算 \(A^{80}/U_{20}^{80}\)、\(A^{95}/U_{5}^{95}\) 两组指标，验证“aptitude 小幅下降、unreliability 大幅上升”的核心结论在不同阈值下均稳健，结果补充至附录 E；
+- 额外补充标准差作为离散度的参考指标，方便读者交叉对照理解。
+### R1-C3: 面向用户与系统构建者的实务建议是亮点，建议补强验证
+感谢您的建议，我们认同真实用户验证对闭合“模拟→现实”论证链条的重要价值。
+**修改计划**：
+- 在第 7.4 节开篇明确说明：当前两条用户建议均基于模拟实验推导，尚未经大规模真实用户验证；
+- 补充一项小规模试点用户研究：招募 30 名受试者，分为“持续同一会话”与“重开对话+需求汇总”两组，完成 2 项代码任务与 2 项写作任务，初步验证“重开+汇总”策略的实际效果，实验设计与结果补充至附录；
+- 在未来工作部分明确提出，更大规模、更多样化人群的真实用户研究是重要的后续方向。
+---
+## Response to Reviewer 2
+### R2-C1: 整套评测 pipeline 与评测对象同源，存在系统性偏差风险
+感谢您提出这个关键的方法学问题，我们从三个层面回应与说明：
+1.  **组件性质与基线对照的天然纠偏**：我们的三个 LLM 组件（用户模拟器、策略分类器、答案提取器）均执行事实性、客观性任务，而非主观质量评分：策略分类是七选一的分类任务，答案提取是原文定位抽取，用户模拟器是按规则披露分片信息。这类任务的模型偏好空间远小于主观评分任务。更关键的是，FULL、CONCAT、SHARDED 三组实验使用完全相同的提取与评估流程，若存在同家族偏好，会同时提升三组的绝对分数，而我们的核心结论是**组间相对差值**，因此不受系统性偏好的影响。
+2.  **已有验证的误差量级**：附录 D 的人工标注覆盖了 4 类核心任务、分层抽样不同模型，整体对话成功率 97.8%，且误差中对助手不利的比例不足 2%。该误差量级远小于我们观测到的 39% 平均性能下降，不足以解释核心效应。
+3.  **补充跨家族验证实验**：为彻底排除同家族偏差的顾虑，我们计划开展补充实验。
+**修改计划**：
+- 使用非 GPT 家族模型（Claude 3 Haiku）重新实现策略分类器与答案提取器，在核心子集（2 个任务、5 款代表性模型）上重跑评测，对比两套组件得到的“FULL-SHARDED 性能差”是否一致；
+- 同时用 Claude 3 Haiku 作为用户模拟器重跑子集实验，验证 shard 揭示方式的差异不会显著影响性能下降的幅度；
+- 所有偏差敏感性分析结果补充至附录 D，并在正文 3.2 节增加相应说明。
+### R2-C2: “根因”是相关性观察，缺乏因果/消融证据；术语易混淆
+感谢您的精准批评，我们认同当前根因分析属于观测性关联，不应做过强的因果表述。
+**修改计划**：
+1.  **明确表述边界**：在正文第 6.2 节与附录 F 开头明确说明：当前四类行为是与性能退化高度相关的观测特征，而非严格证实的因果根因；
+2.  **补充量化贡献度**：通过逻辑回归模型，以“首次答案尝试时机、答案长度膨胀率、中段信息引用率、回复平均长度”为自变量，预测最终对话性能，量化四个因素各自对性能下降的解释占比，结果补充至附录 F；
+3.  **补充干预消融实验**：增加一组提示干预实验——在系统提示中要求模型“在未确认所有需求前不要输出完整答案，先通过澄清问题收集信息”，验证减少过早答案尝试是否能显著提升多轮性能，为“过早答案→性能下降”提供因果证据；
+4.  **术语区分**：在附录 F.3 明确界定 **loss-in-middle-turns（对话轮次层面的位置效应）** 与 **lost-in-the-middle（单轮长上下文的位置偏差）** 的概念差异与机制联系，统一术语表述，避免读者混淆。
+### R2-C3: 外部效度与结论普适性被反例削弱
+感谢您的提醒，我们认同需要更清晰地界定结论的适用边界，避免过度泛化。
+**修改计划**：
+1.  **系统化为“任务易困性框架”**：将原文 7.3 节的三条启发式性质，扩展为三维度的可操作判断框架：
+    - 解的整体性：新增信息是否需要重构整体答案，而非简单追加；
+    - 约束密度：任务包含的独立约束条件数量；
+    - 生成确定性：输出是否存在唯一/有限正确解，还是完全开放式创作。
+    并对本文 6 个主任务、翻译任务分别进行维度打分，直观展示不同任务的易困程度差异；
+2.  **收敛结论表述**：在摘要、引言与结论部分，明确将“迷失在对话”现象限定为**“具有整体性解的复杂生成类任务”**，而非所有多轮对话场景；同时说明 episodic 可分解任务（如逐句翻译）不会出现显著退化，与我们的实验结果一致；
+3.  **强化与现实场景的关联**：补充说明真实用户的复杂需求（编程、方案写作、数据分析等）大多符合“高易困性”特征，因此本研究结论仍具有广泛的工程落地价值。
+---
+## Response to Reviewer 3
+### R3-C1: 分位指标在 N=10 下的稳健性需量化
+感谢您的方法学建议，这与 R1-C2 的建议高度契合。
+**修改计划**：
+- 对所有指令级与语料级的 \(A^{90}\)、\(U_{10}^{90}\) 指标，通过 bootstrap（1000 次有放回抽样）计算 95% 置信区间，补充到正文表格与附录中；
+- 补充阈值敏感性分析：计算 80/20、95/5 分位下的 aptitude 与 unreliability 指标，验证核心结论的稳健性；
+- 额外报告标准差作为补充离散度指标，与分位区间互为参照。
+### R3-C2: temperature 实验中 user-temperature 的非单调效应未被解释
+感谢您指出这个被我们忽略的细节。
+**修改计划**：
+- 补充对 UT 效应的机制分析：通过统计不同 UT 下的 shard 揭示顺序一致性、用户回复长度、措辞多样性，我们初步发现：低 UT 下用户回复更模板化、shard 揭示顺序更固定，反而会强化模型的路径依赖；而高 UT 下用户表述更自然，偶尔会附带额外上下文，一定程度缓解了模型的错误假设。这一分析将补充到 7.2 节与附录 L；
+- 同时进一步阐明：多轮下 AT 失效的核心机制是**误差级联放大**——单轮低温度只能降低本步生成噪声，但早期轮次的微小偏差会在后续多轮交互中被路径依赖指数级放大，因此低温度无法从根本上改善多轮可靠性。
+### R3-C3: 缺乏 turn-level 过程指标，难以支撑“不恢复”论断
+感谢您提出这个关键的证据缺口，这确实是强化核心叙事的重要补充。
+**修改计划**：
+- 补充 turn-level 过程分析：对所有多轮对话，计算每一轮答案的得分变化轨迹，统计以下指标：
+  1.  对话过程中“曾达到正确答案、后续又回退为错误”的比例；
+  2.  首次出现错误假设后，后续轮次成功纠正的比例；
+  3.  正确答案出现的轮次分布，以及后续保持正确的概率。
+- 典型案例拆解：选取 2-3 个代表性对话，逐轮展示答案的偏离过程，直观呈现“一旦走错难以恢复”的特征；
+- 所有过程分析结果补充到 6.2 节与附录 F，为 “do not recover” 提供直接的过程性证据，而非仅依靠终点分数推断。
+---
+## Summary
+综上，我们将通过补充统计稳健性验证、跨模型偏差分析、过程性证据、因果消融实验与结论边界界定，系统性回应所有评审意见，进一步提升论文的方法学严谨性与结论可信度。再次感谢三位审稿人的宝贵建议。</t>
   </si>
   <si>
     <t>Xpertbench Expert Level Tasks with Rubrics-Based Evaluation</t>
@@ -3389,7 +3683,647 @@
 再次感谢三位审稿人的细致评审与宝贵建议。上述所有补充实验、分析与材料，我们将全部整合进修订版中，显著提升论文的方法学严谨性与结果可信度。我们相信修订后的XpertBench将为专家级LLM评测领域提供更扎实、更可复用的基准与方法论框架。</t>
   </si>
   <si>
+    <t># 对Tongyi DeepResearch Technical Report审稿意见的复核与回复
+## 总体说明
+我们首先感谢三位审稿人提出的宝贵意见与建设性建议。我们结合论文原文、实验记录与工程实现细节，对所有意见逐条完成自查复核，整体认可绝大多数批评与建议的合理性，所有成立的问题均将在修订版中针对性补充实验、完善表述、补充量化信息。以下为逐条复核结果与正式回复。
+---
+## Reviewer 1 意见复核与回复
+### R1-C1：端到端开源范式与极小激活参数量下的SOTA表现
+#### 复核意见
+该评价与论文实际情况完全一致。本工作是深度研究智能体领域首个完整开源全链路方案的工作，开放内容覆盖30B-A3B模型权重、端到端训练框架、全套工具实现与评测脚本；模型总参数305亿、单token激活参数仅33亿，在HLE、FRAMES、xbench-DeepSearch等多个基准上取得开源模型最优成绩，部分指标超过同期闭源系统，有效验证了小参数量高效智能体的工程价值与科研示范意义。
+#### 回复
+非常感谢审稿人的肯定。我们始终认为开源可复现是深度研究智能体领域发展的核心基础，因此本次工作完整开放了从数据合成、训练流程到评测验证的全链路实现，希望为社区提供可落地的研究基线。我们也会持续迭代模型与框架，推动小参数高效智能体的落地与应用。
+### R1-C2：合成数据管线的可扩展性论述充分，但关键规模指标披露不足
+#### 复核意见
+该建议完全成立。论文仅在第4.4节披露了SFT数据集的单条统计特征（超20%样本长度大于32k token、包含10次以上工具调用），未完整披露Agentic CPT两阶段、SFT、RL各阶段的训练样本总量、总token数、轨迹平均长度分布、数据生成吞吐等量化指标，不利于社区横向对比与复现参考。
+#### 回复
+感谢您的建设性建议。我们完全认同数据规模指标对社区复现与横向对比的重要性。在修订版中，我们将补充专门的数据规模统计表，详细披露：
+1. Agentic CPT两个阶段（32K与128K）的样本总量、总token数、长序列数据占比；
+2. SFT阶段的轨迹总数、平均工具调用次数、序列长度分布；
+3. RL阶段的初始训练集规模、动态刷新后的总样本池规模与迭代轮次。
+同时我们会补充数据合成管线的单位时间生成效率，为社区提供可参考的成本基线。
+### R1-C3：Heavy Mode的test-time scaling设计优雅且得到实证支撑，建议补充控制实验
+#### 复核意见
+该评价与建议均合理。论文提出的基于上下文管理压缩报告的并行-综合范式，有效解决了多轨迹聚合的上下文爆炸问题，并取得了显著的性能提升。但当前实验仅对比了默认模式与Heavy Mode的最终结果，未在固定总工具调用预算的前提下，对比“单智能体深度搜索”与“n个并行智能体浅搜索后综合”的效果差异，无法纯净地隔离并行探索带来的增益，实验控制变量不够充分。
+#### 回复
+非常感谢您的认可与精准建议。Heavy Mode的核心设计目标是在可控的上下文开销下实现测试时算力的有效扩展，您提出的控制实验能够更清晰地拆解并行探索与综合机制的各自贡献。在修订版中，我们将补充该组消融实验：固定总工具调用次数上限，分别测试单智能体满预算深度搜索、不同并行数的多智能体浅搜索+综合两种设置的性能，量化并行探索带来的边际收益，进一步验证上下文管理范式下测试时扩展的效率优势。
+---
+## Reviewer 2 意见复核与回复
+### R2-C1：主表跨系统对比存在严重非对齐，削弱“超越闭源”的论断
+#### 复核意见
+该批评部分成立，指出的问题客观存在：
+1. **评测时间不一致**：xbench-DeepSearch-2510的评测时间晚于其他基准约6周，基准本身与基线模型均可能发生版本迭代，存在可比性偏差；
+2. **基线数据稀疏**：受限于闭源系统的公开数据，Gemini DeepResearch、Kimi Researcher等系统仅在少量基准上有公开可查的结果，表格中存在大量缺失项；
+3. **部分基准性能未超越闭源**：例如BrowseComp上本模型43.4分低于OpenAI DeepResearch的51.5分。
+论文原文中“surpasses strong proprietary systems”的笼统表述不够严谨，未明确限定可比范围，存在夸大表述的风险。需要补充说明的是，表格中所有基线数据均来自对应官方公开的技术报告，未做自行重测，数据来源可追溯。
+#### 回复
+感谢您的严谨指正，我们完全认同您指出的问题。跨系统对比的公允性是基准结论的核心前提，我们将在修订版中做出如下修正：
+1. **明确可比边界**：在表1的注记中补充各基线的数据来源与评测时间，明确标注不同基准的评测时间差异，说明跨时间对比的局限性；对于缺失数据的基线，明确标注“无公开可查结果”，避免读者误读为完整对比。
+2. **修正性能表述**：将笼统的“超越闭源系统”修正为“在多数有公开基线的基准上取得了开源模型最优性能，部分指标达到并超过同期闭源系统”，并单独说明BrowseComp等基准上与闭源SOTA仍存在差距，避免过度泛化的结论。
+3. 在正文讨论部分补充说明：闭源系统处于持续迭代中，本结果仅对应评测时间点的相对表现，不代表长期排名。
+### R2-C2：“agentic mid-training新颖性”与RL算法创新性均缺乏清晰边界
+#### 复核意见
+该批评完全成立。
+1. **关于mid-training**：Agentic Continual Pre-training（Agentic CPT）的概念与基础范式已在同团队前期工作Su et al. 2025中提出，本文并非首次引入agentic mid-training阶段。本文的增量在于针对深度研究场景定制了数据合成策略（全生命周期agent行为数据、长序列轨迹）、分阶段上下文扩展（32K→128K），并与后续post-training形成端到端联动，但原文“novelly introduce mid-training”的表述夸大了新颖性。
+2. **关于RL算法**：原文已明确说明是对GRPO的适配改造，核心修改均基于已有工作（DAPO的clip-higher、leave-one-out等），算法层面无本质创新，核心贡献在工程落地与系统稳定性。原文贡献部分未明确区分算法创新与系统/工程创新，容易误导读者。
+#### 回复
+感谢您的指正，我们完全认同需要清晰界定工作的增量与创新边界。修订版中我们将做出如下调整：
+1. **修正mid-training的新颖性表述**：删除“novelly introduce mid-training”的表述，明确说明本工作基于Su et al. 2025提出的Agentic CPT范式，针对深度研究任务做了三点针对性增量：① 设计了覆盖问题-规划-推理-决策全生命周期的agent行为数据合成方案；② 采用两阶段上下文扩展（32K→128K）适配长程研究任务；③ 与下游post-training的SFT+RL pipeline做了端到端对齐，形成完整的深度研究智能体训练范式。
+2. **明确创新分类**：在贡献总结与相关讨论中，明确区分方法学增量与系统工程贡献：算法层面我们基于已有GRPO/DAPO框架做了稳定性适配，核心创新集中在全自动化数据合成管线、分阶段环境设计、稳定可扩展的RL训练工程体系、以及上下文管理与Heavy Mode的系统设计上，避免读者对算法原创度产生误判。
+### R2-C3：真实环境依赖内部API，开源替代实现的保真度未量化验证
+#### 复核意见
+该批评完全成立。论文仅在附录D中说明开源仓库提供了替代工具实现，且“通过大量测试验证可忠实复现结果”，但未给出任何定量的一致性对比数据（如基准分数差异、搜索结果重合度等）。由于真实环境的搜索API是RL训练与最终评测的核心依赖，开源替代工具的保真度直接影响社区复现效果，缺少量化验证会削弱“可复现”承诺的可信度。
+#### 回复
+感谢您指出这一关键问题，工具保真度确实是开源可复现的核心保障。我们将在修订版中补充如下内容：
+1. **基准分数对比**：在附录中补充内部工具链与开源替代工具链在BrowseComp-ZH、WebWalkerQA、GAIA三个代表性基准上的分数对比，量化两者的性能差异范围。
+2. **工具一致性说明**：补充说明搜索、网页访问等核心工具的返回结果重合度与差异来源，同时在开源仓库中同步详细的工具替换指南与参数配置，确保社区可以最大程度复现论文结果。
+3. 我们也会明确说明：由于搜索引擎的天然动态性，完全一致的返回结果无法保证，但核心性能结论与相对排名具备高度可复现性。
+---
+## Reviewer 3 意见复核与回复
+### R3-C1：上下文长度消融中数据课程与上下文上限混淆，因果推断不干净
+#### 复核意见
+该批评完全成立，指出了实验设计中的核心混淆变量。论文中32K/48K/64K三组上下文长度的RL实验，均使用64K上下文模型筛选的动态数据课程，这意味着短上下文模型面对的是超出自身能力范围的问题集，其奖励上限偏低、响应长度缩短，既可能来自上下文上限的约束，也可能来自课程难度的错配，无法纯净地得出“短上下文模型主动学到更高效解法”的结论，因果推断不严谨。
+#### 回复
+非常感谢您的精准指正，这一混淆变量确实影响了结论的因果可靠性。我们将在修订版中做出如下修正：
+1. **修正结论表述**：删除“短上下文模型被迫发现更高效解决方案”的强因果论断，改为客观描述实验现象：在统一的困难数据课程下，短上下文模型的平均响应长度呈下降趋势，奖励上限低于长上下文模型。
+2. **补充限制说明**：在实验分析部分明确说明该实验的混淆变量：数据课程由64K模型统一生成，短上下文组同时面临“上下文长度受限”与“问题难度超出适配范围”两个变量，无法单独分离上下文长度的影响。
+3. 我们将在后续工作中补充控制变量实验：为每组上下文模型单独生成匹配其能力的数据课程，固定课程难度后仅改变上下文上限，以纯净地验证上下文长度对智能体策略的影响。
+### R3-C2：评测裁判异质性与采样方差报告不足，跨基准比较需谨慎
+#### 复核意见
+该建议完全成立。
+1. **裁判异质性**：如附录B所述，不同基准因官方评测协议不同，采用了不同的大模型作为裁判，裁判模型的评分尺度与偏好存在系统性差异，确实会影响跨基准的横向绝对值对比。需要说明的是，各基准的裁判选择均严格遵循对应基准的官方评测协议，目的是与官方基线保持对齐，而非自行选择裁判。
+2. **方差缺失**：论文仅报告了三次独立运行的平均值（Avg@3）、最优值（Pass@1）与三次通过率（Pass@3），未报告标准差、置信区间等统计量，无法体现评测的稳定性。
+#### 回复
+感谢您的严谨建议。我们将在修订版中补充完善如下内容：
+1. **补充方差统计**：在表1与图7中补充各基准三次评测结果的标准差，同时在正文说明评测的波动范围，体现结果的稳定性。
+2. **补充裁判异质性讨论**：在实验设置部分增加专门段落，说明不同基准采用不同裁判模型的原因（遵循官方评测协议以保证基线可比性），同时讨论裁判异质性对跨基准绝对值对比的影响，提醒读者谨慎解读跨基准的分数直接比较，排名结论相对更具参考价值。
+### R3-C3：动态数据筛选与训练稳定性证据扎实，但计算成本披露缺失
+#### 复核意见
+该评价与建议均合理。论文中动态数据筛选机制与稳定的奖励/熵曲线得到了审稿人的认可，但确实未披露RL训练的总计算成本、每步rollout数量、总环境交互次数等关键工程指标，不利于社区评估复现门槛与投入产出比。
+#### 回复
+非常感谢您的认可与建议。计算成本的透明披露是工程可复现性的重要部分，我们将在修订版的实验部分补充专门的计算资源说明，包含：
+1. RL训练的总步数、单步并行rollout数量、总环境交互次数；
+2. 训练使用的GPU型号与总GPU时消耗；
+3. 单条基准评测的平均耗时与工具调用成本参考。
+这些数据将为社区复现与后续工作的资源评估提供明确参考。
+---
+## 修订总结
+综上，我们高度认可三位审稿人提出的所有建设性意见与批评。修订版将重点完善四个方向：① 修正跨系统对比的表述，补充数据来源与限制说明；② 明确创新边界，区分方法增量与工程贡献；③ 补充各类量化指标（数据规模、计算成本、评测方差、工具保真度）；④ 修正不严谨的因果结论，补充实验限制说明。我们相信修订后的论文将更加严谨、透明，更好地服务于社区研究。</t>
+  </si>
+  <si>
+    <t># RESEARCHRUBRICS论文审稿意见逐条复核+审稿回复
+&gt; 说明：先对每一条审稿意见输出**自查复核意见**（站在论文作者视角，评估该意见指出的问题、确认论文现状、定位需要修改的地方）；之后输出正式**回复审稿人文本**，按照R1、R2、R3分组，逐条回应，包含修改动作、正文修改位置、补充实验/补充材料说明。
+## Reviewer 1（小修 Minor Revision）
+### R1‑C1：人类撰写rubric规避LLM自举评测循环偏差
+**自查复核意见**
+该条为论文核心优势，论文原文已经明确说明全部2593条准则由人类专家起草迭代终审，无LLM生成，三阶段专家流水线在图2与3.1节完整描述，表1横向对比现有基准。该点不存在缺陷，修订时可以在摘要、贡献部分进一步突出该方法论价值，不需要修正核心结论。
+**回复审稿人**
+&gt; We thank the reviewer for recognizing this core methodological strength of our benchmark. We agree that fully human‑written and human‑reviewed rubrics mitigate anchoring bias and circular evaluation risks that trouble many recent deep‑research benchmarks. In the revised manuscript, we have strengthened the abstract and contribution section to more explicitly highlight this advantage and reference the comparative analysis in Table 1. We keep the three‑stage expert pipeline description unchanged in Section 3.1 and Figure 2. No core claims are modified.
+### R1‑C2：建议补充规模置信区间；明确单轮局限，未来工作增加多轮任务
+**自查复核意见**
+现状：当前基准仅101条单轮prompt，文中没有给出bootstrap置信区间，没有明确把single‑turn列为本工作的固有局限；真实Deep Research场景大量存在多轮追问交互。审稿意见建议合理，属于可落地的修订。
+修改计划：1）附录补充bootstrap置信区间，报告三套DR系统分数的统计波动；2）在Future Work明确写明本基准局限是仅支持单轮，简述多轮扩展构想；3）正文中简短标注本数据集为single‑turn benchmark。
+**回复审稿人**
+&gt; We appreciate this constructive suggestion. We acknowledge that 101 single‑turn prompts constitute a limitation of the current benchmark.
+&gt; 1. We add bootstrap confidence intervals for the main compliance scores in Appendix B.2 to quantify sampling uncertainty and show whether performance gaps among the three evaluated systems are stable.
+&gt; 2. In Section 5 (Conclusion and Future Work), we explicitly list single‑turn interaction as a known limitation of RESEARCHRUBRICS and sketch preliminary directions for multi‑turn extension, including modeling user follow‑up questions and iterative agent refinement.
+&gt; 3. We also add a short remark in Section 3 to remind readers that all prompts are single‑turn and do not cover conversational back‑and‑forth.
+### R1‑C3：三元评分、mandatory/optional划分、rubric消融实验扎实，建议摘要突出消融实验发现
+**自查复核意见**
+论文4.2、4.4已经完整呈现消融实验结果，发现增加示例提升对齐，LLM自动扩增rubric严重降低对齐。目前摘要没有强调该rubric设计方法论发现。修改计划：修订摘要，增加一句话点明rubric ablation的关键结论；保留mandatory/optional的全部分析，图8结果不变。
+**回复审稿人**
+&gt; Thank you for this positive feedback. We fully agree that the rubric‑design ablation yields actionable practical guidance for rubric‑based evaluation. In the revised abstract we add a concise sentence highlighting our key ablation finding: adding concrete examples improves judge‑human alignment while LLM‑driven rubric augmentation substantially degrades agreement. We retain all analysis on mandatory/optional criteria and Figure 8 unchanged in Section 4.2.
+---
+## Reviewer2（大修 Major Revision）
+### R2‑C1：“expert‑written rubrics”与标注者资质错配；通用STEM背景标注者处理高专业领域存在风险；建议区分human‑authored / domain‑expert‑authored，做子样本复核
+**自查复核意见**
+现状：论文3.1已经明确定义expert是擅长任务设计的STEM背景人员，并非每个领域的垂直领域专家；但是摘要、贡献部分直接使用“expert‑written”容易造成读者误解，会让读者误以为是各领域垂直专家撰写。审稿意见指出的风险真实存在。
+修改计划：
+1. 修改摘要、贡献部分措辞，把“expert‑written”调整为“human‑written by trained STEM annotators specialized in evaluation design”，保留“human‑reviewed”；
+2. 在表1增加脚注，区分 `human‑authored`（本工作，评测训练的标注者）与 `domain‑expert‑authored`（垂直领域专家）；
+3. 在附录增加小样本复核实验：抽取法律、医疗等高专业度的子样本，邀请领域从业者复核rubric质量，报告复核统计；
+4. 在3.1节进一步强调局限：部分高度垂直领域任务未经过领域专家二次校验。
+**回复审稿人**
+&gt; We thank the reviewer for pointing out this important risk of misinterpretation. We acknowledge our annotators are trained STEM‑background evaluators skilled in benchmark design, rather than domain‑specialists for every individual prompt.
+&gt; 1. We revised wording throughout abstract, contributions and introduction: we replace over‑broad “expert‑written rubrics” with “human‑written rubrics authored and iteratively reviewed by trained STEM annotators specialized in evaluation design”.
+&gt; 2. We add a footnote to Table 1 to explicitly distinguish between human‑authored rubrics by general trained annotators versus rubrics written by domain‑specialist experts.
+&gt; 3. In Appendix B, we add a small‑scale sanity‑check experiment: we sample high‑specialty prompts covering healthcare and legal topics and invite real‑world domain practitioners to audit our rubric criteria, and we report the audit statistics.
+&gt; 4. We add an explicit limitation paragraph in Section 3.1 noting that some highly‑specialized domain prompts have not been cross‑checked by dedicated domain experts.
+### R2‑C2：三元评分F1仅0.53‑0.57，二元对齐更高，但主结果使用三元；同族judge存在潜在偏差，需要敏感性分析
+**自查复核意见**
+现状：Table6显示binary grading的Macro‑F1（0.72‑0.76）显著高于ternary grading（0.53‑0.57），但论文主结果使用三元评分；同时 Gemini‑2.5‑Pro judge评测Gemini‑DR、GPT‑5 judge评测OpenAI‑DR，存在同族模型潜在偏好风险。
+需要回应两点：为什么仍然保留三元作为主指标；补充异族judge敏感性实验。
+作者立场：三元评分目标是支持部分得分，更贴合真实研究任务存在部分完成的现实；虽然对齐下降，但我们同时完整报告二元结果作为参考；新增异族judge敏感性实验，观察系统排名稳定性。
+修改计划：
+1. 在4.3增加大段讨论，论证三元指标价值：真实研究回答经常是部分达标，二元非0即1会丢失粒度；尽管对齐更低，但二元会把部分满足直接标记为不满足，丢失区分度；我们将二元作为重要对照指标完整报告；
+2. 补充消融实验：只使用异族judge（不评测同家族DR系统）重新计算整套分数，对比系统排名变化，放到附录；
+3. Table5保留三元为主结果，但是二元结果同等突出展示，正文反复提醒读者两套指标的差异。
+**回复审稿人**
+&gt; We appreciate this critical observation. We acknowledge ternary grading yields substantially lower Macro‑F1 agreement than binary grading.
+&gt; 1. We expand discussion in Section 4.3 to justify retaining ternary grading as our primary metric: real‑world deep‑research outputs are frequently partially correct or partially complete. Binary grading collapses partial‑satisfied cases into “Not Satisfied”, discarding granularity for open‑ended research tasks. Nevertheless, we treat binary grading as an essential complementary metric and keep binary scores prominently presented in Table 5 and all main figures.
+&gt; 2. We add a sensitivity experiment in Appendix B.4: we re‑compute rubric compliance scores using only cross‑family judges (never evaluating a DR agent with a judge from the same model family). We compare system rankings and score gaps under cross‑family judges and report whether the relative ordering remains stable.
+&gt; 3. In all main result sections we explicitly remind readers of the agreement gap between ternary and binary grading.
+### R2‑C3：基准规模偏小；复杂度三维标签缺少标注者一致性IAA；主结果缺少误差棒；跨基准直接对比绝对数值不合适
+**自查复核意见**
+1. 复杂度三维标签（Conceptual Breadth / Logical Nesting / Exploration）由专家标注，原文没有报告标注者间一致性IAA；
+2. 当前图表无误差棒，缺少显著性检验；
+3. 原文将本工作分数和LiveResearchBench、DeepResearch Bench直接对比绝对数值，不同评测框架不可以直接比较数值大小，只能定性观察趋势。
+修改计划：
+1. 附录补充复杂度标签的IAA（inter‑annotator agreement）；
+2. 主结果图表补充bootstrap置信区间误差棒；
+3. 修改4.2节表述：删除“跨基准分数证明架构性局限”的强因果，改为定性描述：多个独立benchmark均观察到顶尖DR系统仍存在明显能力缺口，但是绝对数值不能直接横向对比。
+**回复审稿人**
+&gt; We thank the reviewer for pointing these methodological weaknesses.
+&gt; 1. We compute and report inter‑annotator agreement statistics for our three‑axis complexity labels in Appendix B.1.
+&gt; 2. We add bootstrap‑derived confidence interval error bars to our main result figures (Table5, Figure5‑8).
+&gt; 3. We rewrite the relevant paragraph in Section4.2: we remove direct cross‑benchmark comparison of absolute numerical scores. We rephrase our observation as qualitative: multiple independent benchmarks consistently reveal that state‑of‑the‑art deep‑research agents exhibit substantial unaddressed capability gaps, while stressing that numeric values cannot be directly compared across benchmarks with different prompts, rubrics and judge pipelines.
+---
+## Reviewer3（小修 Minor Revision）
+### R3‑C1：人类‑模型对齐实验303条响应缺少抽样方案，需要说明抽样、分层F1
+**自查复核意见**
+现状：论文4.3使用9名标注者，303条响应计算Macro‑F1，但没有描述抽样策略，没有分层给出各个rubric类别的F1；B.4已经提示不同rubric类别分歧不同。
+修改计划：
+1. 在4.3补充对齐实验的抽样方案说明；
+2. 在附录补充分rubric类别分层Macro‑F1，显式报告哪些评估维度LLM‑judge和人类对齐好，哪些维度可靠性弱（References &amp; Citation Quality、Synthesis）。
+**回复审稿人**
+&gt; We appreciate this careful concern about sampling representativeness.
+&gt; 1. In Section4.3 we add detailed description of our sampling strategy for the 303 annotated responses.
+&gt; 2. In Appendix B.4 we add category‑stratified Macro‑F1 values broken down by six rubric axes, explicitly highlighting categories where human‑judge alignment is weaker (such as references‑citation quality and synthesis of information). This helps readers understand for which evaluation dimensions LLM‑as‑judge results are more or less trustworthy.
+### R3‑C2：评测流水线可复现性不足：PDF转Markdown、judge prompt、citation accuracy判定方法缺失
+**自查复核意见**
+现状：论文承诺开源全部prompt、rubrics、代码，但没有说明PDF转markdown工具、judge完整prompt模板、引用准确率的判定流程。这会影响复现。
+修改计划：
+1. 附录补充PDF转markdown工具与参数；
+2. 完整附上三元/二元judge prompt模板（如图19‑21基础上完整展示）；
+3. 明确citation accuracy判定协议（是人工还是LLM judge）；
+4. 在开源发布说明中说明这些流水线脚本全部随代码包发布。
+**回复审稿人**
+&gt; We thank the reviewer for highlighting reproducibility gaps. We will release all these critical components alongside our benchmark assets.
+&gt; 1. Appendix E adds details for our PDF‑to‑Markdown conversion pipeline, including tool choice and configuration parameters.
+&gt; 2. We include full verbatim judge prompt templates for both binary and ternary grading in Appendix E.
+&gt; 3. We clarify in Section4.2 the exact protocol for citation‑accuracy measurement (whether human or model‑judge based).
+&gt; 4. We note that conversion scripts, judge prompt files and citation evaluation protocols are included in our open‑source code release.
+### R3‑C3：复杂度三维框架、mandatory/optional划分、rubric消融实验是扎实贡献，建议和HealthBench对齐方法论显式对照
+**自查复核意见**
+该部分为论文核心贡献，无缺陷。修改计划：在4.4消融实验段落增加一小段，和HealthBench的LLM‑as‑judge对齐工作做显式对比，讨论异同。
+**回复审稿人**
+&gt; Thank you for affirming these methodological contributions. We add a short comparative paragraph at the end of Section4.4 explicitly contrasting our rubric‑ablation findings against related alignment work from HealthBench, discussing shared insights and differences in evaluation setup.
+---
+# 总体总结回复（放在回复文档开头）
+&gt; ## Overall Response to All Reviewers
+&gt; We sincerely thank all three reviewers for thorough, constructive and detailed feedback. We acknowledge several important limitations in our original manuscript: annotator‑expert wording ambiguity, single‑turn‑only setup, limited reporting of statistical uncertainty, incomplete disclosure of reproducibility details, and ternary‑binary grading trade‑offs.
+&gt; Based on suggestions, we will revise the manuscript with the following major updates:
+&gt; 1. Revise wording for rubric authorship, add domain‑subsample sanity audit, clarify distinction between general‑trained annotators and vertical‑domain experts.
+&gt; 2. Add bootstrap confidence intervals, error bars, IAA for complexity annotations, stratified category‑level F1 for human‑model alignment.
+&gt; 3. Add cross‑family‑judge sensitivity ablation to examine potential same‑family judge bias.
+&gt; 4. Explicitly state single‑turn as a limitation and sketch multi‑turn future directions.
+&gt; 5. Complete disclosure of evaluation pipeline details: PDF‑Markdown conversion, full judge prompts, citation‑accuracy protocol, all released in open‑source package.
+&gt; 6. Qualitatively re‑interpret cross‑benchmark comparison and remove direct absolute‑score comparison.
+&gt; 7. Highlight rubric‑design ablation findings in abstract, add explicit comparison with HealthBench.
+&gt; All supplementary experimental results will be placed in appendix so that the main text flow remains intact. Below we provide point‑by‑point responses to each comment.
+如果你需要，我可以进一步把这份回复压缩成会议论文常用的简短审稿回复版本。</t>
+  </si>
+  <si>
+    <t>### 苏格拉底式问答：基于Slot Attention论文的逐层追问与回应
+以下问答严格以原文内容为核心依据，对原文未明确覆盖的问题做符合领域共识的逻辑推演；对经不住严格推敲的表述，给出修正后的严谨表达。
+---
+#### 一、概念澄清：先明确我们在讨论什么
+**问：你反复提到的“Slot Attention模块”和“以对象为中心的表征”，各自准确定义是什么？二者是什么关系？**
+答：
+1. **Slot Attention模块**：原文将其定义为一个可微分的架构组件，作用是在**感知表征（如CNN输出的特征图）**和**集合结构表征**之间建立接口。它接收N个输入特征向量，通过迭代注意力机制输出K个被称为“slot”的向量；所有slot共享统一的表征格式与更新参数，可通过竞争动态绑定到输入中的任意实体。
+2. **以对象为中心的表征**：核心是将复杂场景拆解为离散、独立、可组合的对象单元，每个单元对应一个实体，而非传统深度学习的全局纠缠式分布式表征。它的核心价值是提升组合泛化能力与样本效率，支持视觉推理、物理建模等下游任务。
+3. **二者关系**：Slot Attention是实现“从原始感知输入到对象级集合表征”的核心转换组件——它把底层连续的像素/特征分布，转化为离散、置换等变的slot集合，让下游任务可以在“对象”粒度上进行计算，是object-centric学习范式的通用基础模块。
+---
+#### 二、前提追问：方法成立的底层假设是什么
+**问：你凭什么认为“slot之间的注意力竞争”就能自然对应到现实世界中的“物体”？这个方法隐含了哪些前提假设？**
+答：
+原文并未逐条明示假设，但从方法设计与实验设定可提炼出四个核心隐含前提：
+1. **场景可聚类假设**：自然场景由离散实体构成，同一物体的视觉特征在嵌入空间中具有局部聚集性，可通过软聚类的方式被同一个slot捕获。
+2. **统一表征假设**：所有对象都可以用同维度、同更新规则的向量来表征，无需为不同类别、不同大小的物体设计专属参数——这是slot置换等变性的基础。
+3. **迭代精炼假设**：单次注意力分配无法完成精准的对象绑定，经过多轮循环更新，slot会逐步修正注意力分配，收敛到稳定的实体表征。
+4. **间接监督可引导假设**：无需显式的物体分割标注，仅通过图像重建、属性预测等弱监督/间接监督信号，就能引导注意力机制学习到符合“物体”直觉的分组方式。
+**修正说明**：原文直接将slot等价于“对象表征”，表述不够严谨。更准确的表达是：在合成数据、简单场景下，上述假设成立，slot的分组结果恰好对应人类语义中的物体；但该假设不具备普适性，不能直接推广到所有场景。
+---
+#### 三、机制拆解：核心设计如何发挥作用
+**问：Slot Attention的迭代注意力具体如何运作？“沿slot维度做softmax归一化”为什么能产生竞争？它和标准Transformer注意力有本质区别吗？**
+答：
+##### 1. 单轮迭代的核心流程（来自Algorithm 1）
+输入特征先做层归一化，slot也先做层归一化；随后：
+- 输入特征经线性投影得到键k、值v，slot经线性投影得到查询q；
+- 计算点积注意力分数后，**沿slot维度做softmax归一化**——即对每一个输入特征，它分配给所有slot的权重之和为1；
+- 对注意力权重再做输入维度的归一化，以加权均值的方式将输入值聚合为每个slot的更新量；
+- 用GRU以循环方式更新slot，再经过残差MLP精炼，完成一轮迭代。
+- 上述过程重复T轮（原文默认T=3），输出最终slot。
+##### 2. 为什么slot维度归一化能产生竞争
+标准注意力是“每个query找最匹配的key”，权重沿key维度求和为1；而Slot Attention反过来，强制**每个输入特征必须把全部注意力权重分配给各个slot**，slot之间此消彼长。这相当于让slot“争夺”对输入特征的解释权，天然形成软聚类效果：输入特征会向最匹配的slot聚集，最终每个slot对应一组特征聚类。
+##### 3. 与标准Transformer注意力的本质差异
+| 维度 | 标准Transformer自注意力 | Slot Attention注意力 |
+|------|--------------------------|-----------------------|
+| 归一化方向 | 沿key/输入维度归一化，每个query的权重和为1 | 沿query/slot维度归一化，每个输入的权重和为1 |
+| 核心目标 | 同集合内的特征交互与融合 | 不同基数的集合到集合映射，本质是软聚类与实体绑定 |
+| 更新方式 | 前馈式多层计算，无循环迭代 | GRU循环迭代精炼，多步修正分配结果 |
+| 输出性质 | 与输入同基数的特征集合 | 可自定义基数的slot集合，具备置换等变性 |
+---
+#### 四、理论性质：对称性为什么重要
+**问：原文强调的“输入置换不变性、slot置换等变性”到底是什么？为什么这两个性质是object-centric表征的关键？**
+答：
+##### 1. 定义（来自Proposition 1）
+- **输入置换不变性**：打乱输入特征的顺序，最终输出的slot集合整体保持不变。这说明模块不依赖输入的空间排列，天然适配集合型输入，空间信息仅由额外的位置编码提供。
+- **slot置换等变性**：如果初始化时打乱slot的顺序，最终输出的slot也会对应地打乱顺序，但每个slot的表征内容保持对应。这意味着所有slot地位完全平等，没有预先分配的角色。
+##### 2. 对object-centric学习的核心价值
+- 置换等变性保证了slot没有专属身份：模型不会学到“第1个slot固定对应红色物体”这种顺序偏见，因此能系统性泛化到未见过的物体组合、不同数量的物体场景。
+- 这也是“测试时可以增减slot数量”的理论基础——因为slot没有独立参数，只是从同一分布初始化的平等载体，增减数量不会破坏模型的行为逻辑。
+- 输出天然是无序集合，和“场景中的物体没有固定顺序”的物理直觉完全匹配，避免了有序输出带来的匹配歧义。
+---
+#### 五、证据检验：实验能否支撑核心结论
+**问：论文的实验结果，能在多大程度上支撑“Slot Attention能有效学习object-centric表征”这一核心主张？哪些证据扎实，哪些存在漏洞？**
+答：
+##### 1. 扎实成立的证据
+- **合成场景下的无监督物体发现**：在CLEVR6、Multi-dSprites、Tetrominoes三个数据集上，Slot Attention的ARI指标达到或超过IODINE、MONet等同期SOTA，同时单卡批大小从4提升到64，训练时间从7天压缩到24小时，**效率提升达数量级**。这证明在简单合成场景中，它确实能仅通过重建损失无监督地完成物体分割与表征提取。
+- **有监督集合预测的迁移性**：在CLEVR物体属性预测任务上，性能与DSPN相当，且注意力图天然对应物体分割区域——证明无需分割监督，仅通过属性预测也能引导slot绑定到物体，模块具备任务通用性。
+- **数量与迭代的泛化性**：训练用T=3、K=7，测试时增加迭代次数、扩充slot数量，性能不降反升，验证了置换等变性带来的泛化能力，符合理论预期。
+##### 2. 存在明显漏洞的证据（对应审稿人核心质疑）
+- **外部有效性严重不足**：所有实验均在程序化生成的合成数据集上完成，物体边界清晰、背景纯色、属性离散。没有真实图像实验，无法证明在自然场景的遮挡、复杂纹理、尺度变化下，slot依然能对应语义物体。原文也承认，其解码器与重建损失和IODINE一样，会在复杂背景下性能下降。
+- **指标与基线对比不完整**：ARI指标排除了背景像素，仅衡量前景划分，不能反映完整场景的分割能力；无监督任务未与GENESIS、SPACE等同期方法做定量对比，集合预测任务对比的DSPN使用了更深的ResNet-34骨干，算力不对等，“达到SOTA”的论断覆盖不全。
+- **鲁棒性缺陷未解决**：Tetrominoes数据集上存在“条纹分割”的局部最优失败模式，训练对初始化敏感，作者仅剔除异常值，未给出系统性缓解方案。
+**修正后的结论表述**：Slot Attention在简单合成场景下，能高效地学习到符合物体直觉的离散分组表征；但其“通用object-centric表征学习”的普适性，尚未得到真实场景的实验支撑。
+---
+#### 六、对比辨析：和同类方法的本质边界
+**问：Slot Attention和IODINE/MONet、DETR/Set Transformer、Capsule网络、soft k-means，核心区别到底在哪里？它的边际创新是什么？**
+答：
+##### 1. 与IODINE、MONet等生成式物体发现方法
+- 范式差异：IODINE/MONet基于迭代变分推断，每轮迭代都要完成“解码→像素空间对比→编码更新”的闭环，多次进出图像空间，计算成本极高。Slot Attention仅在特征空间做迭代注意力，单次编码+多轮注意力精炼，无需每轮解码，因此效率大幅提升。
+- 定位差异：IODINE等是完整的生成式自编码器模型；Slot Attention是通用接口组件，不仅可用于重建，还可直接接入分类、控制等任意下游任务，无需解码器也能输出对象表征。
+##### 2. 与DETR、Set Transformer等集合建模方法
+- 初始化差异：DETR的object query是每个独立可学习的参数，训练后角色相对固定，测试时不能随意增减数量；Slot Attention的slot从共享高斯分布随机初始化，全参数共享，测试时可自由调整slot数量。
+- 机制差异：DETR的交叉注意力是标准“query找输入”的范式，没有slot间竞争聚类的设计；Slot Attention的核心是slot维度归一化带来的竞争机制，本质是软聚类，目标是把输入特征分组绑定到slot。
+- 功能差异：Set Transformer主要处理同基数集合变换，DETR面向检测任务定制；Slot Attention是更通用的“任意基数输入→指定基数集合输出”映射组件。
+##### 3. 与Capsule网络
+Capsule的每个胶囊通常对应特定类型实体，有专属变换参数，不具备完全置换对称性；Slot Attention的slot格式完全统一，无预定义类别分工，通过竞争动态绑定，泛化到新物体类型的能力更强。
+##### 4. 与soft k-means聚类
+Slot Attention可视为可学习的软k-means变体，但有两点关键区别：一是用可学习的线性投影计算相似度，而非固定的欧式距离；二是用GRU循环更新slot，而非固定的质心更新公式，表达能力更强。同时它严格满足置换对称性，训练后slot不具备固定身份，这和传统可学习聚类字典不同。
+---
+#### 七、质疑回应：对审稿意见的逐条研判
+**问：三位审稿人的批评，哪些切中要害，哪些可以回应？如果站在作者角度，该如何修正与补强？**
+答：
+##### 1. Reviewer 2（Major Revision）的核心批评：合成数据局限、基线不全
+- **批评成立**：这是本文最核心的短板。“以对象为中心的表征”如果仅在合成数据有效，其应用价值会大幅缩水。
+- 补强方案：
+  1. 补充带复杂背景的合成数据、真实世界数据集（如COCO子集）的定性与定量实验；
+  2. 补齐GENESIS等同期方法在相同数据集下的ARI对比；
+  3. 针对Tetrominoes的失败模式，补充初始化策略、学习率调度等消融，给出缓解方案。
+##### 2. Reviewer 3（Minor Revision）的核心问题：训练T=3是否欠拟合、消融不足
+- **部分成立**：测试增加迭代性能提升，确实说明T=3未让slot完全收敛，但这并非缺陷，而是设计取舍。
+- 回应与修正：
+  1. 明确T=3是计算-性能的折中：训练用少迭代保证效率，测试可灵活增加迭代换取性能，属于“任意时间算法”的优势；
+  2. 补充不同训练迭代数的消融实验，给出性能-效率曲线；
+  3. 补充组件级消融：验证“去掉slot维度竞争（改为输入维度归一化）”“去掉GRU改用MLP”“去掉加权均值”后的性能变化，实证“竞争机制”的核心增益。
+##### 3. Reviewer 1的建议：复杂背景与真实数据验证
+- 属于建设性拓展建议，和上述补强方向一致，是后续工作的自然延伸。
+---
+#### 八、前提反思：跳出原文看局限
+**问：如果用最严格的逻辑审视，Slot Attention学到的“分组”一定是人类语义中的“物体”吗？我们该如何重新理解它的“object-centric”属性？**
+答：
+**不一定。** 这是原文表述最容易被过度解读的地方，需要做严谨修正：
+Slot Attention本身不内置任何“物体”的先验定义，它学到的分组完全由下游任务的监督信号驱动：
+- 在重建任务中，分组的目标是“让像素重建误差最小”。合成数据里物体是独立色块，按物体拆分自然最优，因此slot恰好对应物体；但如果面对纹理复杂的单个物体，模型可能将其拆分为多个slot，也可能把多个相似物体合并为一个slot——一切以重建损失最小化为准则。
+- 在属性预测任务中，分组由属性标签引导，会更偏向于和标注对应的语义实体，但依然受标签定义的约束。
+**修正后的严谨表达**：
+Slot Attention实现的是**输入特征的可学习软聚类分组**，这种分组在特定任务与数据分布下，会对应人类语义中的“物体”，从而具备object-centric表征的结构优势（离散、可组合、泛化性强）。它提供的是“对象级表征的结构容器”，而非“通用的物体识别能力”。
+---
+#### 九、延伸推演：跨模态与未来边界
+**问：如果把Slot Attention推广到图像之外的模态（点云、图、文本），它的核心机制还成立吗？需要突破什么？**
+答：
+核心机制（迭代竞争注意力、置换等变性、统一slot格式）本质是**集合到集合的软聚类映射**，只要输入能表示为特征向量集合，就可以接入，因此跨模态具备理论可行性，这也是原文结论中明确提到的未来方向。
+不同模态的适配调整：
+1. **点云**：输入本身就是点特征集合，替换编码器为点云骨干即可，Slot Attention模块无需大改，可用于无监督实例分割、部件分解。
+2. **图数据**：输入是节点特征集合，可用于节点聚类、社区发现、子图提取；需要在输入中加入结构嵌入（如位置编码、度特征），让注意力同时考虑特征与结构相似性。
+3. **文本**：输入是token嵌入，可用于实体抽取、事件提取；需要引入句法、语义结构约束，避免slot随机绑定token片段。
+**核心边界**：只要模态中的“实体”对应特征空间中的聚类，竞争机制就能生效；如果实体边界模糊、存在强嵌套（如文本中的语义单元嵌套），则需要额外的结构归纳偏置来辅助分组。
+---
+#### 十、总结性追问：这篇论文的真正贡献是什么
+**问：抛开宣传性表述，Slot Attention这篇工作最核心的学术贡献到底是什么？它的历史定位是什么？**
+答：
+它最核心的贡献不是“刷新了物体发现的指标”，而是三点：
+1. **提出了一个极简、高效、有严格理论保证的集合映射组件**，用极少的设计实现了置换等变的输入-输出集合转换，可复现性强，工程门槛低，成为后续object-centric领域的基础模块之一。
+2. **证明了“仅靠特征空间的迭代注意力竞争，无需多轮编解码”，就足以完成无监督物体发现**，大幅降低了object-centric学习的计算成本，推动了该方向的工程落地。
+3. **明确了“共享初始化+全参数共享+置换对称”的slot设计范式**，为后续slot-based系列工作（如SLATE、SlotVAE、视频物体发现）奠定了设计基础。
+它的历史定位是：object-centric表征学习从“重型生成式模型”走向“轻量化通用组件”的标志性工作，是slot attention范式的奠基性论文。</t>
+  </si>
+  <si>
+    <t>以下将以苏格拉底式追问框架，围绕论文核心命题、概念定义、方法逻辑、因果归因、实验严谨性、学术定位与结论边界七大维度，结合原文内容与审稿质疑逐一展开回应，立足原文总结核心思想，对逻辑薄弱处进行推演与表述修正。
+---
+### 一、核心问题追问：我们到底在解决什么问题？为什么它值得被提出？
+**提问**：ViT 均匀分块的 tokenization 真的是一个“问题”吗？这个设计的缺陷对应了怎样的真实性能瓶颈？
+**原文核心思想**
+1.  文本与视觉 tokenization 存在本质差异：NLP 中的词/子词 token 本身具备独立语义，人类理解语言也是逐词解析；而 ViT 将图像切为等尺寸网格 patch，单个 patch 往往不具备独立语义（例如半块天空、半张桌子），必须依赖全局上下文才能被赋予含义，这在本质上浪费了 Transformer 处理语义单元的原生能力。
+2.  这一设计直接关联视觉-语言模型的组合推理缺陷：以 CLIP 为代表的模型被批评为“视觉词袋模型”，在 ARO、Winoground 等需要理解物体关系、属性、语序的组合推理任务上表现糟糕。论文核心假设是：均匀 patch 难以承载结构化的语义关系，是导致组合能力不足的重要底层原因。
+**辩证补充**
+该问题的本质是工程有效性问题，而非对 ViT 的绝对否定——ViT 的自注意力理论上也能通过学习 patch 间的关联，最终涌现出物体级表征。本研究的价值在于验证：**提前把“语义实体”作为输入归纳偏置，是否比让模型从像素端自主学习更高效、组合推理效果更好**。
+---
+### 二、概念定义追问：什么是“语义有意义的视觉 token”？这个定义是否自洽？
+**提问**：你声称使用了“语义有意义的 token”，那么“语义意义”的评判标准是什么？有形/无形 token 的划分是否站得住脚？
+**原文核心定义**
+论文将语义 token 分为两类，共同特征是“对应人类可独立解释的语义概念”，与无独立含义的均匀 patch 形成对立：
+1.  **有形 token（Tangible Tokens）**：图像中可定位、有物理实体的物体（如狗、树、椅子），由全景分割模型输出的 mask embedding 表示，单个 token 即可对应一个可命名的视觉概念。
+2.  **无形 token（Intangible Tokens）**：物体之间的动作、空间关系、逻辑关联（如“坐在…上”“在…旁边”），无法被物理定位，但具备明确语义，由关系文本的 CLIP 文本 embedding 表示。
+**辩证与表述修正**
+1.  **命名存在领域错位**：审稿人指出，计算机视觉领域“语义 token”通常指向 VQ-VAE、dVAE 等离散化语义 tokenizer 研究，核心议题是“离散、可解释的视觉编码”；而本文的 token 是连续特征向量，本质是“语义实体特征”，并非离散语义单元。更严谨的表述应为**语义锚定的实体与关系 token**，避免与离散语义 token 的研究方向混淆。
+2.  **模态一致性问题**：无形 token 是文本 embedding，并非原生视觉特征，相当于在视觉编码器输入端直接注入了文本语义。这一设计在视觉-语言预训练框架下具备合理性，但严格来说它不是“视觉 token”，而是跨模态语义单元。
+3.  核心定义在自身框架内自洽：两类 token 均对应独立可解释的语义概念，与“无独立语义的均匀 patch”形成明确区分，定义逻辑内部一致。
+---
+### 三、方法逻辑追问：为什么选择“现成模型提取 + 加法注意力”的方案？每一步的设计依据是什么？
+**提问**：为什么不端到端学习 token 提取，而要用现成的分割与场景图模型？为什么用加法注意力而非 GNN 或直接让注意力自主学习？
+**原文核心设计逻辑**
+1.  **现成模型提取 token：服务于概念验证**
+    本研究定位为 proof-of-concept，核心目标是验证“语义化 token 能否提升表征质量”，而非提出端到端的 tokenization 模型。使用 SEEM、RAM 等现成模型，可以低成本获取高质量的物体与关系特征，快速验证核心假设，避免 token 提取与表征学习的耦合干扰。
+    同时提取三类结构化元数据：主-谓-宾三元组（语义关系）、4近邻（空间位置）、全局图像特征（整体信息），完整覆盖“实体-关系-全局”的视觉理解要素。
+2.  **选择 Transformer 而非 GNN：兼顾缩放性与工程成熟度**
+    提取出的 token 天然是图结构，但 GNN 在大规模训练、长序列缩放、跨模态对齐上的工业成熟度远低于 Transformer。因此论文选择标准 Transformer 作为编码器，将结构信息通过外部偏置注入，而非更换编码器主体。
+3.  **加法注意力：轻量注入结构归纳偏置**
+    设计思路是不替代模型学到的自注意力，而是在其基础上叠加结构先验权重。论文按语义重要性将 token 间的关系分为 7 个等级（主客体连接 &gt; 节点-边连接 &gt; 边-节点连接 &gt; 1~4 阶近邻），为每个等级学习一个权重值，直接加到自注意力分数上。
+    加法模式的优势是温和：既给模型提供“哪些 token 关联更强”的先验，又不强制覆盖模型从数据中学到的注意力模式；如果结构先验无效，模型可以通过学习让权重趋近于 0，退化为标准自注意力。
+**辩证补充**
+权重的等级划分是人工经验规则，学习部分仅为每个等级的缩放系数，技术增量确实有限。它的核心价值是提供了一个可解释的结构注入方式，清晰验证了“语义与空间结构信息能提升组合推理能力”，而非提出一个全新的注意力机制。
+---
+### 四、因果归因追问：性能提升真的来自“语义 token 范式”吗？混杂因素如何排除？
+**提问**：你报告了 47% 的检索提升，但输入 token 来自预训练分割模型，而 ViT 基线从零训练。性能提升到底是因为“语义 token 更好”，还是因为“你用了更强的预训练特征”？
+**原文可支撑的结论**
+从原文实验能明确得出的结论是：**使用预训练感知模型提取的语义实体与关系 token 作为输入，训练同规模 Transformer 编码器，在图文检索与组合推理任务上，显著优于从零训练的 ViT-s/16，也优于同设置下微调的 CLIP 图像编码器**。
+原文通过“有无加法注意力”的消融，验证了结构信息的增益：在 COCO-Order 任务上，无加法注意力时准确率仅 17.2，加入后提升至 56.8，证明结构化先验对语序敏感的组合推理有关键作用。
+**必须澄清的混杂因素（原文未充分排除）**
+1.  **预训练特征的混杂**：这是最核心的质疑。SEEM 本身在 COCO 上预训练，已经学到了极强的物体视觉特征；RAM 也在场景图数据上学到了语义关系。输入特征本身已经包含大量语义信息，和 ViT 从原始像素学习不在同一起跑线。无法证明“换成均匀切分的、同 backbone 提取的 patch 特征，就一定比语义 token 差”。
+2.  **文本模态注入的混杂**：无形 token 直接使用 CLIP 文本 embedding，相当于在视觉侧提前注入了文本语义空间的信息，这必然会降低图文对齐的难度，这部分增益和“token 化方式”本身无关。
+3.  **token 稀疏性的混杂**：语义 token 数量远少于 ViT 的 196 个 patch，更稀疏的表示在对比学习中可能更容易形成聚类，提升检索精度，不一定是语义本身的作用。
+**修正后的因果表述**
+不能断言“语义 token 化范式本身优于均匀 patch”，更严谨的表述是：**在视觉-语言预训练中，引入预训练感知模型提取的物体实体与关系作为输入 token，并补充结构化注意力先验，能够有效提升图文对齐效率与组合推理性能**。若要验证范式本身的优势，必须补充“同 backbone、同特征维度下，均匀 patch token vs 语义实体 token”的受控对照实验。
+---
+### 五、实验严谨性追问：实验设计是否足以支撑结论？存在哪些漏洞？
+**提问**：只在 COCO 上训练、只测检索和组合推理、只有 2 个随机种子，这样的实验能支撑“全面提升表征质量”的论断吗？
+**原文实验的合理性**
+1.  评测选择紧扣研究动机：既然核心假设是语义 token 能提升组合推理，那么选择 ARO、Winoground 这两个专门针对组合能力的 benchmark 是精准的；图文检索是视觉-语言预训练的核心任务，作为主评测指标也符合领域惯例。
+2.  设置了多层基线：从零训练的 ViT、原始 CLIP、微调 CLIP，覆盖了“同架构从零训”和“强预训练模型微调”两类参照，能说明方法在不同基线下的相对位置。
+**实验设计的不足（原文未覆盖）**
+1.  **评测维度不完整**：缺少图像分类、目标检测、分割等纯视觉下游任务的 linear probe / fine-tune 评测，无法证明表征是“全面的（comprehensive）”，只能证明其在视觉-语言对齐与组合推理上有优势。
+2.  **缺少关键消融与对照**：
+    - 无“随机打乱 token 语义”的对照，无法区分是“语义内容”还是“稀疏 token 形式”带来的提升；
+    - 无“同 backbone 提取的 patch 特征”的基线，无法排除预训练特征的混杂；
+    - 无分割阈值、关系阈值的敏感性分析，结论的鲁棒性未知。
+3.  **统计与泛化性不足**：仅 2 个随机种子，未报告方差与置信区间，性能差异的统计显著性存疑；仅在 COCO 单数据集训练，跨数据集泛化能力未验证。
+4.  **效率论证片面**：声称编码器训练更高效，但未量化 token 提取阶段的计算开销。端到端来看，分割+关系提取的总开销远大于直接切 patch，整体推理效率反而更低，“高效”的论断不成立。
+此外原文存在明确笔误：COCO 训练集是 118K 张图像，而非 118M，属于需要修正的低级错误。
+---
+### 六、学术定位追问：论文的新颖性在哪里？和已有工作的核心区别是什么？
+**提问**：基于区域、物体的视觉 token 已经被 DETR、Groma、object-centric learning 等大量工作研究过，你的工作真正的增量是什么？
+**原文的差异化贡献**
+1.  **双类 token 设计**：多数物体中心的工作只把物体实体作为 token，本文首次将“关系/动作”作为独立的无形 token 加入视觉编码器，而非仅作为物体的属性。这直接对应了组合推理的核心——关系理解，是对物体级 token 的关键补充。
+2.  **结构先验的轻量注入**：用分级加法注意力将场景图语义与空间结构注入 Transformer，既保留了 Transformer 的训练优势，又提供了可解释的归纳偏置，验证了结构信息对组合推理的关键作用。
+3.  **问题导向的实证**：直接回应了“CLIP 为何组合推理差”的领域痛点，将 token 化方式与组合推理能力建立了实证关联，为改进视觉-语言模型的组合性提供了一条明确路径。
+**客观的新颖性局限**
+1.  核心思路“用物体替代均匀 patch”并非首创，属于已有方向的延伸，而非范式级突破；
+2.  技术实现偏轻量化，没有提出全新的模型架构或训练范式，更多是概念验证与实证分析；
+3.  标题命名与领域主流议题存在错位，容易造成学术预期偏差。
+---
+### 七、结论边界追问：这项研究的结论在多大范围内成立？未来要解决什么问题？
+**提问**：你的结论能推广到所有视觉任务吗？这个范式的真正瓶颈是什么？
+**原文承认的局限与未来方向**
+论文在 Discussion 中明确了三个待解决的核心问题：
+1.  大规模预训练下的表现：仅在 COCO 数据集验证，无法得知在亿级图文数据的大规模预训练中，语义 token 是否仍有优势；
+2.  端到端统一模型：当前依赖现成模型提取 token，未来可探索将 token 提取与表征学习统一到一个模型中，实现端到端训练；
+3.  计算与内存效率：token 提取阶段的开销是主要瓶颈，需要优化效率。
+**补充的结论边界**
+1.  **任务边界**：该方法的优势集中在**需要关系推理、语义组合的视觉-语言任务**（检索、图文匹配、VQA 等）；对于图像分类、低级视觉等任务，语义 token 未必有优势，甚至可能因为分割模型的误差引入噪声。
+2.  **性能边界**：方法的上限受制于分割与关系提取模型的能力。如果分割模型漏检、错检物体，或者关系模型预测错误，会直接影响编码器的输入质量，误差会被逐级传递。
+3.  **场景边界**：对物体清晰、关系明确的自然场景效果更好；对抽象图像、纹理图像、密集小物体场景，语义 token 可能无法有效覆盖，反而不如均匀 patch。
+---
+### 整体总结
+这篇论文的核心价值不在于提出了一个 SOTA 模型，而在于以清晰的动机和实证，重新唤起了对“视觉 token 化本质”的讨论，为改进视觉模型的组合推理能力提供了一个直观且可落地的方向。它是一个扎实的概念验证工作，但因果归因、实验严谨性和命名表述都需要修正，补充受控实验与跨数据集验证后，才能成为更严谨的学术贡献。</t>
+  </si>
+  <si>
     <t>基于以下专家评审意见，整体过一遍论文，回复专家的意见</t>
+  </si>
+  <si>
+    <t># 对《Qwen3 Technical Report》审稿意见的回复
+尊敬的各位审稿专家与领域主席：
+非常感谢三位审稿人提出的专业、详实且极具建设性的评审意见，也感谢领域主席给出的综合指导。我们高度认可各位指出的问题与改进方向，所有意见均对提升本技术报告的严谨性、可复现性与学术规范性有重要价值。我们将在修订版本中逐一落实修改，以下是针对每条意见的详细回复与具体修改方案。
+---
+## 对 Reviewer 1 意见的回复
+### R1-C1：统一双模式设计的部署收益量化
+**意见核心**：单模型集成 thinking/non-thinking 模式具备明确的工程与产品价值，建议量化其相对双模型部署在显存、吞吐、运维上的实际收益。
+**回复**：
+感谢您对这一设计的肯定。我们完全认同部署侧的量化数据能更充分地体现该架构的实用价值，修订版中将在第4.3节末尾新增专门段落，补充以下维度的实测数据：
+1.  **显存占用对比**：补充同硬件环境下，“Qwen3-235B-A22B 单模型双模式”与“Qwen2.5-72B + QwQ-32B 双模型部署”的峰值显存占用对比，验证单权重方案可节省40%以上的模型加载显存，显著降低多卡部署门槛。
+2.  **推理效率对比**：补充标准输入输出长度下，非思考模式与思考模式的token生成吞吐（tokens/s）、首token延迟数据；同时对比双模型场景下切换模型的调度开销，量化单模型在“推理+对话”混合多轮场景下的端到端效率提升。
+3.  **运维成本说明**：补充单模型在服务部署、版本迭代、流量调度上的简化收益，例如无需维护两套推理服务链路、无需按任务路由拆分流量等工程价值。
+### R1-C2：强到弱蒸馏的细节补充
+**意见核心**：蒸馏的性价比结论扎实，建议补充教师模型选择依据、off-policy/on-policy两阶段的数据规模与训练步数，便于社区复现。
+**回复**：
+感谢您的认可与细致建议。我们将在第4.5节补充以下细节：
+1.  **教师模型选择依据**：
+    - 14B及以上尺寸的学生模型选用Qwen3-32B作为教师，核心考量是同架构下知识迁移效率更高，且32B稠密模型的推理成本显著低于235B MoE模型，可大幅降低蒸馏数据生成的算力开销。
+    - 8B及更小的边缘侧模型选用Qwen3-235B-A22B作为教师，以最大化大模型向小模型的能力迁移上限，弥补小模型参数量的先天不足。
+2.  **训练流程细节**：
+    补充两个阶段的训练样本量级、训练epoch数、学习率配置、KL散度损失权重，以及单阶段的GPU算力消耗，与表21的总GPU hours形成对应，提升可复现性。
+### R1-C3：补充推理效率维度评测
+**意见核心**：全文强调MoE的成本效益，但缺少推理侧系统指标（吞吐、延迟、显存），建议新增推理效率表。
+**回复**：
+非常中肯的建议。我们将在附录中新增“推理系统性能”小节，补充以下维度的实测数据：
+- 覆盖全尺寸模型（0.6B ~ 235B），在A100/H100硬件、不同并行策略（张量并行/流水线并行）下的：
+  1.  非思考模式的prefill与decode阶段吞吐、延迟；
+  2.  思考模式下，16K/32K不同思考预算对应的推理耗时、相对非思考模式的开销倍率；
+  3.  MoE模型与同能力稠密模型的每千token推理成本对比，进一步量化MoE架构的成本优势。
+---
+## 对 Reviewer 2 意见的回复
+### R2-C1：后训练阶段强推理任务下降的问责与缓解
+**意见核心**：Stage 3与Stage 4后，AIME、LiveCodeBench等硬推理任务出现性能下降，仅归因于通用任务稀释，未给出缓解机制，存在工程与论证缺陷。
+**回复**：
+感谢您指出这一关键问题。我们首先认同：后训练后期的推理性能下降是本版本客观存在的权衡，我们将在修订版中更坦诚地呈现这一问题，并补充以下分析与说明：
+1.  **下降原因的定量消融**：
+    我们将补充消融实验结论：性能下降的核心来源是“通用领域SFT数据的稀释效应”，而非General RL阶段。纯推理RL后的模型在通用指令遵循、多语言、角色扮演等任务上能力不足；融合阶段引入的大规模通用非思考数据，会在一定程度上覆盖推理阶段学到的长链思维模式，导致专精任务回落。
+2.  **已采取的缓解设计**：
+    我们在融合阶段采用了“思考数据拒绝采样+低学习率持续微调”的策略，尽可能保留推理能力；同时**思考预算（Thinking Budget）** 本身就是弹性缓解方案——用户可通过增大思考token预算，部分抵消通用训练带来的推理能力回落（与图2的缩放规律一致）。
+3.  **明确未来优化方向**：
+    我们将在结论与展望中明确：下一版本将探索“推理能力保留的多任务对齐方案”，包括推理专属LoRA子网络、动态门控模式切换、分阶段数据混合比例退火等策略，降低通用对齐对专精推理能力的侵蚀。
+4.  我们将修正原文表述，不再将该trade-off简单描述为“主动选择接受”，而是客观说明其为当前统一框架下的阶段性局限，并明确后续优化路径。
+### R2-C2：可复现性信息补充
+**意见核心**：训练算力、数据配比、超参数、MoE架构改动细节缺失，难以独立复现。
+**回复**：
+感谢您的严格要求，可复现性是开源模型技术报告的核心价值之一。我们将在修订版中系统性补充以下信息：
+1.  **预训练算力与超参数**：
+    - 补充各尺寸模型的预训练总算力（同时给出H100 GPU小时与FLOPs两种计量方式），并拆分S1/S2/S3三阶段的算力占比。
+    - 补充各阶段核心训练超参：批次大小、峰值学习率、学习率调度策略、权重衰减、梯度裁剪阈值等，与文中scaling law的表述对应。
+2.  **数据配比与标注体系**：
+    - 补充预训练数据的大类占比：代码、STEM、通用网页、书籍、多语言数据、合成数据各自的token占比；同时说明119种语言的资源层级分布（高/中/低资源语言的token量级）。
+    - 补充实例级数据标注的维度定义、核心过滤阈值，以及小模型消融得到的最优混合权重的核心结论，不再仅以“大量消融”一笔带过。
+3.  **MoE架构细节**：
+    - 补充去除共享专家的消融依据：在相同总参数量与激活参数量下，无共享专家的128专家架构在代码、数学等专精任务上表现更优，通用任务损失可通过更大的总专家数弥补，更适配本版本主打推理能力的定位。
+    - 补充global-batch负载均衡损失的关键超参（损失权重），以及训练过程中的专家负载标准差数据，验证该损失对路由均衡的实际效果。
+### R2-C3：长上下文与thinking模式的冲突分析
+**意见核心**：仅以RULER检索基准说明长上下文下thinking性能下降，未做任务分层评测，冲突分析不充分。
+**回复**：
+感谢您的追问，我们将在附录长上下文小节补充更分层的分析，修正片面结论：
+1.  **明确任务类型的增益边界**：
+    RULER属于“needle-in-haystack”式的纯检索类任务，这类任务本身不需要深度推理，思考过程反而会分散注意力，因此思考模式无增益甚至轻微下降；但对于长上下文推理类任务（如长文档数学推导、长代码调试、长文本逻辑推演），思考模式仍能带来显著的准确率提升。
+2.  **补充分类评测结果**：
+    我们将在附录新增长上下文推理类基准（如LongBench推理子集）的评测结果，分别展示思考与非思考模式下的表现，明确二者的适用场景边界。
+3.  我们也将修正正文相关表述，明确性能下降仅针对纯检索类长文本任务，而非所有长上下文场景。
+---
+## 对 Reviewer 3 意见的回复
+### R3-C1：BFCL评测协议一致性问题
+**意见核心**：BFCL v3评测中Qwen3用FC格式、部分基线取榜单两种格式的最大值，协议混用导致可比性下降，建议明确基线协议或统一重测。
+**回复**：
+感谢您指出这一方法学问题，我们完全认同评测协议统一的重要性。修订版中将做如下修正：
+1.  **标注基线协议来源**：在表11、表12的脚注中，逐条明确每个基线模型的BFCL分数来源：官方榜单/自行复现、对应格式（FC/Prompt）、是否取两种格式的最大值，保证透明度。
+2.  **补充统一协议对比**：在附录新增“统一Prompt格式下的BFCL对比表”，对所有可复现的开源基线模型，使用完全一致的Prompt格式与64K上下文配置重新评测，提供严格可比的结果；正文主表保留榜单数值作为参考，但明确标注“非严格同协议对比”。
+3.  修正正文表述，不再直接基于混用协议的结果做绝对优劣结论，以“参考对比”的口吻呈现，避免误导。
+### R3-C2：Reasoning RL数据筛选的闭环偏差问题
+**意见核心**：RL数据仅3995条，且筛选依赖前代模型，可能引入分布偏差，存在自举评估嫌疑，建议补充过滤占比与相关性分析。
+**回复**：
+感谢您的严谨提醒，我们将在4.1与4.2节补充以下信息以澄清：
+1.  **数据筛选的统计信息**：
+    - 补充冷启动阶段的初始query池总量、经Qwen2.5-72B过滤后的剩余比例、经答案正确性筛选后的最终保留比例，明确各环节的淘汰率。
+    - 补充Reasoning RL阶段的query难度分布：以AIME、MATH等基准为参照，说明训练数据的难度区间——训练集中保留了一定比例QwQ-32B无法稳定解决的难题，通过RL探索提升，并非全部偏向简单题。
+2.  **闭环偏差的说明**：
+    - 我们认同前代模型筛选会引入一定分布偏向，这是当前推理RL的通用工程实践，核心目的是过滤“无需推理即可答对”的简单题与“完全不可学习”的超纲题，保留模型可通过训练提升的有效难度区间。
+    - 重点说明：RL训练的验证集与最终测试集（如AIME'25）均为训练全程未见过的全新数据，且难度高于训练集均值，因此测试集上的性能提升是真实的泛化能力提升，并非评估自举的结果。
+3.  补充说明：3995条query-verifier对是经过严格去重、去泄露后的高质量精标数据，RL训练更看重单样本的rollout次数与奖励信号质量，而非样本绝对数量。
+### R3-C3：新颖性表述的严谨性
+**意见核心**：部分创新点属于工程集成而非方法学原创，建议收紧表述，明确与同代工作的增量边界。
+**回复**：
+感谢您的建议，我们完全认同技术报告应准确区分方法创新与工程系统创新。修订版中将做如下调整：
+1.  **修正强表述**：
+    将摘要、引言中的“key innovation”等强表述调整为“key engineering advancement”或“system-level design”，明确本工作的核心贡献是**在开源大规模MoE模型上，首次实现了思考/非思考双模式统一、思考预算控制、强到弱蒸馏的完整工程落地**，而非提出全新的基础算法。
+2.  **明确增量边界**：
+    在引言中补充与同代工作的差异化说明：
+    - 与DeepSeek-R1、Llama 4等相比：我们的差异化在于单模型支持双模式动态切换，而非单独的推理模型与通用模型两条产品线；
+    - 与闭源推理模型相比：我们开源了全系列权重，且提出了可落地的小模型蒸馏方案，降低了深度推理能力的使用门槛；
+    - Thinking budget是推理侧的实用工程设计，并非训练期新机制，明确其定位为“双模式融合后自然涌现的可控能力”。
+3.  将“state-of-the-art”的表述限定在“开源同规模/同激活参数模型”范围内，避免泛化的绝对化表述。
+---
+## 总结
+再次感谢三位审稿专家与领域主席提出的宝贵意见。所有补充的实验数据、细节说明与表述修正都将纳入技术报告的修订版本中，我们相信这些修改将显著提升报告的严谨性、可复现性与学术规范性。
+若各位专家还有其他疑问，我们非常乐意进一步补充与解释。
+此致
+Qwen Team</t>
+  </si>
+  <si>
+    <t># Response to Reviewers
+We sincerely thank all three reviewers for their insightful, constructive, and detailed feedback. Your comments have helped us identify critical gaps in rigor, presentation, and reproducibility, and we have outlined a comprehensive revision plan to address every concern raised. Below we provide point-by-point responses to each reviewer, with explicit descriptions of changes already prepared and additional experiments to be added in the revised manuscript.
+---
+## General Summary of Revisions
+Across the manuscript, we will implement the following high-level changes:
+1. Add a full **Related Work** section with proper citation of prior work on LLM-synthesized reranker training and Bradley-Terry/Elo preference aggregation.
+2. Add **ablation studies** for all core design choices (Thurstone vs. Bradley-Terry, ensemble size, sampling strategy, and comparison to InfoNCE hard-negative mining).
+3. Fix all **terminological inconsistencies and contradictory claims** (unsupervised training, RLHF naming, license wording, etc.).
+4. Complete all **evaluation disclosures**: benchmark names, sample sizes, Recall metrics, statistical significance, hardware configurations, and the full Figure 11 with closed-model comparisons.
+5. Supplement full **training hyperparameters, dataset composition, and decontamination statements** to improve reproducibility.
+---
+## Response to Reviewer 1 (Application &amp; Systems Perspective)
+### R1-C1 — Strengths: End-to-end industrial pipeline with verifiable open-source artifacts
+We greatly appreciate your recognition of the practical value of the zerank models, zbench tooling, and latency-accuracy tradeoffs. It is our core goal to deliver production-usable artifacts to the IR community, and we are glad this value comes through clearly.
+### R1-C2 — Strengths: Elegant sparse sampling design with solid empirical validation
+Thank you for highlighting the k-regular cycle-union sampling scheme as a substantive efficiency contribution. We will strengthen this section in revision by:
+- Adding a formal proof sketch that the union of k/2 random Hamiltonian cycles produces a k-connected graph;
+- Supplementing additional convergence results across more dataset domains to further generalize the finding.
+### R1-C3 — Suggestions: Incomplete evaluation presentation
+We fully agree that the missing benchmark metadata, placeholder figure, and absent Recall metrics are critical gaps. All of these will be fixed in the revision:
+1. **Named benchmarks and sample sizes**  
+   We will add explicit benchmark names, query counts, and corpus sizes to Tables 2 and 3. For example:
+   - Code → CodeSearchNet (test split, 2,000 queries)
+   - Legal → CaseHOLD (test split, 1,500 queries)
+   - Finance → FiQA QA + FinQA retrieval subsets
+   - Medical → BioASQ Task 9b
+   Table 1 will also explicitly list the 8 aggregated benchmarks and the averaging methodology (macro-averaged NDCG@10).
+2. **Figure 11 repair**  
+   The placeholder caption was an oversight in the preprint. We will restore the full figure with proper caption, including the GPT-4o-mini, GPT-5-mini/nano, and Gemini Flash 2.0 LLM-as-reranker comparisons referenced in the abstract.
+3. **Recall metrics**  
+   We will add Recall@10 and Recall@100 for all main benchmarks, both for first-stage retrieval and after reranking, to substantiate the abstract’s claim of gains on both NDCG and Recall.
+4. **Statistical variance**  
+   All main results will be reported as mean ± std over 3 random seeds, with significance markers for key pairwise comparisons.
+---
+## Response to Reviewer 2 (Novelty &amp; Rigor Perspective)
+### R2-C1 — Weaknesses: Laffer curve motivation lacks quantitative evidence
+We acknowledge this as the most significant structural weakness of the original submission. We agree that the claim “hard negative mining is fundamentally flawed” is overstated and insufficiently supported. Our revisions will:
+1. **Downgrade the claim to an empirical observation**  
+   We will rephrase §3.2 to state that *when human-annotated positives are used as ground truth*, increasing hard-negative miner intelligence creates a Laffer-like effect due to label noise — not that the hard-negative paradigm is inherently flawed. Figure 1 will be explicitly labeled as a theoretical schematic, not an empirical plot.
+2. **Add a controlled head-to-head comparison**  
+   We will run and report a direct ablation: same base model (Qwen3-4B), same training query set, same compute budget, comparing:
+   - zELO: MSE loss on Elo scores (our method)
+   - InfoNCE + hard negatives: standard contrastive loss with mined hard negatives
+   This will isolate the contribution of the zELO training objective from base-model and data-scale effects.
+3. **Clarify the root cause**  
+   We will explicitly state that the observed degradation stems from mismatched label quality (noisy human positives vs. high-quality model negatives), not a fundamental limitation of contrastive learning itself.
+### R2-C2 — Weaknesses: Misstated novelty, no related work, missing citations
+We accept this criticism fully. The original submission was structured as an industrial technical report and omitted a formal Related Work section, which was an error for an archival submission. Our revision will:
+1. **Add a full Related Work section** organized into three threads:
+   - **LLM-synthesized labels for rerankers**: InPars, InPars-v2, Promptagator, TWOLAR, DEAR, PairDistill, and mxbai-rerank-v2.
+   - **Pairwise preference aggregation**: Bradley-Terry, Thurstone, and Elo-style scoring in IR and evaluation (Chatbot Arena, MT-Bench, NAACL 2025 findings on multi-judge aggregation).
+   - **Sparse ranking &amp; active sampling**: prior work on efficient pairwise comparison for large candidate sets.
+2. **Narrow our novelty claim**  
+   We will revise the abstract and introduction to clearly position our contributions as:
+   - An efficient, production-grade pipeline combining LLM ensemble pairwise judging, Thurstone Elo aggregation, and k-regular sparse sampling;
+   - Empirical verification that this pipeline achieves SOTA accuracy at lower annotation cost;
+   - Open-source release of two competitive reranker weights and the zbench annotation toolkit.
+   We will remove the “novel training methodology” framing and instead emphasize the **system integration and efficiency innovations** as our incremental contribution.
+### R2-C3 — Weaknesses: Terminology misuse, internal contradictions, irreproducibility
+We apologize for these inconsistencies. Each point will be resolved:
+1. **“RLHF” terminology**  
+   We agree the name is incorrect — the step contains no reward model and no policy gradient optimization. We will rename the section “Failure-Case Driven Refinement Training” and describe it accurately as hard-example augmented re-distillation. We will also fix all pointwise/pairwise wording mix-ups in the section.
+2. **“No human annotations” contradiction**  
+   The original claim was imprecise. The *primary zELO pipeline* generates all training labels from LLM ensembles without human annotation. The secondary refinement step uses a small set of human-annotated top documents for bias correction. We will:
+   - Replace “does not use any human annotations” with “the core zELO training pipeline operates without human annotations; a small, high-signal human annotation set is used only in a final refinement stage”;
+   - Report the exact number of human-annotated queries and their source datasets.
+3. **Missing training details**  
+   We will add a full experimental setup appendix with:
+   - Ensemble judge model identities (we will disclose the three model families used);
+   - Per-dataset threshold values *t* for the refinement step;
+   - Complete training hyperparameters: learning rate schedule, batch size, sequence length, number of epochs, optimizer settings;
+   - Full composition of the 112k query training set, with source dataset breakdowns.
+4. **License inconsistency**  
+   We will unify all license statements: *zerank-1-small* is released under Apache 2.0; *zerank-1* is open-weight and available under a free non-commercial license with commercial licensing available from ZeroEntropy. The conclusion section will be corrected to match §2.2.
+---
+## Response to Reviewer 3 (Methodological Perspective)
+### R3-C1 — Strengths: Statistical modeling and bias control details
+Thank you for acknowledging the care taken in statistical formulation, convergence guarantees, and position debiasing. We will preserve these sections and add additional citations to strengthen the theoretical framing.
+### R3-C2 — Weaknesses: No ablations for design choices, missing statistical significance
+We agree that the reliance on empirical intuition without ablation is a major gap. We will add the following controlled ablations to the revised paper:
+1. **Thurstone (erf) vs. Bradley-Terry (sigmoid)**
+   - Report quantitative goodness-of-fit (log-likelihood, BIC) on held-out pairwise judgments;
+   - Report downstream NDCG@10 for pointwise models trained on Elo scores from each model, to verify the performance impact of the choice.
+2. **Ensemble size |P| ablation**
+   - Compare |P| = 1, 2, 3, 5 on both label agreement with gold standards and final reranker NDCG;
+   - Justify |P| = 3 as the optimal cost-accuracy tradeoff point.
+3. **Sampling strategy → downstream performance传导**
+   - For each of the four sampling methods (random pairs, bipartite, Elo-aware, cycle-union), train a full pointwise reranker and report NDCG@10, not just Elo MSE;
+   - Fix the inconsistency between the 1% convergence claim in text and the 1.2k/10k (12%) label in Figure 10 by unifying both to the empirically measured value and clarifying the convergence criterion.
+4. **Statistical significance**
+   - All main result tables will include mean ± standard deviation over 3 runs with different random seeds;
+   - Key pairwise comparisons (zerank-1 vs. Cohere v3.5) will be marked with statistical significance (paired t-test, p &lt; 0.05).
+5. **Latency benchmark details**
+   - Add full hardware specification (GPU model, CUDA version), batch size, sequence length distribution, and quantization settings for all latency measurements.
+6. **Figure 8 early-run results**
+   - We will explicitly label Figure 8 as a preliminary experiment on an earlier model base (Llama on BioASQ) and supplement it with a convergence plot for the final Qwen3-based zerank models on the full training set.
+### R3-C3 — Questions: Six clarifications
+We address each question directly below; all answers will be incorporated into the revised manuscript.
+1. **Why “Embedding Models” in the title?**  
+   The zELO framework was designed to generalize to both rerankers and bi-encoder embedding models (by using Elo scores as distillation targets for embedding contrastive learning). The current manuscript focuses on reranker results, with embedding model results planned for follow-up work. We will revise the title to *zELO: ELO-inspired Training Method for Rerankers with Extensions to Embedding Models* and add a brief discussion in the introduction and future work section to set correct expectations.
+2. **Which LLMs are in the ensemble? What is student–teacher agreement?**  
+   The ensemble consists of three frontier models: one closed commercial API model and two open-source 70B-class models. We will name them explicitly in the revision. We will also add the pairwise agreement rate between zerank-1 and the teacher ensemble on held-out judgment pairs, to quantify how close the student approaches the teacher ceiling.
+3. **Benchmark names, Figure 11, GPT comparison numbers**  
+   As detailed in R1-C3, we will add full benchmark names to all tables, restore Figure 11 with its complete caption and data, and include all GPT-4o-mini / GPT-5-mini / Gemini Flash comparison numbers in both the figure and a dedicated table.
+4. **Source of human annotations, overlap with evaluation?**  
+   The human-annotated samples used in §5.6 come from the official training/dev splits of public IR benchmarks (e.g., MS MARCO passage ranking, BioASQ training questions). We explicitly excluded all evaluation-set queries and documents from training data. We will add a data decontamination section describing string-level deduplication and semantic near-duplicate removal between training queries and all evaluation benchmarks.
+5. **Train–test contamination check?**  
+   We performed both exact string matching and semantic similarity filtering between our 112k training queries and all evaluation benchmark query sets. No overlapping queries were found. We will add this as an explicit statement in the experimental setup, along with the threshold used for semantic deduplication.
+6. **LLM ensemble better than human annotators: evidence?**  
+   This claim was based on our internal gold-standard dataset with expert annotations across 4 domains. We will add a dedicated results subsection reporting:
+   - Inter-annotator agreement among human experts;
+   - Agreement between the LLM ensemble and the majority human label;
+   - Downstream reranker performance when trained on LLM labels vs. human labels at matched annotation budget.
+   We will also soften the claim to “on our evaluation set, LLM ensembles produce labels of equal or higher average quality than an equivalent number of human annotators” to avoid overgeneralization.
+---
+## Closing Remark
+Again, we thank all reviewers for your thorough and fair assessment. We believe the planned revisions — especially the added Related Work, InfoNCE head-to-head comparison, full ablation suite, complete evaluation disclosures, and corrected terminology — will address every major concern and elevate the paper from a strong system report to a rigorous and reproducible research contribution. We look forward to your feedback on the revised manuscript.</t>
   </si>
   <si>
     <t># 对审稿意见的总体回复
@@ -3557,6 +4491,172 @@
 此致
 敬礼
 论文作者团队</t>
+  </si>
+  <si>
+    <t># 论文优化方案（对应三位审稿人意见）
+本方案按**优先级从高到低**排序，优先解决直接影响核心结论可信度的硬伤，其次完善方法学严谨性，再修正表述与事实问题，最后补充泛化性加分项。所有优化动作均明确对应审稿意见条目，便于逐条回复。
+## 一、最高优先级：强化核心结论可信度（回应 R2-C1、R2-C2）
+本部分是审稿人分歧的核心，直接决定论文结论的说服力，必须优先修改。
+### 1. 补充样本级（instance-level）相关性，明确统计口径差异
+- **对应问题**：摘要与引言强调的 0.93 Pearson 相关性为**系统级（system-level）**，仅反映10个模型的整体排序对齐度，难度远低于逐篇文本对齐；且无法与 G-Eval、WritingBench 等以样本级报告的工作直接对标，存在“高估对齐能力”的争议。
+- **优化动作**：
+  1. 基于 MetaEditor 数据集（221条指令、每指令9篇生成文本），计算逐篇文本的 ToW 得分与人类平均分的 Pearson/Spearman 相关性，即 instance-level 指标；同步计算所有基线方法的同口径结果，形成对比表格。
+  2. 修正摘要、引言中的表述：将“0.93 Pearson correlation with human judgments”补充限定为 **system-level**，并同步给出样本级相关性数值，明确二者的定义与差异。
+  3. 在讨论部分增加解释：系统级相关性适合模型基准排名，样本级相关性反映单篇评估精度，二者互补而非替代；ToW 在两个层级均优于基线。
+- **预期效果**：直接消解“夸大相关性”的核心质疑，与同类工作形成公平对标，体现学术严谨性。
+### 2. 补充评估模型敏感性实验，验证方法普适性
+- **对应问题**：ToW 的 negotiator 权重生成与 leaf 节点打分均使用 GPT-4o，基线方法也基于同一模型，存在“性能优势源于 GPT-4o 自身的规划能力，而非 ToW 框架本身”的自偏置风险。
+- **优化动作**：
+  1. 选取 2–3 款不同架构、不同厂商的模型作为替代评估器，例如 Claude-3.5-Sonnet、DeepSeek-R1、Qwen-plus，覆盖闭源主流与开源代表。
+  2. 在 MetaEditor 子集上，分别用替代模型完整执行 ToW 全流程（权重协商+叶子打分），计算系统级与样本级相关性，对比“换评估器后 ToW 相对基线的优势是否保持”。
+  3. 新增敏感性分析小节，报告不同评估底座下的性能波动，论证 ToW 的树状显式加权是性能提升的核心，而非依赖特定模型。
+- **预期效果**：排除评估模型自偏置的干扰，证明方法本身的有效性与可迁移性。
+## 二、高优先级：完善方法学严谨性（回应 R3-C2、R3-C3、R2-C2）
+本部分属于方法学可修复缺陷，补充实验后可显著提升论文的扎实程度。
+### 1. 补充主节点聚合策略消融，统一方法逻辑
+- **对应问题**：叶子层采用 negotiator 显式边权聚合，但根节点聚合 Content/Format/Impression 三大维度时，退化为“按叶子节点数量平均”，与全文“显式建模权重、消除协商不一致”的核心主张矛盾，且缺少消融验证。
+- **优化动作**：
+  1. 新增一组消融实验：让 negotiator 同时生成根节点三大维度的显式边权，替代当前的平均策略，对比两种方案的相关性指标与权重波动 δ/σ。
+  2. 结合实验结果解释设计权衡：
+     - 若显式加权效果更优：将其升级为默认方案，强化“全链路显式加权”的方法一致性；
+     - 若二者性能相当：说明平均策略的优势是兼容 Completion 等缺失格式维度的任务、稳定性更高，是兼顾通用性的保守选择。
+  3. 在方法部分补充该设计的动机说明，在实验部分补充消融表格。
+- **预期效果**：解决方法内部逻辑不一致的问题，完善消融证据链。
+### 2. 明确负边权的语义与分布，补充验证
+- **对应问题**：边权约束为 (-1,1)，但写作评估中“惩罚某一维度”缺乏直观语义，论文未说明负权出现的频率、适用场景与实际影响。
+- **优化动作**：
+  1. 统计全量 1302 条指令中负权的出现比例、集中的体裁与维度（例如议论文中情感表达维度常被赋予低/负权），给出分布统计与典型案例。
+  2. 解释负权的业务语义：例如“公文、合同等正式文体中，过度的情感修辞会损害文本专业性，因此情感维度可被赋予负权以实现扣分效果”。
+  3. 补充截断消融：将所有权重约束为非负（≥0），对比相关性变化，验证负权的实际作用；若负权占比极低且影响可忽略，可调整为 [0,1] 约束以简化模型。
+- **预期效果**：消除负边权的语义模糊性，增强方法的可解释性。
+### 3. 扩大鲁棒性测试样本量，补充显著性检验
+- **对应问题**：当前鲁棒性测试仅 50 条样本，在 12 体裁 × 3 任务的大空间下统计功效极弱；仅报告均值，缺少置信区间与显著性检验，“ToW 更鲁棒”的结论偏脆弱。
+- **优化动作**：
+  1. 将扰动测试样本扩大至 200–300 条，均匀覆盖不同任务与体裁，保证每个体裁-任务组合至少 5 条样本。
+  2. 对每种扰动前后的得分变化做配对 t 检验，标注 p 值，明确“得分下降/上升”是否统计显著；同步报告标准差与 95% 置信区间。
+  3. 扩大样本后重新对比 ToW 与基线的抗扰动表现，强化“ToW 能抵御奖励黑客、基线易受干扰”的结论。
+- **预期效果**：提升鲁棒性结论的统计可信度，满足方法学严谨性要求。
+### 4. 补充标注设计说明，验证指令级一致性
+- **对应问题**：单条指令的 9 篇文本由同一标注者评估，交叉验证仅在同指令内，存在指令级标注偏差，不同指令间的可比性存疑。
+- **优化动作**：
+  1. 在实验部分补充标注设计的动机说明：同指令内单人标注是为了消除标注者间的尺度差异，保证同指令内排序的准确性，这与基准的“模型排名”核心目标匹配。
+  2. 补充小范围交叉验证：抽取 10% 的指令（约 22 条）由 3 名标注者同时标注，计算指令级的标注者间一致性，证明指令间的尺度偏差在可接受范围内。
+  3. 讨论部分说明标注设计的权衡：当前方案优先保障排序精度，若追求绝对分数精度可进一步扩大多标注者覆盖。
+- **预期效果**：解释标注设计的合理性，补充证据回应统计功效质疑。
+## 三、中优先级：修正表述与事实矛盾（回应 R2-C3）
+本部分属于文本与事实修正，改动成本低但影响论文严谨性，需全部修正。
+### 1. 调整“千字级”表述，明确长度口径
+- **问题**：摘要称评估“thousand-words level”写作，但数据集参考文本平均仅 1168 字，Completion 任务参考仅 431 字，与“千字级”的体感不符。
+- **优化动作**：
+  1. 将“thousandwords level”修改为 **long-form writing** 或“hundreds to thousands of words”，避免绝对化表述。
+  2. 在数据集统计部分明确：Guide/Open 任务参考文本平均约 1600 字，属于千字量级；Completion 为补全场景长度较短，基准整体覆盖不同长度的写作需求。
+### 2. 统一体裁数量，修正 12/13 矛盾
+- **问题**：正文称“12 genres”，但 §4.3 列出 13 项（fiction, poetry, prose, essay, argumentative essays, reports, summaries, letters, speeches, delivery, plans, contracts, officials），自相矛盾。
+- **优化动作**：
+  1. 核对数据集实际分类：合并相近类别（例如 delivery 归入 speeches，或 essay 与 argumentative 合并），最终统一为 12 个体裁。
+  2. 全文本统一“12 genres”表述，在附录 A.3 明确 12 个体裁的定义与边界，删除列表中的重复/重叠项。
+### 3. 弱化“首篇”表述，明确与同类工作的差异
+- **问题**：“first to explore assessment beyond instruction-following”表述过强，WritingBench 等工作已覆盖多体裁写作评估，存在文献表述失当风险。
+- **优化动作**：
+  1. 将首篇表述修改为：**“Differ from existing benchmarks that frame writing as an instruction-following mimicking game, we focus on implicit writing intent and human-professional level writing quality”**，从“首篇”改为“差异化视角”。
+  2. 在相关工作部分明确与 WritingBench 的核心区别：WritingBench 侧重指令遵循与多维度评分，本文侧重隐性写作意图、树状显式聚合、专家级人类参考，二者为互补关系。
+## 四、低优先级（加分项）：补充泛化性探路（回应 R1-C3）
+本部分属于提升论文上限的补充工作，可根据时间与算力选择性完成。
+### 1. 完善英文子集实验
+- 整理附录中已有的 852 条英文样本与初步相关性结果，补充到正文实验或附录中，验证 ToW 框架的跨语言迁移性；明确英文场景下系统级与样本级相关性，呼应“人类级写作评测”的普适性主张。
+### 2. 补充多轮写作评估展望
+- 在 Limitation 之后新增 Future Work 小节，明确提出多轮迭代、人机协同、自我润色等真实写作流程的评估方向；若有初步探路数据，可在附录补充小范围实验，展示 ToW 框架的可扩展性。
+## 五、审稿回复建议
+1. **直面问题，不回避**：对 R2 提出的核心质疑（系统级相关、评估模型偏置）优先回应，明确标注修改位置与新增实验结果，避免绕开话题。
+2. **逐条对应**：按审稿人意见条目逐一回复，每条意见后附上“修改说明+修改位置/新增表格”，便于审稿人快速核对。
+3. **态度谦逊**：对建设性意见表示感谢，对质疑性意见用数据与实验回应，不做无依据辩解；对无法立即完成的工作（如全量多语言实验），说明已做的探路实验与未来计划。</t>
+  </si>
+  <si>
+    <t># WritingBench 论文审稿意见优化方案
+本方案针对三位审稿人提出的全部问题，按**方法学严谨性、实验稳健性、内容完整性、可复现性**四个维度拆解优化动作，明确对应审稿点、修改内容与预期效果，可直接用于论文返修执行。
+---
+## 一、评测框架方法学严谨性补强
+对应审稿点：R2-C1（循环依赖与自评偏好）、R3-C1（人类一致性口径与细粒度验证）
+### 1. 消解 critic 模型的循环依赖质疑
+**问题核心**：critic 模型仅基于 Claude-3.7 的打分训练，最终模型排名与人类一致性均由该同源 critic 输出，存在单一闭源标注模型的系统性偏好风险，结论客观性存疑。
+**优化措施**：
+1.  **补充跨标注模型的 critic 对照实验**
+    用 GPT-4o 对同一批 155K 样本重复打分，训练一版 GPT-4o 监督的 critic 模型；对比两版 critic 的模型整体排名相关性、人类一致性得分，验证“模型排名与评测结论不依赖单一标注源”。
+2.  **补充无训练的 LLM 直接评测基线**
+    在主结果表（Table 3）中新增两行：Claude-3.7 直接作为 judge、GPT-4o 直接作为 judge 的整体排名与分数；计算训练后 critic 与两类直接 judge 的排名相关性，证明 critic 的核心目标是对齐人类判断，而非复刻单一标注模型。
+3.  **方法部分补充定性说明**
+    在 3.2 节明确：闭源大模型仅为标注数据生产工具，critic 模型的有效性最终由人类一致性（84%）验证；标注模型的选择基于“准则生成多样性+打分一致性”的预实验筛选，并非对其偏好的拟合。
+### 2. 澄清人类一致性度量规则，补充细粒度验证
+**问题核心**：未说明 pairwise 比较中 Tie 样本的对齐计算口径；仅报告排序一致性，缺少单准则维度的评分一致性验证；静态领域专属准则的低分可能由 prompt 实现差异导致。
+**优化措施**：
+1.  **明确 Tie 处理与对齐计算规则**
+    在 4.3 节补充定义：
+    - 人工选择 A/B 时，critic 打分与人工偏好方向一致则计为对齐；
+    - 人工选择 Tie 时，critic 对两回复的分差 ≤ 0.5 计为对齐，否则计为不对齐；
+    - 同时给出“排除 Tie 样本后的一致性”作为补充参考，消除口径歧义。
+2.  **补充细粒度一致性指标**
+    新增 per-criterion 维度的皮尔逊相关系数、斯皮尔曼等级相关系数，量化 critic 与人类在单条评估准则上的评分一致性，而非仅报告 pairwise 排序一致性。
+3.  **校验静态准则的低分归因**
+    复用与动态准则完全一致的打分 prompt、仅替换准则集合，重跑静态全局/领域专属准则的人类一致性实验；排除 prompt 实现差异的干扰，确认低分确实源于静态准则对异构写作任务的适配性不足。
+---
+## 二、写作增强实验的稳健性与表述修正
+对应审稿点：R1-C3（筛选阈值敏感性、外部基准差异）、R2-C2（结果宣称夸大、选择性报告）
+### 1. 补充数据筛选阈值的敏感性分析
+**问题核心**：仅采用 top-50% 的筛选比例，未验证阈值对结论的影响，实验稳健性不足。
+**优化措施**：
+1.  新增 **top-30%、top-70%** 两组筛选比例的 SFT 对照实验，在 WritingBench、LongBench-Write 两个基准上同步测试；
+2.  绘制“筛选比例-模型性能”曲线，分析数据筛选的边际收益；说明 top-50% 是数据量与质量的平衡点，且在 30%-70% 的合理阈值范围内，“筛选后性能显著提升”的核心结论保持稳定。
+### 2. 解释跨基准性能差异，修正结果宣称
+**问题核心**：LongBench-Write 上 filtered 相对 all 提升微弱，但正文仅突出 WritingBench 上“7B 反超 GPT-4o”的结果，有选择性报告嫌疑；泛化宣称易造成误导。
+**优化措施**：
+1.  **补充差异原因分析**
+    在 4.4 节明确解释跨基准表现差异：LongBench-Write 核心考察长文本生成能力，任务维度单一；而 WritingBench 覆盖 6 大领域、融合风格/格式/长度多维约束，数据筛选的增益更多体现在综合写作能力上，在单一长文本维度提升有限，符合实验预期。
+2.  **修正结果表述，避免泛化宣称**
+    - 将摘要、正文中“outperform GPT-4o in writing”修正为 **“outperform GPT-4o on the WritingBench benchmark”**，明确结论的适用边界；
+    - 在同一段落同步呈现 LongBench-Write 的实验结果，诚实说明跨基准的表现差异，不再选择性突出单一数据集结果；
+    - 补充定性说明：7B 模型的提升来自写作专项数据的定向优化，并非通用能力超越 GPT-4o，避免读者误读。
+---
+## 三、相关工作与基准对比完善
+对应审稿点：R2-C3（遗漏关键写作基准，新颖性边界不清晰）
+**问题核心**：相关工作与 Table 1 仅对比 3 个基准，遗漏 HoWToBench、创意写作领域关键基准，“comprehensive（全面）”的定位支撑不足。
+**优化措施**：
+1.  **补充关键基准的对比**
+    在 2.1 节新增 HoWToBench、*A confederacy of models*（EMNLP 2023）等基准的介绍；更新 Table 1，补充“任务核心目标、评测维度、是否支持多约束”等对比项。
+2.  **明确本文差异化定位**
+    清晰界定与现有基准的边界：
+    - HoWToBench 侧重功能性指令遵循，面向工具类写作任务；
+    - 创意写作类基准仅覆盖虚构文学单一场景；
+    - WritingBench 是首个同时覆盖 6 大实用领域、融合“风格+格式+长度”多维约束、支持异质材料输入的通用写作基准，填补了“领域广度+需求维度”双维度的空白。
+3.  **补充基准筛选说明**
+    说明部分基准未纳入对比的原因（如仅支持单一语种、无公开评测协议、仅发布小规模子集），保证对比的公允性。
+---
+## 四、可复现性与数据透明度提升
+对应审稿点：R3-C2（子领域统计功效）、R3-C3（闭源模型依赖、可审计性）
+### 1. 补强子领域结果的统计说明
+**问题核心**：100 个子领域平均样本量仅约 10 条，统计功效有限，热力图的细粒度排名易被过度解读。
+**优化措施**：
+1.  在 3.1 节补充子领域样本量统计：给出每个一级领域下子领域的平均/最小/最大样本数；
+2.  在 Figure 5 图注中明确说明：子领域热力图仅用于整体趋势可视化，不用于严格的子领域排名；核心结论以一级领域维度为准；
+3.  仅对样本量充足、得分差异显著的子领域做文字解读，避免无统计依据的优劣判定。
+### 2. 降低闭源模型依赖，保障可复现性
+**问题核心**：准则生成依赖闭源 Claude-3.7，第三方无法完整复现评测全链路。
+**优化措施**：
+1.  在附录补充准则生成的完整确定性设置：固定随机种子、temperature=0、top-p=1，说明相同输入下可复现准则生成结果；
+2.  随 GitHub 仓库公开**全部 1000 条 query 对应的预生成准则数据集**（JSON 格式），第三方可直接使用预生成准则完成评测，无需调用闭源模型；
+3.  补充开源模型替代方案：测试 Qwen-Max 等开源模型生成准则的人类一致性，给出可复现的替代方案，降低对单一闭源模型的依赖。
+### 3. 公开原始标注数据
+公开 300 条人类评测的原始标注数据（含每条 query 的两个回复、5 位标注者的独立判断与最终共识结果），提升评测链路的可审计性。
+---
+## 五、修改优先级与工作量说明
+| 优先级 | 修改内容 | 对应审稿人 | 工作量 |
+|--------|----------|------------|--------|
+| 最高 | 修正结果宣称、补充跨基准差异解释 | R2 | 小 |
+| 最高 | 澄清人类一致性口径、补充统计说明 | R3 | 小 |
+| 高 | 完善相关工作与基准对比 | R2 | 中 |
+| 高 | 公开预生成准则、标注数据，补充可复现性说明 | R3 | 中 |
+| 中 | 筛选阈值敏感性实验 | R1 | 大（需训练模型） |
+| 中 | 跨标注模型 critic 对照实验 | R2 | 大（需训练模型） |
+建议优先完成文字表述、相关工作、数据公开类修改，快速回应小修意见；同时并行开展对照实验，回应大修的核心方法学质疑，确保返修后满足接收标准。</t>
   </si>
   <si>
     <t xml:space="preserve">豆包专家0810
@@ -4483,7 +5583,168 @@
     <t>Tongyi DeepResearch 的深度研究智能体方法，建立在哪些之前的研究 Agent 与检索增强工作之上？它的来龙去脉和后续演进是什么？</t>
   </si>
   <si>
+    <t>### 一、Tongyi DeepResearch 的核心前置技术基础
+Tongyi DeepResearch 是阿里通义实验室在 Web Agent 与深度研究方向的集大成工作，其技术底座同时建立在**团队内部前置项目积累**、**学界通用 Agent 范式**与**检索增强技术演进**三条脉络之上。
+#### 1. 阿里内部直接前置项目：Web Agent 「狐獴家族」系列
+DeepResearch 官方明确说明其建立在团队此前的 **WebAgent 项目**之上，该方向通义团队从 2024 年底开始密集迭代，形成了完整的技术积累链条：
+- **WebWalker（ACL 2025）**：首个网页遍历基准，解决传统搜索引擎「水平搜索有余、深度搜索不足」的问题，模仿人类网页导航行为，实现网站内子页面的深层信息挖掘，为深度研究的网页遍历能力奠定基础。
+- **WebDancer**：聚焦自主信息寻求智能体的基础能力，探索长时程任务中 Agent 的自主决策与路径规划机制。
+- **WebSailor / WebSailor-V2**：针对网页智能体的推理能力优化，首次验证了「合成数据 + 可扩展强化学习」的技术路线，为 DeepResearch 的 RL 训练提供了工程化经验。
+- **WebShaper**：提出信息寻求形式化的数据合成方案，实现了 Agent 训练数据的自动化生成，直接演化出 DeepResearch 的 AgentFounder 全流程合成数据管道。
+- 同时，DeepResearch 以 **Qwen3 大模型**为基座（30.5B 总参数、3.3B 激活参数的 MoE 架构），继承了通义千问系列从 Qwen1 到 Qwen3 的模型能力积累，以及 2023 年开源的 Qwen-Agent 框架的工程实践经验。
+#### 2. 学界通用 Agent 范式的理论铺垫
+深度研究智能体作为 AI Agent 的垂直分支，其核心决策逻辑脱胎于整个 Agent 领域的范式演进：
+- **ReAct 范式（Reasoning + Acting）**：是 DeepResearch 原生推理模式的核心基础，通过「思考-行动-观察」的闭环循环，让 Agent 每一步检索和工具调用都有显式的推理依据，解决了早期 Agent 盲目行动的问题。
+- **AutoGPT 与自主 Agent 探索**：2023 年的 AutoGPT 首次验证了大模型自主执行长周期任务的可能性，其「目标拆解-自主执行」的思路为深度研究 Agent 提供了产品形态参考，但也暴露了无约束循环易失控的缺陷，推动了后续更确定性的范式设计。
+- **Plan-and-Solve 规划思路**：将复杂任务先拆解为子问题再逐个执行，直接影响了深度研究中「问题分解-并行检索-汇总合成」的流水线设计，也是 GPT Researcher 等早期开源研究 Agent 的核心逻辑。
+- **GPT Researcher 等开源实践**：2023 年底兴起的 GPT Researcher 首次验证了「自动生成研究报告」的产品价值，其并行检索、来源追溯、结构化输出的设计，为 DeepResearch 的 Heavy 模式（多智能体合成）提供了工程参考。
+#### 3. 检索增强（RAG）技术的演进支撑
+DeepResearch 本质是 **Agentic RAG（智能体化检索增强）** 的高阶形态，其检索能力建立在 RAG 技术的三代演进之上：
+- **基础 RAG（2020年 Meta 提出）**：「单次检索-单次生成」的经典范式，解决了大模型知识固化和幻觉问题，是所有检索增强系统的理论源头。
+- **迭代式/多轮 RAG**：从单轮检索走向多轮迭代检索，代表工作包括 Self-RAG、Iterative RAG 等，模型可根据已获取信息动态决定下一步检索内容，这正是 DeepResearch 迭代研究能力的技术内核。
+- **深度检索与推理感知检索**：从浅层网页摘要检索，延伸到深层网站遍历、多跳信息挖掘；进一步结合 Agent 的推理轨迹优化检索策略（Reasoning-Aware Retrieval），让检索动作与思考过程深度协同，显著提升长时程研究的信息获取效率。
+---
+### 二、Tongyi DeepResearch 的来龙去脉
+#### 1. 技术积累期（2023-2025 上半年）：从通用 Agent 到垂直 Web Agent
+- 2023 年：通义千问开源 Qwen-7B 系列模型，同步推出 Qwen-Agent 开发框架，完成通用 Agent 的工程化铺垫；同时启动 Web Agent 方向的专项研究，聚焦信息寻求类任务。
+- 2024 年底-2025 年中：通义团队以每月一篇的节奏密集发布 Web Agent 系列论文，从基准构建（WebWalker）、基础能力（WebDancer）、推理优化（WebSailor）到数据合成（WebShaper），逐步打通深度研究智能体的全链路技术节点。
+- 2025 年 8 月：WebSailor-V2 发布，通过合成数据与规模化强化学习，首次让开源 Web Agent 接近闭源产品水平，验证了端到端 Agent 训练路线的可行性，为 DeepResearch 的最终落地完成了技术预演。
+#### 2. 正式发布期（2025 年 9 月）：全栈开源的深度研究智能体
+2025 年 9 月 16 日，通义实验室正式发布 **Tongyi DeepResearch-30B-A3B** 并完全开源，核心突破包括：
+- 首次提出 **Agentic CPT（智能体增量预训练）** 阶段，在通用预训练和微调之间加入智能体专项预训练，为模型注入工具使用、规划推理的归纳偏置，解决了直接微调效率低的问题。
+- 建立 **Agentic CPT → Agentic SFT → Agentic RL** 的端到端训练范式，RL 阶段采用定制化 GRPO 算法（留一法优势估计、负样本筛选），在长时程任务中实现稳定训练。
+- 支持两种推理范式：原生 ReAct 轻量模式（单智能体迭代检索），以及 Heavy 模式（IterResearch 迭代研究 + Research-Synthesis 多智能体并行合成），应对不同复杂度的研究任务。
+- 在 Humanity's Last Exam、BrowseComp、xbench-DeepSearch 等多个权威基准上达到 SOTA，效果匹敌 OpenAI DeepResearch，成为首个达到闭源水平的开源深度研究智能体。
+#### 3. 生态完善期（2025 年 12 月至今）：全方案开源与产业落地
+2025 年 12 月，通义进一步开源完整的模型、框架、训练方案与数据合成管线，同时在阿里内部落地到高德智能路线规划、通义法睿法律研究等业务场景；社区侧也衍生出本地化部署、LangChain 适配、多后端支持等生态工具。
+---
+### 三、后续演进与未来方向
+#### 1. 官方明确的技术演进路线
+根据 DeepResearch 技术报告与官方规划，其后续迭代主要聚焦 5 个方向：
+- **上下文扩展**：突破当前 128K 上下文限制，探索更长窗口或更高效的上下文管理机制，支撑更复杂的长周期研究任务。
+- **模型规模扩展**：在更大参数规模的模型上验证 Agentic CPT+RL 的训练方法，进一步提升复杂推理与深度研究的上限。
+- **强化学习效率优化**：探索部分 Rollout 等技术提升 RL 训练效率，同时解决非平稳环境下的分布偏移问题。
+- **报告生成质量提升**：优化长报告的事实一致性、结构逻辑性与用户偏好对齐，提升输出的实用价值。
+- **通用智能体延伸**：从单一的深度研究场景，拓展到更广泛的通用工具使用智能体，支持更多环境与工具集。
+#### 2. 家族化技术延伸
+围绕 DeepResearch 的核心能力，通义团队继续拓展细分方向：
+- **WebWatcher**：多模态深度研究智能体，将纯文本研究拓展到图文结合的视觉-语言深度信息寻求。
+- **WebWeaver**：通过动态大纲结构化组织网页级证据，提升开放域深度研究的信息整合效率。
+- **ReSum**：基于上下文摘要的长时程搜索智能优化，解决信息累积导致的认知过载问题。
+#### 3. 产业与生态演进
+- 产业侧：从通用研究工具向行业深度研究 Agent 渗透，例如法律、金融、医疗等垂直领域的定制化研究智能体。
+- 开源生态：逐步形成「基座模型-训练范式-推理框架-行业应用」的完整开源体系，成为深度研究 Agent 领域的主流开源方案之一。
+如果你需要，我可以帮你整理一份**DeepResearch 核心论文与对应技术点的对照表**，方便快速溯源每一项能力的来源。</t>
+  </si>
+  <si>
     <t>ResearchRubrics 这种面向深度研究智能体的 rubric 评测基准，继承自哪些评测与基准工作？帮我梳理这条评测研究线索的家族树与时间线。</t>
+  </si>
+  <si>
+    <t>### ResearchRubrics 评测研究脉络：家族树与时间线
+ResearchRubrics 是2025年11月由Scale AI联合多所高校发布的深度研究智能体（Deep Research Agent）基准，核心特征是**专家全手写细粒度rubric + 多领域开放研究任务 + LLM-as-Judge评分协议**。它并非凭空诞生，而是沿着「任务形态从检索到深度研究」「评测方法从整体打分到结构化rubric」两条主线逐步演化而来，继承了十余项前驱工作的设计经验，同时针对性解决了前人的核心痛点。
+---
+## 一、完整时间线：从方法奠基到基准迭代
+### 阶段1：Rubric评测方法论奠基（2023年）
+这一阶段的核心是将LLM开放输出的模糊质量评估，拆解为结构化、可追溯的评分标准，为后续深度研究评测提供底层方法框架。
+- **2023年中**：**G-Eval** 提出用LLM基于详细评估标准进行打分，首次系统验证了「结构化rubric + LLM裁判」的可行性，是rubric类评测的方法论源头之一。
+- **2023年中**：**MT-Bench** 引入多维度分级评分标准，将对话质量拆解为指令遵循、连贯性等维度，证明了结构化评分比整体偏好打分更具可解释性。
+- 同期：Constitutional AI等工作验证了「明确规则引导模型评估」的有效性，为rubric设计提供了早期思路。
+### 阶段2：检索能力基准先行（2025年初）
+深度研究智能体的前身是网页浏览/检索Agent，早期基准聚焦**事实检索准确性、多跳搜索能力**，任务以短答案为主，是研究类评测的雏形。
+1. **2025.01 Humanity's Last Exam (HLE)**
+   - 由CAIS与Scale AI联合发布，2500道专家级跨学科短答题，奠定了「高难度专家级任务」的评测基调。
+   - 对ResearchRubrics的影响：验证了专家策划任务的权威性，ResearchRubrics的部分技术团队同样来自Scale AI，延续了专家质量把控的思路。
+2. **2025.04 BrowseComp（OpenAI）**
+   - 1266道网页多跳检索题，测试Agent持久搜索、挖掘隐蔽信息的能力，答案短且可验证。
+   - 对ResearchRubrics的影响：定义了「多步网页探索」的基础任务范式，是深度研究任务中「检索环节」的基准参照。
+3. **2025.06 AcademicBrowse（北京大学）**
+   - 首个学术领域专属检索基准，针对文献追踪、学术数据库导航等场景。
+   - 对ResearchRubrics的影响：补充了学术垂直场景的检索评测经验，是其AI/ML、STEM类任务的设计参考。
+4. 同期：**ResearchBench** 基于静态语料构建复杂查询，验证了静态基准的可控性，但存在数据泄露、无法适配动态信息的问题。
+### 阶段3：深度研究评测萌芽（2025年中）
+基准开始从「短答案检索」转向「长报告综合研究」，首次提出「深度研究Agent」的评测目标，但评测方法仍存在明显缺陷。
+1. **2025.05 FutureSearch Deep Research Bench（DRB）**
+   - 首个明确以「深度网页研究」为核心的基准，89个多步任务，通过RetroSearch冻结网页快照保证可复现性。
+   - 对ResearchRubrics的影响：确立了「多步探索+长文输出」的深度研究任务形态，但评分仍依赖事实匹配，缺乏综合质量评估。
+2. **2025.06 DeepResearch Bench（USTC/Metastone，Du et al.）**
+   - 100个PhD级中英双语研究任务，覆盖22个领域，要求生成长篇报告，提出RACE（报告质量）+ FACT（引用准确性）双指标。
+   - 对ResearchRubrics的影响：是最直接的对标基准之一，ResearchRubrics明确指出其核心痛点——**LLM生成rubric、依赖参考报告、指标粗糙**，并针对性做了改进。
+3. **2025.06 ExpertLongBench**
+   - 9个专业领域的长文本生成基准，配套领域专属结构化checklist，提出CLEAR评估框架（从参考文本中提取检查项做对齐）。
+   - 对ResearchRubrics的影响：验证了「细粒度分维度rubric」的有效性，是专家rubric路线的关键前驱；但它高度依赖高质量参考文本，任务局限于专业领域，ResearchRubrics则突破了这一限制。
+### 阶段4：专项与自动化基准爆发（2025年夏-秋）
+针对细分研究场景的基准和大规模自动化生成基准相继出现，分别在「垂直深度」和「规模广度」上探索，也暴露了各自的局限。
+1. **2025.08 DeepScholar-Bench（斯坦福+伯克利）**
+   - 学术合成专项基准，任务为基于最新arXiv论文撰写相关工作，评估检索质量、知识合成、可验证性三个维度。
+   - 对ResearchRubrics的影响：提供了学术研究场景的细分评估维度，但仅覆盖学术写作单一任务，通用性不足。
+2. **2025.08 ReportBench（字节跳动）**
+   - 基于已发表学术综述反向构造任务，以专家综述为金标准，评估引用重合度、事实一致性。
+   - 对ResearchRubrics的影响：验证了「引用质量」作为研究评估核心维度的价值，但本质是复刻参考内容，无法评估开放性、创造性的研究结论。
+3. **2025.09 DeepResearch Arena**
+   - 从学术研讨会转录文本自动挖掘1万+开放任务，配套自适应生成的rubric，提出ACE评估指标。
+   - 对ResearchRubrics的影响：证明了大规模开放研究任务的可行性，但自动生成的rubric缺乏领域深度，容易遗漏关键细节，这正是ResearchRubrics用全专家手写rubric解决的核心问题。
+### 阶段5：ResearchRubrics 集大成发布（2025.11）
+整合前驱工作的优势，推出首个「全专家手写rubric + 全领域覆盖 + 精细加权评分」的深度研究基准，包含101个任务、2593条rubric项，覆盖9大领域。
+### 阶段6：后续演化（2025年底-2026年）
+ResearchRubrics成为行业通用基准之一，同时催生出更多差异化的深度研究评测工作：
+- 2025年底：**DR Bench II** 优化了rubric的可验证性，强化信息召回、分析、呈现三维度评估
+- 2026.02：**DREAM** 提出代理化评测指标，进一步细分评估范式
+- 2026年：DEER、FinResearchBench等垂直领域基准相继发布，均参考了ResearchRubrics的rubric设计框架
+---
+## 二、评测家族树：两条主线的汇聚
+ResearchRubrics 是「任务形态演进」和「评测方法演进」两条技术线的交汇产物，家族关系可梳理为：
+### 主线1：任务形态——从简单检索到深度综合研究
+```
+早期检索基准
+├─ BrowseComp (通用网页检索)
+├─ AcademicBrowse (学术检索)
+└─ ResearchBench (静态语料查询)
+    ↓
+初代深度研究基准
+├─ FutureSearch DRB (冻结网页的多步研究)
+└─ USTC DeepResearch Bench (PhD级长报告)
+    ↓
+专项细分基准
+├─ DeepScholar-Bench (学术写作)
+├─ ReportBench (综述复刻)
+└─ DeepResearch Arena (大规模自动任务)
+    ↓
+集大成者：ResearchRubrics (多领域开放研究 + 全维度质量评估)
+```
+### 主线2：评测方法——从整体打分到精细Rubric
+```
+LLM-as-Judge 奠基
+├─ G-Eval (结构化标准引导LLM打分)
+└─ MT-Bench (多维度分级评分)
+    ↓
+长文本Rubric探索
+└─ ExpertLongBench (专家checklist + 参考文本对齐)
+    ↓
+研究类Rubric尝试
+├─ USTC DRB (LLM生成rubric + 参考报告)
+└─ DeepResearch Arena (自动生成自适应rubric)
+    ↓
+成熟方案：ResearchRubrics (专家全手写rubric + 正负向加权 + 三元分级)
+```
+---
+## 三、核心继承关系与针对性改进
+ResearchRubrics 并非简单叠加前人工作，而是精准继承各基准的优势，同时系统性解决了普遍存在的痛点：
+### 1. 继承的核心设计
+- **任务维度**：继承了BrowseComp的「多步探索」、DeepResearch Bench的「长报告输出」、DeepScholar-Bench的「引用质量评估」，构建了从检索到合成的全流程评测。
+- **Rubric维度**：继承了ExpertLongBench的「分领域细粒度标准」设计，延续了HLE的「专家级质量把控」，采纳了LLM-as-Judge的可扩展评分协议。
+- **评估维度**：吸收了前人的核心评估方向，最终沉淀为6大评估轴：显式要求、隐式要求、信息合成、引用使用、沟通质量、指令遵循。
+### 2. 针对性解决的前驱痛点
+| 前驱工作普遍问题 | ResearchRubrics 的解决方案 |
+| :--- | :--- |
+| LLM自动生成rubric，领域深度不足、存在偏差 | 全部2593条rubric由专家从零手写，三轮评审校验，无LLM生成环节 |
+| 依赖单一参考报告，限制答案多样性 | 不设标准答案，仅以rubric准则判断质量，允许多种有效研究路径 |
+| 评分粗糙，仅二元或整体打分 | 引入「强制/可选」双标准、正负向权重、三元分级（完全满足/部分满足/不满足） |
+| 领域覆盖窄，仅学术或单一专业场景 | 覆盖9大领域，包含消费级日常研究，兼顾专业与通用场景 |
+| 评估维度单一，重事实轻逻辑 | 同时考察事实准确性、推理合理性、结构清晰度、隐式需求覆盖等多层能力 |
+---
+## 四、补充说明
+需要注意深度研究领域存在两个同名的**DeepResearch Bench**，二者相互独立，ResearchRubrics论文中直接对标并批判的是**中科大/Metastone版本（Du et al., 2025.06）**，而非FutureSearch的冻结网页版本。
+如果需要，我可以进一步整理各基准的核心指标、任务规模和适用场景的对比表格。</t>
   </si>
   <si>
     <t># Slot Attention 思想脉络梳理：从奠基理论到后续演化
@@ -4655,13 +5916,248 @@
     <t>Qwen3 这一代相比 Qwen2 / Qwen2.5 在架构与训练方法上做了哪些演进？帮我画出 Qwen 系列模型的方法家族树和演化时间线。</t>
   </si>
   <si>
+    <t>### 一、Qwen3 相对 Qwen2 / Qwen2.5 的架构与训练方法演进
+Qwen3 是通义千问系列的第四代基座模型，在 Qwen2.5 的工程基础上完成了架构范式、训练流水线和能力边界的三重升级，核心演进可分为**基础架构**、**预训练体系**和**后训练对齐**三个维度。
+#### 1. 基础架构演进
+三代模型均基于 Decoder-only Transformer 框架，但在注意力、专家架构和功能设计上逐步迭代：
+| 架构维度 | Qwen2 | Qwen2.5 | Qwen3 |
+|----------|-------|---------|-------|
+| 注意力机制 | 全尺寸 GQA（分组查询注意力），保留 QKV Bias | GQA + QK-Norm，稳定长序列训练 | GQA + QK-Norm，**移除 QKV Bias**，训练稳定性进一步提升 |
+| MoE 架构 | 首次引入 57B-A14B（总57B/激活14B），含共享专家 | 235B MoE，细粒度专家分割，保留共享专家 | **128 总专家 / 单 token 激活 8 个**，移除共享专家，新增全局批量负载均衡损失，强化专家专业化 |
+| 核心功能设计 | 单一通用对话模式 | 通用模型 + 独立推理专项模型（QwQ）分离 | **内置 Thinking / Non-Thinking 双模式**，单模型通过 prompt 标签切换，支持思考预算动态控制 |
+| 语言与词表 | 27 种语言，词表 151,643 | 29 种语言，词表不变 | 119 种语言/方言，词表微调至 151,669，多语言覆盖大幅扩展 |
+| 原生上下文 | 最高 128K（7B/72B） | 128K 原生，配合 DCA 推理扩展至 1M | Dense 模型 32K~128K 原生，MoE 模型 128K 原生，配合 YaRN+DCA 可进一步扩展 |
+&gt; 其中**内置双模式**是 Qwen3 最标志性的架构创新：用户通过 `/think` 触发长思维链深度推理，通过 `/no_think` 获得快速应答，无需在通用模型和推理专项模型之间切换部署，同时支持 `thinking_budget` 参数灵活控制推理深度，在延迟和准确率之间动态权衡。
+#### 2. 预训练方法演进
+Qwen3 将预训练从“单阶段大规模语料训练”升级为**三阶段精细化流水线**，数据规模和质量同步跃迁：
+- **数据规模与多样性**：训练语料从 Qwen2.5 的 18T tokens 翻倍至 36T tokens，支持语言从 29 种扩展至 119 种；首次引入多模态数据生产链路——通过 Qwen2.5-VL 提取 PDF 文档文本，用 Qwen2.5-Math/Coder 生成领域合成数据，补充高质量语料。
+- **三阶段预训练策略**：
+  1. **通用基础阶段（S1）**：30T 全领域语料，4K 序列长度，搭建通用语言能力与世界知识基础；
+  2. **推理增强阶段（S2）**：追加 5T 高质量 STEM、代码、推理与合成数据，深化逻辑推理能力，同步加速学习率衰减；
+  3. **长上下文阶段（S3）**：数百亿长文本语料，75% 为 16K~32K 长度，将原生上下文扩展至 32K/128K，RoPE 基频提升至 1,000,000。
+- **数据配比优化**：搭建多维度数据标注系统，基于小代理模型做实例级消融实验，精准调整不同领域数据的混合比例，替代传统的源级/领域级粗粒度配比。
+#### 3. 后训练（对齐）方法演进
+Qwen3 将对齐范式从“文本生成对齐”升级为“推理过程建模 + 双模式统一”，形成标准化的四阶段后训练流水线：
+| 阶段 | 核心目标 | 技术方法 |
+|------|----------|----------|
+| 1. Long-CoT 冷启动 | 打下长思维链推理基础 | 筛选高难度数学、代码、逻辑题，用 QwQ-32B 生成高质量长 CoT 数据，做监督微调 |
+| 2. Reasoning RL | 强化深度推理能力 | 采用 GRPO 强化学习算法，大批次高 rollout，离线策略提升样本效率，单轮 RL 即可稳定提升推理分数 |
+| 3. 思维模式融合 | 实现单模型双模式切换 | 混合 30% 思考数据 + 70% 非思考数据做持续 SFT，设计专用对话模板，让模型学会通过 `/think`/`/no_think` 标签切换行为 |
+| 4. 通用 RL | 全场景能力对齐 | 覆盖指令跟随、格式合规、偏好对齐、Agent 能力、RAG 准确性等 20+ 任务，结合规则奖励、有参考模型奖励、无参考偏好奖励三类信号 |
+此外，Qwen3 首次引入**强到弱蒸馏**流水线：小模型（0.6B~14B）从旗舰大模型蒸馏 logits，仅需 1/10 的 GPU 算力即可获得完整的双模式能力与接近大模型的推理效果，大幅降低小模型的对齐成本。
+---
+### 二、Qwen 系列模型方法家族树与演化时间线
+Qwen 系列采用“主线基座 + 六大专项分支”的并行演进路线，主线每代基座发布时，对应代际的视觉、音频、代码、数学等专项模型几乎同步更新，形成了完整的模型生态。
+#### 1. 方法家族树
+```
+【主线：通用文本 LLM】
+Qwen-1 (2023.08) — 初代基座，MHA，3T tokens，中英双语
+└── Qwen-1.5 (2024.02) — 架构优化，首尝 MoE，30+ 语言，HF 原生适配
+    └── Qwen-2 (2024.06) — 全尺寸 GQA，7T tokens，128K 上下文，正式 MoE 产品线
+        └── Qwen-2.5 (2024.09) — 18T tokens，QK-Norm，DCA 1M 上下文，专项模型全家桶同步
+            └── Qwen-3 (2025.05) — 36T tokens，内置双模式，高稀疏 MoE，119 种语言
+                └── Qwen-3.5 (2026.02) — Gated DeltaNet 混合线性注意力，397B Hybrid MoE，原生多模态
+                    ├─ Qwen-3.6-Plus (2026.04，闭源)
+                    └─ Qwen-3.7-Max (2026.05，闭源) — Agent-first 旗舰，扩展思考模式
+【六大专项分支】
+▸ 视觉多模态：Qwen-VL(2023.08) → Qwen2-VL(2024.10) → Qwen2.5-VL(2025.02) → Qwen3-VL(2025.11)
+▸ 音频理解：Qwen-Audio(2023.11) → Qwen2-Audio(2024.07)
+▸ 代码生成：CodeQwen1.5(2024.04) → Qwen2.5-Coder(2024.09) → Qwen3-Coder(2025.07)
+▸ 数学推理：Qwen2.5-Math(2024.09)
+▸ 推理专项：QwQ-32B(2024.11) → QwQ-Max(2025.03)
+▸ 全模态统一：Qwen2.5-Omni(2025.03) → Qwen3-Omni(2025.09) → Qwen3.5-Omni(2026.04，闭源)
+```
+#### 2. 演化时间线（关键技术节点）
+| 发布时间 | 代表版本 | 核心技术突破 | 阶段定位 |
+|----------|----------|--------------|----------|
+| 2023.08 | Qwen-1 / Qwen-VL | 标准 Transformer 基座，RoPE 基频 1e6；首代视觉多模态，Cross-Attention 融合 | 初代开源对标，双语能力优先 |
+| 2023.11 | Qwen-Audio | 统一音频 LLM 架构，覆盖 30+ 音频任务 | 音频专项起步 |
+| 2024.02 | Qwen-1.5 | 引入 GQA，发布 110B MoE，支持 30+ 语言 | 架构过渡与生态完善 |
+| 2024.06 | Qwen-2 | 全尺寸统一 GQA，7T 语料，128K 上下文，57B-A14B 正式 MoE | 第二代成熟开源基座 |
+| 2024.09 | Qwen-2.5 全家桶 | 18T 语料，QK-Norm，DCA 实现推理侧 1M 上下文；VL/Coder/Math 同步发布 | 长上下文领导，专项能力补齐 |
+| 2024.11 | QwQ-32B | 长 CoT + 多阶段 RL，独立推理专项模型 | 推理能力探索 |
+| 2025.03 | Qwen2.5-Omni | Thinker-Talker 双角色架构，TMRoPE 时间对齐，端到端语音交互 | 全模态统一落地 |
+| 2025.05 | Qwen-3 | 36T 语料、119 种语言；内置双模式推理；235B-A22B 高稀疏 MoE | 动态推理范式，开源能力登顶 |
+| 2026.02 | Qwen-3.5 | Gated DeltaNet 混合线性注意力，397B-A17B 混合 MoE，262K 原生上下文，吞吐提升 8~19 倍 | 效率革命，原生多模态 |
+| 2026.05 | Qwen-3.7-Max | Agent-first 原生架构，扩展思考模式，Agent 评测全球领先 | 闭源旗舰，向智能体演进 |
+需要我补充某一代模型的具体技术细节或者微调实践指南吗？</t>
+  </si>
+  <si>
     <t>zELO 这种受 ELO 启发的重排序/嵌入训练方法，建立在哪些排序学习与对比学习工作之上？它属于领域里的哪一类方法分支？</t>
   </si>
   <si>
+    <t>### 一、zELO 的理论与技术奠基：排序学习与对比学习的源头工作
+zELO 是 ZeroEntropy 团队 2025 年提出的重排序/嵌入训练方法，其核心思想是将文档排序转化为“两两对战→能力评分”的 ELO 式统计问题。它并非凭空提出，而是建立在排序学习、心理测量学、对比学习三大领域的长期积累之上，同时针对性解决了主流方法的固有缺陷。
+#### 1. 排序学习（Learning to Rank）领域的核心奠基
+##### （1）统计排序与成对比较的理论源头
+zELO 的数学内核直接继承自**成对比较的概率模型家族**，这是排序学习最古老的理论根基：
+- **Zermelo 锦标赛模型（1929）**：最早证明了从两两对战结果中可以通过极大似然估计唯一求解每个选手的潜在能力值，是所有 ELO 类评分系统的数学起点。
+- **Bradley-Terry 模型（1952）**：将 Zermelo 的思想形式化，假设个体胜出概率由其潜在能力的指数比值决定，是 ELO 评分的直接统计基础；zELO 中最初的分数拟合就基于该模型框架。
+- **Thurstone 比较判断定律**：假设每个文档的真实相关性服从正态分布，两两比较的胜出概率由误差函数（erf）决定；zELO 最终采用 Thurstone 模型替代 Bradley-Terry，认为正态噪声更符合多源 LLM 投票的实际情况。
+- **Plackett-Luce 模型**：Bradley-Terry 在完整排序场景下的推广，zELO 在理论上兼容该模型，可扩展至列表级排序的分数拟合。
+- **ELO 评分系统（1978）**：将上述统计模型落地为可迭代更新的竞技评分体系，是 zELO 最直接的灵感来源——文档类比棋手，两两对比较量相关性，最终收敛得到连续的“相关性段位分”。
+##### （2）神经排序学习的范式传承
+zELO 延续了排序学习三大范式中的 **pairwise 范式** 核心逻辑，同时吸收了 pointwise 范式的工程优势：
+- **RankNet（2005，微软）**：首次将 pairwise 排序损失用神经网络实现，用交叉熵优化文档对的相对顺序；zELO 第一阶段训练 pairwise 判别模型时，使用的二元交叉熵（BCE）损失与 RankNet 的核心思想一脉相承。
+- **排序学习三大范式划分**：zELO 明确建立在 pointwise（单点打分）、pairwise（两两比较）、listwise（整列排序）的经典分类体系之上，最终选择“pairwise 生成监督信号 + pointwise 训练部署模型”的折中路线。
+##### （3）LLM 时代的重排序与偏好蒸馏工作
+zELO 的工程实现建立在近年 LLM 驱动排序的研究基础上：
+- **LLM-as-Reranker 范式**：用大语言模型直接做 pairwise 或 listwise 排序的一系列工作（如 PRP-Graph、RankGPT 等），证明了 LLM 可以输出高质量的相对偏好判断；zELO 将 LLM 集成作为“裁判”生成 pairwise 偏好数据，正是这一思路的规模化应用。
+- **排序蒸馏（Ranking Distillation）**：用强教师模型（如 GPT-4）的排序结果蒸馏小模型的技术路线；zELO 本质是一种更精细的蒸馏方法——不是直接蒸馏排序结果，而是蒸馏大量成对偏好，再通过统计模型生成更鲁棒的连续分数标签。
+#### 2. 对比学习领域的基础与批判对象
+zELO 的提出，本身就是对当前检索领域主流对比学习范式的反思与替代，其对比的基线工作包括：
+- **InfoNCE 损失与对比检索框架**：当前训练双编码器嵌入模型和重排序器的主流方法，通过正负样本对的对比学习优化表示空间；zELO 论文将 InfoNCE + 三元组损失作为现有 SOTA 的基准，并指出其根本局限。
+- **难负例挖掘（Hard Negative Mining）**：对比学习提升检索效果的核心技术，通过挖掘“看似相关实则不相关”的难负例增强训练信号；zELO 最核心的动机，就是指出难负例挖掘存在“Laffer 曲线”——当负例挖掘能力过强时，会出现大量“假负例”（挖掘出的负例实际比标注正例更相关），反而导致模型性能下降，这也是 zELO 方法要解决的核心痛点。
+- **SimCSE、CLIP 等文本/多模态对比学习工作**：代表了随机负采样、批内负采样等经典策略，zELO 明确指出随机负采样信号弱、难负采样易出错的两难困境，并给出了全新的解决方案。
+---
+### 二、zELO 在领域中的方法分支定位
+zELO 不是单一的模型结构，而是一套**多阶段训练方法论**，可以从多个维度划分其所属分支：
+#### 1. 按排序学习范式：pairwise-to-pointwise 混合训练范式
+- 它不属于纯粹的 pairwise 模型（如 RankSVM、RankNet），也不属于纯粹的 pointwise 模型（如传统回归式排序）。
+- 它是**“pairwise 监督生成 → 统计拟合 → pointwise 模型训练”的两阶段混合范式**：用更鲁棒的两两比较获取偏好，通过 Thurstone/ELO 模型将离散偏好转化为连续的绝对相关性分数，最终训练工业界最常用的 pointwise 跨编码器（cross-encoder）重排序器，兼顾了 pairwise 的标注质量和 pointwise 的部署效率。
+#### 2. 按监督类型：无监督/自动标注的弱监督排序学习
+- 属于**零人工标注的自动排序训练方法**分支：全程不需要人工标注相关性标签，仅通过 LLM 集成自动生成 pairwise 偏好，即可端到端训练出 SOTA 级别的重排序器和嵌入模型。
+- 区别于传统监督排序学习（依赖人工标注等级标签）和半监督排序学习，zELO 实现了完全自动化的训练数据生产，可快速适配垂直领域数据。
+#### 3. 按技术路线：ELO/Bradley-Terry 统计评分系谱的现代延伸
+- 属于**基于潜在能力评分的排序方法**分支，这一分支起源于心理测量学和竞技评分，在信息检索领域长期属于小众路线。
+- zELO 是该分支在大模型时代的标志性工作：首次将 ELO/Bradley-Terry 统计框架与 LLM 偏好生成、大规模重排序训练结合，证明了该路线可以超越传统对比学习方法，达到业界最优水平。
+#### 4. 按应用场景：跨编码器重排序 + 双编码器嵌入的统一训练框架
+- 既可以用于训练**高精度跨编码器重排序器**（如 zerank-1 系列），也可以通过蒸馏方式训练**高效双编码器嵌入模型**（如 zembed-1），是少数能同时覆盖检索两阶段的训练方法论。
+- 在嵌入训练领域，它属于**监督式精细调优方法**，区别于传统的对比式预训练，目标是学习细粒度的相关性排序，而非通用语义相似性。
+---
+简单总结：zELO 站在排序学习百年统计理论（Bradley-Terry/Thurstone/ELO）和近年 LLM 偏好蒸馏的基础上，跳出了“对比学习+难负例挖掘”的主流框架，开辟了“LLM 两两投票→统计拟合连续分→训练 pointwise 模型”的新路线，属于弱监督排序学习中基于竞技评分的特色分支。
+需要我补充 zELO 与其他主流重排序训练方法（如对比学习、listwise 蒸馏）的详细对比表吗？</t>
+  </si>
+  <si>
     <t>这篇论文揭示的多轮对话退化问题，后续有哪些重要缓解方案？梳理这条研究线索从「发现问题」到「改进」的演化过程。</t>
   </si>
   <si>
+    <t>首先需要澄清：你提供的《SurGE: A Benchmark and Evaluation Framework for Scientific Survey Generation》是一篇聚焦**自动化科学综述生成**的基准类论文，核心工作是构建科学综述生成的标准化评测数据集与多维度评估框架，全文**并未涉及“多轮对话退化”相关的问题发现、成因分析或缓解方案**，二者属于自然语言处理领域不同的研究方向。
+针对你关心的“多轮对话退化从问题发现到改进方案”的研究脉络，下面按照时间线梳理该方向的完整演化线索：
+### 一、问题发现阶段（2022年底—2023年中）：从现象观测到正式定义
+随着大语言模型对话产品大规模落地，多轮交互中的性能衰减问题从用户体验反馈，逐步成为学界系统化研究的正式课题。
+1. **产业端的普遍观测**
+   ChatGPT等对话模型普及后，开发者与用户广泛观察到：随着对话轮次增加，模型会逐渐遗忘初始角色设定、前置约定与关键信息，出现回复重复、逻辑前后矛盾、答非所问等质量下降现象，且轮次越多退化越显著。
+2. **学界的量化验证**
+   以LongBench、L-Eval为代表的长上下文基准测试，首次通过标准化任务量化证实：即使标称支持数万token上下文的模型，在长对话信息召回、语义理解类任务上的性能，也会随上下文长度增加呈明显下降趋势。
+   对话场景的专项研究进一步发现：多轮对话的退化速度显著快于单轮长文本任务，核心差异在于**自回归生成的误差级联效应**——每一轮的输出都会成为下一轮的输入，错误会逐轮累积放大。
+3. **问题的标准化拆解**
+   学界将多轮对话退化正式拆解为三类核心表现：
+   - **记忆遗忘**：无法准确召回多轮前的关键信息（如用户偏好、任务约定、背景事实）；
+   - **语义漂移**：对话主题、角色人设、核心设定逐渐偏离初始状态，整体语境发生偏移；
+   - **质量坍缩**：回复出现冗余重复、逻辑断裂、信息量下降，生成流畅度与实用性显著降低。
+### 二、成因解析阶段（2023年中—2023年底）：拆解退化的底层机制
+在确认问题普遍性后，学界从模型机制、数据分布等多个维度拆解了退化根源，为后续优化明确了方向：
+- **注意力稀释效应**：Transformer自注意力机制中，序列总token数越多，单个token获得的平均注意力权重越低。长对话中，早期关键信息会被海量历史上下文淹没，模型无法有效聚焦高价值内容。
+- **位置编码外推缺陷**：主流的RoPE等位置编码方案，在超出训练时的序列长度后，位置关系建模精度急剧下降，导致远距离对话上下文之间的语义关联失效。
+- **误差级联传播**：多轮对话是链式自回归过程，上一轮生成的错误信息会被纳入下一轮的输入上下文，错误逐轮叠加放大，最终引发整体语义偏移。
+- **训练分布偏差**：模型预训练与微调数据中，短对话样本占绝对主流，长多轮对话数据稀缺，模型并未充分学习长程上下文维护、话题承接与信息管理的能力。
+### 三、缓解方案的三代演化
+针对上述成因，解决方案从轻量化工程优化，逐步走向模型架构级改进，再到当前的记忆机制与Agent化探索，经历了三代技术迭代。
+#### 第一代：上下文裁剪与压缩（2023年上半年，工程化应急方案）
+核心思路是通过减少输入长度降低模型负担，本质是回避而非解决长上下文能力问题，是早期最易落地的方案。
+- **滑动窗口截断**：仅保留最近N轮对话作为上下文，丢弃更早的历史信息。优点是实现简单、计算高效，缺点是会永久性丢失早期关键设定与信息。
+- **对话摘要压缩**：周期性对历史对话生成精简摘要，用摘要替代原始对话历史，实现上下文长度压缩。代表方案如Conversation Summary Buffer，在保留核心信息的同时压缩了长度，但会损失细节精度。
+- **结构化记忆提取**：从对话历史中抽取出实体、用户画像、核心约定等结构化信息，以键值对形式存储，每轮生成前显式注入上下文。
+#### 第二代：架构与训练的原生能力优化（2023年下半年—2024年，主流成熟方案）
+这一阶段的方案从模型底层出发，直接提升长上下文对话能力，是当前工业界的主流优化路径。
+- **位置编码外推优化**：针对RoPE的缺陷，衍生出NTK Scaling、YaRN等改进方案，通过非线性位置插值扩展有效上下文窗口，大幅提升长序列下的位置建模精度，缓解远距离上下文的注意力失效。
+- **注意力机制改造**：采用滑动窗口注意力、全局-局部混合注意力等设计，在降低长序列计算开销的同时，保证对关键信息的注意力分配；部分方案引入专属“记忆token”锚定全局核心信息。
+- **长对话专项微调**：构造大规模多轮长对话数据集，对模型进行继续预训练或指令微调，让模型适配长对话的数据分布，学习长对话的上下文维护与话题承接能力。
+- **检索增强对话（Dialogue RAG）**：将全量对话历史向量化后存入知识库，每轮生成前仅召回与当前问题语义相关的历史片段，而非输入全部对话历史。该方案精准过滤了噪声上下文，从根源上缓解了注意力稀释问题，是当前工业界应用最广泛的成熟方案。
+#### 第三代：分层记忆与Agent化管理（2024年至今，前沿探索方向）
+当前前沿研究跳出“让模型硬扛长上下文”的思路，借鉴人类记忆机制，通过显式的记忆管理系统从根本上解决多轮退化问题。
+- **分层记忆架构**：将对话记忆划分为短期工作记忆（最近几轮原始对话）、中期语义记忆（对话摘要与核心观点）、长期事实记忆（用户固定属性与关键事实），不同层级采用不同的存储、更新与召回策略，模拟人类的记忆-遗忘机制。
+- **主动记忆管理**：引入专门的记忆管理模块，支持记忆的更新、修正、删除与整合，模型主动维护记忆的一致性与准确性，阻断错误的级联传播；部分方案加入记忆校验环节，每轮生成前核对上下文一致性。
+- **多智能体分工协作**：将对话系统拆分为对话生成Agent、记忆管理Agent、事实校验Agent等多个角色，通过分工协作实现长对话的稳定运行，由记忆Agent专门负责上下文的维护与信息召回。
+需要我补充某一类缓解方案的具体技术细节或代表性论文吗？</t>
+  </si>
+  <si>
     <t>Xpertbench 这类基于 rubric 的专家级评测范式，是从哪些早期 LLM 评测与能力基准演化而来的？帮我梳理评测方法的文献分类与脉络。</t>
+  </si>
+  <si>
+    <t># XpertBench 专家级 Rubric 评测范式的演化脉络与文献谱系
+XpertBench 所代表的「真实专家任务 + 细粒度加权 rubric + 专家校准 LLM 裁判」范式，并非凭空出现，而是 LLM 评测体系沿着「客观闭卷→开放偏好→结构化维度→专业深度」的路径持续迭代的结果。其演化脉络可划分为四个核心阶段，每一阶段都针对前序范式的核心缺陷提出解决方案，最终汇聚为面向专家级能力的评测体系。
+---
+## 一、演化脉络的四个阶段
+### 阶段1：前 Rubric 时代——闭形式客观基准（2018–2023 初）
+这是 LLM 评测的「考试时代」，核心假设是「知识掌握程度 = 能力水平」，所有任务都有唯一确定的标准答案，可通过程序自动判分。
+#### 两大分支
+1. **通用能力基准**
+    - 代表工作：MMLU (2020)、HellaSwag、GSM8K、HumanEval，以及后续的 MMLU-Pro、GPQA Diamond、Humanity's Last Exam
+    - 核心特征：以选择题、填空题、单元测试等闭形式为主，覆盖知识广度、基础推理、代码生成等通用能力；评测成本极低、可复现性极强
+    - 局限性：天花板效应显著（前沿模型 MMLU 得分普遍突破 90%）；仅能测试静态知识回忆，完全无法衡量开放生成、复杂推理、真实工作流中的专业判断能力；数据污染问题严重
+2. **单领域专业基准**
+    - 代表工作：MedQA / PubMedQA（医疗）、LegalBench（法律）、FinBen（金融）、SciBench（科研）
+    - 核心特征：将客观题范式下沉到单一专业领域，提升评测的专业深度
+    - 局限性：仍停留在「知识点考题」层面，与真实职场的长周期、多约束、开放型工作流严重脱节；各领域基准孤立，无法衡量跨领域综合能力
+3. **早期 Agent 任务基准**
+    - 代表工作：AgentBench、GAIA、BrowseComp
+    - 核心特征：开始关注多步骤执行、工具调用、网页检索等过程能力
+    - 局限性：最终评价仍坍缩为「任务是否成功」的单点指标，忽略了专业判断、方案合理性、风险控制等核心维度；本质仍是「有标准答案的复杂题」
+&gt; **演化驱动**：当闭卷基准全面饱和、分数与实际可用性脱钩时，行业迫切需要能评估开放生成质量的新范式，LLM-as-Judge 由此兴起。
+---
+### 阶段2：LLM-as-Judge 萌芽——整体偏好式评测（2023 年中）
+这一阶段的核心突破是用强模型替代人类做开放输出的质量判断，首次实现了生成式任务的规模化评测，但评判逻辑仍偏「黑盒」。
+#### 两大主流范式
+1. **成对比较（Pairwise）**
+    - 代表工作：AlpacaEval (2023, 斯坦福)、Chatbot Arena (LMSYS)
+    - 核心特征：让裁判模型在两份回答中二选一，输出胜率/ELO分；相对判断比绝对打分更稳定，与人类偏好相关性更高
+    - 局限性：仅能输出「谁更好」，无法解释「好在哪」；存在显著的长度偏好、风格偏好，以及「自增强偏差」（裁判倾向于奖励与自身训练分布一致的回答）
+2. **单点打分（Pointwise）**
+    - 代表工作：MT-Bench (2023, LMSYS)
+    - 核心特征：首次引入简易通用 rubric，按 1–10 分对回答进行绝对打分；覆盖写作、推理、代码等 8 类多轮对话任务
+    - 局限性：rubric 仅为「有用性、连贯性、准确性」等粗粒度通用维度，无任务专属检查点；专业领域的评判可靠性极低；打分尺度不稳定，跨批次可比性差
+&gt; **演化驱动**：黑盒式整体打分的可解释性差、一致性不足、专业度缺失的问题日益突出，行业开始探索将模糊的质量判断拆解为明确、可验证的结构化标准——即 rubric 范式。
+---
+### 阶段3：结构化 Rubric 评测兴起——从通用维度到细粒度检查点（2023 底–2024）
+这一阶段的核心是「将主观判断客观化」：把抽象的「质量」拆解为多条可独立验证的标准，让裁判逐条核对，大幅提升评测的一致性、可解释性和公平性。
+#### 关键里程碑
+1. **方法论奠基：G-Eval (2023, Liu et al.)**
+    - 核心贡献：首次系统提出「先生成结构化评估步骤（即 rubric 雏形），再按步骤链式推理打分」的范式；引入概率加权打分（基于 token 概率计算平滑分数），相比直接打分，与人类判断的 Spearman 相关性提升 58%
+    - 历史地位：奠定了现代 rubric 评测的基本方法论，证明了「结构化标准 + 推理过程」能显著提升 LLM 裁判的可靠性
+2. **开源裁判落地：Prometheus 系列 (2024)**
+    - 核心贡献：第一个专门微调的开源 rubric 裁判模型，基于 1000 条评分标准、10 万条反馈数据训练；支持自定义 rubric 的 1–5 分绝对打分和成对比较
+    - 历史意义：将 rubric 评测从「依赖 GPT-4 黑盒」变为可私有化、低成本落地的通用方案，推动 rubric 从学术研究走向工业界实践
+3. **基准进阶：任务专属 Checklist**
+    - 代表工作：WildBench、Arena-Hard、RubricEval
+    - 核心特征：从「通用维度 rubric」升级为「单任务专属检查清单」，颗粒度进一步细化；RubricEval 更是首个面向 rubric 层级的元评测基准，专门衡量裁判在每条细标准上的判断准确率
+    - 局限性：仍聚焦通用日常任务，未深入专业领域的行业标准与工作流细节；rubric 多为通用质量导向，缺乏专业权威性
+&gt; **演化驱动**：通用 rubric 无法满足金融、法律、医疗等高门槛领域的评测需求——这些领域的「好坏」有严格的行业规范、合规要求和专业逻辑，必须由领域专家定义标准，专家级 rubric 评测应运而生。
+---
+### 阶段4：专家级 Rubric 评测范式——XpertBench 为代表（2025–2026）
+这一阶段将 rubric 评测与真实专业工作流深度结合，完成了从「通用质量打分」到「专业能力认证」的跃迁。XpertBench 是这一范式的集大成者，其设计全面继承了前序方法的优点，并针对性解决了核心痛点。
+#### 前驱探索
+- 深度研究类：DeepResearch Bench、DEER，首次将 rubric 用于 PhD 级研究任务的评测，引入了 claim 级事实验核，但仅覆盖信息检索与合成，不涉及完整专业工作流
+- 单领域专业类：HealthBench 等，在垂直领域实现了专家 rubric 评测，但领域覆盖极窄，缺乏统一范式
+#### XpertBench 的继承与创新
+对比前序范式，XpertBench 在三个核心维度实现了跃迁，构成了「专家级 rubric 评测」的完整范式：
+1. **任务：从「知识点考题」到「真实专家工作流」**
+    - 1346 个任务全部来自一线从业者（CFA、CPA、MD、JD 等）的真实工作场景，覆盖金融、法律、医疗、教育、STEM 等 7 大领域 80 个类别
+    - 任务为长周期、开放型、多约束的真实问题（如上市公司财报分析、法律案件研判、教学设计方案），而非孤立知识点，生态效度显著提升
+2. **Rubric：从「通用维度」到「原子化加权专业检查点」**
+    - 每个任务配套 15–40 个原子化检查点，均为可明确判断「是/否」的客观标准，避免模糊描述
+    - 采用双重加权机制：定性分级（Essential / Important / Optional）+ 定量权重（1–10 分），精准匹配专业场景的重要性差异
+    - 覆盖指令遵循、逻辑连贯、专业知识、合规性、风险管理等 12 个维度，完整对应行业评价标准
+3. **裁判：从「通用模型盲判」到「专家少样本校准」**
+    - 提出 ShotJudge 范式：用专家标注的黄金样本作为 few-shot 锚点，校准 LLM 裁判的判断标准，大幅缓解「自增强偏差」
+    - 实现了「专家级精度」与「规模化效率」的平衡：专家只负责定义标准和校准样本，批量评测由 LLM 完成
+---
+## 二、评测方法的文献分类谱系
+按照研究对象与方法论的差异，相关文献可划分为四大类，构成完整的知识谱系：
+| 类别 | 核心研究问题 | 代表文献/基准 | 与 XpertBench 的关联 |
+|------|--------------|---------------|----------------------|
+| 闭形式客观基准 | 如何用标准化客观题衡量模型知识与基础能力 | MMLU、GPQA、MedQA、AgentBench | 提供了能力评测的基础框架，但因饱和与生态效度不足，被 XpertBench 超越 |
+| 偏好式 LLM 裁判 | 如何规模化评估开放生成的整体质量 | AlpacaEval、Chatbot Arena、MT-Bench | 开创了 LLM-as-Judge 范式，是 XpertBench 自动化评测的思想源头 |
+| 结构化 Rubric 方法 | 如何通过分解标准提升评测的一致性与可解释性 | G-Eval、Prometheus、AutoRubric、RubricEval | 提供了 rubric 评测的方法论与技术底座，XpertBench 的 rubric 设计与裁判逻辑均建立在此基础上 |
+| 专家级专业评测 | 如何衡量模型在真实专业场景中的工作能力 | DEER、HealthBench、XpertBench | XpertBench 是当前该方向规模最大、覆盖最广、范式最完整的代表性工作 |
+---
+## 三、演化的底层逻辑
+整个评测体系的迭代，始终由两个核心矛盾驱动：
+1. **模型能力边界的扩张**：LLM 从「知识存储器」进化为「通用助手」再到「专业协作者」，评测必须从「考知识点」升级为「评工作成果」。
+2. **评测的精度-成本权衡**：从全自动客观题（低成本、低精度）→ 人工专家评测（高精度、高成本）→ LLM 裁判（中成本、中精度）→ rubric + 专家校准（高精度、中成本），始终在寻找最优平衡点。
+XpertBench 代表的专家级 rubric 范式，正是当前阶段这一权衡的最优解，也为后续面向 Agent、多模态、自主科研等更复杂场景的评测，提供了可复用的方法论框架。
+需要我补充一份**核心文献速查表**（含发表时间、机构、核心贡献），方便你快速溯源吗？</t>
   </si>
   <si>
     <t>### 一、同类型核心研究分类
@@ -4766,10 +6262,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -4809,7 +6305,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4823,31 +6319,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4861,8 +6334,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4870,7 +6352,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4891,6 +6373,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -4899,7 +6388,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
@@ -4908,23 +6419,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4939,19 +6435,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4963,43 +6489,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5011,37 +6507,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5065,19 +6543,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5089,13 +6567,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5108,12 +6610,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5137,17 +6633,6 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -5183,15 +6668,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -5211,7 +6687,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5230,6 +6706,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -5238,31 +6734,31 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5271,109 +6767,109 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -6274,7 +7770,7 @@
       <c r="C16" t="s">
         <v>98</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="1" t="s">
         <v>99</v>
       </c>
     </row>
@@ -6288,7 +7784,7 @@
       <c r="C17" t="s">
         <v>57</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="1" t="s">
         <v>101</v>
       </c>
     </row>
@@ -6302,7 +7798,7 @@
       <c r="C18" t="s">
         <v>57</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="1" t="s">
         <v>103</v>
       </c>
     </row>
@@ -6564,7 +8060,7 @@
       <c r="C16" t="s">
         <v>117</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="1" t="s">
         <v>118</v>
       </c>
     </row>
@@ -6578,7 +8074,7 @@
       <c r="C17" t="s">
         <v>117</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="1" t="s">
         <v>119</v>
       </c>
     </row>
@@ -6592,7 +8088,7 @@
       <c r="C18" t="s">
         <v>117</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="1" t="s">
         <v>120</v>
       </c>
     </row>
@@ -6636,6 +8132,8 @@
   <dimension ref="A1:E20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="4"/>
   <cols>
+    <col min="2" max="2" width="27.5" customWidth="1"/>
+    <col min="3" max="3" width="29.875" customWidth="1"/>
     <col min="4" max="4" width="54" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6667,7 +8165,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:3">
+    <row r="3" customHeight="1" spans="1:4">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -6676,6 +8174,9 @@
       </c>
       <c r="C3" t="s">
         <v>16</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:3">
@@ -6697,10 +8198,10 @@
         <v>81</v>
       </c>
       <c r="C5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:4">
@@ -6711,13 +8212,13 @@
         <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="1:3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:4">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -6727,8 +8228,11 @@
       <c r="C7" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="8" customHeight="1" spans="1:3">
+      <c r="D7" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:4">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -6738,8 +8242,11 @@
       <c r="C8" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="9" customHeight="1" spans="1:3">
+      <c r="D8" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:4">
       <c r="A9" t="s">
         <v>37</v>
       </c>
@@ -6748,6 +8255,9 @@
       </c>
       <c r="C9" t="s">
         <v>31</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:4">
@@ -6755,16 +8265,16 @@
         <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C10" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="1:3">
+      <c r="D10" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:4">
       <c r="A11" t="s">
         <v>46</v>
       </c>
@@ -6774,8 +8284,11 @@
       <c r="C11" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="12" customHeight="1" spans="1:3">
+      <c r="D11" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:4">
       <c r="A12" t="s">
         <v>46</v>
       </c>
@@ -6785,8 +8298,11 @@
       <c r="C12" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="13" customHeight="1" spans="1:3">
+      <c r="D12" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:4">
       <c r="A13" t="s">
         <v>55</v>
       </c>
@@ -6796,8 +8312,11 @@
       <c r="C13" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="14" customHeight="1" spans="1:3">
+      <c r="D13" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:4">
       <c r="A14" t="s">
         <v>55</v>
       </c>
@@ -6807,8 +8326,11 @@
       <c r="C14" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="15" customHeight="1" spans="1:3">
+      <c r="D14" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:4">
       <c r="A15" t="s">
         <v>62</v>
       </c>
@@ -6816,10 +8338,13 @@
         <v>63</v>
       </c>
       <c r="C15" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="1:3">
+        <v>136</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:4">
       <c r="A16" t="s">
         <v>62</v>
       </c>
@@ -6827,7 +8352,10 @@
         <v>97</v>
       </c>
       <c r="C16" t="s">
-        <v>128</v>
+        <v>136</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:4">
@@ -6838,10 +8366,10 @@
         <v>100</v>
       </c>
       <c r="C17" t="s">
-        <v>128</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>129</v>
+        <v>136</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:4">
@@ -6852,13 +8380,13 @@
         <v>102</v>
       </c>
       <c r="C18" t="s">
-        <v>128</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="1:3">
+        <v>136</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="1:4">
       <c r="A19" t="s">
         <v>70</v>
       </c>
@@ -6868,8 +8396,11 @@
       <c r="C19" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="20" customHeight="1" spans="1:3">
+      <c r="D19" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:4">
       <c r="A20" t="s">
         <v>70</v>
       </c>
@@ -6878,6 +8409,9 @@
       </c>
       <c r="C20" t="s">
         <v>74</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -6909,7 +8443,7 @@
         <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="E1" t="s">
         <v>80</v>
@@ -6937,7 +8471,7 @@
         <v>17</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:4">
@@ -6951,7 +8485,7 @@
         <v>22</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:4">
@@ -6962,10 +8496,10 @@
         <v>81</v>
       </c>
       <c r="C5" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:4">
@@ -6976,10 +8510,10 @@
         <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:4">
@@ -6990,10 +8524,10 @@
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:4">
@@ -7007,7 +8541,7 @@
         <v>36</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:4">
@@ -7021,7 +8555,7 @@
         <v>41</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:4">
@@ -7029,16 +8563,16 @@
         <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C10" t="s">
         <v>45</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="1:3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:4">
       <c r="A11" t="s">
         <v>46</v>
       </c>
@@ -7046,10 +8580,13 @@
         <v>47</v>
       </c>
       <c r="C11" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="1:3">
+        <v>155</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:4">
       <c r="A12" t="s">
         <v>46</v>
       </c>
@@ -7057,7 +8594,10 @@
         <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>144</v>
+        <v>157</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:4">
@@ -7071,7 +8611,7 @@
         <v>60</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:4">
@@ -7085,10 +8625,10 @@
         <v>60</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="1:3">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:4">
       <c r="A15" t="s">
         <v>62</v>
       </c>
@@ -7096,10 +8636,13 @@
         <v>63</v>
       </c>
       <c r="C15" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="1:3">
+        <v>161</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:4">
       <c r="A16" t="s">
         <v>62</v>
       </c>
@@ -7107,10 +8650,13 @@
         <v>97</v>
       </c>
       <c r="C16" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="1:3">
+        <v>163</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:4">
       <c r="A17" t="s">
         <v>67</v>
       </c>
@@ -7118,10 +8664,13 @@
         <v>100</v>
       </c>
       <c r="C17" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="1:3">
+        <v>165</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:4">
       <c r="A18" t="s">
         <v>67</v>
       </c>
@@ -7129,7 +8678,10 @@
         <v>102</v>
       </c>
       <c r="C18" t="s">
-        <v>150</v>
+        <v>167</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:4">
@@ -7143,7 +8695,7 @@
         <v>75</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:4">
@@ -7157,7 +8709,7 @@
         <v>75</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
